--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,26 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B05FB6-1F48-433D-A272-595852576E15}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962D61D4-FEA8-49D1-A12F-D18474EF20BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="23040" windowHeight="8400" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化计划主表" sheetId="30" r:id="rId1"/>
+    <sheet name="硫化换模计划" sheetId="31" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$5:$P$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化计划主表!$A$6:$CF$6</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">硫化计划主表!$E$5:$CC$6</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -64,8 +79,68 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Admin</author>
+  </authors>
+  <commentList>
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{D7A23125-C526-4BBF-B223-17F371571350}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+只换活字块如果为是，需要回填“在机模具号”</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{086F0567-1AC6-4764-A1ED-D54DFB9DF7DC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+备注栏可以编辑</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="250">
   <si>
     <t/>
   </si>
@@ -1106,19 +1181,732 @@
   <si>
     <t>{.totalDailyPlanQty}</t>
   </si>
+  <si>
+    <t>planDate</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>classIndex</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>lhMachineName</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>planOrder</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>leftRightMould</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>beforeMaterialCode</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>beforeMaterialDesc</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterMaterialCode</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterMaterialDesc</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>mouldCode</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>remark</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{title}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{version}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">序号
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">计划日期
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">班次
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">机台
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">计划顺位
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">左右模
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">当前物料
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">计划物料 
+</t>
+    <phoneticPr fontId="32" type="noConversion"/>
+  </si>
+  <si>
+    <t>换模类型（按时间或按余量收尾）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>干冰清洗</t>
+  </si>
+  <si>
+    <t>喷砂清洗</t>
+  </si>
+  <si>
+    <t>只换活字块</t>
+  </si>
+  <si>
+    <t>模具号</t>
+  </si>
+  <si>
+    <t>TT</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ngày tháng</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca thay </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Máy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>STT k</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ho</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ch </t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Trái ph</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ả</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ủ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>a khuôn</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mã li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u k</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ho</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">ch  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>đ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ang l</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u hóa (tr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ớ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>c khi thay)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mô t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ả</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> v</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ậ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>t li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u (tr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ớ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>c khi thay)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mã li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u k</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ho</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ch  (sau khi thay)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Mô t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ả</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> v</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ậ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>t li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color indexed="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u (sau khi thay)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.seq}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.planDate}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.classIndex}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lhMachineCode}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.planOrder}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.leftRightMould}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.beforeMaterialCode}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>beforeMaterialDesc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.afterMaterialCode}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.afterMaterialDesc}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.changeType}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.isDryIceClean}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.isSandblastingClean}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.isReplaceBlock}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.mouldCode}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.remark}</t>
+    <phoneticPr fontId="122" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="[$-10804]0;\(0\)"/>
     <numFmt numFmtId="178" formatCode="m/d;@"/>
     <numFmt numFmtId="179" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="180" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="122" x14ac:knownFonts="1">
+  <fonts count="129" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1793,6 +2581,56 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1828,7 +2666,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2067,8 +2905,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="209">
+  <cellStyleXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -2306,8 +3234,9 @@
     <xf numFmtId="43" fontId="114" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2315,19 +3244,16 @@
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="117" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2345,63 +3271,36 @@
     <xf numFmtId="0" fontId="117" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="117" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="117" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2414,15 +3313,12 @@
     <xf numFmtId="0" fontId="119" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="115" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="115" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="119" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2432,70 +3328,52 @@
     <xf numFmtId="0" fontId="119" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="119" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="119" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="116" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="115" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="115" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="115" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="115" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="115" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="115" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="116" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="116" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="116" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2552,8 +3430,98 @@
     <xf numFmtId="0" fontId="117" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="209" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="100" fillId="0" borderId="0" xfId="209" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="0" xfId="209" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="0" xfId="209" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="123" fillId="0" borderId="20" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="123" fillId="0" borderId="21" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="123" fillId="0" borderId="22" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="23" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="4" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="24" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="100" fillId="0" borderId="25" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="26" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="8" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="15" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="15" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="27" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="26" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="8" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="15" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="15" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="2" borderId="27" xfId="209" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="11" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="100" fillId="0" borderId="1" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="100" fillId="0" borderId="1" xfId="209" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="3" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="3" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="10" xfId="209" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="209">
+  <cellStyles count="210">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2753,6 +3721,7 @@
     <cellStyle name="常规 2 2" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
     <cellStyle name="常规 2 3" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
     <cellStyle name="常规 2 4" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="常规 2 5" xfId="209" xr:uid="{981F861F-399E-4794-AD36-C8A6E3E93A36}"/>
     <cellStyle name="常规 9" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
     <cellStyle name="千位分隔 3" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
     <cellStyle name="千位分隔 3 2" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
@@ -3033,6 +4002,85 @@
         <a:xfrm>
           <a:off x="0" y="66675"/>
           <a:ext cx="2000250" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9F88F98-7919-4F70-A3C9-F5F77938C20F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19050" y="19050"/>
+          <a:ext cx="1485900" cy="523875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3358,334 +4406,402 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CF7"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="16" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5" style="16" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.75" style="16" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.125" style="16" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="20" customWidth="1"/>
-    <col min="6" max="6" width="11.875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.25" style="20" customWidth="1"/>
-    <col min="8" max="8" width="36.875" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15.75" style="20" customWidth="1"/>
-    <col min="10" max="11" width="6.375" style="21" customWidth="1"/>
-    <col min="12" max="12" width="6.125" style="22" customWidth="1"/>
-    <col min="13" max="13" width="6.375" style="22" customWidth="1"/>
-    <col min="14" max="14" width="3.75" style="22" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="22" customWidth="1"/>
-    <col min="16" max="16" width="3.75" style="22" customWidth="1"/>
-    <col min="17" max="17" width="4.625" style="22" customWidth="1"/>
-    <col min="18" max="18" width="5.375" style="22" customWidth="1"/>
-    <col min="19" max="22" width="3.75" style="22" customWidth="1"/>
-    <col min="23" max="23" width="6.75" style="22" customWidth="1"/>
-    <col min="24" max="24" width="3.75" style="22" customWidth="1"/>
-    <col min="25" max="25" width="4.625" style="22" customWidth="1"/>
-    <col min="26" max="26" width="5.375" style="22" customWidth="1"/>
-    <col min="27" max="30" width="3.75" style="22" customWidth="1"/>
-    <col min="31" max="31" width="6.75" style="22" customWidth="1"/>
-    <col min="32" max="32" width="3.75" style="22" customWidth="1"/>
-    <col min="33" max="33" width="4.625" style="22" customWidth="1"/>
-    <col min="34" max="34" width="5.375" style="22" customWidth="1"/>
-    <col min="35" max="38" width="3.75" style="22" customWidth="1"/>
-    <col min="39" max="39" width="6.75" style="22" customWidth="1"/>
-    <col min="40" max="40" width="3.75" style="22" customWidth="1"/>
-    <col min="41" max="41" width="4.625" style="22" customWidth="1"/>
-    <col min="42" max="42" width="5.375" style="22" customWidth="1"/>
-    <col min="43" max="46" width="3.75" style="22" customWidth="1"/>
-    <col min="47" max="47" width="6.75" style="22" customWidth="1"/>
-    <col min="48" max="48" width="3.75" style="22" customWidth="1"/>
-    <col min="49" max="49" width="4.625" style="22" customWidth="1"/>
-    <col min="50" max="50" width="5.375" style="22" customWidth="1"/>
-    <col min="51" max="54" width="3.75" style="22" customWidth="1"/>
-    <col min="55" max="55" width="6.75" style="22" customWidth="1"/>
-    <col min="56" max="56" width="3.75" style="22" customWidth="1"/>
-    <col min="57" max="57" width="4.625" style="22" customWidth="1"/>
-    <col min="58" max="58" width="5.375" style="22" customWidth="1"/>
-    <col min="59" max="62" width="3.75" style="22" customWidth="1"/>
-    <col min="63" max="63" width="6.75" style="22" customWidth="1"/>
-    <col min="64" max="64" width="3.75" style="22" customWidth="1"/>
-    <col min="65" max="65" width="4.625" style="22" customWidth="1"/>
-    <col min="66" max="66" width="5.375" style="22" customWidth="1"/>
-    <col min="67" max="70" width="3.75" style="22" customWidth="1"/>
-    <col min="71" max="71" width="6.75" style="22" customWidth="1"/>
-    <col min="72" max="72" width="3.75" style="22" customWidth="1"/>
-    <col min="73" max="73" width="4.625" style="22" customWidth="1"/>
-    <col min="74" max="74" width="5.375" style="22" customWidth="1"/>
-    <col min="75" max="77" width="3.75" style="22" customWidth="1"/>
-    <col min="78" max="78" width="6.625" style="20" customWidth="1"/>
-    <col min="79" max="79" width="4.625" style="20" customWidth="1"/>
-    <col min="80" max="80" width="9.375" style="23" customWidth="1"/>
-    <col min="81" max="81" width="34.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="6.75" style="21" customWidth="1"/>
-    <col min="83" max="84" width="8.375" style="21" customWidth="1"/>
-    <col min="85" max="92" width="9.875" style="15" bestFit="1" customWidth="1"/>
-    <col min="93" max="16384" width="9.125" style="15"/>
+    <col min="1" max="1" width="5.3984375" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.69921875" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.69921875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="11.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.19921875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="36.8984375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="15.69921875" style="10" customWidth="1"/>
+    <col min="10" max="11" width="6.3984375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.09765625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="6.3984375" style="10" customWidth="1"/>
+    <col min="14" max="14" width="3.69921875" style="10" customWidth="1"/>
+    <col min="15" max="15" width="6.69921875" style="10" customWidth="1"/>
+    <col min="16" max="16" width="3.69921875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="4.59765625" style="10" customWidth="1"/>
+    <col min="18" max="18" width="5.3984375" style="10" customWidth="1"/>
+    <col min="19" max="22" width="3.69921875" style="10" customWidth="1"/>
+    <col min="23" max="23" width="6.69921875" style="10" customWidth="1"/>
+    <col min="24" max="24" width="3.69921875" style="10" customWidth="1"/>
+    <col min="25" max="25" width="4.59765625" style="10" customWidth="1"/>
+    <col min="26" max="26" width="5.3984375" style="10" customWidth="1"/>
+    <col min="27" max="30" width="3.69921875" style="10" customWidth="1"/>
+    <col min="31" max="31" width="6.69921875" style="10" customWidth="1"/>
+    <col min="32" max="32" width="3.69921875" style="10" customWidth="1"/>
+    <col min="33" max="33" width="4.59765625" style="10" customWidth="1"/>
+    <col min="34" max="34" width="5.3984375" style="10" customWidth="1"/>
+    <col min="35" max="38" width="3.69921875" style="10" customWidth="1"/>
+    <col min="39" max="39" width="6.69921875" style="10" customWidth="1"/>
+    <col min="40" max="40" width="3.69921875" style="10" customWidth="1"/>
+    <col min="41" max="41" width="4.59765625" style="10" customWidth="1"/>
+    <col min="42" max="42" width="5.3984375" style="10" customWidth="1"/>
+    <col min="43" max="46" width="3.69921875" style="10" customWidth="1"/>
+    <col min="47" max="47" width="6.69921875" style="10" customWidth="1"/>
+    <col min="48" max="48" width="3.69921875" style="10" customWidth="1"/>
+    <col min="49" max="49" width="4.59765625" style="10" customWidth="1"/>
+    <col min="50" max="50" width="5.3984375" style="10" customWidth="1"/>
+    <col min="51" max="54" width="3.69921875" style="10" customWidth="1"/>
+    <col min="55" max="55" width="6.69921875" style="10" customWidth="1"/>
+    <col min="56" max="56" width="3.69921875" style="10" customWidth="1"/>
+    <col min="57" max="57" width="4.59765625" style="10" customWidth="1"/>
+    <col min="58" max="58" width="5.3984375" style="10" customWidth="1"/>
+    <col min="59" max="62" width="3.69921875" style="10" customWidth="1"/>
+    <col min="63" max="63" width="6.69921875" style="10" customWidth="1"/>
+    <col min="64" max="64" width="3.69921875" style="10" customWidth="1"/>
+    <col min="65" max="65" width="4.59765625" style="10" customWidth="1"/>
+    <col min="66" max="66" width="5.3984375" style="10" customWidth="1"/>
+    <col min="67" max="70" width="3.69921875" style="10" customWidth="1"/>
+    <col min="71" max="71" width="6.69921875" style="10" customWidth="1"/>
+    <col min="72" max="72" width="3.69921875" style="10" customWidth="1"/>
+    <col min="73" max="73" width="4.59765625" style="10" customWidth="1"/>
+    <col min="74" max="74" width="5.3984375" style="10" customWidth="1"/>
+    <col min="75" max="77" width="3.69921875" style="10" customWidth="1"/>
+    <col min="78" max="78" width="6.59765625" style="10" customWidth="1"/>
+    <col min="79" max="79" width="4.59765625" style="10" customWidth="1"/>
+    <col min="80" max="80" width="9.3984375" style="14" customWidth="1"/>
+    <col min="81" max="81" width="34.19921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="6.69921875" style="2" customWidth="1"/>
+    <col min="83" max="84" width="8.3984375" style="2" customWidth="1"/>
+    <col min="85" max="92" width="9.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="93" max="16384" width="9.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" hidden="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="20" t="s">
+    <row r="1" spans="1:84" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="U1" s="22" t="s">
+      <c r="U1" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="V1" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="W1" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="X1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Y1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="Z1" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="AA1" s="22" t="s">
+      <c r="AA1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AB1" s="22" t="s">
+      <c r="AB1" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AC1" s="22" t="s">
+      <c r="AC1" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AD1" s="22" t="s">
+      <c r="AD1" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AE1" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AF1" s="22" t="s">
+      <c r="AF1" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="AG1" s="22" t="s">
+      <c r="AG1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AH1" s="22" t="s">
+      <c r="AH1" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="AI1" s="22" t="s">
+      <c r="AI1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AJ1" s="22" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="AK1" s="22" t="s">
+      <c r="AK1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="AL1" s="22" t="s">
+      <c r="AL1" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="AM1" s="22" t="s">
+      <c r="AM1" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="AN1" s="22" t="s">
+      <c r="AN1" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="AO1" s="22" t="s">
+      <c r="AO1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AP1" s="22" t="s">
+      <c r="AP1" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="AQ1" s="22" t="s">
+      <c r="AQ1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AR1" s="22" t="s">
+      <c r="AR1" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="AS1" s="22" t="s">
+      <c r="AS1" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="AT1" s="22" t="s">
+      <c r="AT1" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="AU1" s="22" t="s">
+      <c r="AU1" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="AV1" s="22" t="s">
+      <c r="AV1" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AW1" s="22" t="s">
+      <c r="AW1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="AX1" s="22" t="s">
+      <c r="AX1" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="AY1" s="22" t="s">
+      <c r="AY1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="AZ1" s="22" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="BA1" s="22" t="s">
+      <c r="BA1" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="BB1" s="22" t="s">
+      <c r="BB1" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="BC1" s="22" t="s">
+      <c r="BC1" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="BD1" s="22" t="s">
+      <c r="BD1" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="BE1" s="22" t="s">
+      <c r="BE1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="BF1" s="22" t="s">
+      <c r="BF1" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="BG1" s="22" t="s">
+      <c r="BG1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="BH1" s="22" t="s">
+      <c r="BH1" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="BI1" s="22" t="s">
+      <c r="BI1" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="BJ1" s="22" t="s">
+      <c r="BJ1" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="BK1" s="22" t="s">
+      <c r="BK1" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="BL1" s="22" t="s">
+      <c r="BL1" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="BM1" s="22" t="s">
+      <c r="BM1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="BN1" s="22" t="s">
+      <c r="BN1" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="BO1" s="22" t="s">
+      <c r="BO1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="BP1" s="22" t="s">
+      <c r="BP1" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="BQ1" s="22" t="s">
+      <c r="BQ1" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="BR1" s="22" t="s">
+      <c r="BR1" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="BS1" s="22" t="s">
+      <c r="BS1" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="BT1" s="22" t="s">
+      <c r="BT1" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="BU1" s="22" t="s">
+      <c r="BU1" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="BV1" s="22" t="s">
+      <c r="BV1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="BW1" s="22" t="s">
+      <c r="BW1" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="BX1" s="22" t="s">
+      <c r="BX1" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="BY1" s="22" t="s">
+      <c r="BY1" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="BZ1" s="20" t="s">
+      <c r="BZ1" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="CA1" s="20" t="s">
+      <c r="CA1" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="CB1" s="23" t="s">
+      <c r="CB1" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="CC1" s="24" t="s">
+      <c r="CC1" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="CD1" s="21" t="s">
+      <c r="CD1" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="CE1" s="21" t="s">
+      <c r="CE1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="CF1" s="21" t="s">
+      <c r="CF1" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:84" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:84" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="64" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="50"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
       <c r="O2" s="2"/>
-      <c r="AV2" s="53" t="s">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="36" t="s">
         <v>49</v>
       </c>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
       <c r="BA2" s="2"/>
-      <c r="CD2" s="15"/>
-      <c r="CE2" s="2"/>
-      <c r="CF2" s="2"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
     </row>
-    <row r="3" spans="1:84" s="29" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:84" s="20" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3696,7 +4812,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="20" t="s">
         <v>35</v>
       </c>
       <c r="N3" s="6"/>
@@ -3762,10 +4878,9 @@
       <c r="BD3" s="4"/>
       <c r="BE3" s="5"/>
       <c r="BF3" s="6"/>
-      <c r="BG3" s="7"/>
+      <c r="BG3" s="6"/>
       <c r="BH3" s="6"/>
-      <c r="BI3" s="45"/>
-      <c r="BJ3" s="46"/>
+      <c r="BJ3" s="33"/>
       <c r="BK3" s="4">
         <f>SUM(BK7:BK108138)</f>
         <v>0</v>
@@ -3782,9 +4897,9 @@
         <f>O3+W3+AE3+AM3+AU3+BC3+BK3+BS3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="48"/>
+      <c r="CD3" s="34"/>
     </row>
-    <row r="4" spans="1:84" s="29" customFormat="1" ht="17.850000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:84" s="20" customFormat="1" ht="17.850000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3795,7 +4910,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="M4" s="47" t="s">
+      <c r="M4" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N4" s="6"/>
@@ -3857,632 +4972,632 @@
       <c r="BW4" s="6"/>
       <c r="BZ4" s="4"/>
       <c r="CB4" s="4"/>
-      <c r="CD4" s="49"/>
+      <c r="CD4" s="35"/>
     </row>
-    <row r="5" spans="1:84" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="27">
+    <row r="5" spans="1:84" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
         <f>BC3+BK3+BS3</f>
         <v>0</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="M5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="71" t="s">
+      <c r="N5" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="72"/>
-      <c r="U5" s="73"/>
-      <c r="V5" s="80" t="s">
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="W5" s="72"/>
-      <c r="X5" s="72"/>
-      <c r="Y5" s="72"/>
-      <c r="Z5" s="72"/>
-      <c r="AA5" s="72"/>
-      <c r="AB5" s="72"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="78" t="s">
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="55"/>
+      <c r="AC5" s="64"/>
+      <c r="AD5" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AE5" s="75"/>
-      <c r="AF5" s="75"/>
-      <c r="AG5" s="75"/>
-      <c r="AH5" s="75"/>
-      <c r="AI5" s="75"/>
-      <c r="AJ5" s="75"/>
-      <c r="AK5" s="76"/>
-      <c r="AL5" s="74" t="s">
+      <c r="AE5" s="58"/>
+      <c r="AF5" s="58"/>
+      <c r="AG5" s="58"/>
+      <c r="AH5" s="58"/>
+      <c r="AI5" s="58"/>
+      <c r="AJ5" s="58"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="AM5" s="75"/>
-      <c r="AN5" s="75"/>
-      <c r="AO5" s="75"/>
-      <c r="AP5" s="75"/>
-      <c r="AQ5" s="75"/>
-      <c r="AR5" s="75"/>
-      <c r="AS5" s="76"/>
-      <c r="AT5" s="74" t="s">
+      <c r="AM5" s="58"/>
+      <c r="AN5" s="58"/>
+      <c r="AO5" s="58"/>
+      <c r="AP5" s="58"/>
+      <c r="AQ5" s="58"/>
+      <c r="AR5" s="58"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="AU5" s="75"/>
-      <c r="AV5" s="75"/>
-      <c r="AW5" s="75"/>
-      <c r="AX5" s="75"/>
-      <c r="AY5" s="75"/>
-      <c r="AZ5" s="75"/>
-      <c r="BA5" s="77"/>
-      <c r="BB5" s="67" t="s">
+      <c r="AU5" s="58"/>
+      <c r="AV5" s="58"/>
+      <c r="AW5" s="58"/>
+      <c r="AX5" s="58"/>
+      <c r="AY5" s="58"/>
+      <c r="AZ5" s="58"/>
+      <c r="BA5" s="60"/>
+      <c r="BB5" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="BC5" s="68"/>
-      <c r="BD5" s="68"/>
-      <c r="BE5" s="68"/>
-      <c r="BF5" s="68"/>
-      <c r="BG5" s="68"/>
-      <c r="BH5" s="68"/>
-      <c r="BI5" s="69"/>
-      <c r="BJ5" s="70" t="s">
+      <c r="BC5" s="51"/>
+      <c r="BD5" s="51"/>
+      <c r="BE5" s="51"/>
+      <c r="BF5" s="51"/>
+      <c r="BG5" s="51"/>
+      <c r="BH5" s="51"/>
+      <c r="BI5" s="52"/>
+      <c r="BJ5" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="BK5" s="68"/>
-      <c r="BL5" s="68"/>
-      <c r="BM5" s="68"/>
-      <c r="BN5" s="68"/>
-      <c r="BO5" s="68"/>
-      <c r="BP5" s="68"/>
-      <c r="BQ5" s="69"/>
-      <c r="BR5" s="70" t="s">
+      <c r="BK5" s="51"/>
+      <c r="BL5" s="51"/>
+      <c r="BM5" s="51"/>
+      <c r="BN5" s="51"/>
+      <c r="BO5" s="51"/>
+      <c r="BP5" s="51"/>
+      <c r="BQ5" s="52"/>
+      <c r="BR5" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="BS5" s="68"/>
-      <c r="BT5" s="68"/>
-      <c r="BU5" s="68"/>
-      <c r="BV5" s="68"/>
-      <c r="BW5" s="68"/>
-      <c r="BX5" s="68"/>
-      <c r="BY5" s="79"/>
-      <c r="BZ5" s="65" t="s">
+      <c r="BS5" s="51"/>
+      <c r="BT5" s="51"/>
+      <c r="BU5" s="51"/>
+      <c r="BV5" s="51"/>
+      <c r="BW5" s="51"/>
+      <c r="BX5" s="51"/>
+      <c r="BY5" s="62"/>
+      <c r="BZ5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="CA5" s="66"/>
-      <c r="CB5" s="13" t="s">
+      <c r="CA5" s="49"/>
+      <c r="CB5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="CC5" s="13" t="s">
+      <c r="CC5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="CD5" s="32" t="s">
+      <c r="CD5" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="CE5" s="13" t="s">
+      <c r="CE5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="CF5" s="13" t="s">
+      <c r="CF5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:84" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.15">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:84" s="12" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="11"/>
+      <c r="J6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="33" t="s">
+      <c r="L6" s="16"/>
+      <c r="M6" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="N6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O6" s="30" t="s">
+      <c r="O6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="30" t="s">
+      <c r="P6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="Q6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="30" t="s">
+      <c r="R6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="31" t="s">
+      <c r="S6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="T6" s="30" t="s">
+      <c r="T6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="U6" s="30" t="s">
+      <c r="U6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="V6" s="30" t="s">
+      <c r="V6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="30" t="s">
+      <c r="W6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="30" t="s">
+      <c r="X6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="Y6" s="30" t="s">
+      <c r="Y6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="30" t="s">
+      <c r="Z6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="AA6" s="31" t="s">
+      <c r="AA6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="AB6" s="30" t="s">
+      <c r="AB6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="AC6" s="35" t="s">
+      <c r="AC6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AD6" s="39" t="s">
+      <c r="AD6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="37" t="s">
+      <c r="AE6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AF6" s="37" t="s">
+      <c r="AF6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="AG6" s="37" t="s">
+      <c r="AG6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AH6" s="37" t="s">
+      <c r="AH6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="AI6" s="38" t="s">
+      <c r="AI6" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AJ6" s="37" t="s">
+      <c r="AJ6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AK6" s="37" t="s">
+      <c r="AK6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AL6" s="37" t="s">
+      <c r="AL6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="AM6" s="37" t="s">
+      <c r="AM6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AN6" s="37" t="s">
+      <c r="AN6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="AO6" s="37" t="s">
+      <c r="AO6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AP6" s="37" t="s">
+      <c r="AP6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="AQ6" s="38" t="s">
+      <c r="AQ6" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AR6" s="37" t="s">
+      <c r="AR6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AS6" s="37" t="s">
+      <c r="AS6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AT6" s="37" t="s">
+      <c r="AT6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AU6" s="37" t="s">
+      <c r="AU6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AV6" s="37" t="s">
+      <c r="AV6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="AW6" s="37" t="s">
+      <c r="AW6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AX6" s="37" t="s">
+      <c r="AX6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="AY6" s="38" t="s">
+      <c r="AY6" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AZ6" s="37" t="s">
+      <c r="AZ6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="BA6" s="40" t="s">
+      <c r="BA6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="BB6" s="43" t="s">
+      <c r="BB6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="BC6" s="41" t="s">
+      <c r="BC6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="BD6" s="41" t="s">
+      <c r="BD6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="BE6" s="41" t="s">
+      <c r="BE6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="BF6" s="41" t="s">
+      <c r="BF6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="BG6" s="42" t="s">
+      <c r="BG6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="BH6" s="42" t="s">
+      <c r="BH6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="BI6" s="42" t="s">
+      <c r="BI6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="BJ6" s="42" t="s">
+      <c r="BJ6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="BK6" s="42" t="s">
+      <c r="BK6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="BL6" s="42" t="s">
+      <c r="BL6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="BM6" s="42" t="s">
+      <c r="BM6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="BN6" s="42" t="s">
+      <c r="BN6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="BO6" s="42" t="s">
+      <c r="BO6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="BP6" s="42" t="s">
+      <c r="BP6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="BQ6" s="42" t="s">
+      <c r="BQ6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="BR6" s="42" t="s">
+      <c r="BR6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="BS6" s="42" t="s">
+      <c r="BS6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="BT6" s="42" t="s">
+      <c r="BT6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="BU6" s="42" t="s">
+      <c r="BU6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="BV6" s="42" t="s">
+      <c r="BV6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="BW6" s="42" t="s">
+      <c r="BW6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="BX6" s="42" t="s">
+      <c r="BX6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="BY6" s="44" t="s">
+      <c r="BY6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="BZ6" s="10" t="s">
+      <c r="BZ6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="CA6" s="8" t="s">
+      <c r="CA6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CB6" s="12" t="s">
+      <c r="CB6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="CC6" s="12" t="s">
+      <c r="CC6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="CD6" s="9"/>
-      <c r="CE6" s="12" t="s">
+      <c r="CD6" s="8"/>
+      <c r="CE6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="CF6" s="12" t="s">
+      <c r="CF6" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:84" ht="48" x14ac:dyDescent="0.15">
-      <c r="E7" s="54" t="s">
+    <row r="7" spans="1:84" ht="45.6" x14ac:dyDescent="0.25">
+      <c r="E7" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="56" t="s">
+      <c r="G7" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="57" t="s">
+      <c r="H7" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="54" t="e">
+      <c r="J7" s="37" t="e">
         <f>CF7-CE7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="L7" s="54" t="s">
+      <c r="L7" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="M7" s="58" t="s">
+      <c r="M7" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="59" t="s">
+      <c r="N7" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="60" t="s">
+      <c r="O7" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="P7" s="60" t="s">
+      <c r="P7" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="Q7" s="60" t="s">
+      <c r="Q7" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="R7" s="60" t="s">
+      <c r="R7" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="S7" s="60" t="s">
+      <c r="S7" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="T7" s="60" t="s">
+      <c r="T7" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="U7" s="60" t="s">
+      <c r="U7" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="V7" s="60" t="s">
+      <c r="V7" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="W7" s="60" t="s">
+      <c r="W7" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="X7" s="60" t="s">
+      <c r="X7" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="Y7" s="60" t="s">
+      <c r="Y7" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="Z7" s="60" t="s">
+      <c r="Z7" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="AA7" s="60" t="s">
+      <c r="AA7" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="AB7" s="60" t="s">
+      <c r="AB7" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="AC7" s="60" t="s">
+      <c r="AC7" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="AD7" s="60" t="s">
+      <c r="AD7" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="AE7" s="60" t="s">
+      <c r="AE7" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="AF7" s="60" t="s">
+      <c r="AF7" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="AG7" s="60" t="s">
+      <c r="AG7" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="AH7" s="60" t="s">
+      <c r="AH7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="AI7" s="60" t="s">
+      <c r="AI7" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="AJ7" s="60" t="s">
+      <c r="AJ7" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="AK7" s="60" t="s">
+      <c r="AK7" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="AL7" s="60" t="s">
+      <c r="AL7" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="AM7" s="60" t="s">
+      <c r="AM7" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="AN7" s="60" t="s">
+      <c r="AN7" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="AO7" s="60" t="s">
+      <c r="AO7" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="AP7" s="60" t="s">
+      <c r="AP7" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="AQ7" s="60" t="s">
+      <c r="AQ7" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="AR7" s="60" t="s">
+      <c r="AR7" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="AS7" s="60" t="s">
+      <c r="AS7" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="AT7" s="60" t="s">
+      <c r="AT7" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="AU7" s="60" t="s">
+      <c r="AU7" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="AV7" s="60" t="s">
+      <c r="AV7" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="AW7" s="60" t="s">
+      <c r="AW7" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="AX7" s="60" t="s">
+      <c r="AX7" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="AY7" s="60" t="s">
+      <c r="AY7" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="AZ7" s="60" t="s">
+      <c r="AZ7" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="BA7" s="60" t="s">
+      <c r="BA7" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="BB7" s="60" t="s">
+      <c r="BB7" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="BC7" s="60" t="s">
+      <c r="BC7" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="BD7" s="60" t="s">
+      <c r="BD7" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="BE7" s="60" t="s">
+      <c r="BE7" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="BF7" s="60" t="s">
+      <c r="BF7" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="BG7" s="60" t="s">
+      <c r="BG7" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="BH7" s="60" t="s">
+      <c r="BH7" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="BI7" s="60" t="s">
+      <c r="BI7" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="BJ7" s="60" t="s">
+      <c r="BJ7" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="BK7" s="60" t="s">
+      <c r="BK7" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="BL7" s="60" t="s">
+      <c r="BL7" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="BM7" s="60" t="s">
+      <c r="BM7" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="BN7" s="60" t="s">
+      <c r="BN7" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="BO7" s="60" t="s">
+      <c r="BO7" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="BP7" s="60" t="s">
+      <c r="BP7" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="BQ7" s="60" t="s">
+      <c r="BQ7" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="BR7" s="60" t="s">
+      <c r="BR7" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="BS7" s="60" t="s">
+      <c r="BS7" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="BT7" s="60" t="s">
+      <c r="BT7" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="BU7" s="60" t="s">
+      <c r="BU7" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="BV7" s="60" t="s">
+      <c r="BV7" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="BW7" s="60" t="s">
+      <c r="BW7" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="BX7" s="60" t="s">
+      <c r="BX7" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="BY7" s="61" t="s">
+      <c r="BY7" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="BZ7" s="62" t="e">
+      <c r="BZ7" s="45" t="e">
         <f>BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA7" s="63" t="e">
+      <c r="CA7" s="46" t="e">
         <f>BL7+BT7+BD7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CB7" s="63" t="e">
+      <c r="CB7" s="46" t="e">
         <f>O7+W7+AE7+AM7+AU7+BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CC7" s="55" t="s">
+      <c r="CC7" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD7" s="36" t="s">
+      <c r="CD7" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="CE7" s="36" t="s">
+      <c r="CE7" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="CF7" s="55" t="s">
+      <c r="CF7" s="38" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4501,53 +5616,37 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="20" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="19" priority="16" stopIfTrue="1"/>
+  <conditionalFormatting sqref="H5:I6">
+    <cfRule type="duplicateValues" dxfId="14" priority="24201" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="24202" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="24203" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="18" priority="17" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="18" stopIfTrue="1"/>
+  <conditionalFormatting sqref="J5:K6">
+    <cfRule type="duplicateValues" dxfId="11" priority="24204" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24205" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24206" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="16" priority="13" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="14" stopIfTrue="1"/>
+  <conditionalFormatting sqref="L5:L6">
+    <cfRule type="duplicateValues" dxfId="8" priority="24207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="24208" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="24209" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M6">
+    <cfRule type="duplicateValues" dxfId="5" priority="24210" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="24211" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="24212" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="CD5">
-    <cfRule type="duplicateValues" dxfId="14" priority="1" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CD5">
-    <cfRule type="duplicateValues" dxfId="13" priority="2" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:I6">
-    <cfRule type="duplicateValues" dxfId="11" priority="24201" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:I6">
-    <cfRule type="duplicateValues" dxfId="10" priority="24202" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="24203" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K6">
-    <cfRule type="duplicateValues" dxfId="8" priority="24204" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K6">
-    <cfRule type="duplicateValues" dxfId="7" priority="24205" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="24206" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="5" priority="24207" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="4" priority="24208" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="24209" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M6">
-    <cfRule type="duplicateValues" dxfId="2" priority="24210" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M6">
-    <cfRule type="duplicateValues" dxfId="1" priority="24211" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="24212" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BV6 AX6 AP6 BF6 AH6 BN6 Z6 R6" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4562,4 +5661,258 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62573C9F-0BAA-495D-8B20-F6E1FC4807AD}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.8984375" style="65" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" style="66" customWidth="1"/>
+    <col min="3" max="4" width="11.3984375" style="67" customWidth="1"/>
+    <col min="5" max="5" width="8" style="65" customWidth="1"/>
+    <col min="6" max="6" width="14.296875" style="67" customWidth="1"/>
+    <col min="7" max="7" width="14.296875" style="65" customWidth="1"/>
+    <col min="8" max="8" width="35.3984375" style="67" customWidth="1"/>
+    <col min="9" max="9" width="14.296875" style="65" customWidth="1"/>
+    <col min="10" max="10" width="35.3984375" style="68" customWidth="1"/>
+    <col min="11" max="11" width="10.69921875" style="68" customWidth="1"/>
+    <col min="12" max="13" width="6.8984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.8984375" style="67" customWidth="1"/>
+    <col min="15" max="15" width="23.19921875" style="67" customWidth="1"/>
+    <col min="16" max="16" width="21.09765625" style="67" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="67"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="12" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="O1" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="P1" s="67" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="71"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="75"/>
+    </row>
+    <row r="4" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="79" t="s">
+        <v>219</v>
+      </c>
+      <c r="M4" s="79" t="s">
+        <v>220</v>
+      </c>
+      <c r="N4" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="O4" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="P4" s="80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="37.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A5" s="81" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="82" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="77" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="G5" s="77" t="s">
+        <v>229</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>230</v>
+      </c>
+      <c r="I5" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>232</v>
+      </c>
+      <c r="K5" s="83"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="O5" s="84"/>
+      <c r="P5" s="85" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="23.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" s="87" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" s="89" t="s">
+        <v>238</v>
+      </c>
+      <c r="F6" s="90" t="s">
+        <v>239</v>
+      </c>
+      <c r="G6" s="90" t="s">
+        <v>240</v>
+      </c>
+      <c r="H6" s="90" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="89" t="s">
+        <v>242</v>
+      </c>
+      <c r="J6" s="91" t="s">
+        <v>243</v>
+      </c>
+      <c r="K6" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="L6" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="M6" s="93" t="s">
+        <v>246</v>
+      </c>
+      <c r="N6" s="93" t="s">
+        <v>247</v>
+      </c>
+      <c r="O6" s="93" t="s">
+        <v>248</v>
+      </c>
+      <c r="P6" s="94" t="s">
+        <v>249</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:P5" xr:uid="{4349BEB0-D369-4858-9ED4-D698ADBC337B}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E14DCB-C98A-481B-BDDE-5A82E60BEAB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12555" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化计划主表" sheetId="30" r:id="rId1"/>
@@ -12,54 +18,43 @@
     <sheet name="排产小结" sheetId="32" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$5:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化计划主表!$A$6:$CF$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$5:$P$6</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">硫化计划主表!$E$5:$CC$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>项田昊</author>
   </authors>
   <commentList>
-    <comment ref="CC5" authorId="0">
+    <comment ref="CC5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>可编辑</t>
         </r>
       </text>
     </comment>
-    <comment ref="CD5" authorId="0">
+    <comment ref="CD5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>多台的用“，”分开</t>
@@ -71,19 +66,19 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="O4" authorId="0">
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Admin:</t>
         </r>
@@ -91,21 +86,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 只换活字块如果为是，需要回填“在机模具号”</t>
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Admin:</t>
         </r>
@@ -113,7 +108,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 备注栏可以编辑</t>
@@ -125,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="296">
   <si>
     <t>lhMachineCode</t>
   </si>
@@ -169,9 +164,6 @@
     <t>class1Type</t>
   </si>
   <si>
-    <t>mouldMethod</t>
-  </si>
-  <si>
     <t>class1Analysis</t>
   </si>
   <si>
@@ -302,15 +294,6 @@
   </si>
   <si>
     <t>class8Dot</t>
-  </si>
-  <si>
-    <t>dailyPlanQty</t>
-  </si>
-  <si>
-    <t>totalFinishQty</t>
-  </si>
-  <si>
-    <t>totalPlanQty</t>
   </si>
   <si>
     <t>remark</t>
@@ -328,6 +311,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -339,7 +323,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -349,6 +333,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -359,7 +344,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -369,6 +354,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -379,7 +365,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -389,6 +375,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -399,7 +386,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -409,6 +396,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -419,7 +407,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -429,6 +417,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -439,7 +428,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -449,6 +438,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -459,7 +449,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -469,6 +459,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -479,7 +470,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -489,6 +480,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -499,7 +491,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -509,6 +501,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -520,6 +513,7 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -529,7 +523,7 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -538,6 +532,7 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -676,6 +671,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>L</t>
@@ -686,7 +682,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -696,6 +692,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa trong ca</t>
@@ -727,6 +724,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*示方类型
@@ -738,7 +736,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -748,6 +746,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng thức</t>
@@ -775,6 +774,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -785,7 +785,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ổ</t>
     </r>
@@ -795,6 +795,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng</t>
@@ -810,7 +811,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -820,7 +821,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">n hàng </t>
     </r>
@@ -832,6 +833,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -842,7 +844,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -852,6 +854,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -861,7 +864,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -870,7 +873,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ợ</t>
     </r>
@@ -879,6 +882,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng l</t>
@@ -888,7 +892,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -897,6 +901,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">u hóa </t>
@@ -906,7 +911,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đạ</t>
     </r>
@@ -915,6 +920,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">t </t>
@@ -1080,9 +1086,6 @@
     <t>{.class6Type}</t>
   </si>
   <si>
-    <t>{.class6MouldMethod}</t>
-  </si>
-  <si>
     <t>{.class6Analysis}</t>
   </si>
   <si>
@@ -1120,9 +1123,6 @@
   </si>
   <si>
     <t>{.class8FinishQty}</t>
-  </si>
-  <si>
-    <t>{.class8LeftRightMould}</t>
   </si>
   <si>
     <t>{.class8Type}</t>
@@ -1244,6 +1244,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>STT k</t>
@@ -1254,7 +1255,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1264,6 +1265,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1274,7 +1276,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1284,6 +1286,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ch </t>
@@ -1296,6 +1299,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Trái ph</t>
@@ -1306,7 +1310,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1316,6 +1320,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i c</t>
@@ -1326,7 +1331,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -1336,6 +1341,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>a khuôn</t>
@@ -1348,6 +1354,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã li</t>
@@ -1358,7 +1365,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1368,6 +1375,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u k</t>
@@ -1378,7 +1386,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1388,6 +1396,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1398,7 +1407,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1408,6 +1417,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ch  </t>
@@ -1418,7 +1428,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1428,6 +1438,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ang l</t>
@@ -1438,7 +1449,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1448,6 +1459,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa (tr</t>
@@ -1458,7 +1470,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1468,7 +1480,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ớ</t>
     </r>
@@ -1478,6 +1490,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c khi thay)</t>
@@ -1490,6 +1503,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mô t</t>
@@ -1500,7 +1514,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1510,6 +1524,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> v</t>
@@ -1520,7 +1535,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ậ</t>
     </r>
@@ -1530,6 +1545,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t li</t>
@@ -1540,7 +1556,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1550,6 +1566,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u (tr</t>
@@ -1560,7 +1577,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1570,7 +1587,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ớ</t>
     </r>
@@ -1580,6 +1597,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c khi thay)</t>
@@ -1592,6 +1610,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã li</t>
@@ -1602,7 +1621,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1612,6 +1631,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u k</t>
@@ -1622,7 +1642,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1632,6 +1652,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1642,7 +1663,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1652,6 +1673,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch  (sau khi thay)</t>
@@ -1664,6 +1686,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mô t</t>
@@ -1674,7 +1697,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1684,6 +1707,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> v</t>
@@ -1694,7 +1718,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ậ</t>
     </r>
@@ -1704,6 +1728,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t li</t>
@@ -1714,7 +1739,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1724,6 +1749,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u (sau khi thay)</t>
@@ -1752,6 +1778,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>{.</t>
@@ -1761,6 +1788,7 @@
         <b/>
         <sz val="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>beforeMaterialDesc</t>
@@ -1769,6 +1797,7 @@
       <rPr>
         <sz val="9"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>}</t>
@@ -1805,7 +1834,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>成型</t>
     </r>
@@ -1815,7 +1845,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Thành hình</t>
     </r>
@@ -1826,7 +1856,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>夜班</t>
     </r>
@@ -1835,7 +1866,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ca đêm </t>
     </r>
@@ -1846,7 +1877,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>早班</t>
     </r>
@@ -1855,7 +1887,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ca sáng </t>
     </r>
@@ -1866,7 +1898,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>中班</t>
     </r>
@@ -1875,7 +1908,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ca trưa </t>
     </r>
@@ -1886,7 +1919,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>合计</t>
     </r>
@@ -1895,7 +1929,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Tổng </t>
     </r>
@@ -1918,7 +1952,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>试制</t>
     </r>
@@ -1927,7 +1962,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Thử nghiệm </t>
     </r>
@@ -1941,7 +1976,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>量试</t>
     </r>
@@ -1950,7 +1986,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Thử nghiệm số lượng</t>
     </r>
@@ -1964,7 +2000,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>规格切换</t>
     </r>
@@ -1973,7 +2010,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 Thay quy cách </t>
@@ -1988,7 +2025,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>小胶种</t>
     </r>
@@ -1997,7 +2035,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 
 Loại su nhỏ</t>
@@ -2016,7 +2054,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>硫化</t>
     </r>
@@ -2026,7 +2065,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Lưu hóa</t>
     </r>
@@ -2049,7 +2088,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>硫化开动</t>
     </r>
@@ -2058,7 +2098,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 Số lượng máy lưu hóa</t>
@@ -2082,7 +2122,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>模具交替</t>
     </r>
@@ -2091,7 +2132,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Thay khuôn </t>
     </r>
@@ -2108,7 +2149,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>模具清洗</t>
     </r>
@@ -2117,7 +2159,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Vệ sinh khuôn </t>
     </r>
@@ -2131,7 +2173,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="0"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>备注</t>
     </r>
@@ -2140,7 +2183,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Ghi chú</t>
     </r>
@@ -2156,17 +2199,73 @@
   </si>
   <si>
     <t>{lhRemark}</t>
+  </si>
+  <si>
+    <t>{.class8LeftRightMould}</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.class6MouldMethod}</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>class1LeftRightMould</t>
+  </si>
+  <si>
+    <t>class1MouldMethod</t>
+  </si>
+  <si>
+    <t>class2LeftRightMould</t>
+  </si>
+  <si>
+    <t>class2MouldMethod</t>
+  </si>
+  <si>
+    <t>class3LeftRightMould</t>
+  </si>
+  <si>
+    <t>class3MouldMethod</t>
+  </si>
+  <si>
+    <t>class4LeftRightMould</t>
+  </si>
+  <si>
+    <t>class4MouldMethod</t>
+  </si>
+  <si>
+    <t>class5LeftRightMould</t>
+  </si>
+  <si>
+    <t>class5MouldMethod</t>
+  </si>
+  <si>
+    <t>class6LeftRightMould</t>
+  </si>
+  <si>
+    <t>class6MouldMethod</t>
+  </si>
+  <si>
+    <t>class7LeftRightMould</t>
+  </si>
+  <si>
+    <t>class7MouldMethod</t>
+  </si>
+  <si>
+    <t>class8LeftRightMould</t>
+  </si>
+  <si>
+    <t>class8MouldMethod</t>
+  </si>
+  <si>
+    <t>totalDailyPlanQty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -2174,7 +2273,7 @@
     <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -2185,55 +2284,60 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2241,6 +2345,7 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2248,12 +2353,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2261,197 +2368,42 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2459,6 +2411,26 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2467,13 +2439,14 @@
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2481,33 +2454,34 @@
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Calibri"/>
-      <charset val="163"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Segoe UI"/>
-      <charset val="238"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <charset val="163"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2515,52 +2489,59 @@
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2591,194 +2572,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="37">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -3118,312 +2913,367 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="61">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="177" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="41" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="41" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="12" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3433,374 +3283,73 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="12" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="61">
+  <cellStyles count="13">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma 2" xfId="49"/>
-    <cellStyle name="Excel Built-in Normal" xfId="50"/>
-    <cellStyle name="Normal 10" xfId="51"/>
-    <cellStyle name="Normal 12 3" xfId="52"/>
-    <cellStyle name="Normal 2 2" xfId="53"/>
-    <cellStyle name="Normal 20 3" xfId="54"/>
-    <cellStyle name="Normal 91" xfId="55"/>
-    <cellStyle name="Percent 2" xfId="56"/>
-    <cellStyle name="常规 2" xfId="57"/>
-    <cellStyle name="常规 2 5" xfId="58"/>
-    <cellStyle name="千位分隔 3" xfId="59"/>
-    <cellStyle name="千位分隔 3 3" xfId="60"/>
+    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3817,12 +3366,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3838,13 +3390,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="572799" name="图片 21"/>
+        <xdr:cNvPr id="572799" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007FBD0800}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3895,7 +3453,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3911,13 +3469,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4248,1251 +3812,1241 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CF7"/>
-  <sheetFormatPr defaultColWidth="9.1" defaultRowHeight="11.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.4" style="54" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5" style="54" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7" style="54" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1" style="54" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7" style="55" customWidth="1"/>
-    <col min="6" max="6" width="11.9" style="56" customWidth="1"/>
-    <col min="7" max="7" width="33.2" style="55" customWidth="1"/>
-    <col min="8" max="8" width="36.9" style="55" customWidth="1"/>
-    <col min="9" max="9" width="15.7" style="55" customWidth="1"/>
-    <col min="10" max="11" width="6.4" style="56" customWidth="1"/>
-    <col min="12" max="12" width="6.1" style="55" customWidth="1"/>
-    <col min="13" max="13" width="6.4" style="55" customWidth="1"/>
-    <col min="14" max="14" width="3.7" style="55" customWidth="1"/>
-    <col min="15" max="15" width="6.7" style="55" customWidth="1"/>
-    <col min="16" max="16" width="3.7" style="55" customWidth="1"/>
-    <col min="17" max="17" width="4.6" style="55" customWidth="1"/>
-    <col min="18" max="18" width="5.4" style="55" customWidth="1"/>
-    <col min="19" max="22" width="3.7" style="55" customWidth="1"/>
-    <col min="23" max="23" width="6.7" style="55" customWidth="1"/>
-    <col min="24" max="24" width="3.7" style="55" customWidth="1"/>
-    <col min="25" max="25" width="4.6" style="55" customWidth="1"/>
-    <col min="26" max="26" width="5.4" style="55" customWidth="1"/>
-    <col min="27" max="30" width="3.7" style="55" customWidth="1"/>
-    <col min="31" max="31" width="6.7" style="55" customWidth="1"/>
-    <col min="32" max="32" width="3.7" style="55" customWidth="1"/>
-    <col min="33" max="33" width="4.6" style="55" customWidth="1"/>
-    <col min="34" max="34" width="5.4" style="55" customWidth="1"/>
-    <col min="35" max="38" width="3.7" style="55" customWidth="1"/>
-    <col min="39" max="39" width="6.7" style="55" customWidth="1"/>
-    <col min="40" max="40" width="3.7" style="55" customWidth="1"/>
-    <col min="41" max="41" width="4.6" style="55" customWidth="1"/>
-    <col min="42" max="42" width="5.4" style="55" customWidth="1"/>
-    <col min="43" max="46" width="3.7" style="55" customWidth="1"/>
-    <col min="47" max="47" width="6.7" style="55" customWidth="1"/>
-    <col min="48" max="48" width="3.7" style="55" customWidth="1"/>
-    <col min="49" max="49" width="4.6" style="55" customWidth="1"/>
-    <col min="50" max="50" width="5.4" style="55" customWidth="1"/>
-    <col min="51" max="54" width="3.7" style="55" customWidth="1"/>
-    <col min="55" max="55" width="6.7" style="55" customWidth="1"/>
-    <col min="56" max="56" width="3.7" style="55" customWidth="1"/>
-    <col min="57" max="57" width="4.6" style="55" customWidth="1"/>
-    <col min="58" max="58" width="5.4" style="55" customWidth="1"/>
-    <col min="59" max="62" width="3.7" style="55" customWidth="1"/>
-    <col min="63" max="63" width="6.7" style="55" customWidth="1"/>
-    <col min="64" max="64" width="3.7" style="55" customWidth="1"/>
-    <col min="65" max="65" width="4.6" style="55" customWidth="1"/>
-    <col min="66" max="66" width="5.4" style="55" customWidth="1"/>
-    <col min="67" max="70" width="3.7" style="55" customWidth="1"/>
-    <col min="71" max="71" width="6.7" style="55" customWidth="1"/>
-    <col min="72" max="72" width="3.7" style="55" customWidth="1"/>
-    <col min="73" max="73" width="4.6" style="55" customWidth="1"/>
-    <col min="74" max="74" width="5.4" style="55" customWidth="1"/>
-    <col min="75" max="77" width="3.7" style="55" customWidth="1"/>
-    <col min="78" max="78" width="6.6" style="55" customWidth="1"/>
-    <col min="79" max="79" width="4.6" style="55" customWidth="1"/>
-    <col min="80" max="80" width="9.4" style="57" customWidth="1"/>
-    <col min="81" max="81" width="34.2" style="58" customWidth="1"/>
-    <col min="82" max="82" width="6.7" style="56" customWidth="1"/>
-    <col min="83" max="84" width="8.4" style="56" customWidth="1"/>
-    <col min="85" max="92" width="9.9" style="54" customWidth="1"/>
-    <col min="93" max="16384" width="9.1" style="54"/>
+    <col min="1" max="1" width="5.375" style="32" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="32" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.75" style="32" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="32" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="33" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="34" customWidth="1"/>
+    <col min="7" max="7" width="33.25" style="33" customWidth="1"/>
+    <col min="8" max="8" width="36.875" style="33" customWidth="1"/>
+    <col min="9" max="9" width="15.75" style="33" customWidth="1"/>
+    <col min="10" max="11" width="6.375" style="34" customWidth="1"/>
+    <col min="12" max="12" width="6.125" style="33" customWidth="1"/>
+    <col min="13" max="13" width="6.375" style="33" customWidth="1"/>
+    <col min="14" max="14" width="3.75" style="33" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="33" customWidth="1"/>
+    <col min="16" max="16" width="3.75" style="33" customWidth="1"/>
+    <col min="17" max="17" width="4.625" style="33" customWidth="1"/>
+    <col min="18" max="18" width="5.375" style="33" customWidth="1"/>
+    <col min="19" max="22" width="3.75" style="33" customWidth="1"/>
+    <col min="23" max="23" width="6.75" style="33" customWidth="1"/>
+    <col min="24" max="24" width="3.75" style="33" customWidth="1"/>
+    <col min="25" max="25" width="4.625" style="33" customWidth="1"/>
+    <col min="26" max="26" width="5.375" style="33" customWidth="1"/>
+    <col min="27" max="30" width="3.75" style="33" customWidth="1"/>
+    <col min="31" max="31" width="6.75" style="33" customWidth="1"/>
+    <col min="32" max="32" width="3.75" style="33" customWidth="1"/>
+    <col min="33" max="33" width="4.625" style="33" customWidth="1"/>
+    <col min="34" max="34" width="5.375" style="33" customWidth="1"/>
+    <col min="35" max="38" width="3.75" style="33" customWidth="1"/>
+    <col min="39" max="39" width="6.75" style="33" customWidth="1"/>
+    <col min="40" max="40" width="3.75" style="33" customWidth="1"/>
+    <col min="41" max="41" width="4.625" style="33" customWidth="1"/>
+    <col min="42" max="42" width="5.375" style="33" customWidth="1"/>
+    <col min="43" max="46" width="3.75" style="33" customWidth="1"/>
+    <col min="47" max="47" width="6.75" style="33" customWidth="1"/>
+    <col min="48" max="48" width="3.75" style="33" customWidth="1"/>
+    <col min="49" max="49" width="4.625" style="33" customWidth="1"/>
+    <col min="50" max="50" width="5.375" style="33" customWidth="1"/>
+    <col min="51" max="54" width="3.75" style="33" customWidth="1"/>
+    <col min="55" max="55" width="6.75" style="33" customWidth="1"/>
+    <col min="56" max="56" width="3.75" style="33" customWidth="1"/>
+    <col min="57" max="57" width="4.625" style="33" customWidth="1"/>
+    <col min="58" max="58" width="5.375" style="33" customWidth="1"/>
+    <col min="59" max="62" width="3.75" style="33" customWidth="1"/>
+    <col min="63" max="63" width="6.75" style="33" customWidth="1"/>
+    <col min="64" max="64" width="3.75" style="33" customWidth="1"/>
+    <col min="65" max="65" width="4.625" style="33" customWidth="1"/>
+    <col min="66" max="66" width="5.375" style="33" customWidth="1"/>
+    <col min="67" max="70" width="3.75" style="33" customWidth="1"/>
+    <col min="71" max="71" width="6.75" style="33" customWidth="1"/>
+    <col min="72" max="72" width="3.75" style="33" customWidth="1"/>
+    <col min="73" max="73" width="4.625" style="33" customWidth="1"/>
+    <col min="74" max="74" width="5.375" style="33" customWidth="1"/>
+    <col min="75" max="77" width="3.75" style="33" customWidth="1"/>
+    <col min="78" max="78" width="6.625" style="33" customWidth="1"/>
+    <col min="79" max="79" width="4.625" style="33" customWidth="1"/>
+    <col min="80" max="80" width="9.375" style="35" customWidth="1"/>
+    <col min="81" max="81" width="34.25" style="36" customWidth="1"/>
+    <col min="82" max="82" width="6.75" style="34" customWidth="1"/>
+    <col min="83" max="84" width="8.375" style="34" customWidth="1"/>
+    <col min="85" max="92" width="9.875" style="32" customWidth="1"/>
+    <col min="93" max="16384" width="9.125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:84">
-      <c r="E1" s="55" t="s">
+    <row r="1" spans="1:84" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="55" t="s">
+      <c r="L1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="55" t="s">
+      <c r="M1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="55" t="s">
+      <c r="N1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="55" t="s">
+      <c r="O1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="55" t="s">
+      <c r="P1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" s="55" t="s">
+      <c r="Q1" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="R1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="55" t="s">
+      <c r="S1" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="T1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="55" t="s">
+      <c r="U1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="55" t="s">
+      <c r="V1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="55" t="s">
+      <c r="W1" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="X1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="55" t="s">
+      <c r="Y1" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="Z1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z1" s="55" t="s">
+      <c r="AA1" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="AB1" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB1" s="55" t="s">
+      <c r="AC1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="55" t="s">
+      <c r="AD1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="55" t="s">
+      <c r="AE1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="AE1" s="55" t="s">
+      <c r="AF1" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="AF1" s="55" t="s">
+      <c r="AG1" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="AH1" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="AG1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH1" s="55" t="s">
+      <c r="AI1" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="AJ1" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="AI1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ1" s="55" t="s">
+      <c r="AK1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="AK1" s="55" t="s">
+      <c r="AL1" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="AL1" s="55" t="s">
+      <c r="AM1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="AM1" s="55" t="s">
+      <c r="AN1" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="55" t="s">
+      <c r="AO1" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="AP1" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP1" s="55" t="s">
+      <c r="AQ1" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="AR1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR1" s="55" t="s">
+      <c r="AS1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" s="55" t="s">
+      <c r="AT1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" s="55" t="s">
+      <c r="AU1" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="55" t="s">
+      <c r="AV1" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="55" t="s">
+      <c r="AW1" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="AX1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="AX1" s="55" t="s">
+      <c r="AY1" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="AZ1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="AY1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ1" s="55" t="s">
+      <c r="BA1" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="BA1" s="55" t="s">
+      <c r="BB1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" s="55" t="s">
+      <c r="BC1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" s="55" t="s">
+      <c r="BD1" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" s="55" t="s">
+      <c r="BE1" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="BF1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="BF1" s="55" t="s">
+      <c r="BG1" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="BH1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="BG1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH1" s="55" t="s">
+      <c r="BI1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" s="55" t="s">
+      <c r="BJ1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="BJ1" s="55" t="s">
+      <c r="BK1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="BK1" s="55" t="s">
+      <c r="BL1" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="BL1" s="55" t="s">
+      <c r="BM1" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="BN1" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="BM1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="BN1" s="55" t="s">
+      <c r="BO1" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="BP1" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="BO1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="BP1" s="55" t="s">
+      <c r="BQ1" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="BQ1" s="55" t="s">
+      <c r="BR1" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="BR1" s="55" t="s">
+      <c r="BS1" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="BS1" s="55" t="s">
+      <c r="BT1" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="BT1" s="55" t="s">
+      <c r="BU1" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="BV1" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="BU1" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="BV1" s="55" t="s">
+      <c r="BW1" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="BX1" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="BW1" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX1" s="55" t="s">
+      <c r="BY1" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="BY1" s="55" t="s">
+      <c r="CC1" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="BZ1" s="55" t="s">
+      <c r="CD1" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="CA1" s="55" t="s">
+      <c r="CE1" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="CF1" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="CB1" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="CC1" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="CD1" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="CE1" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="CF1" s="56" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1" spans="1:84">
-      <c r="A2" s="54" t="e">
+    <row r="2" spans="1:84" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="32" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="54"/>
-      <c r="AC2" s="54"/>
-      <c r="AD2" s="54"/>
-      <c r="AE2" s="54"/>
-      <c r="AF2" s="54"/>
-      <c r="AG2" s="54"/>
-      <c r="AH2" s="54"/>
-      <c r="AI2" s="54"/>
-      <c r="AJ2" s="54"/>
-      <c r="AK2" s="54"/>
-      <c r="AL2" s="54"/>
-      <c r="AM2" s="54"/>
-      <c r="AN2" s="54"/>
-      <c r="AO2" s="54"/>
-      <c r="AP2" s="54"/>
-      <c r="AQ2" s="54"/>
-      <c r="AR2" s="54"/>
-      <c r="AS2" s="54"/>
-      <c r="AT2" s="54"/>
-      <c r="AU2" s="54"/>
-      <c r="AV2" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW2" s="54"/>
-      <c r="AX2" s="54"/>
-      <c r="AY2" s="54"/>
-      <c r="AZ2" s="54"/>
-      <c r="BA2" s="56"/>
-      <c r="BB2" s="54"/>
-      <c r="BC2" s="54"/>
-      <c r="BD2" s="54"/>
-      <c r="BE2" s="54"/>
-      <c r="BF2" s="54"/>
-      <c r="BG2" s="54"/>
-      <c r="BH2" s="54"/>
-      <c r="BI2" s="54"/>
-      <c r="BJ2" s="54"/>
-      <c r="BK2" s="54"/>
-      <c r="BL2" s="54"/>
-      <c r="BM2" s="54"/>
-      <c r="BN2" s="54"/>
-      <c r="BO2" s="54"/>
-      <c r="BP2" s="54"/>
-      <c r="BQ2" s="54"/>
-      <c r="BR2" s="54"/>
-      <c r="BS2" s="54"/>
-      <c r="BT2" s="54"/>
-      <c r="BU2" s="54"/>
-      <c r="BV2" s="54"/>
-      <c r="BW2" s="54"/>
-      <c r="BX2" s="54"/>
-      <c r="BY2" s="54"/>
-      <c r="BZ2" s="54"/>
-      <c r="CA2" s="54"/>
-      <c r="CB2" s="54"/>
-      <c r="CC2" s="54"/>
-      <c r="CD2" s="54"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="37"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
+      <c r="AS2" s="32"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="34"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+      <c r="BD2" s="32"/>
+      <c r="BE2" s="32"/>
+      <c r="BF2" s="32"/>
+      <c r="BG2" s="32"/>
+      <c r="BH2" s="32"/>
+      <c r="BI2" s="32"/>
+      <c r="BJ2" s="32"/>
+      <c r="BK2" s="32"/>
+      <c r="BL2" s="32"/>
+      <c r="BM2" s="32"/>
+      <c r="BN2" s="32"/>
+      <c r="BO2" s="32"/>
+      <c r="BP2" s="32"/>
+      <c r="BQ2" s="32"/>
+      <c r="BR2" s="32"/>
+      <c r="BS2" s="32"/>
+      <c r="BT2" s="32"/>
+      <c r="BU2" s="32"/>
+      <c r="BV2" s="32"/>
+      <c r="BW2" s="32"/>
+      <c r="BX2" s="32"/>
+      <c r="BY2" s="32"/>
+      <c r="BZ2" s="32"/>
+      <c r="CA2" s="32"/>
+      <c r="CB2" s="32"/>
+      <c r="CC2" s="32"/>
+      <c r="CD2" s="32"/>
     </row>
-    <row r="3" s="52" customFormat="1" ht="17.85" customHeight="1" spans="1:84">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="M3" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62">
+    <row r="3" spans="1:84" s="30" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="M3" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40">
         <f>SUM(O7:O108138)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="63">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="41">
         <f>SUM(W7:W108138)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="63"/>
-      <c r="Y3" s="63"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="64"/>
-      <c r="AB3" s="63"/>
-      <c r="AC3" s="63"/>
-      <c r="AD3" s="63"/>
-      <c r="AE3" s="63" t="e">
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41" t="e">
         <f>SUM(CB7:CB108138)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF3" s="64"/>
-      <c r="AG3" s="63"/>
-      <c r="AH3" s="63"/>
-      <c r="AI3" s="63"/>
-      <c r="AJ3" s="63"/>
-      <c r="AK3" s="64"/>
-      <c r="AL3" s="63"/>
-      <c r="AM3" s="63">
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41">
         <f>SUM(AM7:AM108138)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="63"/>
-      <c r="AO3" s="63"/>
-      <c r="AP3" s="64"/>
-      <c r="AQ3" s="63"/>
-      <c r="AR3" s="63"/>
-      <c r="AS3" s="63"/>
-      <c r="AT3" s="63"/>
-      <c r="AU3" s="64">
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="42">
         <f>SUM(AU7:AU108138)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="63"/>
-      <c r="AW3" s="63"/>
-      <c r="AX3" s="63"/>
-      <c r="AY3" s="63"/>
-      <c r="AZ3" s="64"/>
-      <c r="BA3" s="63"/>
-      <c r="BB3" s="63"/>
-      <c r="BC3" s="63">
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="41"/>
+      <c r="AX3" s="41"/>
+      <c r="AY3" s="41"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="41"/>
+      <c r="BB3" s="41"/>
+      <c r="BC3" s="41">
         <f>SUM(BC7:BC108138)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="63"/>
-      <c r="BE3" s="64"/>
-      <c r="BF3" s="62"/>
-      <c r="BG3" s="62"/>
-      <c r="BH3" s="62"/>
-      <c r="BJ3" s="65"/>
-      <c r="BK3" s="63">
+      <c r="BD3" s="41"/>
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="40"/>
+      <c r="BG3" s="40"/>
+      <c r="BH3" s="40"/>
+      <c r="BJ3" s="43"/>
+      <c r="BK3" s="41">
         <f>SUM(BK7:BK108138)</f>
         <v>0</v>
       </c>
-      <c r="BS3" s="63">
+      <c r="BS3" s="41">
         <f>SUM(BS7:BS108138)</f>
         <v>0</v>
       </c>
-      <c r="BZ3" s="63">
+      <c r="BZ3" s="41">
         <f>BC3+BK3+BS3</f>
         <v>0</v>
       </c>
-      <c r="CB3" s="63" t="e">
+      <c r="CB3" s="41" t="e">
         <f>O3+W3+AE3+AM3+AU3+BC3+BK3+BS3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="66"/>
+      <c r="CD3" s="44"/>
     </row>
-    <row r="4" s="52" customFormat="1" ht="17.85" customHeight="1" spans="1:84">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="M4" s="52" t="s">
+    <row r="4" spans="1:84" s="30" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="M4" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AO4" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="42"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62" t="s">
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="42"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="42"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="63" t="s">
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="BP4" s="42"/>
+      <c r="BQ4" s="41"/>
+      <c r="BR4" s="41"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="41"/>
+      <c r="BU4" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="Z4" s="63"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AO4" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="63"/>
-      <c r="AR4" s="63"/>
-      <c r="AS4" s="63"/>
-      <c r="AT4" s="64"/>
-      <c r="AU4" s="63"/>
-      <c r="AV4" s="63"/>
-      <c r="AW4" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX4" s="63"/>
-      <c r="AY4" s="64"/>
-      <c r="AZ4" s="63"/>
-      <c r="BA4" s="63"/>
-      <c r="BB4" s="63"/>
-      <c r="BC4" s="63"/>
-      <c r="BD4" s="64"/>
-      <c r="BL4" s="63"/>
-      <c r="BM4" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="BN4" s="63"/>
-      <c r="BO4" s="63"/>
-      <c r="BP4" s="64"/>
-      <c r="BQ4" s="63"/>
-      <c r="BR4" s="63"/>
-      <c r="BS4" s="63"/>
-      <c r="BT4" s="63"/>
-      <c r="BU4" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="BW4" s="62"/>
-      <c r="BZ4" s="63"/>
-      <c r="CB4" s="63"/>
-      <c r="CD4" s="67"/>
+      <c r="BW4" s="40"/>
+      <c r="BZ4" s="41"/>
+      <c r="CB4" s="41"/>
+      <c r="CD4" s="45"/>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:84">
-      <c r="A5" s="68">
+    <row r="5" spans="1:84" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="46">
         <f>BC3+BK3+BS3</f>
         <v>0</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="70" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="J5" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="K5" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="L5" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="M5" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="N5" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="70" t="s">
+      <c r="O5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="84"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="L5" s="70" t="s">
+      <c r="W5" s="84"/>
+      <c r="X5" s="84"/>
+      <c r="Y5" s="84"/>
+      <c r="Z5" s="84"/>
+      <c r="AA5" s="84"/>
+      <c r="AB5" s="84"/>
+      <c r="AC5" s="87"/>
+      <c r="AD5" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="AE5" s="89"/>
+      <c r="AF5" s="89"/>
+      <c r="AG5" s="89"/>
+      <c r="AH5" s="89"/>
+      <c r="AI5" s="89"/>
+      <c r="AJ5" s="89"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="N5" s="115" t="s">
+      <c r="AM5" s="89"/>
+      <c r="AN5" s="89"/>
+      <c r="AO5" s="89"/>
+      <c r="AP5" s="89"/>
+      <c r="AQ5" s="89"/>
+      <c r="AR5" s="89"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="73"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="116" t="s">
+      <c r="AU5" s="89"/>
+      <c r="AV5" s="89"/>
+      <c r="AW5" s="89"/>
+      <c r="AX5" s="89"/>
+      <c r="AY5" s="89"/>
+      <c r="AZ5" s="89"/>
+      <c r="BA5" s="92"/>
+      <c r="BB5" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="W5" s="73"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="73"/>
-      <c r="Z5" s="73"/>
-      <c r="AA5" s="73"/>
-      <c r="AB5" s="73"/>
-      <c r="AC5" s="76"/>
-      <c r="AD5" s="77" t="s">
+      <c r="BC5" s="77"/>
+      <c r="BD5" s="77"/>
+      <c r="BE5" s="77"/>
+      <c r="BF5" s="77"/>
+      <c r="BG5" s="77"/>
+      <c r="BH5" s="77"/>
+      <c r="BI5" s="78"/>
+      <c r="BJ5" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="AE5" s="78"/>
-      <c r="AF5" s="78"/>
-      <c r="AG5" s="78"/>
-      <c r="AH5" s="78"/>
-      <c r="AI5" s="78"/>
-      <c r="AJ5" s="78"/>
-      <c r="AK5" s="79"/>
-      <c r="AL5" s="80" t="s">
+      <c r="BK5" s="77"/>
+      <c r="BL5" s="77"/>
+      <c r="BM5" s="77"/>
+      <c r="BN5" s="77"/>
+      <c r="BO5" s="77"/>
+      <c r="BP5" s="77"/>
+      <c r="BQ5" s="78"/>
+      <c r="BR5" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="AM5" s="78"/>
-      <c r="AN5" s="78"/>
-      <c r="AO5" s="78"/>
-      <c r="AP5" s="78"/>
-      <c r="AQ5" s="78"/>
-      <c r="AR5" s="78"/>
-      <c r="AS5" s="79"/>
-      <c r="AT5" s="80" t="s">
+      <c r="BS5" s="77"/>
+      <c r="BT5" s="77"/>
+      <c r="BU5" s="77"/>
+      <c r="BV5" s="77"/>
+      <c r="BW5" s="77"/>
+      <c r="BX5" s="77"/>
+      <c r="BY5" s="80"/>
+      <c r="BZ5" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AU5" s="78"/>
-      <c r="AV5" s="78"/>
-      <c r="AW5" s="78"/>
-      <c r="AX5" s="78"/>
-      <c r="AY5" s="78"/>
-      <c r="AZ5" s="78"/>
-      <c r="BA5" s="81"/>
-      <c r="BB5" s="82" t="s">
+      <c r="CA5" s="82"/>
+      <c r="CB5" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="BC5" s="83"/>
-      <c r="BD5" s="83"/>
-      <c r="BE5" s="83"/>
-      <c r="BF5" s="83"/>
-      <c r="BG5" s="83"/>
-      <c r="BH5" s="83"/>
-      <c r="BI5" s="84"/>
-      <c r="BJ5" s="85" t="s">
+      <c r="CC5" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="BK5" s="83"/>
-      <c r="BL5" s="83"/>
-      <c r="BM5" s="83"/>
-      <c r="BN5" s="83"/>
-      <c r="BO5" s="83"/>
-      <c r="BP5" s="83"/>
-      <c r="BQ5" s="84"/>
-      <c r="BR5" s="85" t="s">
+      <c r="CD5" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="BS5" s="83"/>
-      <c r="BT5" s="83"/>
-      <c r="BU5" s="83"/>
-      <c r="BV5" s="83"/>
-      <c r="BW5" s="83"/>
-      <c r="BX5" s="83"/>
-      <c r="BY5" s="86"/>
-      <c r="BZ5" s="87" t="s">
+      <c r="CE5" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="CA5" s="88"/>
-      <c r="CB5" s="70" t="s">
+      <c r="CF5" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="CC5" s="70" t="s">
+    </row>
+    <row r="6" spans="1:84" s="31" customFormat="1" ht="72" x14ac:dyDescent="0.15">
+      <c r="A6" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="CD5" s="71" t="s">
+      <c r="B6" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="CE5" s="70" t="s">
+      <c r="C6" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="CF5" s="70" t="s">
+      <c r="F6" s="51" t="s">
         <v>97</v>
       </c>
+      <c r="G6" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="52"/>
+      <c r="M6" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="N6" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="R6" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="S6" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="T6" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="U6" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="V6" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="W6" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="X6" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y6" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z6" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA6" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB6" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC6" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD6" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE6" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF6" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG6" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH6" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI6" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ6" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK6" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="AL6" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="AM6" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN6" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO6" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="AP6" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ6" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR6" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS6" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT6" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="AU6" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="AV6" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW6" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="AX6" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY6" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ6" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="BA6" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="BB6" s="60" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC6" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD6" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE6" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF6" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="BG6" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="BH6" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="BI6" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="BJ6" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK6" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL6" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM6" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN6" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO6" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="BP6" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="BQ6" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="BR6" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS6" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="BT6" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="BU6" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="BV6" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="BW6" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="BX6" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="BY6" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ6" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA6" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB6" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="CC6" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="CD6" s="64"/>
+      <c r="CE6" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="CF6" s="51" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="6" s="53" customFormat="1" ht="69" spans="1:84">
-      <c r="A6" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="90" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="90" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="L6" s="91"/>
-      <c r="M6" s="92" t="s">
-        <v>106</v>
-      </c>
-      <c r="N6" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="O6" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="P6" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q6" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="R6" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="S6" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="T6" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="U6" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="V6" s="94" t="s">
-        <v>107</v>
-      </c>
-      <c r="W6" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="X6" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y6" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z6" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA6" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB6" s="94" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC6" s="95" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD6" s="96" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE6" s="97" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF6" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG6" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH6" s="97" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI6" s="97" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ6" s="97" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK6" s="97" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL6" s="97" t="s">
-        <v>115</v>
-      </c>
-      <c r="AM6" s="97" t="s">
-        <v>108</v>
-      </c>
-      <c r="AN6" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="AO6" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP6" s="97" t="s">
-        <v>111</v>
-      </c>
-      <c r="AQ6" s="97" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR6" s="97" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS6" s="97" t="s">
-        <v>114</v>
-      </c>
-      <c r="AT6" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU6" s="97" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV6" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="AW6" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX6" s="97" t="s">
-        <v>111</v>
-      </c>
-      <c r="AY6" s="97" t="s">
-        <v>112</v>
-      </c>
-      <c r="AZ6" s="97" t="s">
-        <v>113</v>
-      </c>
-      <c r="BA6" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="BB6" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="BC6" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD6" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE6" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="BF6" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="BG6" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="BH6" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="BI6" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="BJ6" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="BK6" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL6" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM6" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="BN6" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="BO6" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="BP6" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ6" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR6" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="BS6" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="BT6" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="BU6" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="BV6" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="BW6" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="BX6" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="BY6" s="101" t="s">
-        <v>114</v>
-      </c>
-      <c r="BZ6" s="102" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA6" s="70" t="s">
-        <v>109</v>
-      </c>
-      <c r="CB6" s="90" t="s">
+    <row r="7" spans="1:84" ht="48" x14ac:dyDescent="0.15">
+      <c r="E7" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="CC6" s="90" t="s">
+      <c r="F7" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="CD6" s="103"/>
-      <c r="CE6" s="90" t="s">
+      <c r="G7" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="CF6" s="90" t="s">
+      <c r="H7" s="68" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="7" ht="46" spans="1:84">
-      <c r="E7" s="104" t="s">
+      <c r="I7" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="F7" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="G7" s="106" t="s">
-        <v>123</v>
-      </c>
-      <c r="H7" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="I7" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="J7" s="104" t="e">
+      <c r="J7" s="65" t="e">
         <f>CF7-CE7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="104" t="s">
+      <c r="K7" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="L7" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="M7" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="N7" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="O7" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="L7" s="104" t="s">
+      <c r="P7" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="M7" s="108" t="s">
+      <c r="Q7" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="N7" s="109" t="s">
+      <c r="R7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="O7" s="110" t="s">
+      <c r="S7" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="P7" s="110" t="s">
+      <c r="T7" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="Q7" s="110" t="s">
+      <c r="U7" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="R7" s="110" t="s">
+      <c r="V7" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="S7" s="110" t="s">
+      <c r="W7" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="T7" s="110" t="s">
+      <c r="X7" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="U7" s="110" t="s">
+      <c r="Y7" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="V7" s="110" t="s">
+      <c r="Z7" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="W7" s="110" t="s">
+      <c r="AA7" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="X7" s="110" t="s">
+      <c r="AB7" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="Y7" s="110" t="s">
+      <c r="AC7" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="Z7" s="110" t="s">
+      <c r="AD7" s="71" t="s">
         <v>141</v>
       </c>
-      <c r="AA7" s="110" t="s">
+      <c r="AE7" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="AB7" s="110" t="s">
+      <c r="AF7" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="AC7" s="110" t="s">
+      <c r="AG7" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="AD7" s="110" t="s">
+      <c r="AH7" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="110" t="s">
+      <c r="AI7" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="AF7" s="110" t="s">
+      <c r="AJ7" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="AG7" s="110" t="s">
+      <c r="AK7" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="AH7" s="110" t="s">
+      <c r="AL7" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="AI7" s="110" t="s">
+      <c r="AM7" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="AJ7" s="110" t="s">
+      <c r="AN7" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="AK7" s="110" t="s">
+      <c r="AO7" s="71" t="s">
         <v>152</v>
       </c>
-      <c r="AL7" s="110" t="s">
+      <c r="AP7" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="AM7" s="110" t="s">
+      <c r="AQ7" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="AN7" s="110" t="s">
+      <c r="AR7" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AO7" s="110" t="s">
+      <c r="AS7" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="AP7" s="110" t="s">
+      <c r="AT7" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="AQ7" s="110" t="s">
+      <c r="AU7" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="AR7" s="110" t="s">
+      <c r="AV7" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="AS7" s="110" t="s">
+      <c r="AW7" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="AT7" s="110" t="s">
+      <c r="AX7" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="AU7" s="110" t="s">
+      <c r="AY7" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="AV7" s="110" t="s">
+      <c r="AZ7" s="71" t="s">
         <v>163</v>
       </c>
-      <c r="AW7" s="110" t="s">
+      <c r="BA7" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="AX7" s="110" t="s">
+      <c r="BB7" s="71" t="s">
         <v>165</v>
       </c>
-      <c r="AY7" s="110" t="s">
+      <c r="BC7" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="AZ7" s="110" t="s">
+      <c r="BD7" s="71" t="s">
         <v>167</v>
       </c>
-      <c r="BA7" s="110" t="s">
+      <c r="BE7" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="BB7" s="110" t="s">
+      <c r="BF7" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="BC7" s="110" t="s">
+      <c r="BG7" s="71" t="s">
+        <v>278</v>
+      </c>
+      <c r="BH7" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="BD7" s="110" t="s">
+      <c r="BI7" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="BE7" s="110" t="s">
+      <c r="BJ7" s="71" t="s">
         <v>172</v>
       </c>
-      <c r="BF7" s="110" t="s">
+      <c r="BK7" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="BG7" s="110" t="s">
+      <c r="BL7" s="71" t="s">
         <v>174</v>
       </c>
-      <c r="BH7" s="110" t="s">
+      <c r="BM7" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="BI7" s="110" t="s">
+      <c r="BN7" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="BJ7" s="110" t="s">
+      <c r="BO7" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="BK7" s="110" t="s">
+      <c r="BP7" s="71" t="s">
         <v>178</v>
       </c>
-      <c r="BL7" s="110" t="s">
+      <c r="BQ7" s="71" t="s">
         <v>179</v>
       </c>
-      <c r="BM7" s="110" t="s">
+      <c r="BR7" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="BN7" s="110" t="s">
+      <c r="BS7" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="BO7" s="110" t="s">
+      <c r="BT7" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="BP7" s="110" t="s">
+      <c r="BU7" s="71" t="s">
+        <v>277</v>
+      </c>
+      <c r="BV7" s="71" t="s">
         <v>183</v>
       </c>
-      <c r="BQ7" s="110" t="s">
+      <c r="BW7" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="BR7" s="110" t="s">
+      <c r="BX7" s="71" t="s">
         <v>185</v>
       </c>
-      <c r="BS7" s="110" t="s">
+      <c r="BY7" s="72" t="s">
         <v>186</v>
       </c>
-      <c r="BT7" s="110" t="s">
-        <v>187</v>
-      </c>
-      <c r="BU7" s="110" t="s">
-        <v>188</v>
-      </c>
-      <c r="BV7" s="110" t="s">
-        <v>189</v>
-      </c>
-      <c r="BW7" s="110" t="s">
-        <v>190</v>
-      </c>
-      <c r="BX7" s="110" t="s">
-        <v>191</v>
-      </c>
-      <c r="BY7" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="BZ7" s="112" t="e">
+      <c r="BZ7" s="73" t="e">
         <f>BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA7" s="113" t="e">
+      <c r="CA7" s="74" t="e">
         <f>BL7+BT7+BD7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CB7" s="113" t="e">
+      <c r="CB7" s="74" t="e">
         <f>O7+W7+AE7+AM7+AU7+BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CC7" s="105" t="s">
-        <v>193</v>
-      </c>
-      <c r="CD7" s="114" t="s">
-        <v>194</v>
-      </c>
-      <c r="CE7" s="114" t="s">
-        <v>195</v>
-      </c>
-      <c r="CF7" s="105" t="s">
-        <v>196</v>
+      <c r="CC7" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="CD7" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="CE7" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="CF7" s="66" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:CF7" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A6:CF7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="9">
+    <mergeCell ref="BB5:BI5"/>
+    <mergeCell ref="BJ5:BQ5"/>
+    <mergeCell ref="BR5:BY5"/>
+    <mergeCell ref="BZ5:CA5"/>
     <mergeCell ref="N5:U5"/>
     <mergeCell ref="V5:AC5"/>
     <mergeCell ref="AD5:AK5"/>
     <mergeCell ref="AL5:AS5"/>
     <mergeCell ref="AT5:BA5"/>
-    <mergeCell ref="BB5:BI5"/>
-    <mergeCell ref="BJ5:BQ5"/>
-    <mergeCell ref="BR5:BY5"/>
-    <mergeCell ref="BZ5:CA5"/>
   </mergeCells>
+  <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="CD5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="0" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="0" priority="24207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="24207" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M6">
-    <cfRule type="duplicateValues" dxfId="0" priority="24210" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="24210" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:I6">
-    <cfRule type="duplicateValues" dxfId="0" priority="24201" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="24201" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K6">
     <cfRule type="duplicateValues" dxfId="0" priority="24204" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6 Z6 AH6 AP6 AX6 BF6 BN6 BV6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6 Z6 AH6 AP6 AX6 BF6 BN6 BV6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="23" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" scale="23" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="82" max="1048575" man="1"/>
   </colBreaks>
@@ -5502,472 +5056,470 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.9" style="22" customWidth="1"/>
-    <col min="2" max="2" width="11.4" style="23" customWidth="1"/>
-    <col min="3" max="4" width="11.4" style="24" customWidth="1"/>
-    <col min="5" max="5" width="8" style="22" customWidth="1"/>
-    <col min="6" max="6" width="14.3" style="24" customWidth="1"/>
-    <col min="7" max="7" width="14.3" style="22" customWidth="1"/>
-    <col min="8" max="8" width="35.4" style="24" customWidth="1"/>
-    <col min="9" max="9" width="14.3" style="22" customWidth="1"/>
-    <col min="10" max="10" width="35.4" style="25" customWidth="1"/>
-    <col min="11" max="11" width="10.7" style="25" customWidth="1"/>
-    <col min="12" max="14" width="6.9" style="24" customWidth="1"/>
-    <col min="15" max="15" width="23.2" style="24" customWidth="1"/>
-    <col min="16" max="16" width="21.1" style="24" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="24"/>
+    <col min="1" max="1" width="5.875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="8" customWidth="1"/>
+    <col min="3" max="4" width="11.375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="8" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="7" customWidth="1"/>
+    <col min="8" max="8" width="35.375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="7" customWidth="1"/>
+    <col min="10" max="10" width="35.375" style="10" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="10" customWidth="1"/>
+    <col min="12" max="14" width="6.875" style="9" customWidth="1"/>
+    <col min="15" max="15" width="23.25" style="9" customWidth="1"/>
+    <col min="16" max="16" width="21.125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.25" hidden="1" spans="1:16">
-      <c r="B1" s="23" t="s">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="J1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="O1" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="P1" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="93" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="22" t="s">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="95"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="96" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="99"/>
+    </row>
+    <row r="4" spans="1:16" ht="25.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="B4" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="C4" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="D4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="P1" s="24" t="s">
-        <v>62</v>
+      <c r="E4" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="P4" s="15" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" spans="1:16">
-      <c r="A2" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="28"/>
+    <row r="5" spans="1:16" ht="36" x14ac:dyDescent="0.15">
+      <c r="A5" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="K5" s="18"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="20" t="s">
+        <v>114</v>
+      </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:16">
-      <c r="A3" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="32"/>
-    </row>
-    <row r="4" ht="25.2" customHeight="1" spans="1:16">
-      <c r="A4" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="N4" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" ht="40" spans="1:16">
-      <c r="A5" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="34" t="s">
+    <row r="6" spans="1:16" ht="23.65" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="B6" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="C6" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="D6" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="F6" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="G6" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="K5" s="40"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" ht="23.7" customHeight="1" spans="1:16">
-      <c r="A6" s="43" t="s">
+      <c r="H6" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="I6" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="J6" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="D6" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="46" t="s">
+      <c r="K6" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="L6" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="M6" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="N6" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="I6" s="46" t="s">
+      <c r="O6" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="J6" s="48" t="s">
-        <v>238</v>
-      </c>
-      <c r="K6" s="49" t="s">
-        <v>239</v>
-      </c>
-      <c r="L6" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="M6" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="N6" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="O6" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>193</v>
+      <c r="P6" s="29" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:P6" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A5:P6" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
+    <col min="1" max="1" width="18.125" customWidth="1"/>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="17.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
     <col min="5" max="5" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.15">
+      <c r="A1" s="110" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A2" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="105"/>
+      <c r="B3" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="1"/>
     </row>
-    <row r="2" ht="15.5" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="B4" s="111" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="1"/>
     </row>
-    <row r="3" ht="15.5" spans="1:6">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B5" s="100" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="B6" s="100" t="s">
         <v>253</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="1"/>
     </row>
-    <row r="4" ht="15.5" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="2"/>
+      <c r="C7" s="112" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="113"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="1"/>
     </row>
-    <row r="5" ht="15.5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A8" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="1"/>
     </row>
-    <row r="6" ht="15.5" spans="1:6">
-      <c r="A6" s="4" t="s">
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A9" s="105"/>
+      <c r="B9" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C9" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="2"/>
+      <c r="D9" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="1"/>
     </row>
-    <row r="7" ht="31" spans="1:6">
-      <c r="A7" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="13" t="s">
+    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.15">
+      <c r="A10" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
-    <row r="8" ht="15.5" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="2"/>
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="108" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="100" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="101"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="1"/>
     </row>
-    <row r="9" ht="15.5" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="F9" s="2"/>
+    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="109"/>
+      <c r="C12" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="1"/>
     </row>
-    <row r="10" ht="46.5" spans="1:6">
-      <c r="A10" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E10" s="6" t="s">
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A13" s="106" t="s">
         <v>272</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="1"/>
     </row>
-    <row r="11" ht="15.5" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="C11" s="10" t="s">
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.15">
+      <c r="A14" s="107"/>
+      <c r="B14" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" ht="15.5" spans="1:6">
-      <c r="A12" s="4" t="s">
+      <c r="C14" s="103" t="s">
         <v>276</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" ht="15.5" spans="1:6">
-      <c r="A13" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" ht="15.5" spans="1:6">
-      <c r="A14" s="21"/>
-      <c r="B14" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="2"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -5985,7 +5537,7 @@
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
   </mergeCells>
+  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,60 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E14DCB-C98A-481B-BDDE-5A82E60BEAB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12555" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="硫化计划主表" sheetId="30" r:id="rId1"/>
     <sheet name="硫化换模计划" sheetId="31" r:id="rId2"/>
-    <sheet name="排产小结" sheetId="32" r:id="rId3"/>
+    <sheet name="排产小结" sheetId="33" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化计划主表!$A$6:$CF$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$5:$P$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化计划主表!$A$6:$CF$7</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">硫化计划主表!$E$5:$CC$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>项田昊</author>
   </authors>
   <commentList>
-    <comment ref="CC5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="CC5" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>可编辑</t>
         </r>
       </text>
     </comment>
-    <comment ref="CD5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="CD5" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>多台的用“，”分开</t>
@@ -66,19 +71,19 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="O4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Admin:</t>
         </r>
@@ -86,21 +91,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 只换活字块如果为是，需要回填“在机模具号”</t>
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="P4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Admin:</t>
         </r>
@@ -108,7 +113,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 备注栏可以编辑</t>
@@ -158,12 +163,15 @@
     <t>class1FinishQty</t>
   </si>
   <si>
-    <t>leftRightMould</t>
+    <t>class1LeftRightMould</t>
   </si>
   <si>
     <t>class1Type</t>
   </si>
   <si>
+    <t>class1MouldMethod</t>
+  </si>
+  <si>
     <t>class1Analysis</t>
   </si>
   <si>
@@ -179,9 +187,15 @@
     <t>class2FinishQty</t>
   </si>
   <si>
+    <t>class2LeftRightMould</t>
+  </si>
+  <si>
     <t>class2Type</t>
   </si>
   <si>
+    <t>class2MouldMethod</t>
+  </si>
+  <si>
     <t>class2Analysis</t>
   </si>
   <si>
@@ -197,9 +211,15 @@
     <t>class3FinishQty</t>
   </si>
   <si>
+    <t>class3LeftRightMould</t>
+  </si>
+  <si>
     <t>class3Type</t>
   </si>
   <si>
+    <t>class3MouldMethod</t>
+  </si>
+  <si>
     <t>class3Analysis</t>
   </si>
   <si>
@@ -215,9 +235,15 @@
     <t>class4FinishQty</t>
   </si>
   <si>
+    <t>class4LeftRightMould</t>
+  </si>
+  <si>
     <t>class4Type</t>
   </si>
   <si>
+    <t>class4MouldMethod</t>
+  </si>
+  <si>
     <t>class4Analysis</t>
   </si>
   <si>
@@ -233,9 +259,15 @@
     <t>class5FinishQty</t>
   </si>
   <si>
+    <t>class5LeftRightMould</t>
+  </si>
+  <si>
     <t>class5Type</t>
   </si>
   <si>
+    <t>class5MouldMethod</t>
+  </si>
+  <si>
     <t>class5Analysis</t>
   </si>
   <si>
@@ -251,9 +283,15 @@
     <t>class6FinishQty</t>
   </si>
   <si>
+    <t>class6LeftRightMould</t>
+  </si>
+  <si>
     <t>class6Type</t>
   </si>
   <si>
+    <t>class6MouldMethod</t>
+  </si>
+  <si>
     <t>class6Analysis</t>
   </si>
   <si>
@@ -269,9 +307,15 @@
     <t>class7FinishQty</t>
   </si>
   <si>
+    <t>class7LeftRightMould</t>
+  </si>
+  <si>
     <t>class7Type</t>
   </si>
   <si>
+    <t>class7MouldMethod</t>
+  </si>
+  <si>
     <t>class7Analysis</t>
   </si>
   <si>
@@ -287,9 +331,15 @@
     <t>class8FinishQty</t>
   </si>
   <si>
+    <t>class8LeftRightMould</t>
+  </si>
+  <si>
     <t>class8Type</t>
   </si>
   <si>
+    <t>class8MouldMethod</t>
+  </si>
+  <si>
     <t>class8Analysis</t>
   </si>
   <si>
@@ -300,6 +350,9 @@
   </si>
   <si>
     <t>cxMachineCode</t>
+  </si>
+  <si>
+    <t>totalDailyPlanQty</t>
   </si>
   <si>
     <t>todayNightFinishQty</t>
@@ -311,7 +364,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -323,7 +375,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -333,7 +385,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -344,7 +395,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -354,7 +405,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -365,7 +415,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -375,7 +425,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -386,7 +435,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -396,7 +445,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -407,7 +455,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -417,7 +465,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -428,7 +475,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -438,7 +485,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -449,7 +495,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -459,7 +505,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -470,7 +515,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -480,7 +525,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -491,7 +535,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -501,7 +545,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -513,7 +556,6 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -523,7 +565,7 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -532,7 +574,6 @@
         <sz val="9"/>
         <color indexed="8"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -671,7 +712,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>L</t>
@@ -682,7 +722,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -692,7 +732,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa trong ca</t>
@@ -724,7 +763,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>*示方类型
@@ -736,7 +774,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -746,7 +784,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng thức</t>
@@ -774,7 +811,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -785,7 +821,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ổ</t>
     </r>
@@ -795,7 +831,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng</t>
@@ -811,7 +846,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -821,7 +856,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">n hàng </t>
     </r>
@@ -833,7 +868,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -844,7 +878,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -854,7 +888,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -864,7 +897,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -873,7 +906,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ợ</t>
     </r>
@@ -882,7 +915,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng l</t>
@@ -892,7 +924,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -901,7 +933,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">u hóa </t>
@@ -911,7 +942,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đạ</t>
     </r>
@@ -920,7 +951,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">t </t>
@@ -1086,6 +1116,9 @@
     <t>{.class6Type}</t>
   </si>
   <si>
+    <t>{.class6MouldMethod}</t>
+  </si>
+  <si>
     <t>{.class6Analysis}</t>
   </si>
   <si>
@@ -1125,6 +1158,9 @@
     <t>{.class8FinishQty}</t>
   </si>
   <si>
+    <t>{.class8LeftRightMould}</t>
+  </si>
+  <si>
     <t>{.class8Type}</t>
   </si>
   <si>
@@ -1159,6 +1195,9 @@
   </si>
   <si>
     <t>planOrder</t>
+  </si>
+  <si>
+    <t>leftRightMould</t>
   </si>
   <si>
     <t>beforeMaterialCode</t>
@@ -1244,7 +1283,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>STT k</t>
@@ -1255,7 +1293,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1265,7 +1303,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1276,7 +1313,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1286,7 +1323,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ch </t>
@@ -1299,7 +1335,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Trái ph</t>
@@ -1310,7 +1345,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1320,7 +1355,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i c</t>
@@ -1331,7 +1365,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -1341,7 +1375,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>a khuôn</t>
@@ -1354,7 +1387,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã li</t>
@@ -1365,7 +1397,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1375,7 +1407,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u k</t>
@@ -1386,7 +1417,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1396,7 +1427,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1407,7 +1437,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1417,7 +1447,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ch  </t>
@@ -1428,7 +1457,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1438,7 +1467,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ang l</t>
@@ -1449,7 +1477,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1459,7 +1487,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa (tr</t>
@@ -1470,7 +1497,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1480,7 +1507,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ớ</t>
     </r>
@@ -1490,7 +1517,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c khi thay)</t>
@@ -1503,7 +1529,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mô t</t>
@@ -1514,7 +1539,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1524,7 +1549,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> v</t>
@@ -1535,7 +1559,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ậ</t>
     </r>
@@ -1545,7 +1569,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t li</t>
@@ -1556,7 +1579,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1566,7 +1589,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u (tr</t>
@@ -1577,7 +1599,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1587,7 +1609,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ớ</t>
     </r>
@@ -1597,7 +1619,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c khi thay)</t>
@@ -1610,7 +1631,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã li</t>
@@ -1621,7 +1641,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1631,7 +1651,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u k</t>
@@ -1642,7 +1661,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -1652,7 +1671,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -1663,7 +1681,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1673,7 +1691,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch  (sau khi thay)</t>
@@ -1686,7 +1703,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mô t</t>
@@ -1697,7 +1713,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -1707,7 +1723,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> v</t>
@@ -1718,7 +1733,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ậ</t>
     </r>
@@ -1728,7 +1743,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t li</t>
@@ -1739,7 +1753,7 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1749,7 +1763,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u (sau khi thay)</t>
@@ -1778,7 +1791,6 @@
       <rPr>
         <sz val="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>{.</t>
@@ -1788,7 +1800,6 @@
         <b/>
         <sz val="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>beforeMaterialDesc</t>
@@ -1797,7 +1808,6 @@
       <rPr>
         <sz val="9"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>}</t>
@@ -1828,214 +1838,67 @@
     <t>{titleDate}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
+    <t>成型 Thành hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜班 Ca đêm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">早班 Ca sáng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">中班 Ca trưa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">合计 Tổng </t>
+  </si>
+  <si>
+    <t>{cxNightQty}</t>
+  </si>
+  <si>
+    <t>{cxMorningQty}</t>
+  </si>
+  <si>
+    <t>{cxMiddleQty}</t>
+  </si>
+  <si>
+    <t>{cxTotalQty}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试制 Thử nghiệm </t>
+  </si>
+  <si>
+    <t>{cxSetupInfo}</t>
+  </si>
+  <si>
+    <t>量试 Thử nghiệm số lượng</t>
+  </si>
+  <si>
+    <t>{cxTrialInfo}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规格切换
+Thay quy cách </t>
+  </si>
+  <si>
+    <t>{cxSpecSwitch}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>成型</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+        <charset val="0"/>
+      </rPr>
+      <t>小胶种</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Thành hình</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>夜班</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ca đêm </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>早班</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ca sáng </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中班</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ca trưa </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>合计</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Tổng </t>
-    </r>
-  </si>
-  <si>
-    <t>{cxNightQty}</t>
-  </si>
-  <si>
-    <t>{cxMorningQty}</t>
-  </si>
-  <si>
-    <t>{cxMiddleQty}</t>
-  </si>
-  <si>
-    <t>{cxTotalQty}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>试制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Thử nghiệm </t>
-    </r>
-  </si>
-  <si>
-    <t>{cxSetupInfo}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>量试</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Thử nghiệm số lượng</t>
-    </r>
-  </si>
-  <si>
-    <t>{cxTrialInfo}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>规格切换</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Thay quy cách </t>
-    </r>
-  </si>
-  <si>
-    <t>{cxSpecSwitch}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小胶种</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="0"/>
       </rPr>
       <t xml:space="preserve"> 
 Loại su nhỏ</t>
@@ -2048,27 +1911,7 @@
     <t>{.specPattern}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硫化</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Lưu hóa</t>
-    </r>
+    <t>硫化 Lưu hóa</t>
   </si>
   <si>
     <t>{lhNightQty}</t>
@@ -2083,26 +1926,8 @@
     <t>{lhTotalQty}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硫化开动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>硫化开动
 Số lượng máy lưu hóa</t>
-    </r>
   </si>
   <si>
     <t>{lhNightMachines}</t>
@@ -2117,25 +1942,7 @@
     <t>{lhTotalMachines}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模具交替</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Thay khuôn </t>
-    </r>
+    <t xml:space="preserve">模具交替 Thay khuôn </t>
   </si>
   <si>
     <t>{mouldCleanDate}</t>
@@ -2144,49 +1951,13 @@
     <t>{mouldChangeInfo}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模具清洗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Vệ sinh khuôn </t>
-    </r>
+    <t xml:space="preserve">模具清洗 Vệ sinh khuôn </t>
   </si>
   <si>
     <t>{mouldCleanInfo}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>备注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ghi chú</t>
-    </r>
+    <t>备注 Ghi chú</t>
   </si>
   <si>
     <t>成型</t>
@@ -2199,73 +1970,17 @@
   </si>
   <si>
     <t>{lhRemark}</t>
-  </si>
-  <si>
-    <t>{.class8LeftRightMould}</t>
-    <phoneticPr fontId="38" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.class6MouldMethod}</t>
-    <phoneticPr fontId="38" type="noConversion"/>
-  </si>
-  <si>
-    <t>class1LeftRightMould</t>
-  </si>
-  <si>
-    <t>class1MouldMethod</t>
-  </si>
-  <si>
-    <t>class2LeftRightMould</t>
-  </si>
-  <si>
-    <t>class2MouldMethod</t>
-  </si>
-  <si>
-    <t>class3LeftRightMould</t>
-  </si>
-  <si>
-    <t>class3MouldMethod</t>
-  </si>
-  <si>
-    <t>class4LeftRightMould</t>
-  </si>
-  <si>
-    <t>class4MouldMethod</t>
-  </si>
-  <si>
-    <t>class5LeftRightMould</t>
-  </si>
-  <si>
-    <t>class5MouldMethod</t>
-  </si>
-  <si>
-    <t>class6LeftRightMould</t>
-  </si>
-  <si>
-    <t>class6MouldMethod</t>
-  </si>
-  <si>
-    <t>class7LeftRightMould</t>
-  </si>
-  <si>
-    <t>class7MouldMethod</t>
-  </si>
-  <si>
-    <t>class8LeftRightMould</t>
-  </si>
-  <si>
-    <t>class8MouldMethod</t>
-  </si>
-  <si>
-    <t>totalDailyPlanQty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="10">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -2273,71 +1988,72 @@
     <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2345,7 +2061,6 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2353,14 +2068,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2368,61 +2081,209 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2430,118 +2291,101 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Cambria"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2572,8 +2416,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -2913,443 +2943,689 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="29" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="42" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="7" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="8" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="9" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="12" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="12" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="13">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+  <cellStyles count="61">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma 2" xfId="49"/>
+    <cellStyle name="Excel Built-in Normal" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="51"/>
+    <cellStyle name="Normal 12 3" xfId="52"/>
+    <cellStyle name="Normal 2 2" xfId="53"/>
+    <cellStyle name="Normal 20 3" xfId="54"/>
+    <cellStyle name="Normal 91" xfId="55"/>
+    <cellStyle name="Percent 2" xfId="56"/>
+    <cellStyle name="常规 2" xfId="57"/>
+    <cellStyle name="常规 2 5" xfId="58"/>
+    <cellStyle name="千位分隔 3" xfId="59"/>
+    <cellStyle name="千位分隔 3 3" xfId="60"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3366,15 +3642,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3390,19 +3663,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="572799" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007FBD0800}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="572799" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3417,7 +3684,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="66675"/>
-          <a:ext cx="1998345" cy="683895"/>
+          <a:ext cx="2000250" cy="683895"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3453,7 +3720,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3469,19 +3736,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3496,7 +3757,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22860" y="15240"/>
-          <a:ext cx="1485900" cy="527685"/>
+          <a:ext cx="1482090" cy="527685"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3812,1241 +4073,1242 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CF7"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="11.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="32" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5" style="32" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.75" style="32" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.125" style="32" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="33" customWidth="1"/>
-    <col min="6" max="6" width="11.875" style="34" customWidth="1"/>
-    <col min="7" max="7" width="33.25" style="33" customWidth="1"/>
-    <col min="8" max="8" width="36.875" style="33" customWidth="1"/>
-    <col min="9" max="9" width="15.75" style="33" customWidth="1"/>
-    <col min="10" max="11" width="6.375" style="34" customWidth="1"/>
-    <col min="12" max="12" width="6.125" style="33" customWidth="1"/>
-    <col min="13" max="13" width="6.375" style="33" customWidth="1"/>
-    <col min="14" max="14" width="3.75" style="33" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="33" customWidth="1"/>
-    <col min="16" max="16" width="3.75" style="33" customWidth="1"/>
-    <col min="17" max="17" width="4.625" style="33" customWidth="1"/>
-    <col min="18" max="18" width="5.375" style="33" customWidth="1"/>
-    <col min="19" max="22" width="3.75" style="33" customWidth="1"/>
-    <col min="23" max="23" width="6.75" style="33" customWidth="1"/>
-    <col min="24" max="24" width="3.75" style="33" customWidth="1"/>
-    <col min="25" max="25" width="4.625" style="33" customWidth="1"/>
-    <col min="26" max="26" width="5.375" style="33" customWidth="1"/>
-    <col min="27" max="30" width="3.75" style="33" customWidth="1"/>
-    <col min="31" max="31" width="6.75" style="33" customWidth="1"/>
-    <col min="32" max="32" width="3.75" style="33" customWidth="1"/>
-    <col min="33" max="33" width="4.625" style="33" customWidth="1"/>
-    <col min="34" max="34" width="5.375" style="33" customWidth="1"/>
-    <col min="35" max="38" width="3.75" style="33" customWidth="1"/>
-    <col min="39" max="39" width="6.75" style="33" customWidth="1"/>
-    <col min="40" max="40" width="3.75" style="33" customWidth="1"/>
-    <col min="41" max="41" width="4.625" style="33" customWidth="1"/>
-    <col min="42" max="42" width="5.375" style="33" customWidth="1"/>
-    <col min="43" max="46" width="3.75" style="33" customWidth="1"/>
-    <col min="47" max="47" width="6.75" style="33" customWidth="1"/>
-    <col min="48" max="48" width="3.75" style="33" customWidth="1"/>
-    <col min="49" max="49" width="4.625" style="33" customWidth="1"/>
-    <col min="50" max="50" width="5.375" style="33" customWidth="1"/>
-    <col min="51" max="54" width="3.75" style="33" customWidth="1"/>
-    <col min="55" max="55" width="6.75" style="33" customWidth="1"/>
-    <col min="56" max="56" width="3.75" style="33" customWidth="1"/>
-    <col min="57" max="57" width="4.625" style="33" customWidth="1"/>
-    <col min="58" max="58" width="5.375" style="33" customWidth="1"/>
-    <col min="59" max="62" width="3.75" style="33" customWidth="1"/>
-    <col min="63" max="63" width="6.75" style="33" customWidth="1"/>
-    <col min="64" max="64" width="3.75" style="33" customWidth="1"/>
-    <col min="65" max="65" width="4.625" style="33" customWidth="1"/>
-    <col min="66" max="66" width="5.375" style="33" customWidth="1"/>
-    <col min="67" max="70" width="3.75" style="33" customWidth="1"/>
-    <col min="71" max="71" width="6.75" style="33" customWidth="1"/>
-    <col min="72" max="72" width="3.75" style="33" customWidth="1"/>
-    <col min="73" max="73" width="4.625" style="33" customWidth="1"/>
-    <col min="74" max="74" width="5.375" style="33" customWidth="1"/>
-    <col min="75" max="77" width="3.75" style="33" customWidth="1"/>
-    <col min="78" max="78" width="6.625" style="33" customWidth="1"/>
-    <col min="79" max="79" width="4.625" style="33" customWidth="1"/>
-    <col min="80" max="80" width="9.375" style="35" customWidth="1"/>
-    <col min="81" max="81" width="34.25" style="36" customWidth="1"/>
-    <col min="82" max="82" width="6.75" style="34" customWidth="1"/>
-    <col min="83" max="84" width="8.375" style="34" customWidth="1"/>
-    <col min="85" max="92" width="9.875" style="32" customWidth="1"/>
-    <col min="93" max="16384" width="9.125" style="32"/>
+    <col min="1" max="1" width="5.375" style="54" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="54" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.75" style="54" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.125" style="54" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="55" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="56" customWidth="1"/>
+    <col min="7" max="7" width="33.25" style="55" customWidth="1"/>
+    <col min="8" max="8" width="36.875" style="55" customWidth="1"/>
+    <col min="9" max="9" width="15.75" style="55" customWidth="1"/>
+    <col min="10" max="11" width="6.375" style="56" customWidth="1"/>
+    <col min="12" max="12" width="6.125" style="55" customWidth="1"/>
+    <col min="13" max="13" width="6.375" style="55" customWidth="1"/>
+    <col min="14" max="14" width="3.75" style="55" customWidth="1"/>
+    <col min="15" max="15" width="6.75" style="55" customWidth="1"/>
+    <col min="16" max="16" width="3.75" style="55" customWidth="1"/>
+    <col min="17" max="17" width="4.625" style="55" customWidth="1"/>
+    <col min="18" max="18" width="5.375" style="55" customWidth="1"/>
+    <col min="19" max="22" width="3.75" style="55" customWidth="1"/>
+    <col min="23" max="23" width="6.75" style="55" customWidth="1"/>
+    <col min="24" max="24" width="3.75" style="55" customWidth="1"/>
+    <col min="25" max="25" width="4.625" style="55" customWidth="1"/>
+    <col min="26" max="26" width="5.375" style="55" customWidth="1"/>
+    <col min="27" max="30" width="3.75" style="55" customWidth="1"/>
+    <col min="31" max="31" width="6.75" style="55" customWidth="1"/>
+    <col min="32" max="32" width="3.75" style="55" customWidth="1"/>
+    <col min="33" max="33" width="4.625" style="55" customWidth="1"/>
+    <col min="34" max="34" width="5.375" style="55" customWidth="1"/>
+    <col min="35" max="38" width="3.75" style="55" customWidth="1"/>
+    <col min="39" max="39" width="6.75" style="55" customWidth="1"/>
+    <col min="40" max="40" width="3.75" style="55" customWidth="1"/>
+    <col min="41" max="41" width="4.625" style="55" customWidth="1"/>
+    <col min="42" max="42" width="5.375" style="55" customWidth="1"/>
+    <col min="43" max="46" width="3.75" style="55" customWidth="1"/>
+    <col min="47" max="47" width="6.75" style="55" customWidth="1"/>
+    <col min="48" max="48" width="3.75" style="55" customWidth="1"/>
+    <col min="49" max="49" width="4.625" style="55" customWidth="1"/>
+    <col min="50" max="50" width="5.375" style="55" customWidth="1"/>
+    <col min="51" max="54" width="3.75" style="55" customWidth="1"/>
+    <col min="55" max="55" width="6.75" style="55" customWidth="1"/>
+    <col min="56" max="56" width="3.75" style="55" customWidth="1"/>
+    <col min="57" max="57" width="4.625" style="55" customWidth="1"/>
+    <col min="58" max="58" width="5.375" style="55" customWidth="1"/>
+    <col min="59" max="62" width="3.75" style="55" customWidth="1"/>
+    <col min="63" max="63" width="6.75" style="55" customWidth="1"/>
+    <col min="64" max="64" width="3.75" style="55" customWidth="1"/>
+    <col min="65" max="65" width="4.625" style="55" customWidth="1"/>
+    <col min="66" max="66" width="5.375" style="55" customWidth="1"/>
+    <col min="67" max="70" width="3.75" style="55" customWidth="1"/>
+    <col min="71" max="71" width="6.75" style="55" customWidth="1"/>
+    <col min="72" max="72" width="3.75" style="55" customWidth="1"/>
+    <col min="73" max="73" width="4.625" style="55" customWidth="1"/>
+    <col min="74" max="74" width="5.375" style="55" customWidth="1"/>
+    <col min="75" max="77" width="3.75" style="55" customWidth="1"/>
+    <col min="78" max="78" width="6.625" style="55" customWidth="1"/>
+    <col min="79" max="79" width="4.625" style="55" customWidth="1"/>
+    <col min="80" max="80" width="9.375" style="57" customWidth="1"/>
+    <col min="81" max="81" width="34.25" style="58" customWidth="1"/>
+    <col min="82" max="82" width="6.75" style="56" customWidth="1"/>
+    <col min="83" max="84" width="8.375" style="56" customWidth="1"/>
+    <col min="85" max="92" width="9.875" style="54" customWidth="1"/>
+    <col min="93" max="16384" width="9.125" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E1" s="33" t="s">
+    <row r="1" ht="47.25" hidden="1" customHeight="1" spans="1:84">
+      <c r="E1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="R1" s="33" t="s">
+      <c r="Q1" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="T1" s="33" t="s">
+      <c r="S1" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="33" t="s">
+      <c r="T1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="33" t="s">
+      <c r="U1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="33" t="s">
+      <c r="V1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="33" t="s">
+      <c r="W1" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="Z1" s="33" t="s">
+      <c r="X1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB1" s="33" t="s">
+      <c r="Y1" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="33" t="s">
+      <c r="Z1" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="33" t="s">
+      <c r="AA1" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="33" t="s">
+      <c r="AB1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="33" t="s">
+      <c r="AC1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="AH1" s="33" t="s">
+      <c r="AD1" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="AI1" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="AJ1" s="33" t="s">
+      <c r="AE1" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="33" t="s">
+      <c r="AF1" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="33" t="s">
+      <c r="AG1" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="33" t="s">
+      <c r="AH1" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="33" t="s">
+      <c r="AI1" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="AP1" s="33" t="s">
+      <c r="AJ1" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="AR1" s="33" t="s">
+      <c r="AK1" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="AS1" s="33" t="s">
+      <c r="AL1" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="AT1" s="33" t="s">
+      <c r="AM1" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="AU1" s="33" t="s">
+      <c r="AN1" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="AV1" s="33" t="s">
+      <c r="AO1" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="AW1" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="AX1" s="33" t="s">
+      <c r="AP1" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="AY1" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="AZ1" s="33" t="s">
+      <c r="AQ1" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="BA1" s="33" t="s">
+      <c r="AR1" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="BB1" s="33" t="s">
+      <c r="AS1" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="BC1" s="33" t="s">
+      <c r="AT1" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="BD1" s="33" t="s">
+      <c r="AU1" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BE1" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="BF1" s="33" t="s">
+      <c r="AV1" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="BH1" s="33" t="s">
+      <c r="AW1" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="BI1" s="33" t="s">
+      <c r="AX1" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="BJ1" s="33" t="s">
+      <c r="AY1" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="BK1" s="33" t="s">
+      <c r="AZ1" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="BL1" s="33" t="s">
+      <c r="BA1" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="BM1" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="BN1" s="33" t="s">
+      <c r="BB1" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="BO1" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="BP1" s="33" t="s">
+      <c r="BC1" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="BQ1" s="33" t="s">
+      <c r="BD1" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="BR1" s="33" t="s">
+      <c r="BE1" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="BS1" s="33" t="s">
+      <c r="BF1" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="BT1" s="33" t="s">
+      <c r="BG1" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="BU1" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="BV1" s="33" t="s">
+      <c r="BH1" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="BW1" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="BX1" s="33" t="s">
+      <c r="BI1" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="BY1" s="33" t="s">
+      <c r="BJ1" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="CC1" s="36" t="s">
+      <c r="BK1" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="CD1" s="34" t="s">
+      <c r="BL1" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="CE1" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="CF1" s="34" t="s">
+      <c r="BM1" s="55" t="s">
         <v>60</v>
       </c>
+      <c r="BN1" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO1" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="BP1" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="BQ1" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="BR1" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT1" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU1" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV1" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW1" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX1" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="CC1" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="CD1" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="CE1" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="CF1" s="56" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" spans="1:84" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="e">
+    <row r="2" ht="29.25" customHeight="1" spans="1:84">
+      <c r="A2" s="54" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="32"/>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="34"/>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="32"/>
-      <c r="BE2" s="32"/>
-      <c r="BF2" s="32"/>
-      <c r="BG2" s="32"/>
-      <c r="BH2" s="32"/>
-      <c r="BI2" s="32"/>
-      <c r="BJ2" s="32"/>
-      <c r="BK2" s="32"/>
-      <c r="BL2" s="32"/>
-      <c r="BM2" s="32"/>
-      <c r="BN2" s="32"/>
-      <c r="BO2" s="32"/>
-      <c r="BP2" s="32"/>
-      <c r="BQ2" s="32"/>
-      <c r="BR2" s="32"/>
-      <c r="BS2" s="32"/>
-      <c r="BT2" s="32"/>
-      <c r="BU2" s="32"/>
-      <c r="BV2" s="32"/>
-      <c r="BW2" s="32"/>
-      <c r="BX2" s="32"/>
-      <c r="BY2" s="32"/>
-      <c r="BZ2" s="32"/>
-      <c r="CA2" s="32"/>
-      <c r="CB2" s="32"/>
-      <c r="CC2" s="32"/>
-      <c r="CD2" s="32"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="59"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="54"/>
+      <c r="AI2" s="54"/>
+      <c r="AJ2" s="54"/>
+      <c r="AK2" s="54"/>
+      <c r="AL2" s="54"/>
+      <c r="AM2" s="54"/>
+      <c r="AN2" s="54"/>
+      <c r="AO2" s="54"/>
+      <c r="AP2" s="54"/>
+      <c r="AQ2" s="54"/>
+      <c r="AR2" s="54"/>
+      <c r="AS2" s="54"/>
+      <c r="AT2" s="54"/>
+      <c r="AU2" s="54"/>
+      <c r="AV2" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW2" s="54"/>
+      <c r="AX2" s="54"/>
+      <c r="AY2" s="54"/>
+      <c r="AZ2" s="54"/>
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="54"/>
+      <c r="BC2" s="54"/>
+      <c r="BD2" s="54"/>
+      <c r="BE2" s="54"/>
+      <c r="BF2" s="54"/>
+      <c r="BG2" s="54"/>
+      <c r="BH2" s="54"/>
+      <c r="BI2" s="54"/>
+      <c r="BJ2" s="54"/>
+      <c r="BK2" s="54"/>
+      <c r="BL2" s="54"/>
+      <c r="BM2" s="54"/>
+      <c r="BN2" s="54"/>
+      <c r="BO2" s="54"/>
+      <c r="BP2" s="54"/>
+      <c r="BQ2" s="54"/>
+      <c r="BR2" s="54"/>
+      <c r="BS2" s="54"/>
+      <c r="BT2" s="54"/>
+      <c r="BU2" s="54"/>
+      <c r="BV2" s="54"/>
+      <c r="BW2" s="54"/>
+      <c r="BX2" s="54"/>
+      <c r="BY2" s="54"/>
+      <c r="BZ2" s="54"/>
+      <c r="CA2" s="54"/>
+      <c r="CB2" s="54"/>
+      <c r="CC2" s="54"/>
+      <c r="CD2" s="54"/>
     </row>
-    <row r="3" spans="1:84" s="30" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="M3" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40">
+    <row r="3" s="52" customFormat="1" ht="17.85" customHeight="1" spans="1:84">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="M3" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62">
         <f>SUM(O7:O108138)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="41">
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="63">
         <f>SUM(W7:W108138)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41" t="e">
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="64"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63" t="e">
         <f>SUM(CB7:CB108138)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="42"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41">
+      <c r="AF3" s="64"/>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
+      <c r="AI3" s="63"/>
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="64"/>
+      <c r="AL3" s="63"/>
+      <c r="AM3" s="63">
         <f>SUM(AM7:AM108138)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="42"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="41"/>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="42">
+      <c r="AN3" s="63"/>
+      <c r="AO3" s="63"/>
+      <c r="AP3" s="64"/>
+      <c r="AQ3" s="63"/>
+      <c r="AR3" s="63"/>
+      <c r="AS3" s="63"/>
+      <c r="AT3" s="63"/>
+      <c r="AU3" s="64">
         <f>SUM(AU7:AU108138)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="41">
+      <c r="AV3" s="63"/>
+      <c r="AW3" s="63"/>
+      <c r="AX3" s="63"/>
+      <c r="AY3" s="63"/>
+      <c r="AZ3" s="64"/>
+      <c r="BA3" s="63"/>
+      <c r="BB3" s="63"/>
+      <c r="BC3" s="63">
         <f>SUM(BC7:BC108138)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="42"/>
-      <c r="BF3" s="40"/>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="40"/>
-      <c r="BJ3" s="43"/>
-      <c r="BK3" s="41">
+      <c r="BD3" s="63"/>
+      <c r="BE3" s="64"/>
+      <c r="BF3" s="62"/>
+      <c r="BG3" s="62"/>
+      <c r="BH3" s="62"/>
+      <c r="BJ3" s="65"/>
+      <c r="BK3" s="63">
         <f>SUM(BK7:BK108138)</f>
         <v>0</v>
       </c>
-      <c r="BS3" s="41">
+      <c r="BS3" s="63">
         <f>SUM(BS7:BS108138)</f>
         <v>0</v>
       </c>
-      <c r="BZ3" s="41">
+      <c r="BZ3" s="63">
         <f>BC3+BK3+BS3</f>
         <v>0</v>
       </c>
-      <c r="CB3" s="41" t="e">
+      <c r="CB3" s="63" t="e">
         <f>O3+W3+AE3+AM3+AU3+BC3+BK3+BS3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="44"/>
+      <c r="CD3" s="66"/>
     </row>
-    <row r="4" spans="1:84" s="30" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="M4" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="42"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="41"/>
-      <c r="AO4" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP4" s="41"/>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="41"/>
-      <c r="AS4" s="41"/>
-      <c r="AT4" s="42"/>
-      <c r="AU4" s="41"/>
-      <c r="AV4" s="41"/>
-      <c r="AW4" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX4" s="41"/>
-      <c r="AY4" s="42"/>
-      <c r="AZ4" s="41"/>
-      <c r="BA4" s="41"/>
-      <c r="BB4" s="41"/>
-      <c r="BC4" s="41"/>
-      <c r="BD4" s="42"/>
-      <c r="BL4" s="41"/>
-      <c r="BM4" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="BN4" s="41"/>
-      <c r="BO4" s="41"/>
-      <c r="BP4" s="42"/>
-      <c r="BQ4" s="41"/>
-      <c r="BR4" s="41"/>
-      <c r="BS4" s="41"/>
-      <c r="BT4" s="41"/>
-      <c r="BU4" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="BW4" s="40"/>
-      <c r="BZ4" s="41"/>
-      <c r="CB4" s="41"/>
-      <c r="CD4" s="45"/>
+    <row r="4" s="52" customFormat="1" ht="17.85" customHeight="1" spans="1:84">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="M4" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z4" s="63"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AO4" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP4" s="63"/>
+      <c r="AQ4" s="63"/>
+      <c r="AR4" s="63"/>
+      <c r="AS4" s="63"/>
+      <c r="AT4" s="64"/>
+      <c r="AU4" s="63"/>
+      <c r="AV4" s="63"/>
+      <c r="AW4" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX4" s="63"/>
+      <c r="AY4" s="64"/>
+      <c r="AZ4" s="63"/>
+      <c r="BA4" s="63"/>
+      <c r="BB4" s="63"/>
+      <c r="BC4" s="63"/>
+      <c r="BD4" s="64"/>
+      <c r="BL4" s="63"/>
+      <c r="BM4" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN4" s="63"/>
+      <c r="BO4" s="63"/>
+      <c r="BP4" s="64"/>
+      <c r="BQ4" s="63"/>
+      <c r="BR4" s="63"/>
+      <c r="BS4" s="63"/>
+      <c r="BT4" s="63"/>
+      <c r="BU4" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="BW4" s="62"/>
+      <c r="BZ4" s="63"/>
+      <c r="CB4" s="63"/>
+      <c r="CD4" s="67"/>
     </row>
-    <row r="5" spans="1:84" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="46">
+    <row r="5" ht="36" customHeight="1" spans="1:84">
+      <c r="A5" s="68">
         <f>BC3+BK3+BS3</f>
         <v>0</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="L5" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="86" t="s">
-        <v>81</v>
-      </c>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="84"/>
-      <c r="Z5" s="84"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="84"/>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="88" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE5" s="89"/>
-      <c r="AF5" s="89"/>
-      <c r="AG5" s="89"/>
-      <c r="AH5" s="89"/>
-      <c r="AI5" s="89"/>
-      <c r="AJ5" s="89"/>
-      <c r="AK5" s="90"/>
-      <c r="AL5" s="91" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM5" s="89"/>
-      <c r="AN5" s="89"/>
-      <c r="AO5" s="89"/>
-      <c r="AP5" s="89"/>
-      <c r="AQ5" s="89"/>
-      <c r="AR5" s="89"/>
-      <c r="AS5" s="90"/>
-      <c r="AT5" s="91" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU5" s="89"/>
-      <c r="AV5" s="89"/>
-      <c r="AW5" s="89"/>
-      <c r="AX5" s="89"/>
-      <c r="AY5" s="89"/>
-      <c r="AZ5" s="89"/>
-      <c r="BA5" s="92"/>
-      <c r="BB5" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC5" s="77"/>
-      <c r="BD5" s="77"/>
-      <c r="BE5" s="77"/>
-      <c r="BF5" s="77"/>
-      <c r="BG5" s="77"/>
-      <c r="BH5" s="77"/>
-      <c r="BI5" s="78"/>
-      <c r="BJ5" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="BK5" s="77"/>
-      <c r="BL5" s="77"/>
-      <c r="BM5" s="77"/>
-      <c r="BN5" s="77"/>
-      <c r="BO5" s="77"/>
-      <c r="BP5" s="77"/>
-      <c r="BQ5" s="78"/>
-      <c r="BR5" s="79" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="BS5" s="77"/>
-      <c r="BT5" s="77"/>
-      <c r="BU5" s="77"/>
-      <c r="BV5" s="77"/>
-      <c r="BW5" s="77"/>
-      <c r="BX5" s="77"/>
-      <c r="BY5" s="80"/>
-      <c r="BZ5" s="81" t="s">
+      <c r="F5" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="CA5" s="82"/>
-      <c r="CB5" s="48" t="s">
+      <c r="G5" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="CC5" s="48" t="s">
+      <c r="H5" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="CD5" s="49" t="s">
+      <c r="I5" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="CE5" s="48" t="s">
+      <c r="J5" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="CF5" s="48" t="s">
+      <c r="K5" s="70" t="s">
         <v>93</v>
       </c>
+      <c r="L5" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="115" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="116" t="s">
+        <v>97</v>
+      </c>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="73"/>
+      <c r="Z5" s="73"/>
+      <c r="AA5" s="73"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="76"/>
+      <c r="AD5" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE5" s="78"/>
+      <c r="AF5" s="78"/>
+      <c r="AG5" s="78"/>
+      <c r="AH5" s="78"/>
+      <c r="AI5" s="78"/>
+      <c r="AJ5" s="78"/>
+      <c r="AK5" s="79"/>
+      <c r="AL5" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM5" s="78"/>
+      <c r="AN5" s="78"/>
+      <c r="AO5" s="78"/>
+      <c r="AP5" s="78"/>
+      <c r="AQ5" s="78"/>
+      <c r="AR5" s="78"/>
+      <c r="AS5" s="79"/>
+      <c r="AT5" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="78"/>
+      <c r="AV5" s="78"/>
+      <c r="AW5" s="78"/>
+      <c r="AX5" s="78"/>
+      <c r="AY5" s="78"/>
+      <c r="AZ5" s="78"/>
+      <c r="BA5" s="81"/>
+      <c r="BB5" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC5" s="83"/>
+      <c r="BD5" s="83"/>
+      <c r="BE5" s="83"/>
+      <c r="BF5" s="83"/>
+      <c r="BG5" s="83"/>
+      <c r="BH5" s="83"/>
+      <c r="BI5" s="84"/>
+      <c r="BJ5" s="85" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK5" s="83"/>
+      <c r="BL5" s="83"/>
+      <c r="BM5" s="83"/>
+      <c r="BN5" s="83"/>
+      <c r="BO5" s="83"/>
+      <c r="BP5" s="83"/>
+      <c r="BQ5" s="84"/>
+      <c r="BR5" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS5" s="83"/>
+      <c r="BT5" s="83"/>
+      <c r="BU5" s="83"/>
+      <c r="BV5" s="83"/>
+      <c r="BW5" s="83"/>
+      <c r="BX5" s="83"/>
+      <c r="BY5" s="86"/>
+      <c r="BZ5" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="CA5" s="88"/>
+      <c r="CB5" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="CC5" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="CD5" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="CE5" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="CF5" s="70" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="6" spans="1:84" s="31" customFormat="1" ht="72" x14ac:dyDescent="0.15">
-      <c r="A6" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="K6" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="N6" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="O6" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="P6" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q6" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="R6" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="S6" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="T6" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="U6" s="55" t="s">
+    <row r="6" s="53" customFormat="1" ht="69" spans="1:84">
+      <c r="A6" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="V6" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="W6" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="X6" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y6" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z6" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA6" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB6" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC6" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD6" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE6" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF6" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG6" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH6" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI6" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ6" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="AK6" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL6" s="58" t="s">
+      <c r="B6" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="AM6" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="AN6" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="AO6" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="AP6" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="AQ6" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR6" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="AS6" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT6" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="AU6" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="AV6" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="AW6" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="AX6" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY6" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ6" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="BA6" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="BB6" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="BC6" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="BD6" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="BE6" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="BF6" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="BG6" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="BH6" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="BI6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="BJ6" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK6" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="BL6" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="BM6" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="BN6" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO6" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="BP6" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="BQ6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="BR6" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS6" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="BT6" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="BU6" s="61" t="s">
-        <v>106</v>
-      </c>
-      <c r="BV6" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="BW6" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="BX6" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="BY6" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="BZ6" s="63" t="s">
+      <c r="C6" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="69"/>
+      <c r="E6" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="CA6" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="CB6" s="51" t="s">
+      <c r="F6" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="CC6" s="51" t="s">
+      <c r="G6" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="CD6" s="64"/>
-      <c r="CE6" s="51" t="s">
+      <c r="H6" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="CF6" s="51" t="s">
+      <c r="I6" s="90"/>
+      <c r="J6" s="90" t="s">
         <v>116</v>
       </c>
+      <c r="K6" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="91"/>
+      <c r="M6" s="92" t="s">
+        <v>118</v>
+      </c>
+      <c r="N6" s="93" t="s">
+        <v>119</v>
+      </c>
+      <c r="O6" s="94" t="s">
+        <v>120</v>
+      </c>
+      <c r="P6" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q6" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="R6" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="S6" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="T6" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="U6" s="94" t="s">
+        <v>126</v>
+      </c>
+      <c r="V6" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="W6" s="94" t="s">
+        <v>120</v>
+      </c>
+      <c r="X6" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y6" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z6" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA6" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB6" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC6" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD6" s="96" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE6" s="97" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF6" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG6" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH6" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI6" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ6" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK6" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL6" s="97" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM6" s="97" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN6" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="AO6" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP6" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ6" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR6" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS6" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT6" s="97" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU6" s="97" t="s">
+        <v>120</v>
+      </c>
+      <c r="AV6" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW6" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX6" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY6" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ6" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA6" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB6" s="99" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC6" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD6" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE6" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF6" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG6" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH6" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI6" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ6" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK6" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="BL6" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM6" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="BN6" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="BO6" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP6" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ6" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR6" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="BS6" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="BT6" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU6" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="BV6" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW6" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="BX6" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="BY6" s="101" t="s">
+        <v>126</v>
+      </c>
+      <c r="BZ6" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA6" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="CB6" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="CC6" s="90" t="s">
+        <v>130</v>
+      </c>
+      <c r="CD6" s="103"/>
+      <c r="CE6" s="90" t="s">
+        <v>131</v>
+      </c>
+      <c r="CF6" s="90" t="s">
+        <v>132</v>
+      </c>
     </row>
-    <row r="7" spans="1:84" ht="48" x14ac:dyDescent="0.15">
-      <c r="E7" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" s="65" t="e">
+    <row r="7" ht="46" spans="1:84">
+      <c r="E7" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="105" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="106" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="107" t="s">
+        <v>137</v>
+      </c>
+      <c r="J7" s="104" t="e">
         <f>CF7-CE7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="L7" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="M7" s="69" t="s">
-        <v>124</v>
-      </c>
-      <c r="N7" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="O7" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="P7" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q7" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="R7" s="71" t="s">
-        <v>129</v>
-      </c>
-      <c r="S7" s="71" t="s">
-        <v>130</v>
-      </c>
-      <c r="T7" s="71" t="s">
-        <v>131</v>
-      </c>
-      <c r="U7" s="71" t="s">
-        <v>132</v>
-      </c>
-      <c r="V7" s="71" t="s">
-        <v>133</v>
-      </c>
-      <c r="W7" s="71" t="s">
-        <v>134</v>
-      </c>
-      <c r="X7" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y7" s="71" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z7" s="71" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA7" s="71" t="s">
+      <c r="K7" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="AB7" s="71" t="s">
+      <c r="L7" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="AC7" s="71" t="s">
+      <c r="M7" s="108" t="s">
         <v>140</v>
       </c>
-      <c r="AD7" s="71" t="s">
+      <c r="N7" s="109" t="s">
         <v>141</v>
       </c>
-      <c r="AE7" s="71" t="s">
+      <c r="O7" s="110" t="s">
         <v>142</v>
       </c>
-      <c r="AF7" s="71" t="s">
+      <c r="P7" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="AG7" s="71" t="s">
+      <c r="Q7" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="AH7" s="71" t="s">
+      <c r="R7" s="110" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="71" t="s">
+      <c r="S7" s="110" t="s">
         <v>146</v>
       </c>
-      <c r="AJ7" s="71" t="s">
+      <c r="T7" s="110" t="s">
         <v>147</v>
       </c>
-      <c r="AK7" s="71" t="s">
+      <c r="U7" s="110" t="s">
         <v>148</v>
       </c>
-      <c r="AL7" s="71" t="s">
+      <c r="V7" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="AM7" s="71" t="s">
+      <c r="W7" s="110" t="s">
         <v>150</v>
       </c>
-      <c r="AN7" s="71" t="s">
+      <c r="X7" s="110" t="s">
         <v>151</v>
       </c>
-      <c r="AO7" s="71" t="s">
+      <c r="Y7" s="110" t="s">
         <v>152</v>
       </c>
-      <c r="AP7" s="71" t="s">
+      <c r="Z7" s="110" t="s">
         <v>153</v>
       </c>
-      <c r="AQ7" s="71" t="s">
+      <c r="AA7" s="110" t="s">
         <v>154</v>
       </c>
-      <c r="AR7" s="71" t="s">
+      <c r="AB7" s="110" t="s">
         <v>155</v>
       </c>
-      <c r="AS7" s="71" t="s">
+      <c r="AC7" s="110" t="s">
         <v>156</v>
       </c>
-      <c r="AT7" s="71" t="s">
+      <c r="AD7" s="110" t="s">
         <v>157</v>
       </c>
-      <c r="AU7" s="71" t="s">
+      <c r="AE7" s="110" t="s">
         <v>158</v>
       </c>
-      <c r="AV7" s="71" t="s">
+      <c r="AF7" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="AW7" s="71" t="s">
+      <c r="AG7" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="AX7" s="71" t="s">
+      <c r="AH7" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="AY7" s="71" t="s">
+      <c r="AI7" s="110" t="s">
         <v>162</v>
       </c>
-      <c r="AZ7" s="71" t="s">
+      <c r="AJ7" s="110" t="s">
         <v>163</v>
       </c>
-      <c r="BA7" s="71" t="s">
+      <c r="AK7" s="110" t="s">
         <v>164</v>
       </c>
-      <c r="BB7" s="71" t="s">
+      <c r="AL7" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="BC7" s="71" t="s">
+      <c r="AM7" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="BD7" s="71" t="s">
+      <c r="AN7" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="BE7" s="71" t="s">
+      <c r="AO7" s="110" t="s">
         <v>168</v>
       </c>
-      <c r="BF7" s="71" t="s">
+      <c r="AP7" s="110" t="s">
         <v>169</v>
       </c>
-      <c r="BG7" s="71" t="s">
-        <v>278</v>
-      </c>
-      <c r="BH7" s="71" t="s">
+      <c r="AQ7" s="110" t="s">
         <v>170</v>
       </c>
-      <c r="BI7" s="71" t="s">
+      <c r="AR7" s="110" t="s">
         <v>171</v>
       </c>
-      <c r="BJ7" s="71" t="s">
+      <c r="AS7" s="110" t="s">
         <v>172</v>
       </c>
-      <c r="BK7" s="71" t="s">
+      <c r="AT7" s="110" t="s">
         <v>173</v>
       </c>
-      <c r="BL7" s="71" t="s">
+      <c r="AU7" s="110" t="s">
         <v>174</v>
       </c>
-      <c r="BM7" s="71" t="s">
+      <c r="AV7" s="110" t="s">
         <v>175</v>
       </c>
-      <c r="BN7" s="71" t="s">
+      <c r="AW7" s="110" t="s">
         <v>176</v>
       </c>
-      <c r="BO7" s="71" t="s">
+      <c r="AX7" s="110" t="s">
         <v>177</v>
       </c>
-      <c r="BP7" s="71" t="s">
+      <c r="AY7" s="110" t="s">
         <v>178</v>
       </c>
-      <c r="BQ7" s="71" t="s">
+      <c r="AZ7" s="110" t="s">
         <v>179</v>
       </c>
-      <c r="BR7" s="71" t="s">
+      <c r="BA7" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="BS7" s="71" t="s">
+      <c r="BB7" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="BT7" s="71" t="s">
+      <c r="BC7" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="BU7" s="71" t="s">
-        <v>277</v>
-      </c>
-      <c r="BV7" s="71" t="s">
+      <c r="BD7" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="BW7" s="71" t="s">
+      <c r="BE7" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="BX7" s="71" t="s">
+      <c r="BF7" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="BY7" s="72" t="s">
+      <c r="BG7" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="BZ7" s="73" t="e">
+      <c r="BH7" s="110" t="s">
+        <v>187</v>
+      </c>
+      <c r="BI7" s="110" t="s">
+        <v>188</v>
+      </c>
+      <c r="BJ7" s="110" t="s">
+        <v>189</v>
+      </c>
+      <c r="BK7" s="110" t="s">
+        <v>190</v>
+      </c>
+      <c r="BL7" s="110" t="s">
+        <v>191</v>
+      </c>
+      <c r="BM7" s="110" t="s">
+        <v>192</v>
+      </c>
+      <c r="BN7" s="110" t="s">
+        <v>193</v>
+      </c>
+      <c r="BO7" s="110" t="s">
+        <v>194</v>
+      </c>
+      <c r="BP7" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="BQ7" s="110" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR7" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="BS7" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="BT7" s="110" t="s">
+        <v>199</v>
+      </c>
+      <c r="BU7" s="110" t="s">
+        <v>200</v>
+      </c>
+      <c r="BV7" s="110" t="s">
+        <v>201</v>
+      </c>
+      <c r="BW7" s="110" t="s">
+        <v>202</v>
+      </c>
+      <c r="BX7" s="110" t="s">
+        <v>203</v>
+      </c>
+      <c r="BY7" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="BZ7" s="112" t="e">
         <f>BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA7" s="74" t="e">
+      <c r="CA7" s="113" t="e">
         <f>BL7+BT7+BD7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CB7" s="74" t="e">
+      <c r="CB7" s="113" t="e">
         <f>O7+W7+AE7+AM7+AU7+BC7+BK7+BS7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CC7" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="CD7" s="75" t="s">
-        <v>188</v>
-      </c>
-      <c r="CE7" s="75" t="s">
-        <v>189</v>
-      </c>
-      <c r="CF7" s="66" t="s">
-        <v>190</v>
+      <c r="CC7" s="105" t="s">
+        <v>205</v>
+      </c>
+      <c r="CD7" s="114" t="s">
+        <v>206</v>
+      </c>
+      <c r="CE7" s="114" t="s">
+        <v>207</v>
+      </c>
+      <c r="CF7" s="105" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:CF7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:CF7" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="9">
-    <mergeCell ref="BB5:BI5"/>
-    <mergeCell ref="BJ5:BQ5"/>
-    <mergeCell ref="BR5:BY5"/>
-    <mergeCell ref="BZ5:CA5"/>
     <mergeCell ref="N5:U5"/>
     <mergeCell ref="V5:AC5"/>
     <mergeCell ref="AD5:AK5"/>
     <mergeCell ref="AL5:AS5"/>
     <mergeCell ref="AT5:BA5"/>
+    <mergeCell ref="BB5:BI5"/>
+    <mergeCell ref="BJ5:BQ5"/>
+    <mergeCell ref="BR5:BY5"/>
+    <mergeCell ref="BZ5:CA5"/>
   </mergeCells>
-  <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="CD5">
-    <cfRule type="duplicateValues" dxfId="5" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G4">
-    <cfRule type="duplicateValues" dxfId="4" priority="13" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="duplicateValues" dxfId="3" priority="24207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24207" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M6">
-    <cfRule type="duplicateValues" dxfId="2" priority="24210" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24210" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:I6">
-    <cfRule type="duplicateValues" dxfId="1" priority="24201" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24201" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K6">
     <cfRule type="duplicateValues" dxfId="0" priority="24204" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6 Z6 AH6 AP6 AX6 BF6 BN6 BV6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6 Z6 AH6 AP6 AX6 BF6 BN6 BV6">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="23" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="23" orientation="landscape"/>
+  <headerFooter/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="82" max="1048575" man="1"/>
   </colBreaks>
@@ -5056,488 +5318,475 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="8" customWidth="1"/>
-    <col min="3" max="4" width="11.375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="8" style="7" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="9" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="7" customWidth="1"/>
-    <col min="8" max="8" width="35.375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="7" customWidth="1"/>
-    <col min="10" max="10" width="35.375" style="10" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="10" customWidth="1"/>
-    <col min="12" max="14" width="6.875" style="9" customWidth="1"/>
-    <col min="15" max="15" width="23.25" style="9" customWidth="1"/>
-    <col min="16" max="16" width="21.125" style="9" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="9"/>
+    <col min="1" max="1" width="5.875" style="22" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="23" customWidth="1"/>
+    <col min="3" max="4" width="11.375" style="24" customWidth="1"/>
+    <col min="5" max="5" width="8" style="22" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="24" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="22" customWidth="1"/>
+    <col min="8" max="8" width="35.375" style="24" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="22" customWidth="1"/>
+    <col min="10" max="10" width="35.375" style="25" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="25" customWidth="1"/>
+    <col min="12" max="14" width="6.875" style="24" customWidth="1"/>
+    <col min="15" max="15" width="23.25" style="24" customWidth="1"/>
+    <col min="16" max="16" width="21.125" style="24" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>58</v>
+    <row r="1" ht="12.25" hidden="1" spans="1:16">
+      <c r="B1" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="93" t="s">
-        <v>200</v>
-      </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="95"/>
+    <row r="2" ht="33.75" customHeight="1" spans="1:16">
+      <c r="A2" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="28"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="99"/>
+    <row r="3" ht="15.75" customHeight="1" spans="1:16">
+      <c r="A3" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="32"/>
     </row>
-    <row r="4" spans="1:16" ht="25.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="12" t="s">
+    <row r="4" ht="25.15" customHeight="1" spans="1:16">
+      <c r="A4" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" ht="40" spans="1:16">
+      <c r="A5" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" s="40"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" ht="23.65" customHeight="1" spans="1:16">
+      <c r="A6" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>250</v>
+      </c>
+      <c r="J6" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="K6" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="M6" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="N6" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="P6" s="51" t="s">
         <v>205</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="O4" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="36" x14ac:dyDescent="0.15">
-      <c r="A5" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="23.65" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>187</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P6" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A5:P6" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
   </mergeCells>
-  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="B1:F14"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="18.125" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="21.75" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="29.1916666666667" customWidth="1"/>
+    <col min="3" max="6" width="26.6916666666667" customWidth="1"/>
+    <col min="7" max="32" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.15">
-      <c r="A1" s="110" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="1"/>
+    <row r="1" s="1" customFormat="1" ht="40.5" customHeight="1" spans="2:6">
+      <c r="B1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A2" s="104" t="s">
-        <v>239</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="1"/>
+    <row r="2" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B2" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>262</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A3" s="105"/>
-      <c r="B3" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F3" s="1"/>
+    <row r="3" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B3" s="5"/>
+      <c r="C3" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>266</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="111" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="1"/>
+    <row r="4" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B4" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B5" s="100" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="1"/>
+    <row r="5" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B5" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="100" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="1"/>
+    <row r="6" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B6" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="112" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="1"/>
+    <row r="7" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B7" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A8" s="104" t="s">
-        <v>257</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="1"/>
+    <row r="8" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B8" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>262</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A9" s="105"/>
-      <c r="B9" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" s="1"/>
+    <row r="9" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B9" s="5"/>
+      <c r="C9" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>280</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.15">
-      <c r="A10" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="1"/>
+    <row r="10" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B10" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="108" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="100" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="1"/>
+    <row r="11" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B11" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B12" s="109"/>
-      <c r="C12" s="100" t="s">
-        <v>271</v>
-      </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="1"/>
+    <row r="12" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B12" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A13" s="106" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" s="103" t="s">
-        <v>274</v>
-      </c>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="1"/>
+    <row r="13" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B13" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
-    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.15">
-      <c r="A14" s="107"/>
-      <c r="B14" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="103" t="s">
-        <v>276</v>
-      </c>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="1"/>
+    <row r="14" s="1" customFormat="1" ht="35.45" customHeight="1" spans="2:6">
+      <c r="B14" s="21"/>
+      <c r="C14" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
-  <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885B73C6-9DC7-4BB1-AF7C-B0F2670D7630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -18,7 +12,7 @@
     <sheet name="排产小结" sheetId="34" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$3:$P$4</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,14 +33,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="205">
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -58,7 +51,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -68,7 +61,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -79,7 +71,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -89,7 +81,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -100,7 +91,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -110,7 +101,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -121,7 +111,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -131,7 +121,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -142,7 +131,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -152,7 +141,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -163,7 +151,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -173,7 +161,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -184,7 +171,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -194,7 +181,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -205,7 +191,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -215,7 +201,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -226,7 +211,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -236,7 +221,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -248,7 +232,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -258,7 +241,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -267,7 +250,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -313,15 +295,14 @@
 </t>
   </si>
   <si>
-    <t>早班 Ca sáng 05/15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+    <t>早班 Ca sáng {shiftDate1}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -331,7 +312,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -340,19 +321,17 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>u 05/15</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u {shiftDate2}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -362,7 +341,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -371,22 +350,20 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>êm 05/16</t>
-    </r>
-  </si>
-  <si>
-    <t>早班 Ca sáng 05/16</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>êm {shiftDate3}</t>
+    </r>
+  </si>
+  <si>
+    <t>早班 Ca sáng {shiftDate4}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -396,7 +373,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -405,19 +382,17 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>u 05/16</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u {shiftDate5}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -427,7 +402,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -436,17 +411,42 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>êm 05/17</t>
-    </r>
-  </si>
-  <si>
-    <t>早班 Ca sáng 05/17</t>
-  </si>
-  <si>
-    <t>中班 Ca chiều 05/16</t>
+        <charset val="134"/>
+      </rPr>
+      <t>êm {shiftDate6}</t>
+    </r>
+  </si>
+  <si>
+    <t>早班 Ca sáng {shiftDate7}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中班 Ca chi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ề</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u {shiftDate8}</t>
+    </r>
   </si>
   <si>
     <t>合计
@@ -500,7 +500,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -510,7 +509,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="163"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -519,7 +518,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> l</t>
@@ -529,7 +527,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="163"/>
       </rPr>
       <t>ầ</t>
     </r>
@@ -538,7 +536,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n s</t>
@@ -548,7 +545,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="163"/>
       </rPr>
       <t>ử</t>
     </r>
@@ -557,7 +554,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> d</t>
@@ -567,7 +563,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="163"/>
       </rPr>
       <t>ụ</t>
     </r>
@@ -576,7 +572,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng phao L/R</t>
@@ -630,7 +625,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -640,7 +634,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -649,7 +643,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ng </t>
@@ -659,7 +652,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="163"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -668,7 +661,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy TH</t>
@@ -693,7 +685,7 @@
     <t>{.materialDesc}</t>
   </si>
   <si>
-    <t>{.mainMaterialCode}</t>
+    <t>{.embryoCode}</t>
   </si>
   <si>
     <t>{.mainMaterialDesc}</t>
@@ -702,6 +694,9 @@
     <t>{.structureName}</t>
   </si>
   <si>
+    <t>{.dailyPlanQty}</t>
+  </si>
+  <si>
     <t>{.embryoStock}</t>
   </si>
   <si>
@@ -903,6 +898,15 @@
     <t>{.class8Dot}</t>
   </si>
   <si>
+    <t>{.nightPlanQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.nightFinishQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.totalPlanQtyFormula}</t>
+  </si>
+  <si>
     <t>{.cxMachineCode}</t>
   </si>
   <si>
@@ -913,6 +917,9 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{title}</t>
   </si>
   <si>
     <t xml:space="preserve">序号
@@ -943,6 +950,12 @@
 </t>
   </si>
   <si>
+    <t>示方类型</t>
+  </si>
+  <si>
+    <t>按时间下机</t>
+  </si>
+  <si>
     <t>干冰清洗</t>
   </si>
   <si>
@@ -964,6 +977,285 @@
     <t xml:space="preserve">Ca thay </t>
   </si>
   <si>
+    <t>Trái phải của khuôn</t>
+  </si>
+  <si>
+    <t>Mã liệu kế hoạch  đang lưu hóa (trước khi thay)</t>
+  </si>
+  <si>
+    <t>Mô tả vật liệu (trước khi thay)</t>
+  </si>
+  <si>
+    <t>Mã liệu kế hoạch  (sau khi thay)</t>
+  </si>
+  <si>
+    <t>Mô tả vật liệu (sau khi thay)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Lo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ạ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i ph</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ươ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ng th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ứ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Xu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ố</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ng máy theo th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ờ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>i gian</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> sinh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <charset val="238"/>
+      </rPr>
+      <t>đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">á </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> sinh cát （VSC）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Ch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ỉ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> thay l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ắ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Mã s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ố</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> khuôn （MSK）</t>
+    </r>
+  </si>
+  <si>
     <t>{.seq}</t>
   </si>
   <si>
@@ -979,10 +1271,19 @@
     <t>{.beforeMaterialCode}</t>
   </si>
   <si>
+    <t>{.beforeMaterialDesc}</t>
+  </si>
+  <si>
     <t>{.afterMaterialCode}</t>
   </si>
   <si>
     <t>{.afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{.afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{.endType}</t>
   </si>
   <si>
     <t>{.isDryIceClean}</t>
@@ -1015,7 +1316,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca tr</t>
@@ -1025,7 +1325,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1035,7 +1334,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a </t>
@@ -1068,7 +1366,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>量试 Thử nghiệm số l</t>
@@ -1078,7 +1375,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1088,7 +1384,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng</t>
@@ -1121,7 +1416,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化计划
@@ -1133,7 +1427,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1143,7 +1437,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1155,7 +1448,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化开动
@@ -1166,7 +1458,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1176,7 +1467,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng máy l</t>
@@ -1186,7 +1476,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1196,7 +1485,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1231,308 +1519,17 @@
   </si>
   <si>
     <t>{lhRemark}</t>
-  </si>
-  <si>
-    <t>{.endType}</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.afterMaterialType}</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.beforeMaterialDesc}</t>
-  </si>
-  <si>
-    <r>
-      <t>Mã s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ố</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> khuôn （MSK）</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Ch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ỉ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> thay l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ắ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>c</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ệ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> sinh cát （VSC）</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ệ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> sinh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="3"/>
-        <charset val="238"/>
-      </rPr>
-      <t>đ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">á </t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Xu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ố</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ng máy theo th</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ờ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>i gian</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Lo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ạ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>i ph</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="3"/>
-        <charset val="238"/>
-      </rPr>
-      <t>ươ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ng th</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="163"/>
-      </rPr>
-      <t>ứ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>c</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mô tả vật liệu (sau khi thay)</t>
-  </si>
-  <si>
-    <t>Mã liệu kế hoạch  (sau khi thay)</t>
-  </si>
-  <si>
-    <t>Mô tả vật liệu (trước khi thay)</t>
-  </si>
-  <si>
-    <t>Mã liệu kế hoạch  đang lưu hóa (trước khi thay)</t>
-  </si>
-  <si>
-    <t>Trái phải của khuôn</t>
-  </si>
-  <si>
-    <t>按时间下机</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>示方类型</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>{title}</t>
-    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="11">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -1541,7 +1538,7 @@
     <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="45">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1550,21 +1547,18 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1572,49 +1566,213 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1622,122 +1780,68 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <family val="3"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1768,8 +1872,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1887,6 +2177,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1917,100 +2227,391 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="4"/>
       </top>
-      <bottom/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2037,7 +2638,7 @@
     <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2049,9 +2650,18 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2067,123 +2677,84 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="12" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="13" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="27" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="28" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="13">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+  <cellStyles count="61">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma 2" xfId="49"/>
+    <cellStyle name="Excel Built-in Normal" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="51"/>
+    <cellStyle name="Normal 12 3" xfId="52"/>
+    <cellStyle name="Normal 2 2" xfId="53"/>
+    <cellStyle name="Normal 20 3" xfId="54"/>
+    <cellStyle name="Normal 91" xfId="55"/>
+    <cellStyle name="Percent 2" xfId="56"/>
+    <cellStyle name="常规 2" xfId="57"/>
+    <cellStyle name="常规 2 5" xfId="58"/>
+    <cellStyle name="千位分隔 3" xfId="59"/>
+    <cellStyle name="千位分隔 3 3" xfId="60"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2202,15 +2773,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2226,19 +2794,55 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13970" y="33020"/>
+          <a:ext cx="1104900" cy="324485"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>628649</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>143193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2263,7 +2867,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2279,19 +2883,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D9737FD-07B7-459B-93C0-0A071F2BE1CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2305,8 +2903,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="55577" y="16896"/>
-          <a:ext cx="1446971" cy="186764"/>
+          <a:off x="51435" y="20320"/>
+          <a:ext cx="1134745" cy="386715"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2622,1325 +3220,1319 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC5"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.7" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="6.3984375" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" customWidth="1"/>
-    <col min="3" max="3" width="32.59765625" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
-    <col min="5" max="5" width="32.59765625" customWidth="1"/>
-    <col min="6" max="6" width="17.09765625" customWidth="1"/>
-    <col min="7" max="8" width="5.59765625" customWidth="1"/>
-    <col min="9" max="9" width="6.09765625" customWidth="1"/>
-    <col min="10" max="10" width="5.59765625" customWidth="1"/>
-    <col min="11" max="11" width="3.09765625" customWidth="1"/>
-    <col min="12" max="18" width="5.09765625" customWidth="1"/>
-    <col min="19" max="19" width="3.09765625" customWidth="1"/>
-    <col min="20" max="26" width="5.09765625" customWidth="1"/>
-    <col min="27" max="27" width="3.09765625" customWidth="1"/>
-    <col min="28" max="34" width="5.09765625" customWidth="1"/>
-    <col min="35" max="35" width="3.09765625" customWidth="1"/>
-    <col min="36" max="42" width="5.09765625" customWidth="1"/>
-    <col min="43" max="43" width="3.09765625" customWidth="1"/>
-    <col min="44" max="50" width="5.09765625" customWidth="1"/>
-    <col min="51" max="51" width="3.09765625" customWidth="1"/>
-    <col min="52" max="58" width="5.09765625" customWidth="1"/>
-    <col min="59" max="59" width="3.09765625" customWidth="1"/>
-    <col min="60" max="66" width="5.09765625" customWidth="1"/>
-    <col min="67" max="67" width="3.09765625" customWidth="1"/>
-    <col min="68" max="74" width="5.09765625" customWidth="1"/>
-    <col min="75" max="77" width="5.59765625" customWidth="1"/>
-    <col min="78" max="78" width="9.59765625" customWidth="1"/>
-    <col min="79" max="79" width="7.59765625" customWidth="1"/>
-    <col min="80" max="80" width="9.59765625" customWidth="1"/>
-    <col min="81" max="81" width="25.69921875" customWidth="1"/>
+    <col min="1" max="1" width="6.44166666666667" customWidth="1"/>
+    <col min="2" max="2" width="9.56666666666667" customWidth="1"/>
+    <col min="3" max="3" width="32.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="9.56666666666667" customWidth="1"/>
+    <col min="5" max="5" width="32.5666666666667" customWidth="1"/>
+    <col min="6" max="6" width="17.0666666666667" customWidth="1"/>
+    <col min="7" max="8" width="5.56666666666667" customWidth="1"/>
+    <col min="9" max="9" width="6.06666666666667" customWidth="1"/>
+    <col min="10" max="10" width="5.56666666666667" customWidth="1"/>
+    <col min="11" max="11" width="3.06666666666667" customWidth="1"/>
+    <col min="12" max="18" width="5.06666666666667" customWidth="1"/>
+    <col min="19" max="19" width="3.06666666666667" customWidth="1"/>
+    <col min="20" max="26" width="5.06666666666667" customWidth="1"/>
+    <col min="27" max="27" width="3.06666666666667" customWidth="1"/>
+    <col min="28" max="34" width="5.06666666666667" customWidth="1"/>
+    <col min="35" max="35" width="3.06666666666667" customWidth="1"/>
+    <col min="36" max="42" width="5.06666666666667" customWidth="1"/>
+    <col min="43" max="43" width="3.06666666666667" customWidth="1"/>
+    <col min="44" max="50" width="5.06666666666667" customWidth="1"/>
+    <col min="51" max="51" width="3.06666666666667" customWidth="1"/>
+    <col min="52" max="58" width="5.06666666666667" customWidth="1"/>
+    <col min="59" max="59" width="3.06666666666667" customWidth="1"/>
+    <col min="60" max="66" width="5.06666666666667" customWidth="1"/>
+    <col min="67" max="67" width="3.06666666666667" customWidth="1"/>
+    <col min="68" max="74" width="5.06666666666667" customWidth="1"/>
+    <col min="75" max="77" width="5.625" customWidth="1"/>
+    <col min="78" max="78" width="9.625" customWidth="1"/>
+    <col min="79" max="79" width="7.56666666666667" customWidth="1"/>
+    <col min="80" max="80" width="9.625" customWidth="1"/>
+    <col min="81" max="81" width="25.6916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" ht="16.95" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="17" t="s">
+    <row r="1" customFormat="1" ht="16.9" customHeight="1" spans="1:81">
+      <c r="A1" s="5"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="19" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="20"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2"/>
-      <c r="BH1" s="2"/>
-      <c r="BI1" s="2"/>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-      <c r="BY1" s="2"/>
-      <c r="BZ1" s="2"/>
-      <c r="CA1" s="20"/>
-      <c r="CB1" s="20"/>
-      <c r="CC1" s="2"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="43"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5"/>
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="5"/>
+      <c r="BC1" s="5"/>
+      <c r="BD1" s="5"/>
+      <c r="BE1" s="5"/>
+      <c r="BF1" s="5"/>
+      <c r="BG1" s="5"/>
+      <c r="BH1" s="5"/>
+      <c r="BI1" s="5"/>
+      <c r="BJ1" s="5"/>
+      <c r="BK1" s="5"/>
+      <c r="BL1" s="5"/>
+      <c r="BM1" s="5"/>
+      <c r="BN1" s="5"/>
+      <c r="BO1" s="5"/>
+      <c r="BP1" s="5"/>
+      <c r="BQ1" s="5"/>
+      <c r="BR1" s="5"/>
+      <c r="BS1" s="5"/>
+      <c r="BT1" s="5"/>
+      <c r="BU1" s="5"/>
+      <c r="BV1" s="5"/>
+      <c r="BW1" s="5"/>
+      <c r="BX1" s="5"/>
+      <c r="BY1" s="5"/>
+      <c r="BZ1" s="5"/>
+      <c r="CA1" s="43"/>
+      <c r="CB1" s="43"/>
+      <c r="CC1" s="5"/>
     </row>
-    <row r="2" spans="1:81" ht="16.95" customHeight="1">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23" t="s">
+    <row r="2" customFormat="1" ht="16.9" customHeight="1" spans="1:81">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22">
-        <f>SUM(L5:L107934)</f>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45">
         <v>0</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="21">
-        <f>SUM(T5:T107934)</f>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="44">
         <v>0</v>
       </c>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21" t="e">
-        <f>SUM(BY5:BY107934)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21">
-        <f>SUM(AJ5:AJ107934)</f>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44">
+        <f>SUM(AB5:AB108138)</f>
         <v>0</v>
       </c>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="21"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="21"/>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
-      <c r="AQ2" s="21"/>
-      <c r="AR2" s="25">
-        <f>SUM(AR5:AR107934)</f>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44">
+        <f>SUM(AJ5:AJ108138)</f>
         <v>0</v>
       </c>
-      <c r="AS2" s="21"/>
-      <c r="AT2" s="21"/>
-      <c r="AU2" s="21"/>
-      <c r="AV2" s="21"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="21"/>
-      <c r="AY2" s="21"/>
-      <c r="AZ2" s="21">
-        <f>SUM(AZ5:AZ107934)</f>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="48"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="48">
+        <f>SUM(AR5:AR108138)</f>
         <v>0</v>
       </c>
-      <c r="BA2" s="21"/>
-      <c r="BB2" s="25"/>
-      <c r="BC2" s="22"/>
-      <c r="BD2" s="22"/>
-      <c r="BE2" s="22"/>
-      <c r="BF2" s="24"/>
-      <c r="BG2" s="26"/>
-      <c r="BH2" s="21">
-        <f>SUM(BH5:BH107934)</f>
+      <c r="AS2" s="44"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="44"/>
+      <c r="AV2" s="44"/>
+      <c r="AW2" s="48"/>
+      <c r="AX2" s="44"/>
+      <c r="AY2" s="44"/>
+      <c r="AZ2" s="44">
+        <f>SUM(AZ5:AZ108138)</f>
         <v>0</v>
       </c>
-      <c r="BI2" s="24"/>
-      <c r="BJ2" s="24"/>
-      <c r="BK2" s="24"/>
-      <c r="BL2" s="24"/>
-      <c r="BM2" s="24"/>
-      <c r="BN2" s="24"/>
-      <c r="BO2" s="24"/>
-      <c r="BP2" s="21">
-        <f>SUM(BP5:BP107934)</f>
+      <c r="BA2" s="44"/>
+      <c r="BB2" s="48"/>
+      <c r="BC2" s="45"/>
+      <c r="BD2" s="45"/>
+      <c r="BE2" s="45"/>
+      <c r="BF2" s="47"/>
+      <c r="BG2" s="49"/>
+      <c r="BH2" s="44">
+        <f>SUM(BH5:BH108138)</f>
         <v>0</v>
       </c>
-      <c r="BQ2" s="24"/>
-      <c r="BR2" s="24"/>
-      <c r="BS2" s="24"/>
-      <c r="BT2" s="24"/>
-      <c r="BU2" s="24"/>
-      <c r="BV2" s="24"/>
-      <c r="BW2" s="21">
-        <f>AZ2+BH2+BP2</f>
+      <c r="BI2" s="47"/>
+      <c r="BJ2" s="47"/>
+      <c r="BK2" s="47"/>
+      <c r="BL2" s="47"/>
+      <c r="BM2" s="47"/>
+      <c r="BN2" s="47"/>
+      <c r="BO2" s="47"/>
+      <c r="BP2" s="44">
+        <f>SUM(BP5:BP108138)</f>
         <v>0</v>
       </c>
-      <c r="BX2" s="24"/>
-      <c r="BY2" s="21" t="e">
-        <f>L2+T2+AB2+AJ2+AR2+AZ2+BH2+BP2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="24"/>
-      <c r="CB2" s="24"/>
-      <c r="CC2" s="24"/>
+      <c r="BQ2" s="47"/>
+      <c r="BR2" s="47"/>
+      <c r="BS2" s="47"/>
+      <c r="BT2" s="47"/>
+      <c r="BU2" s="47"/>
+      <c r="BV2" s="47"/>
+      <c r="BW2" s="44">
+        <f>SUM(BW5:BW108138)</f>
+        <v>0</v>
+      </c>
+      <c r="BX2" s="47"/>
+      <c r="BY2" s="44">
+        <f>SUM(BY5:BY108138)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ2" s="50"/>
+      <c r="CA2" s="47"/>
+      <c r="CB2" s="47"/>
+      <c r="CC2" s="47"/>
     </row>
-    <row r="3" spans="1:81" ht="34.200000000000003">
-      <c r="A3" s="28" t="s">
+    <row r="3" customFormat="1" ht="34.5" spans="1:81">
+      <c r="A3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50" t="s">
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="52" t="s">
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52" t="s">
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="53"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="52"/>
-      <c r="AM3" s="52"/>
-      <c r="AN3" s="52"/>
-      <c r="AO3" s="52"/>
-      <c r="AP3" s="52"/>
-      <c r="AQ3" s="52" t="s">
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="53"/>
+      <c r="AP3" s="53"/>
+      <c r="AQ3" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="AR3" s="52"/>
-      <c r="AS3" s="52"/>
-      <c r="AT3" s="52"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="47" t="s">
+      <c r="AR3" s="53"/>
+      <c r="AS3" s="53"/>
+      <c r="AT3" s="53"/>
+      <c r="AU3" s="53"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="53"/>
+      <c r="AY3" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="AZ3" s="47"/>
-      <c r="BA3" s="47"/>
-      <c r="BB3" s="47"/>
-      <c r="BC3" s="47"/>
-      <c r="BD3" s="47"/>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47" t="s">
+      <c r="AZ3" s="54"/>
+      <c r="BA3" s="54"/>
+      <c r="BB3" s="54"/>
+      <c r="BC3" s="54"/>
+      <c r="BD3" s="54"/>
+      <c r="BE3" s="54"/>
+      <c r="BF3" s="54"/>
+      <c r="BG3" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="BH3" s="47"/>
-      <c r="BI3" s="47"/>
-      <c r="BJ3" s="47"/>
-      <c r="BK3" s="47"/>
-      <c r="BL3" s="47"/>
-      <c r="BM3" s="47"/>
-      <c r="BN3" s="47"/>
-      <c r="BO3" s="47" t="s">
+      <c r="BH3" s="54"/>
+      <c r="BI3" s="54"/>
+      <c r="BJ3" s="54"/>
+      <c r="BK3" s="54"/>
+      <c r="BL3" s="54"/>
+      <c r="BM3" s="54"/>
+      <c r="BN3" s="54"/>
+      <c r="BO3" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="BP3" s="47"/>
-      <c r="BQ3" s="47"/>
-      <c r="BR3" s="47"/>
-      <c r="BS3" s="47"/>
-      <c r="BT3" s="47"/>
-      <c r="BU3" s="47"/>
-      <c r="BV3" s="47"/>
-      <c r="BW3" s="48" t="s">
+      <c r="BP3" s="54"/>
+      <c r="BQ3" s="54"/>
+      <c r="BR3" s="54"/>
+      <c r="BS3" s="54"/>
+      <c r="BT3" s="54"/>
+      <c r="BU3" s="54"/>
+      <c r="BV3" s="54"/>
+      <c r="BW3" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="BX3" s="49"/>
-      <c r="BY3" s="28" t="s">
+      <c r="BX3" s="56"/>
+      <c r="BY3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="BZ3" s="28" t="s">
+      <c r="BZ3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="CA3" s="28" t="s">
+      <c r="CA3" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="CB3" s="28" t="s">
+      <c r="CB3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="CC3" s="28" t="s">
+      <c r="CC3" s="51" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:81" ht="46.8">
-      <c r="A4" s="31" t="s">
+    <row r="4" customFormat="1" ht="57.5" spans="1:81">
+      <c r="A4" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="O4" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="29" t="s">
+      <c r="Q4" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="R4" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="29" t="s">
+      <c r="S4" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="T4" s="29" t="s">
+      <c r="T4" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="U4" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="29" t="s">
+      <c r="V4" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="X4" s="29" t="s">
+      <c r="X4" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="Y4" s="29" t="s">
+      <c r="Y4" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="29" t="s">
+      <c r="Z4" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AD4" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AE4" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AF4" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AG4" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AH4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AJ4" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AK4" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AL4" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AM4" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AN4" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AO4" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AP4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AQ4" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="AR4" s="32" t="s">
+      <c r="AR4" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AS4" s="32" t="s">
+      <c r="AS4" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="AT4" s="32" t="s">
+      <c r="AT4" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="AU4" s="32" t="s">
+      <c r="AU4" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AV4" s="32" t="s">
+      <c r="AV4" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="AW4" s="32" t="s">
+      <c r="AW4" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="AX4" s="32" t="s">
+      <c r="AX4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="AY4" s="33" t="s">
+      <c r="AY4" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AZ4" s="33" t="s">
+      <c r="AZ4" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="BA4" s="33" t="s">
+      <c r="BA4" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="BB4" s="33" t="s">
+      <c r="BB4" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="BC4" s="33" t="s">
+      <c r="BC4" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="BD4" s="33" t="s">
+      <c r="BD4" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="BE4" s="33" t="s">
+      <c r="BE4" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="BF4" s="33" t="s">
+      <c r="BF4" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="BG4" s="33" t="s">
+      <c r="BG4" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="BH4" s="33" t="s">
+      <c r="BH4" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="BI4" s="33" t="s">
+      <c r="BI4" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="BJ4" s="33" t="s">
+      <c r="BJ4" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="BK4" s="33" t="s">
+      <c r="BK4" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="BL4" s="33" t="s">
+      <c r="BL4" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="BM4" s="33" t="s">
+      <c r="BM4" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="BN4" s="33" t="s">
+      <c r="BN4" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="BO4" s="33" t="s">
+      <c r="BO4" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="BP4" s="33" t="s">
+      <c r="BP4" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="BQ4" s="33" t="s">
+      <c r="BQ4" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="BR4" s="33" t="s">
+      <c r="BR4" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="BS4" s="33" t="s">
+      <c r="BS4" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="BT4" s="33" t="s">
+      <c r="BT4" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="BU4" s="33" t="s">
+      <c r="BU4" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="BV4" s="33" t="s">
+      <c r="BV4" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="BW4" s="30" t="s">
+      <c r="BW4" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="BX4" s="30" t="s">
+      <c r="BX4" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="BY4" s="31" t="s">
+      <c r="BY4" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="BZ4" s="31" t="s">
+      <c r="BZ4" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="CA4" s="31" t="s">
+      <c r="CA4" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="CB4" s="31" t="s">
+      <c r="CB4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="CC4" s="31" t="s">
+      <c r="CC4" s="57" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="45.6">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="1" ht="46" spans="1:81">
+      <c r="A5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="3" t="e">
-        <f>CB5-CA5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="I5" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="J5" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="K5" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="L5" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="M5" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="N5" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="O5" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="Q5" s="37" t="s">
+      <c r="P5" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="R5" s="37" t="s">
+      <c r="Q5" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="R5" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="T5" s="37" t="s">
+      <c r="S5" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="U5" s="37" t="s">
+      <c r="T5" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="V5" s="37" t="s">
+      <c r="U5" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="W5" s="37" t="s">
+      <c r="V5" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="X5" s="37" t="s">
+      <c r="W5" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" s="37" t="s">
+      <c r="X5" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="Z5" s="37" t="s">
+      <c r="Y5" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="AA5" s="37" t="s">
+      <c r="Z5" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="AB5" s="37" t="s">
+      <c r="AA5" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="AC5" s="37" t="s">
+      <c r="AB5" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="AD5" s="37" t="s">
+      <c r="AC5" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="AE5" s="37" t="s">
+      <c r="AD5" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="AF5" s="37" t="s">
+      <c r="AE5" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="AG5" s="37" t="s">
+      <c r="AF5" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="AH5" s="37" t="s">
+      <c r="AG5" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="AI5" s="37" t="s">
+      <c r="AH5" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="AJ5" s="37" t="s">
+      <c r="AI5" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="AK5" s="37" t="s">
+      <c r="AJ5" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="AL5" s="37" t="s">
+      <c r="AK5" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="AM5" s="37" t="s">
+      <c r="AL5" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AN5" s="37" t="s">
+      <c r="AM5" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="AO5" s="37" t="s">
+      <c r="AN5" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="AP5" s="37" t="s">
+      <c r="AO5" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="AQ5" s="37" t="s">
+      <c r="AP5" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="AR5" s="37" t="s">
+      <c r="AQ5" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="AS5" s="37" t="s">
+      <c r="AR5" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="AT5" s="37" t="s">
+      <c r="AS5" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="AU5" s="37" t="s">
+      <c r="AT5" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="AV5" s="37" t="s">
+      <c r="AU5" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="AW5" s="37" t="s">
+      <c r="AV5" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="AX5" s="37" t="s">
+      <c r="AW5" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="AY5" s="37" t="s">
+      <c r="AX5" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="AZ5" s="37" t="s">
+      <c r="AY5" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="BA5" s="37" t="s">
+      <c r="AZ5" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="BB5" s="37" t="s">
+      <c r="BA5" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="BC5" s="37" t="s">
+      <c r="BB5" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="BD5" s="37" t="s">
+      <c r="BC5" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="BE5" s="37" t="s">
+      <c r="BD5" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="BF5" s="37" t="s">
+      <c r="BE5" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="BG5" s="37" t="s">
+      <c r="BF5" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="BH5" s="37" t="s">
+      <c r="BG5" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="BI5" s="37" t="s">
+      <c r="BH5" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="BJ5" s="37" t="s">
+      <c r="BI5" s="63" t="s">
         <v>111</v>
       </c>
-      <c r="BK5" s="37" t="s">
+      <c r="BJ5" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="BL5" s="37" t="s">
+      <c r="BK5" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="BM5" s="37" t="s">
+      <c r="BL5" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="BN5" s="37" t="s">
+      <c r="BM5" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="BO5" s="37" t="s">
+      <c r="BN5" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="BP5" s="37" t="s">
+      <c r="BO5" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="BQ5" s="37" t="s">
+      <c r="BP5" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="BR5" s="37" t="s">
+      <c r="BQ5" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="BS5" s="37" t="s">
+      <c r="BR5" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="BT5" s="37" t="s">
+      <c r="BS5" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="BU5" s="37" t="s">
+      <c r="BT5" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="BV5" s="38" t="s">
+      <c r="BU5" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="BW5" s="37" t="e">
-        <f>AZ5+BH5+BP5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BX5" s="37" t="e">
-        <f>BI5+BQ5+BA5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BY5" s="37" t="e">
-        <f>L5+T5+AB5+AJ5+AR5+AZ5+BH5+BP5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BZ5" s="39" t="s">
+      <c r="BV5" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="CA5" s="39" t="s">
+      <c r="BW5" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="CB5" s="3" t="s">
+      <c r="BX5" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="CC5" s="3" t="s">
+      <c r="BY5" s="63" t="s">
         <v>127</v>
+      </c>
+      <c r="BZ5" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA5" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="CB5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC5" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="AY3:BF3"/>
-    <mergeCell ref="BG3:BN3"/>
-    <mergeCell ref="BO3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
     <mergeCell ref="K3:R3"/>
     <mergeCell ref="S3:Z3"/>
     <mergeCell ref="AA3:AH3"/>
     <mergeCell ref="AI3:AP3"/>
     <mergeCell ref="AQ3:AX3"/>
+    <mergeCell ref="AY3:BF3"/>
+    <mergeCell ref="BG3:BN3"/>
+    <mergeCell ref="BO3:BV3"/>
+    <mergeCell ref="BW3:BX3"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
   <conditionalFormatting sqref="C2:D2">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4 W4 AE4 AM4 AU4 BC4 BK4 BS4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4 W4 AE4 AM4 AU4 BC4 BK4 BS4">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15395E71-A6C7-4B3F-983D-BC63B27DFCA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="3" style="7" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="8.8984375" style="8" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="5.59765625" style="9" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="4.69921875" style="9" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="10.19921875" style="7" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="34.09765625" style="10" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.19921875" style="7" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="34.09765625" style="10" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="8.69921875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="5.796875" style="10" customWidth="1" collapsed="1"/>
-    <col min="12" max="14" width="5.796875" style="9" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="27.3984375" style="9" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="9" style="9" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="8" style="9"/>
-    <col min="19" max="16384" width="8" style="9" collapsed="1"/>
+    <col min="1" max="1" width="3" style="24" customWidth="1"/>
+    <col min="2" max="2" width="8.9" style="25" customWidth="1"/>
+    <col min="3" max="4" width="5.6" style="26" customWidth="1"/>
+    <col min="5" max="5" width="4.7" style="26" customWidth="1"/>
+    <col min="6" max="6" width="10.2" style="24" customWidth="1"/>
+    <col min="7" max="7" width="34.1" style="27" customWidth="1"/>
+    <col min="8" max="8" width="10.2" style="24" customWidth="1"/>
+    <col min="9" max="9" width="34.1" style="27" customWidth="1"/>
+    <col min="10" max="10" width="8.7" style="27" customWidth="1"/>
+    <col min="11" max="11" width="5.8" style="27" customWidth="1"/>
+    <col min="12" max="14" width="5.8" style="26" customWidth="1"/>
+    <col min="15" max="15" width="27.4" style="26" customWidth="1"/>
+    <col min="16" max="16" width="9" style="26" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33.75" customHeight="1">
-      <c r="A1" s="14"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="43"/>
+    <row r="1" ht="33.75" customHeight="1" spans="1:16">
+      <c r="A1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="32"/>
     </row>
-    <row r="2" spans="1:16" s="40" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="42" t="s">
+    <row r="2" s="23" customFormat="1" ht="34.2" customHeight="1" spans="1:16">
+      <c r="A2" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="P2" s="33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" s="23" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+      <c r="A3" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="K3" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="L3" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="O3" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" ht="11.4" customHeight="1" spans="1:16">
+      <c r="A4" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="L2" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="N2" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="O2" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="40" customFormat="1" ht="68.25" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="J3" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="K3" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="L3" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="N3" s="41" t="s">
-        <v>188</v>
-      </c>
-      <c r="O3" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="P3" s="41" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="11.4" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:P4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8.7" defaultRowHeight="11.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="18.09765625" style="1" customWidth="1"/>
-    <col min="2" max="5" width="15.59765625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.69921875" style="1"/>
+    <col min="1" max="1" width="18.1" style="1" customWidth="1"/>
+    <col min="2" max="5" width="15.6" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A1" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="2"/>
+    <row r="1" ht="34.5" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A2" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="2"/>
+    <row r="2" ht="25.2" customHeight="1" spans="1:6">
+      <c r="A2" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="2"/>
+    <row r="3" ht="25.2" customHeight="1" spans="1:6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="2"/>
+    <row r="4" ht="30" customHeight="1" spans="1:6">
+      <c r="A4" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="2"/>
+    <row r="5" ht="30" customHeight="1" spans="1:6">
+      <c r="A5" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="2"/>
+    <row r="6" ht="30" customHeight="1" spans="1:6">
+      <c r="A6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="2"/>
+    <row r="7" ht="30" customHeight="1" spans="1:6">
+      <c r="A7" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A8" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="2"/>
+    <row r="8" ht="25.2" customHeight="1" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A9" s="58"/>
-      <c r="B9" s="4" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C9" s="4" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D9" s="3" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E9" s="4" t="e">
+    <row r="9" ht="25.2" customHeight="1" spans="1:6">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
+        <f>硫化日计划!AB2</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <f>硫化日计划!AJ2</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <f>硫化日计划!AR2</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <f>SUM(B9:D9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="4">
-        <f ca="1">COUNTA(#REF!:OFFSET(#REF!,COUNTA(#REF!)-1,0))-1</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="4">
-        <f ca="1">COUNTA(#REF!:OFFSET(#REF!,COUNTA(#REF!)-1,0))-1</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <f ca="1">COUNTA(#REF!:OFFSET(#REF!,COUNTA(#REF!)-1,0))-1</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <f ca="1">SUM(B10:D10)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="2"/>
+    <row r="10" ht="25.2" customHeight="1" spans="1:6">
+      <c r="A10" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="9">
+        <f>COUNTA(硫化日计划!$AB$5:AB1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="9">
+        <f>COUNTA(硫化日计划!$AJ$5:AJ1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
+        <f>COUNTA(硫化日计划!$AR$5:AR1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <f>SUM(B10:D10)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="2"/>
+    <row r="11" ht="30" customHeight="1" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="2"/>
+    <row r="12" ht="30" customHeight="1" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="59" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="2"/>
+    <row r="13" ht="30" customHeight="1" spans="1:6">
+      <c r="A13" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="2"/>
+    <row r="14" ht="30" customHeight="1" spans="1:6">
+      <c r="A14" s="22"/>
+      <c r="B14" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3958,7 +4550,7 @@
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -1785,24 +1785,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="0"/>
       <name val="Cambria"/>
       <charset val="134"/>
@@ -1816,14 +1798,26 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1838,6 +1832,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4408,7 +4408,7 @@
       <c r="E6" s="12"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:6">
+    <row r="7" ht="90" customHeight="1" spans="1:6">
       <c r="A7" s="14" t="s">
         <v>190</v>
       </c>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -609,7 +609,7 @@
 Chú ý</t>
   </si>
   <si>
-    <t xml:space="preserve">*DOT
+    <t xml:space="preserve">*DOT DOT
 </t>
   </si>
   <si>
@@ -1786,8 +1786,8 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
@@ -1799,20 +1799,14 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Segoe UI"/>
-      <charset val="238"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
+      <name val="Segoe UI"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1837,6 +1831,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -3839,7 +3839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="46" spans="1:81">
+    <row r="5" customFormat="1" ht="80" customHeight="1" spans="1:81">
       <c r="A5" s="22" t="s">
         <v>51</v>
       </c>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A57891-6B1F-48BA-96DB-5C9034DD64E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12555" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -16,24 +22,11 @@
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="286">
   <si>
     <r>
       <rPr>
@@ -51,7 +44,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -71,7 +64,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -91,7 +84,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -111,7 +104,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -131,7 +124,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -151,7 +144,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -171,7 +164,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -191,7 +184,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -211,7 +204,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -241,7 +234,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -312,7 +305,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -341,7 +334,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -373,7 +366,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -402,7 +395,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -434,7 +427,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -1427,7 +1420,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1519,26 +1512,266 @@
   </si>
   <si>
     <t>{lhRemark}</t>
+  </si>
+  <si>
+    <t>lhMachineCode</t>
+  </si>
+  <si>
+    <t>materialCode</t>
+  </si>
+  <si>
+    <t>materialDesc</t>
+  </si>
+  <si>
+    <t>embryoCode</t>
+  </si>
+  <si>
+    <t>mainMaterialDesc</t>
+  </si>
+  <si>
+    <t>structureName</t>
+  </si>
+  <si>
+    <t>dailyPlanQty</t>
+  </si>
+  <si>
+    <t>embryoStock</t>
+  </si>
+  <si>
+    <t>replaceCapsuleCountLeftRight</t>
+  </si>
+  <si>
+    <t>singleMouldShiftQty</t>
+  </si>
+  <si>
+    <t>class1Order</t>
+  </si>
+  <si>
+    <t>class1PlanQty</t>
+  </si>
+  <si>
+    <t>class1FinishQty</t>
+  </si>
+  <si>
+    <t>class1LeftRightMould</t>
+  </si>
+  <si>
+    <t>class1Type</t>
+  </si>
+  <si>
+    <t>class1MouldMethod</t>
+  </si>
+  <si>
+    <t>class1Analysis</t>
+  </si>
+  <si>
+    <t>class1Dot</t>
+  </si>
+  <si>
+    <t>class2Order</t>
+  </si>
+  <si>
+    <t>class2PlanQty</t>
+  </si>
+  <si>
+    <t>class2FinishQty</t>
+  </si>
+  <si>
+    <t>class2LeftRightMould</t>
+  </si>
+  <si>
+    <t>class2Type</t>
+  </si>
+  <si>
+    <t>class2MouldMethod</t>
+  </si>
+  <si>
+    <t>class2Analysis</t>
+  </si>
+  <si>
+    <t>class2Dot</t>
+  </si>
+  <si>
+    <t>class3Order</t>
+  </si>
+  <si>
+    <t>class3PlanQty</t>
+  </si>
+  <si>
+    <t>class3FinishQty</t>
+  </si>
+  <si>
+    <t>class3LeftRightMould</t>
+  </si>
+  <si>
+    <t>class3Type</t>
+  </si>
+  <si>
+    <t>class3MouldMethod</t>
+  </si>
+  <si>
+    <t>class3Analysis</t>
+  </si>
+  <si>
+    <t>class3Dot</t>
+  </si>
+  <si>
+    <t>class4Order</t>
+  </si>
+  <si>
+    <t>class4PlanQty</t>
+  </si>
+  <si>
+    <t>class4FinishQty</t>
+  </si>
+  <si>
+    <t>class4LeftRightMould</t>
+  </si>
+  <si>
+    <t>class4Type</t>
+  </si>
+  <si>
+    <t>class4MouldMethod</t>
+  </si>
+  <si>
+    <t>class4Analysis</t>
+  </si>
+  <si>
+    <t>class4Dot</t>
+  </si>
+  <si>
+    <t>class5Order</t>
+  </si>
+  <si>
+    <t>class5PlanQty</t>
+  </si>
+  <si>
+    <t>class5FinishQty</t>
+  </si>
+  <si>
+    <t>class5LeftRightMould</t>
+  </si>
+  <si>
+    <t>class5Type</t>
+  </si>
+  <si>
+    <t>class5MouldMethod</t>
+  </si>
+  <si>
+    <t>class5Analysis</t>
+  </si>
+  <si>
+    <t>class5Dot</t>
+  </si>
+  <si>
+    <t>class6Order</t>
+  </si>
+  <si>
+    <t>class6PlanQty</t>
+  </si>
+  <si>
+    <t>class6FinishQty</t>
+  </si>
+  <si>
+    <t>class6LeftRightMould</t>
+  </si>
+  <si>
+    <t>class6Type</t>
+  </si>
+  <si>
+    <t>class6MouldMethod</t>
+  </si>
+  <si>
+    <t>class6Analysis</t>
+  </si>
+  <si>
+    <t>class6Dot</t>
+  </si>
+  <si>
+    <t>class7Order</t>
+  </si>
+  <si>
+    <t>class7PlanQty</t>
+  </si>
+  <si>
+    <t>class7FinishQty</t>
+  </si>
+  <si>
+    <t>class7LeftRightMould</t>
+  </si>
+  <si>
+    <t>class7Type</t>
+  </si>
+  <si>
+    <t>class7MouldMethod</t>
+  </si>
+  <si>
+    <t>class7Analysis</t>
+  </si>
+  <si>
+    <t>class7Dot</t>
+  </si>
+  <si>
+    <t>class8Order</t>
+  </si>
+  <si>
+    <t>class8PlanQty</t>
+  </si>
+  <si>
+    <t>class8FinishQty</t>
+  </si>
+  <si>
+    <t>class8LeftRightMould</t>
+  </si>
+  <si>
+    <t>class8Type</t>
+  </si>
+  <si>
+    <t>class8MouldMethod</t>
+  </si>
+  <si>
+    <t>class8Analysis</t>
+  </si>
+  <si>
+    <t>class8Dot</t>
+  </si>
+  <si>
+    <t>nightPlanQtyTotal</t>
+  </si>
+  <si>
+    <t>nightFinishQtyTotal</t>
+  </si>
+  <si>
+    <t>totalPlanQtyFormula</t>
+  </si>
+  <si>
+    <t>cxMachineCode</t>
+  </si>
+  <si>
+    <t>totalDailyPlanQty</t>
+  </si>
+  <si>
+    <t>todayNightFinishQty</t>
+  </si>
+  <si>
+    <t>remark</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="11">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="m/d;@"/>
-    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="179" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="180" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="m/d;@"/>
+    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="181" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="182" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="183" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="184" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1616,150 +1849,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
@@ -1768,7 +1857,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1794,13 +1883,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1819,7 +1908,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1832,16 +1921,27 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1872,194 +1972,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="22">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2226,277 +2140,188 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="61">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2506,255 +2331,63 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="61">
+  <cellStyles count="13">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma 2" xfId="49"/>
-    <cellStyle name="Excel Built-in Normal" xfId="50"/>
-    <cellStyle name="Normal 10" xfId="51"/>
-    <cellStyle name="Normal 12 3" xfId="52"/>
-    <cellStyle name="Normal 2 2" xfId="53"/>
-    <cellStyle name="Normal 20 3" xfId="54"/>
-    <cellStyle name="Normal 91" xfId="55"/>
-    <cellStyle name="Percent 2" xfId="56"/>
-    <cellStyle name="常规 2" xfId="57"/>
-    <cellStyle name="常规 2 5" xfId="58"/>
-    <cellStyle name="千位分隔 3" xfId="59"/>
-    <cellStyle name="千位分隔 3 3" xfId="60"/>
+    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2773,34 +2406,43 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>14287</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>143193</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 21"/>
+        <xdr:cNvPr id="5" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2825,24 +2467,30 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>14287</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>143193</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2867,7 +2515,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2883,13 +2531,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3220,1327 +2874,1567 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:CC5"/>
-  <sheetFormatPr defaultColWidth="8.7" defaultRowHeight="15" outlineLevelRow="4"/>
+  <dimension ref="A1:CC6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.44166666666667" customWidth="1"/>
-    <col min="2" max="2" width="9.56666666666667" customWidth="1"/>
-    <col min="3" max="3" width="32.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="9.56666666666667" customWidth="1"/>
-    <col min="5" max="5" width="32.5666666666667" customWidth="1"/>
-    <col min="6" max="6" width="17.0666666666667" customWidth="1"/>
-    <col min="7" max="8" width="5.56666666666667" customWidth="1"/>
-    <col min="9" max="9" width="6.06666666666667" customWidth="1"/>
-    <col min="10" max="10" width="5.56666666666667" customWidth="1"/>
-    <col min="11" max="11" width="3.06666666666667" customWidth="1"/>
-    <col min="12" max="18" width="5.06666666666667" customWidth="1"/>
-    <col min="19" max="19" width="3.06666666666667" customWidth="1"/>
-    <col min="20" max="26" width="5.06666666666667" customWidth="1"/>
-    <col min="27" max="27" width="3.06666666666667" customWidth="1"/>
-    <col min="28" max="34" width="5.06666666666667" customWidth="1"/>
-    <col min="35" max="35" width="3.06666666666667" customWidth="1"/>
-    <col min="36" max="42" width="5.06666666666667" customWidth="1"/>
-    <col min="43" max="43" width="3.06666666666667" customWidth="1"/>
-    <col min="44" max="50" width="5.06666666666667" customWidth="1"/>
-    <col min="51" max="51" width="3.06666666666667" customWidth="1"/>
-    <col min="52" max="58" width="5.06666666666667" customWidth="1"/>
-    <col min="59" max="59" width="3.06666666666667" customWidth="1"/>
-    <col min="60" max="66" width="5.06666666666667" customWidth="1"/>
-    <col min="67" max="67" width="3.06666666666667" customWidth="1"/>
-    <col min="68" max="74" width="5.06666666666667" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="8" width="5.625" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="10" width="5.625" customWidth="1"/>
+    <col min="11" max="11" width="3.125" customWidth="1"/>
+    <col min="12" max="18" width="5.125" customWidth="1"/>
+    <col min="19" max="19" width="3.125" customWidth="1"/>
+    <col min="20" max="26" width="5.125" customWidth="1"/>
+    <col min="27" max="27" width="3.125" customWidth="1"/>
+    <col min="28" max="34" width="5.125" customWidth="1"/>
+    <col min="35" max="35" width="3.125" customWidth="1"/>
+    <col min="36" max="42" width="5.125" customWidth="1"/>
+    <col min="43" max="43" width="3.125" customWidth="1"/>
+    <col min="44" max="50" width="5.125" customWidth="1"/>
+    <col min="51" max="51" width="3.125" customWidth="1"/>
+    <col min="52" max="58" width="5.125" customWidth="1"/>
+    <col min="59" max="59" width="3.125" customWidth="1"/>
+    <col min="60" max="66" width="5.125" customWidth="1"/>
+    <col min="67" max="67" width="3.125" customWidth="1"/>
+    <col min="68" max="74" width="5.125" customWidth="1"/>
     <col min="75" max="77" width="5.625" customWidth="1"/>
     <col min="78" max="78" width="9.625" customWidth="1"/>
-    <col min="79" max="79" width="7.56666666666667" customWidth="1"/>
+    <col min="79" max="79" width="7.625" customWidth="1"/>
     <col min="80" max="80" width="9.625" customWidth="1"/>
-    <col min="81" max="81" width="25.6916666666667" customWidth="1"/>
+    <col min="81" max="81" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="16.9" customHeight="1" spans="1:81">
-      <c r="A1" s="5"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40" t="s">
+    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J1" t="s">
+        <v>214</v>
+      </c>
+      <c r="K1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" t="s">
+        <v>217</v>
+      </c>
+      <c r="N1" t="s">
+        <v>218</v>
+      </c>
+      <c r="O1" t="s">
+        <v>219</v>
+      </c>
+      <c r="P1" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>221</v>
+      </c>
+      <c r="R1" t="s">
+        <v>222</v>
+      </c>
+      <c r="S1" t="s">
+        <v>223</v>
+      </c>
+      <c r="T1" t="s">
+        <v>224</v>
+      </c>
+      <c r="U1" t="s">
+        <v>225</v>
+      </c>
+      <c r="V1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W1" t="s">
+        <v>227</v>
+      </c>
+      <c r="X1" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>254</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>256</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>258</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>259</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>260</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>261</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>262</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>263</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>264</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>265</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>266</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>267</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>268</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>269</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>270</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>271</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>272</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>273</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>274</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>275</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>276</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>277</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>278</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>279</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>280</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>281</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>282</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>283</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>284</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="42" t="s">
+      <c r="D2" s="25"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="43"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5"/>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="5"/>
-      <c r="BF1" s="5"/>
-      <c r="BG1" s="5"/>
-      <c r="BH1" s="5"/>
-      <c r="BI1" s="5"/>
-      <c r="BJ1" s="5"/>
-      <c r="BK1" s="5"/>
-      <c r="BL1" s="5"/>
-      <c r="BM1" s="5"/>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
-      <c r="BP1" s="5"/>
-      <c r="BQ1" s="5"/>
-      <c r="BR1" s="5"/>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
-      <c r="BU1" s="5"/>
-      <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
-      <c r="BX1" s="5"/>
-      <c r="BY1" s="5"/>
-      <c r="BZ1" s="5"/>
-      <c r="CA1" s="43"/>
-      <c r="CB1" s="43"/>
-      <c r="CC1" s="5"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="2"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="2"/>
+      <c r="BC2" s="2"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BG2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+      <c r="BJ2" s="2"/>
+      <c r="BK2" s="2"/>
+      <c r="BL2" s="2"/>
+      <c r="BM2" s="2"/>
+      <c r="BN2" s="2"/>
+      <c r="BO2" s="2"/>
+      <c r="BP2" s="2"/>
+      <c r="BQ2" s="2"/>
+      <c r="BR2" s="2"/>
+      <c r="BS2" s="2"/>
+      <c r="BT2" s="2"/>
+      <c r="BU2" s="2"/>
+      <c r="BV2" s="2"/>
+      <c r="BW2" s="2"/>
+      <c r="BX2" s="2"/>
+      <c r="BY2" s="2"/>
+      <c r="BZ2" s="2"/>
+      <c r="CA2" s="27"/>
+      <c r="CB2" s="27"/>
+      <c r="CC2" s="2"/>
     </row>
-    <row r="2" customFormat="1" ht="16.9" customHeight="1" spans="1:81">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46" t="s">
+    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45">
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29">
         <v>0</v>
       </c>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="44">
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="28">
         <v>0</v>
       </c>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44">
-        <f>SUM(AB5:AB108138)</f>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28">
+        <f>SUM(AB6:AB108139)</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44">
-        <f>SUM(AJ5:AJ108138)</f>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28">
+        <f>SUM(AJ6:AJ108139)</f>
         <v>0</v>
       </c>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="44"/>
-      <c r="AM2" s="48"/>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="44"/>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="48">
-        <f>SUM(AR5:AR108138)</f>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="32"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="32">
+        <f>SUM(AR6:AR108139)</f>
         <v>0</v>
       </c>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="44"/>
-      <c r="AU2" s="44"/>
-      <c r="AV2" s="44"/>
-      <c r="AW2" s="48"/>
-      <c r="AX2" s="44"/>
-      <c r="AY2" s="44"/>
-      <c r="AZ2" s="44">
-        <f>SUM(AZ5:AZ108138)</f>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="32"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28">
+        <f>SUM(AZ6:AZ108139)</f>
         <v>0</v>
       </c>
-      <c r="BA2" s="44"/>
-      <c r="BB2" s="48"/>
-      <c r="BC2" s="45"/>
-      <c r="BD2" s="45"/>
-      <c r="BE2" s="45"/>
-      <c r="BF2" s="47"/>
-      <c r="BG2" s="49"/>
-      <c r="BH2" s="44">
-        <f>SUM(BH5:BH108138)</f>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="32"/>
+      <c r="BC3" s="29"/>
+      <c r="BD3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="33"/>
+      <c r="BH3" s="28">
+        <f>SUM(BH6:BH108139)</f>
         <v>0</v>
       </c>
-      <c r="BI2" s="47"/>
-      <c r="BJ2" s="47"/>
-      <c r="BK2" s="47"/>
-      <c r="BL2" s="47"/>
-      <c r="BM2" s="47"/>
-      <c r="BN2" s="47"/>
-      <c r="BO2" s="47"/>
-      <c r="BP2" s="44">
-        <f>SUM(BP5:BP108138)</f>
+      <c r="BI3" s="31"/>
+      <c r="BJ3" s="31"/>
+      <c r="BK3" s="31"/>
+      <c r="BL3" s="31"/>
+      <c r="BM3" s="31"/>
+      <c r="BN3" s="31"/>
+      <c r="BO3" s="31"/>
+      <c r="BP3" s="28">
+        <f>SUM(BP6:BP108139)</f>
         <v>0</v>
       </c>
-      <c r="BQ2" s="47"/>
-      <c r="BR2" s="47"/>
-      <c r="BS2" s="47"/>
-      <c r="BT2" s="47"/>
-      <c r="BU2" s="47"/>
-      <c r="BV2" s="47"/>
-      <c r="BW2" s="44">
-        <f>SUM(BW5:BW108138)</f>
+      <c r="BQ3" s="31"/>
+      <c r="BR3" s="31"/>
+      <c r="BS3" s="31"/>
+      <c r="BT3" s="31"/>
+      <c r="BU3" s="31"/>
+      <c r="BV3" s="31"/>
+      <c r="BW3" s="28">
+        <f>SUM(BW6:BW108139)</f>
         <v>0</v>
       </c>
-      <c r="BX2" s="47"/>
-      <c r="BY2" s="44">
-        <f>SUM(BY5:BY108138)</f>
+      <c r="BX3" s="31"/>
+      <c r="BY3" s="28">
+        <f>SUM(BY6:BY108139)</f>
         <v>0</v>
       </c>
-      <c r="BZ2" s="50"/>
-      <c r="CA2" s="47"/>
-      <c r="CB2" s="47"/>
-      <c r="CC2" s="47"/>
+      <c r="BZ3" s="34"/>
+      <c r="CA3" s="31"/>
+      <c r="CB3" s="31"/>
+      <c r="CC3" s="31"/>
     </row>
-    <row r="3" customFormat="1" ht="34.5" spans="1:81">
-      <c r="A3" s="51" t="s">
+    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
+      <c r="A4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E4" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H4" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J4" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="K4" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="66" t="s">
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
-      <c r="AA3" s="53" t="s">
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53" t="s">
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="53"/>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="53"/>
-      <c r="AQ3" s="53" t="s">
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="AR3" s="53"/>
-      <c r="AS3" s="53"/>
-      <c r="AT3" s="53"/>
-      <c r="AU3" s="53"/>
-      <c r="AV3" s="53"/>
-      <c r="AW3" s="53"/>
-      <c r="AX3" s="53"/>
-      <c r="AY3" s="54" t="s">
+      <c r="AR4" s="49"/>
+      <c r="AS4" s="49"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="AZ3" s="54"/>
-      <c r="BA3" s="54"/>
-      <c r="BB3" s="54"/>
-      <c r="BC3" s="54"/>
-      <c r="BD3" s="54"/>
-      <c r="BE3" s="54"/>
-      <c r="BF3" s="54"/>
-      <c r="BG3" s="54" t="s">
+      <c r="AZ4" s="50"/>
+      <c r="BA4" s="50"/>
+      <c r="BB4" s="50"/>
+      <c r="BC4" s="50"/>
+      <c r="BD4" s="50"/>
+      <c r="BE4" s="50"/>
+      <c r="BF4" s="50"/>
+      <c r="BG4" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="BH3" s="54"/>
-      <c r="BI3" s="54"/>
-      <c r="BJ3" s="54"/>
-      <c r="BK3" s="54"/>
-      <c r="BL3" s="54"/>
-      <c r="BM3" s="54"/>
-      <c r="BN3" s="54"/>
-      <c r="BO3" s="54" t="s">
+      <c r="BH4" s="50"/>
+      <c r="BI4" s="50"/>
+      <c r="BJ4" s="50"/>
+      <c r="BK4" s="50"/>
+      <c r="BL4" s="50"/>
+      <c r="BM4" s="50"/>
+      <c r="BN4" s="50"/>
+      <c r="BO4" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="BP3" s="54"/>
-      <c r="BQ3" s="54"/>
-      <c r="BR3" s="54"/>
-      <c r="BS3" s="54"/>
-      <c r="BT3" s="54"/>
-      <c r="BU3" s="54"/>
-      <c r="BV3" s="54"/>
-      <c r="BW3" s="55" t="s">
+      <c r="BP4" s="50"/>
+      <c r="BQ4" s="50"/>
+      <c r="BR4" s="50"/>
+      <c r="BS4" s="50"/>
+      <c r="BT4" s="50"/>
+      <c r="BU4" s="50"/>
+      <c r="BV4" s="50"/>
+      <c r="BW4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="BX3" s="56"/>
-      <c r="BY3" s="51" t="s">
+      <c r="BX4" s="52"/>
+      <c r="BY4" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="BZ3" s="51" t="s">
+      <c r="BZ4" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="CA3" s="51" t="s">
+      <c r="CA4" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="CB3" s="51" t="s">
+      <c r="CB4" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="CC3" s="51" t="s">
+      <c r="CC4" s="35" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="57.5" spans="1:81">
-      <c r="A4" s="57" t="s">
+    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
+      <c r="A5" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B5" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C5" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D5" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="E5" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="F5" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="G5" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="H5" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="I5" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="57" t="s">
+      <c r="J5" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N5" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="52" t="s">
+      <c r="P5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="52" t="s">
+      <c r="Q5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="52" t="s">
+      <c r="R5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="52" t="s">
+      <c r="S5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="T4" s="52" t="s">
+      <c r="T5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="52" t="s">
+      <c r="U5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="52" t="s">
+      <c r="V5" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="W4" s="52" t="s">
+      <c r="W5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="X4" s="52" t="s">
+      <c r="X5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="Y4" s="52" t="s">
+      <c r="Y5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="Z4" s="52" t="s">
+      <c r="Z5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="AA4" s="58" t="s">
+      <c r="AA5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="AB4" s="58" t="s">
+      <c r="AB5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AC4" s="58" t="s">
+      <c r="AC5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="58" t="s">
+      <c r="AD5" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AE4" s="58" t="s">
+      <c r="AE5" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AF4" s="58" t="s">
+      <c r="AF5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="AG4" s="58" t="s">
+      <c r="AG5" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="AH4" s="58" t="s">
+      <c r="AH5" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AI4" s="58" t="s">
+      <c r="AI5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="AJ4" s="58" t="s">
+      <c r="AJ5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AK4" s="58" t="s">
+      <c r="AK5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AL4" s="58" t="s">
+      <c r="AL5" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AM4" s="58" t="s">
+      <c r="AM5" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AN4" s="58" t="s">
+      <c r="AN5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="AO4" s="58" t="s">
+      <c r="AO5" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="AP4" s="58" t="s">
+      <c r="AP5" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AQ4" s="58" t="s">
+      <c r="AQ5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="AR4" s="58" t="s">
+      <c r="AR5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="AS4" s="58" t="s">
+      <c r="AS5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AT4" s="58" t="s">
+      <c r="AT5" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AU4" s="58" t="s">
+      <c r="AU5" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AV4" s="58" t="s">
+      <c r="AV5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="AW4" s="58" t="s">
+      <c r="AW5" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="AX4" s="58" t="s">
+      <c r="AX5" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AY4" s="59" t="s">
+      <c r="AY5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="AZ4" s="59" t="s">
+      <c r="AZ5" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="BA4" s="59" t="s">
+      <c r="BA5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="BB4" s="59" t="s">
+      <c r="BB5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="BC4" s="59" t="s">
+      <c r="BC5" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="BD4" s="59" t="s">
+      <c r="BD5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="BE4" s="59" t="s">
+      <c r="BE5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="BF4" s="59" t="s">
+      <c r="BF5" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="BG4" s="59" t="s">
+      <c r="BG5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="BH4" s="59" t="s">
+      <c r="BH5" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="BI4" s="59" t="s">
+      <c r="BI5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="BJ4" s="59" t="s">
+      <c r="BJ5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="BK4" s="59" t="s">
+      <c r="BK5" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="BL4" s="59" t="s">
+      <c r="BL5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="BM4" s="59" t="s">
+      <c r="BM5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="BN4" s="59" t="s">
+      <c r="BN5" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="BO4" s="59" t="s">
+      <c r="BO5" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="BP4" s="59" t="s">
+      <c r="BP5" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="BQ4" s="59" t="s">
+      <c r="BQ5" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="BR4" s="59" t="s">
+      <c r="BR5" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="BS4" s="59" t="s">
+      <c r="BS5" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="BT4" s="59" t="s">
+      <c r="BT5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="BU4" s="59" t="s">
+      <c r="BU5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="BV4" s="59" t="s">
+      <c r="BV5" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="BW4" s="55" t="s">
+      <c r="BW5" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="BX4" s="55" t="s">
+      <c r="BX5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="BY4" s="57" t="s">
+      <c r="BY5" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="BZ4" s="57" t="s">
+      <c r="BZ5" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="CA4" s="57" t="s">
+      <c r="CA5" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="CB4" s="57" t="s">
+      <c r="CB5" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="CC4" s="57" t="s">
+      <c r="CC5" s="38" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="80" customHeight="1" spans="1:81">
-      <c r="A5" s="22" t="s">
+    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C6" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D6" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E6" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F6" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J6" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="62" t="s">
+      <c r="K6" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L6" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M6" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O6" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P6" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="Q5" s="63" t="s">
+      <c r="Q6" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="R5" s="63" t="s">
+      <c r="R6" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="S5" s="63" t="s">
+      <c r="S6" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="T5" s="63" t="s">
+      <c r="T6" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="U5" s="63" t="s">
+      <c r="U6" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="V5" s="63" t="s">
+      <c r="V6" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="W5" s="63" t="s">
+      <c r="W6" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="X5" s="63" t="s">
+      <c r="X6" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="Y5" s="63" t="s">
+      <c r="Y6" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="Z5" s="63" t="s">
+      <c r="Z6" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="AA5" s="63" t="s">
+      <c r="AA6" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="AB5" s="63" t="s">
+      <c r="AB6" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="AC5" s="63" t="s">
+      <c r="AC6" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="AD5" s="63" t="s">
+      <c r="AD6" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="AE5" s="63" t="s">
+      <c r="AE6" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="AF5" s="63" t="s">
+      <c r="AF6" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="AG5" s="63" t="s">
+      <c r="AG6" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="AH5" s="63" t="s">
+      <c r="AH6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="AI5" s="63" t="s">
+      <c r="AI6" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="AJ5" s="63" t="s">
+      <c r="AJ6" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="AK5" s="63" t="s">
+      <c r="AK6" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="AL5" s="63" t="s">
+      <c r="AL6" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="AM5" s="63" t="s">
+      <c r="AM6" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="AN5" s="63" t="s">
+      <c r="AN6" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="AO5" s="63" t="s">
+      <c r="AO6" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="AP5" s="63" t="s">
+      <c r="AP6" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="AQ5" s="63" t="s">
+      <c r="AQ6" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="AR5" s="63" t="s">
+      <c r="AR6" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="AS5" s="63" t="s">
+      <c r="AS6" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="AT5" s="63" t="s">
+      <c r="AT6" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="AU5" s="63" t="s">
+      <c r="AU6" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="AV5" s="63" t="s">
+      <c r="AV6" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="AW5" s="63" t="s">
+      <c r="AW6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="AX5" s="63" t="s">
+      <c r="AX6" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="AY5" s="63" t="s">
+      <c r="AY6" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="AZ5" s="63" t="s">
+      <c r="AZ6" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="BA5" s="63" t="s">
+      <c r="BA6" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="BB5" s="63" t="s">
+      <c r="BB6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="BC5" s="63" t="s">
+      <c r="BC6" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="BD5" s="63" t="s">
+      <c r="BD6" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="BE5" s="63" t="s">
+      <c r="BE6" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="BF5" s="63" t="s">
+      <c r="BF6" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="BG5" s="63" t="s">
+      <c r="BG6" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="BH5" s="63" t="s">
+      <c r="BH6" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="BI5" s="63" t="s">
+      <c r="BI6" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="BJ5" s="63" t="s">
+      <c r="BJ6" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="BK5" s="63" t="s">
+      <c r="BK6" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="BL5" s="63" t="s">
+      <c r="BL6" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="BM5" s="63" t="s">
+      <c r="BM6" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="BN5" s="63" t="s">
+      <c r="BN6" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="BO5" s="63" t="s">
+      <c r="BO6" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="BP5" s="63" t="s">
+      <c r="BP6" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="BQ5" s="63" t="s">
+      <c r="BQ6" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="BR5" s="63" t="s">
+      <c r="BR6" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="BS5" s="63" t="s">
+      <c r="BS6" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="BT5" s="63" t="s">
+      <c r="BT6" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="BU5" s="63" t="s">
+      <c r="BU6" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="BV5" s="64" t="s">
+      <c r="BV6" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="BW5" s="63" t="s">
+      <c r="BW6" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" s="63" t="s">
+      <c r="BX6" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="BY5" s="63" t="s">
+      <c r="BY6" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="BZ5" s="65" t="s">
+      <c r="BZ6" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="CA5" s="65" t="s">
+      <c r="CA6" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="CB5" s="7" t="s">
+      <c r="CB6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="CC5" s="7" t="s">
+      <c r="CC6" s="3" t="s">
         <v>131</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="K3:R3"/>
-    <mergeCell ref="S3:Z3"/>
-    <mergeCell ref="AA3:AH3"/>
-    <mergeCell ref="AI3:AP3"/>
-    <mergeCell ref="AQ3:AX3"/>
-    <mergeCell ref="AY3:BF3"/>
-    <mergeCell ref="BG3:BN3"/>
-    <mergeCell ref="BO3:BV3"/>
-    <mergeCell ref="BW3:BX3"/>
+    <mergeCell ref="AY4:BF4"/>
+    <mergeCell ref="BG4:BN4"/>
+    <mergeCell ref="BO4:BV4"/>
+    <mergeCell ref="BW4:BX4"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="S4:Z4"/>
+    <mergeCell ref="AA4:AH4"/>
+    <mergeCell ref="AI4:AP4"/>
+    <mergeCell ref="AQ4:AX4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C2:D2">
+  <phoneticPr fontId="27" type="noConversion"/>
+  <conditionalFormatting sqref="C3:D3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4 W4 AE4 AM4 AU4 BC4 BK4 BS4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 W5 AE5 AM5 AU5 BC5 BK5 BS5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3" style="24" customWidth="1"/>
-    <col min="2" max="2" width="8.9" style="25" customWidth="1"/>
-    <col min="3" max="4" width="5.6" style="26" customWidth="1"/>
-    <col min="5" max="5" width="4.7" style="26" customWidth="1"/>
-    <col min="6" max="6" width="10.2" style="24" customWidth="1"/>
-    <col min="7" max="7" width="34.1" style="27" customWidth="1"/>
-    <col min="8" max="8" width="10.2" style="24" customWidth="1"/>
-    <col min="9" max="9" width="34.1" style="27" customWidth="1"/>
-    <col min="10" max="10" width="8.7" style="27" customWidth="1"/>
-    <col min="11" max="11" width="5.8" style="27" customWidth="1"/>
-    <col min="12" max="14" width="5.8" style="26" customWidth="1"/>
-    <col min="15" max="15" width="27.4" style="26" customWidth="1"/>
-    <col min="16" max="16" width="9" style="26" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="26"/>
+    <col min="1" max="1" width="3" style="8" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="8" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="8" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="11" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="11" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="10" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="10" customWidth="1"/>
+    <col min="16" max="16" width="9" style="10" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1" spans="1:16">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30" t="s">
+    <row r="1" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="32"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="16"/>
     </row>
-    <row r="2" s="23" customFormat="1" ht="34.2" customHeight="1" spans="1:16">
-      <c r="A2" s="33" t="s">
+    <row r="2" spans="1:16" s="7" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="O2" s="33" t="s">
+      <c r="O2" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="P2" s="33" t="s">
+      <c r="P2" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" s="23" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="L3" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="34" t="s">
+      <c r="M3" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="N3" s="34" t="s">
+      <c r="N3" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="O3" s="34" t="s">
+      <c r="O3" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="P3" s="34" t="s">
+      <c r="P3" s="18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" ht="11.4" customHeight="1" spans="1:16">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="O4" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="19" t="s">
         <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:P4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A3:P4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.7" defaultRowHeight="11.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.1" style="1" customWidth="1"/>
-    <col min="2" max="5" width="15.6" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7" style="1"/>
+    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34.5" customHeight="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="2"/>
     </row>
-    <row r="2" ht="25.2" customHeight="1" spans="1:6">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="2"/>
     </row>
-    <row r="3" ht="25.2" customHeight="1" spans="1:6">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="65"/>
+      <c r="B3" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="5"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="2"/>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:6">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="5"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="2"/>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="5"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="2"/>
     </row>
-    <row r="7" ht="90" customHeight="1" spans="1:6">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="5"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="2"/>
     </row>
-    <row r="8" ht="25.2" customHeight="1" spans="1:6">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="2"/>
     </row>
-    <row r="9" ht="25.2" customHeight="1" spans="1:6">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9">
-        <f>硫化日计划!AB2</f>
+    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="65"/>
+      <c r="B9" s="4">
+        <f>硫化日计划!AB3</f>
         <v>0</v>
       </c>
-      <c r="C9" s="9">
-        <f>硫化日计划!AJ2</f>
+      <c r="C9" s="4">
+        <f>硫化日计划!AJ3</f>
         <v>0</v>
       </c>
-      <c r="D9" s="7">
-        <f>硫化日计划!AR2</f>
+      <c r="D9" s="3">
+        <f>硫化日计划!AR3</f>
         <v>0</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="4">
         <f>SUM(B9:D9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="2"/>
     </row>
-    <row r="10" ht="25.2" customHeight="1" spans="1:6">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="9">
-        <f>COUNTA(硫化日计划!$AB$5:AB1048576)</f>
+      <c r="B10" s="4">
+        <f>COUNTA(硫化日计划!$AB$6:AB1048576)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="9">
-        <f>COUNTA(硫化日计划!$AJ$5:AJ1048576)</f>
+      <c r="C10" s="4">
+        <f>COUNTA(硫化日计划!$AJ$6:AJ1048576)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="9">
-        <f>COUNTA(硫化日计划!$AR$5:AR1048576)</f>
+      <c r="D10" s="4">
+        <f>COUNTA(硫化日计划!$AR$6:AR1048576)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="4">
         <f>SUM(B10:D10)</f>
         <v>3</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="2"/>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:6">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="5"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="2"/>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:6">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="5"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="2"/>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:6">
-      <c r="A13" s="20" t="s">
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="66" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="5"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="2"/>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:6">
-      <c r="A14" s="22"/>
-      <c r="B14" s="7" t="s">
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="67"/>
+      <c r="B14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="63" t="s">
         <v>204</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
@@ -4549,8 +4443,13 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C7:E7"/>
   </mergeCells>
+  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -711,10 +711,10 @@
     <t>{.class1LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class1Type}</t>
-  </si>
-  <si>
-    <t>{.class1MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class1Analysis}</t>
@@ -735,10 +735,10 @@
     <t>{.class2LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class2Type}</t>
-  </si>
-  <si>
-    <t>{.class2MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class2Analysis}</t>
@@ -759,10 +759,10 @@
     <t>{.class3LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class3Type}</t>
-  </si>
-  <si>
-    <t>{.class3MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class3Analysis}</t>
@@ -783,10 +783,10 @@
     <t>{.class4LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class4Type}</t>
-  </si>
-  <si>
-    <t>{.class4MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class4Analysis}</t>
@@ -807,10 +807,10 @@
     <t>{.class5LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class5Type}</t>
-  </si>
-  <si>
-    <t>{.class5MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class5Analysis}</t>
@@ -831,10 +831,10 @@
     <t>{.class6LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class6Type}</t>
-  </si>
-  <si>
-    <t>{.class6MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class6Analysis}</t>
@@ -855,10 +855,10 @@
     <t>{.class7LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class7Type}</t>
-  </si>
-  <si>
-    <t>{.class7MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class7Analysis}</t>
@@ -879,10 +879,10 @@
     <t>{.class8LeftRightMould}</t>
   </si>
   <si>
-    <t>{.class8Type}</t>
-  </si>
-  <si>
-    <t>{.class8MouldMethod}</t>
+    <t>{.isEnd}</t>
+  </si>
+  <si>
+    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class8Analysis}</t>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -2961,11 +2961,15 @@
       <c r="N1" t="s">
         <v>218</v>
       </c>
-      <c r="O1" t="s">
-        <v>219</v>
-      </c>
-      <c r="P1" t="s">
-        <v>220</v>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>class1IsEnd</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>class1LhType</t>
+        </is>
       </c>
       <c r="Q1" t="s">
         <v>221</v>
@@ -2985,11 +2989,15 @@
       <c r="V1" t="s">
         <v>226</v>
       </c>
-      <c r="W1" t="s">
-        <v>227</v>
-      </c>
-      <c r="X1" t="s">
-        <v>228</v>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>class2IsEnd</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>class2LhType</t>
+        </is>
       </c>
       <c r="Y1" t="s">
         <v>229</v>
@@ -3009,11 +3017,15 @@
       <c r="AD1" t="s">
         <v>234</v>
       </c>
-      <c r="AE1" t="s">
-        <v>235</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>236</v>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>class3IsEnd</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>class3LhType</t>
+        </is>
       </c>
       <c r="AG1" t="s">
         <v>237</v>
@@ -3033,11 +3045,15 @@
       <c r="AL1" t="s">
         <v>242</v>
       </c>
-      <c r="AM1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>244</v>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class4IsEnd</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class4LhType</t>
+        </is>
       </c>
       <c r="AO1" t="s">
         <v>245</v>
@@ -3057,11 +3073,15 @@
       <c r="AT1" t="s">
         <v>250</v>
       </c>
-      <c r="AU1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>252</v>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class5IsEnd</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>class5LhType</t>
+        </is>
       </c>
       <c r="AW1" t="s">
         <v>253</v>
@@ -3081,11 +3101,15 @@
       <c r="BB1" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" t="s">
-        <v>259</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>260</v>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>class6IsEnd</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>class6LhType</t>
+        </is>
       </c>
       <c r="BE1" t="s">
         <v>261</v>
@@ -3105,11 +3129,15 @@
       <c r="BJ1" t="s">
         <v>266</v>
       </c>
-      <c r="BK1" t="s">
-        <v>267</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>268</v>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>class7IsEnd</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>class7LhType</t>
+        </is>
       </c>
       <c r="BM1" t="s">
         <v>269</v>
@@ -3129,11 +3157,15 @@
       <c r="BR1" t="s">
         <v>274</v>
       </c>
-      <c r="BS1" t="s">
-        <v>275</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>276</v>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>class8IsEnd</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>class8LhType</t>
+        </is>
       </c>
       <c r="BU1" t="s">
         <v>277</v>
@@ -3782,11 +3814,15 @@
       <c r="N6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="44" t="s">
-        <v>65</v>
-      </c>
-      <c r="P6" s="44" t="s">
-        <v>66</v>
+      <c r="O6" s="44" t="inlineStr">
+        <is>
+          <t>{.class1IsEnd}</t>
+        </is>
+      </c>
+      <c r="P6" s="44" t="inlineStr">
+        <is>
+          <t>{.class1LhType}</t>
+        </is>
       </c>
       <c r="Q6" s="44" t="s">
         <v>67</v>
@@ -3806,11 +3842,15 @@
       <c r="V6" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" s="44" t="s">
-        <v>74</v>
+      <c r="W6" s="44" t="inlineStr">
+        <is>
+          <t>{.class2IsEnd}</t>
+        </is>
+      </c>
+      <c r="X6" s="44" t="inlineStr">
+        <is>
+          <t>{.class2LhType}</t>
+        </is>
       </c>
       <c r="Y6" s="44" t="s">
         <v>75</v>
@@ -3830,11 +3870,15 @@
       <c r="AD6" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="AE6" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF6" s="44" t="s">
-        <v>82</v>
+      <c r="AE6" s="44" t="inlineStr">
+        <is>
+          <t>{.class3IsEnd}</t>
+        </is>
+      </c>
+      <c r="AF6" s="44" t="inlineStr">
+        <is>
+          <t>{.class3LhType}</t>
+        </is>
       </c>
       <c r="AG6" s="44" t="s">
         <v>83</v>
@@ -3854,11 +3898,15 @@
       <c r="AL6" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="AM6" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN6" s="44" t="s">
-        <v>90</v>
+      <c r="AM6" s="44" t="inlineStr">
+        <is>
+          <t>{.class4IsEnd}</t>
+        </is>
+      </c>
+      <c r="AN6" s="44" t="inlineStr">
+        <is>
+          <t>{.class4LhType}</t>
+        </is>
       </c>
       <c r="AO6" s="44" t="s">
         <v>91</v>
@@ -3878,11 +3926,15 @@
       <c r="AT6" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="AU6" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV6" s="44" t="s">
-        <v>98</v>
+      <c r="AU6" s="44" t="inlineStr">
+        <is>
+          <t>{.class5IsEnd}</t>
+        </is>
+      </c>
+      <c r="AV6" s="44" t="inlineStr">
+        <is>
+          <t>{.class5LhType}</t>
+        </is>
       </c>
       <c r="AW6" s="44" t="s">
         <v>99</v>
@@ -3902,11 +3954,15 @@
       <c r="BB6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="BC6" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD6" s="44" t="s">
-        <v>106</v>
+      <c r="BC6" s="44" t="inlineStr">
+        <is>
+          <t>{.class6IsEnd}</t>
+        </is>
+      </c>
+      <c r="BD6" s="44" t="inlineStr">
+        <is>
+          <t>{.class6LhType}</t>
+        </is>
       </c>
       <c r="BE6" s="44" t="s">
         <v>107</v>
@@ -3926,11 +3982,15 @@
       <c r="BJ6" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="BK6" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="BL6" s="44" t="s">
-        <v>114</v>
+      <c r="BK6" s="44" t="inlineStr">
+        <is>
+          <t>{.class7IsEnd}</t>
+        </is>
+      </c>
+      <c r="BL6" s="44" t="inlineStr">
+        <is>
+          <t>{.class7LhType}</t>
+        </is>
       </c>
       <c r="BM6" s="44" t="s">
         <v>115</v>
@@ -3950,11 +4010,15 @@
       <c r="BR6" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="BS6" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT6" s="44" t="s">
-        <v>122</v>
+      <c r="BS6" s="44" t="inlineStr">
+        <is>
+          <t>{.class8IsEnd}</t>
+        </is>
+      </c>
+      <c r="BT6" s="44" t="inlineStr">
+        <is>
+          <t>{.class8LhType}</t>
+        </is>
       </c>
       <c r="BU6" s="44" t="s">
         <v>123</v>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A57891-6B1F-48BA-96DB-5C9034DD64E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254B4A9A-9748-458A-AD8F-B1BE36283C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12555" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -18,21 +18,35 @@
     <sheet name="排产小结" sheetId="34" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$3:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$4:$P$5</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="302">
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -54,6 +68,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -74,6 +89,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -94,6 +110,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -114,6 +131,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -134,6 +152,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -154,6 +173,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -174,6 +194,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -194,6 +215,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -214,6 +236,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -225,6 +248,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -243,6 +267,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -296,6 +321,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -314,6 +340,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate2}</t>
@@ -325,6 +352,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -343,6 +371,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate3}</t>
@@ -357,6 +386,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -375,6 +405,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate5}</t>
@@ -386,6 +417,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -404,6 +436,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate6}</t>
@@ -418,6 +451,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -436,6 +470,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate8}</t>
@@ -493,6 +528,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -502,7 +538,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -511,6 +547,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> l</t>
@@ -520,7 +557,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ầ</t>
     </r>
@@ -529,6 +566,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n s</t>
@@ -538,7 +576,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ử</t>
     </r>
@@ -547,6 +585,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> d</t>
@@ -556,7 +595,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ụ</t>
     </r>
@@ -565,6 +604,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng phao L/R</t>
@@ -618,6 +658,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -627,7 +668,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -636,6 +677,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ng </t>
@@ -645,7 +687,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -654,6 +696,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy TH</t>
@@ -711,12 +754,6 @@
     <t>{.class1LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class1Analysis}</t>
   </si>
   <si>
@@ -735,12 +772,6 @@
     <t>{.class2LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class2Analysis}</t>
   </si>
   <si>
@@ -759,12 +790,6 @@
     <t>{.class3LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class3Analysis}</t>
   </si>
   <si>
@@ -783,12 +808,6 @@
     <t>{.class4LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class4Analysis}</t>
   </si>
   <si>
@@ -807,12 +826,6 @@
     <t>{.class5LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class5Analysis}</t>
   </si>
   <si>
@@ -831,12 +844,6 @@
     <t>{.class6LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class6Analysis}</t>
   </si>
   <si>
@@ -855,12 +862,6 @@
     <t>{.class7LeftRightMould}</t>
   </si>
   <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
-  </si>
-  <si>
     <t>{.class7Analysis}</t>
   </si>
   <si>
@@ -877,12 +878,6 @@
   </si>
   <si>
     <t>{.class8LeftRightMould}</t>
-  </si>
-  <si>
-    <t>{.isEnd}</t>
-  </si>
-  <si>
-    <t>{.trialStatus}</t>
   </si>
   <si>
     <t>{.class8Analysis}</t>
@@ -990,6 +985,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Lo</t>
@@ -999,7 +995,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1008,6 +1004,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i ph</t>
@@ -1017,7 +1014,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -1026,6 +1023,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng th</t>
@@ -1035,7 +1033,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -1044,6 +1042,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1055,6 +1054,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Xu</t>
@@ -1064,7 +1064,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1073,6 +1073,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy theo th</t>
@@ -1082,7 +1083,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ờ</t>
     </r>
@@ -1091,6 +1092,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i gian</t>
@@ -1102,6 +1104,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1111,7 +1114,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1120,6 +1123,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh </t>
@@ -1129,7 +1133,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="238"/>
+        <family val="2"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1138,6 +1142,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">á </t>
@@ -1149,6 +1154,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1158,7 +1164,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1167,6 +1173,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh cát （VSC）</t>
@@ -1178,6 +1185,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Ch</t>
@@ -1187,7 +1195,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ỉ</t>
     </r>
@@ -1196,6 +1204,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> thay l</t>
@@ -1205,7 +1214,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ắ</t>
     </r>
@@ -1214,6 +1223,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1225,6 +1235,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã s</t>
@@ -1234,7 +1245,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="163"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1243,6 +1254,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> khuôn （MSK）</t>
@@ -1309,6 +1321,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca tr</t>
@@ -1318,6 +1331,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1327,6 +1341,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a </t>
@@ -1359,6 +1374,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>量试 Thử nghiệm số l</t>
@@ -1368,6 +1384,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1377,6 +1394,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng</t>
@@ -1409,6 +1427,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化计划
@@ -1430,6 +1449,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1441,6 +1461,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化开动
@@ -1451,6 +1472,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1460,6 +1482,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng máy l</t>
@@ -1469,6 +1492,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1478,6 +1502,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1556,12 +1581,6 @@
     <t>class1LeftRightMould</t>
   </si>
   <si>
-    <t>class1Type</t>
-  </si>
-  <si>
-    <t>class1MouldMethod</t>
-  </si>
-  <si>
     <t>class1Analysis</t>
   </si>
   <si>
@@ -1580,12 +1599,6 @@
     <t>class2LeftRightMould</t>
   </si>
   <si>
-    <t>class2Type</t>
-  </si>
-  <si>
-    <t>class2MouldMethod</t>
-  </si>
-  <si>
     <t>class2Analysis</t>
   </si>
   <si>
@@ -1604,12 +1617,6 @@
     <t>class3LeftRightMould</t>
   </si>
   <si>
-    <t>class3Type</t>
-  </si>
-  <si>
-    <t>class3MouldMethod</t>
-  </si>
-  <si>
     <t>class3Analysis</t>
   </si>
   <si>
@@ -1628,12 +1635,6 @@
     <t>class4LeftRightMould</t>
   </si>
   <si>
-    <t>class4Type</t>
-  </si>
-  <si>
-    <t>class4MouldMethod</t>
-  </si>
-  <si>
     <t>class4Analysis</t>
   </si>
   <si>
@@ -1652,12 +1653,6 @@
     <t>class5LeftRightMould</t>
   </si>
   <si>
-    <t>class5Type</t>
-  </si>
-  <si>
-    <t>class5MouldMethod</t>
-  </si>
-  <si>
     <t>class5Analysis</t>
   </si>
   <si>
@@ -1676,12 +1671,6 @@
     <t>class6LeftRightMould</t>
   </si>
   <si>
-    <t>class6Type</t>
-  </si>
-  <si>
-    <t>class6MouldMethod</t>
-  </si>
-  <si>
     <t>class6Analysis</t>
   </si>
   <si>
@@ -1700,12 +1689,6 @@
     <t>class7LeftRightMould</t>
   </si>
   <si>
-    <t>class7Type</t>
-  </si>
-  <si>
-    <t>class7MouldMethod</t>
-  </si>
-  <si>
     <t>class7Analysis</t>
   </si>
   <si>
@@ -1724,12 +1707,6 @@
     <t>class8LeftRightMould</t>
   </si>
   <si>
-    <t>class8Type</t>
-  </si>
-  <si>
-    <t>class8MouldMethod</t>
-  </si>
-  <si>
     <t>class8Analysis</t>
   </si>
   <si>
@@ -1755,6 +1732,150 @@
   </si>
   <si>
     <t>remark</t>
+  </si>
+  <si>
+    <t>class1IsEnd</t>
+  </si>
+  <si>
+    <t>class1LhType</t>
+  </si>
+  <si>
+    <t>class2IsEnd</t>
+  </si>
+  <si>
+    <t>class2LhType</t>
+  </si>
+  <si>
+    <t>class3IsEnd</t>
+  </si>
+  <si>
+    <t>class3LhType</t>
+  </si>
+  <si>
+    <t>class4IsEnd</t>
+  </si>
+  <si>
+    <t>class4LhType</t>
+  </si>
+  <si>
+    <t>class5IsEnd</t>
+  </si>
+  <si>
+    <t>class5LhType</t>
+  </si>
+  <si>
+    <t>class6IsEnd</t>
+  </si>
+  <si>
+    <t>class6LhType</t>
+  </si>
+  <si>
+    <t>class7IsEnd</t>
+  </si>
+  <si>
+    <t>class7LhType</t>
+  </si>
+  <si>
+    <t>class8IsEnd</t>
+  </si>
+  <si>
+    <t>class8LhType</t>
+  </si>
+  <si>
+    <t>{.class1IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class1LhType}</t>
+  </si>
+  <si>
+    <t>{.class2IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class2LhType}</t>
+  </si>
+  <si>
+    <t>{.class3IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class3LhType}</t>
+  </si>
+  <si>
+    <t>{.class4IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class4LhType}</t>
+  </si>
+  <si>
+    <t>{.class5IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class5LhType}</t>
+  </si>
+  <si>
+    <t>{.class6IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class6LhType}</t>
+  </si>
+  <si>
+    <t>{.class7IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class7LhType}</t>
+  </si>
+  <si>
+    <t>{.class8IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class8LhType}</t>
+  </si>
+  <si>
+    <t>{seq}</t>
+  </si>
+  <si>
+    <t>{planDate}</t>
+  </si>
+  <si>
+    <t>{classIndex}</t>
+  </si>
+  <si>
+    <t>{lhMachineCode}</t>
+  </si>
+  <si>
+    <t>{leftRightMould}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialCode}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialCode}</t>
+  </si>
+  <si>
+    <t>{afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{endType}</t>
+  </si>
+  <si>
+    <t>{isDryIceClean}</t>
+  </si>
+  <si>
+    <t>{isSandblastingClean}</t>
+  </si>
+  <si>
+    <t>{isReplaceBlock}</t>
+  </si>
+  <si>
+    <t>{mouldCode}</t>
+  </si>
+  <si>
+    <t>{remark}</t>
   </si>
 </sst>
 </file>
@@ -1763,15 +1884,15 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="m/d;@"/>
-    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="181" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="182" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="183" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="184" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="m/d;@"/>
+    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="179" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="180" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1780,18 +1901,21 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1799,52 +1923,61 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1852,6 +1985,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1862,6 +1996,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1869,6 +2004,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1876,7 +2012,7 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="163"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1895,12 +2031,13 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="Segoe UI"/>
-      <charset val="238"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1915,6 +2052,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1932,11 +2070,18 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -2143,15 +2288,15 @@
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2159,14 +2304,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2184,7 +2329,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
@@ -2193,25 +2338,25 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2226,7 +2371,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2247,25 +2392,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2292,17 +2437,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2313,15 +2479,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2367,10 +2524,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2520,13 +2677,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>51767</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>20706</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>279538</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>407495</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2884,318 +3041,286 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="9.625" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="8" width="5.625" customWidth="1"/>
-    <col min="9" max="9" width="6.125" customWidth="1"/>
-    <col min="10" max="10" width="5.625" customWidth="1"/>
-    <col min="11" max="11" width="3.125" customWidth="1"/>
-    <col min="12" max="18" width="5.125" customWidth="1"/>
-    <col min="19" max="19" width="3.125" customWidth="1"/>
-    <col min="20" max="26" width="5.125" customWidth="1"/>
-    <col min="27" max="27" width="3.125" customWidth="1"/>
-    <col min="28" max="34" width="5.125" customWidth="1"/>
-    <col min="35" max="35" width="3.125" customWidth="1"/>
-    <col min="36" max="42" width="5.125" customWidth="1"/>
-    <col min="43" max="43" width="3.125" customWidth="1"/>
-    <col min="44" max="50" width="5.125" customWidth="1"/>
-    <col min="51" max="51" width="3.125" customWidth="1"/>
-    <col min="52" max="58" width="5.125" customWidth="1"/>
-    <col min="59" max="59" width="3.125" customWidth="1"/>
-    <col min="60" max="66" width="5.125" customWidth="1"/>
-    <col min="67" max="67" width="3.125" customWidth="1"/>
-    <col min="68" max="74" width="5.125" customWidth="1"/>
-    <col min="75" max="77" width="5.625" customWidth="1"/>
-    <col min="78" max="78" width="9.625" customWidth="1"/>
-    <col min="79" max="79" width="7.625" customWidth="1"/>
-    <col min="80" max="80" width="9.625" customWidth="1"/>
-    <col min="81" max="81" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" customWidth="1"/>
+    <col min="3" max="3" width="32.59765625" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" customWidth="1"/>
+    <col min="5" max="5" width="32.59765625" customWidth="1"/>
+    <col min="6" max="6" width="17.09765625" customWidth="1"/>
+    <col min="7" max="8" width="5.59765625" customWidth="1"/>
+    <col min="9" max="9" width="6.09765625" customWidth="1"/>
+    <col min="10" max="10" width="5.59765625" customWidth="1"/>
+    <col min="11" max="11" width="3.09765625" customWidth="1"/>
+    <col min="12" max="18" width="5.09765625" customWidth="1"/>
+    <col min="19" max="19" width="3.09765625" customWidth="1"/>
+    <col min="20" max="26" width="5.09765625" customWidth="1"/>
+    <col min="27" max="27" width="3.09765625" customWidth="1"/>
+    <col min="28" max="34" width="5.09765625" customWidth="1"/>
+    <col min="35" max="35" width="3.09765625" customWidth="1"/>
+    <col min="36" max="42" width="5.09765625" customWidth="1"/>
+    <col min="43" max="43" width="3.09765625" customWidth="1"/>
+    <col min="44" max="50" width="5.09765625" customWidth="1"/>
+    <col min="51" max="51" width="3.09765625" customWidth="1"/>
+    <col min="52" max="58" width="5.09765625" customWidth="1"/>
+    <col min="59" max="59" width="3.09765625" customWidth="1"/>
+    <col min="60" max="66" width="5.09765625" customWidth="1"/>
+    <col min="67" max="67" width="3.09765625" customWidth="1"/>
+    <col min="68" max="74" width="5.09765625" customWidth="1"/>
+    <col min="75" max="77" width="5.59765625" customWidth="1"/>
+    <col min="78" max="78" width="9.59765625" customWidth="1"/>
+    <col min="79" max="79" width="7.59765625" customWidth="1"/>
+    <col min="80" max="80" width="9.59765625" customWidth="1"/>
+    <col min="81" max="81" width="25.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:81" hidden="1">
       <c r="A1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O1" t="s">
+        <v>254</v>
+      </c>
+      <c r="P1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>203</v>
+      </c>
+      <c r="R1" t="s">
+        <v>204</v>
+      </c>
+      <c r="S1" t="s">
         <v>205</v>
       </c>
-      <c r="B1" t="s">
+      <c r="T1" t="s">
         <v>206</v>
       </c>
-      <c r="C1" t="s">
+      <c r="U1" t="s">
         <v>207</v>
       </c>
-      <c r="D1" t="s">
+      <c r="V1" t="s">
         <v>208</v>
       </c>
-      <c r="E1" t="s">
+      <c r="W1" t="s">
+        <v>256</v>
+      </c>
+      <c r="X1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y1" t="s">
         <v>209</v>
       </c>
-      <c r="F1" t="s">
+      <c r="Z1" t="s">
         <v>210</v>
       </c>
-      <c r="G1" t="s">
+      <c r="AA1" t="s">
         <v>211</v>
       </c>
-      <c r="H1" t="s">
+      <c r="AB1" t="s">
         <v>212</v>
       </c>
-      <c r="I1" t="s">
+      <c r="AC1" t="s">
         <v>213</v>
       </c>
-      <c r="J1" t="s">
+      <c r="AD1" t="s">
         <v>214</v>
       </c>
-      <c r="K1" t="s">
+      <c r="AE1" t="s">
+        <v>258</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AG1" t="s">
         <v>215</v>
       </c>
-      <c r="L1" t="s">
+      <c r="AH1" t="s">
         <v>216</v>
       </c>
-      <c r="M1" t="s">
+      <c r="AI1" t="s">
         <v>217</v>
       </c>
-      <c r="N1" t="s">
+      <c r="AJ1" t="s">
         <v>218</v>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>class1IsEnd</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>class1LhType</t>
-        </is>
-      </c>
-      <c r="Q1" t="s">
+      <c r="AK1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>261</v>
+      </c>
+      <c r="AO1" t="s">
         <v>221</v>
       </c>
-      <c r="R1" t="s">
+      <c r="AP1" t="s">
         <v>222</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AQ1" t="s">
         <v>223</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AR1" t="s">
         <v>224</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AS1" t="s">
         <v>225</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AT1" t="s">
         <v>226</v>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>class2IsEnd</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>class2LhType</t>
-        </is>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AU1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>263</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AY1" t="s">
         <v>229</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AZ1" t="s">
         <v>230</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="BA1" t="s">
         <v>231</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="BB1" t="s">
         <v>232</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="BC1" t="s">
+        <v>264</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>265</v>
+      </c>
+      <c r="BE1" t="s">
         <v>233</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="BF1" t="s">
         <v>234</v>
       </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>class3IsEnd</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>class3LhType</t>
-        </is>
-      </c>
-      <c r="AG1" t="s">
+      <c r="BG1" t="s">
+        <v>235</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>236</v>
+      </c>
+      <c r="BI1" t="s">
         <v>237</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="BJ1" t="s">
         <v>238</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="BK1" t="s">
+        <v>266</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>267</v>
+      </c>
+      <c r="BM1" t="s">
         <v>239</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="BN1" t="s">
         <v>240</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="BO1" t="s">
         <v>241</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="BP1" t="s">
         <v>242</v>
       </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>class4IsEnd</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>class4LhType</t>
-        </is>
-      </c>
-      <c r="AO1" t="s">
+      <c r="BQ1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>268</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>269</v>
+      </c>
+      <c r="BU1" t="s">
         <v>245</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BV1" t="s">
         <v>246</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BW1" t="s">
         <v>247</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BX1" t="s">
         <v>248</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BY1" t="s">
         <v>249</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BZ1" t="s">
         <v>250</v>
       </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>class5IsEnd</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>class5LhType</t>
-        </is>
-      </c>
-      <c r="AW1" t="s">
+      <c r="CA1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CC1" t="s">
         <v>253</v>
       </c>
-      <c r="AX1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>256</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>257</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>258</v>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>class6IsEnd</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>class6LhType</t>
-        </is>
-      </c>
-      <c r="BE1" t="s">
-        <v>261</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>262</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>263</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>264</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>265</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>266</v>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>class7IsEnd</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>class7LhType</t>
-        </is>
-      </c>
-      <c r="BM1" t="s">
-        <v>269</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>270</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>271</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>272</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>273</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>class8IsEnd</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>class8LhType</t>
-        </is>
-      </c>
-      <c r="BU1" t="s">
-        <v>277</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>278</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>279</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>280</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>281</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>282</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>283</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>284</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>285</v>
-      </c>
     </row>
-    <row r="2" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:81" ht="16.95" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24" t="s">
@@ -3282,7 +3407,7 @@
       <c r="CB2" s="27"/>
       <c r="CC2" s="2"/>
     </row>
-    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:81" ht="16.95" customHeight="1">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3395,7 +3520,7 @@
       <c r="CB3" s="31"/>
       <c r="CC3" s="31"/>
     </row>
-    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:81" ht="34.200000000000003">
       <c r="A4" s="35" t="s">
         <v>3</v>
       </c>
@@ -3426,90 +3551,90 @@
       <c r="J4" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="47" t="s">
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="49" t="s">
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="49"/>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49" t="s">
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="56"/>
+      <c r="AI4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
-      <c r="AL4" s="49"/>
-      <c r="AM4" s="49"/>
-      <c r="AN4" s="49"/>
-      <c r="AO4" s="49"/>
-      <c r="AP4" s="49"/>
-      <c r="AQ4" s="49" t="s">
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="56"/>
+      <c r="AL4" s="56"/>
+      <c r="AM4" s="56"/>
+      <c r="AN4" s="56"/>
+      <c r="AO4" s="56"/>
+      <c r="AP4" s="56"/>
+      <c r="AQ4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="AR4" s="49"/>
-      <c r="AS4" s="49"/>
-      <c r="AT4" s="49"/>
-      <c r="AU4" s="49"/>
-      <c r="AV4" s="49"/>
-      <c r="AW4" s="49"/>
-      <c r="AX4" s="49"/>
-      <c r="AY4" s="50" t="s">
+      <c r="AR4" s="56"/>
+      <c r="AS4" s="56"/>
+      <c r="AT4" s="56"/>
+      <c r="AU4" s="56"/>
+      <c r="AV4" s="56"/>
+      <c r="AW4" s="56"/>
+      <c r="AX4" s="56"/>
+      <c r="AY4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="AZ4" s="50"/>
-      <c r="BA4" s="50"/>
-      <c r="BB4" s="50"/>
-      <c r="BC4" s="50"/>
-      <c r="BD4" s="50"/>
-      <c r="BE4" s="50"/>
-      <c r="BF4" s="50"/>
-      <c r="BG4" s="50" t="s">
+      <c r="AZ4" s="51"/>
+      <c r="BA4" s="51"/>
+      <c r="BB4" s="51"/>
+      <c r="BC4" s="51"/>
+      <c r="BD4" s="51"/>
+      <c r="BE4" s="51"/>
+      <c r="BF4" s="51"/>
+      <c r="BG4" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="BH4" s="50"/>
-      <c r="BI4" s="50"/>
-      <c r="BJ4" s="50"/>
-      <c r="BK4" s="50"/>
-      <c r="BL4" s="50"/>
-      <c r="BM4" s="50"/>
-      <c r="BN4" s="50"/>
-      <c r="BO4" s="50" t="s">
+      <c r="BH4" s="51"/>
+      <c r="BI4" s="51"/>
+      <c r="BJ4" s="51"/>
+      <c r="BK4" s="51"/>
+      <c r="BL4" s="51"/>
+      <c r="BM4" s="51"/>
+      <c r="BN4" s="51"/>
+      <c r="BO4" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="BP4" s="50"/>
-      <c r="BQ4" s="50"/>
-      <c r="BR4" s="50"/>
-      <c r="BS4" s="50"/>
-      <c r="BT4" s="50"/>
-      <c r="BU4" s="50"/>
-      <c r="BV4" s="50"/>
-      <c r="BW4" s="51" t="s">
+      <c r="BP4" s="51"/>
+      <c r="BQ4" s="51"/>
+      <c r="BR4" s="51"/>
+      <c r="BS4" s="51"/>
+      <c r="BT4" s="51"/>
+      <c r="BU4" s="51"/>
+      <c r="BV4" s="51"/>
+      <c r="BW4" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="BX4" s="52"/>
+      <c r="BX4" s="53"/>
       <c r="BY4" s="35" t="s">
         <v>22</v>
       </c>
@@ -3526,7 +3651,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:81" ht="46.8">
       <c r="A5" s="38" t="s">
         <v>27</v>
       </c>
@@ -3771,7 +3896,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
@@ -3814,238 +3939,206 @@
       <c r="N6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="44" t="inlineStr">
-        <is>
-          <t>{.class1IsEnd}</t>
-        </is>
-      </c>
-      <c r="P6" s="44" t="inlineStr">
-        <is>
-          <t>{.class1LhType}</t>
-        </is>
+      <c r="O6" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="P6" s="44" t="s">
+        <v>271</v>
       </c>
       <c r="Q6" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="R6" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="44" t="s">
+      <c r="T6" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="U6" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="T6" s="44" t="s">
+      <c r="V6" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="W6" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="X6" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y6" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="V6" s="44" t="s">
+      <c r="Z6" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="W6" s="44" t="inlineStr">
-        <is>
-          <t>{.class2IsEnd}</t>
-        </is>
-      </c>
-      <c r="X6" s="44" t="inlineStr">
-        <is>
-          <t>{.class2LhType}</t>
-        </is>
-      </c>
-      <c r="Y6" s="44" t="s">
+      <c r="AA6" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB6" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="Z6" s="44" t="s">
+      <c r="AD6" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="AA6" s="44" t="s">
+      <c r="AE6" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="AF6" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="AG6" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="AB6" s="44" t="s">
+      <c r="AH6" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="AC6" s="44" t="s">
+      <c r="AI6" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AJ6" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="AE6" s="44" t="inlineStr">
-        <is>
-          <t>{.class3IsEnd}</t>
-        </is>
-      </c>
-      <c r="AF6" s="44" t="inlineStr">
-        <is>
-          <t>{.class3LhType}</t>
-        </is>
-      </c>
-      <c r="AG6" s="44" t="s">
+      <c r="AK6" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL6" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM6" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="AN6" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="AO6" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="AH6" s="44" t="s">
+      <c r="AP6" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="AI6" s="44" t="s">
+      <c r="AQ6" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="AR6" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="AK6" s="44" t="s">
+      <c r="AS6" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AT6" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="AM6" s="44" t="inlineStr">
-        <is>
-          <t>{.class4IsEnd}</t>
-        </is>
-      </c>
-      <c r="AN6" s="44" t="inlineStr">
-        <is>
-          <t>{.class4LhType}</t>
-        </is>
-      </c>
-      <c r="AO6" s="44" t="s">
+      <c r="AU6" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="AV6" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="AW6" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX6" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY6" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="AP6" s="44" t="s">
+      <c r="AZ6" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="AQ6" s="44" t="s">
+      <c r="BA6" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="AR6" s="44" t="s">
+      <c r="BB6" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="AS6" s="44" t="s">
+      <c r="BC6" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="BD6" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="BE6" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="AT6" s="44" t="s">
+      <c r="BF6" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="AU6" s="44" t="inlineStr">
-        <is>
-          <t>{.class5IsEnd}</t>
-        </is>
-      </c>
-      <c r="AV6" s="44" t="inlineStr">
-        <is>
-          <t>{.class5LhType}</t>
-        </is>
-      </c>
-      <c r="AW6" s="44" t="s">
+      <c r="BG6" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH6" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="BI6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="AX6" s="44" t="s">
+      <c r="BJ6" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="AY6" s="44" t="s">
+      <c r="BK6" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="BL6" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="BM6" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="AZ6" s="44" t="s">
+      <c r="BN6" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="BA6" s="44" t="s">
+      <c r="BO6" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="BB6" s="44" t="s">
+      <c r="BP6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="BC6" s="44" t="inlineStr">
-        <is>
-          <t>{.class6IsEnd}</t>
-        </is>
-      </c>
-      <c r="BD6" s="44" t="inlineStr">
-        <is>
-          <t>{.class6LhType}</t>
-        </is>
-      </c>
-      <c r="BE6" s="44" t="s">
+      <c r="BQ6" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="BR6" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="BS6" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="BT6" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="BU6" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="BF6" s="44" t="s">
+      <c r="BV6" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="BG6" s="44" t="s">
+      <c r="BW6" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="BH6" s="44" t="s">
+      <c r="BX6" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="BI6" s="44" t="s">
+      <c r="BY6" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="BJ6" s="44" t="s">
+      <c r="BZ6" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="BK6" s="44" t="inlineStr">
-        <is>
-          <t>{.class7IsEnd}</t>
-        </is>
-      </c>
-      <c r="BL6" s="44" t="inlineStr">
-        <is>
-          <t>{.class7LhType}</t>
-        </is>
-      </c>
-      <c r="BM6" s="44" t="s">
+      <c r="CA6" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="CB6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="CC6" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="BN6" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="BO6" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="BP6" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="BQ6" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR6" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="BS6" s="44" t="inlineStr">
-        <is>
-          <t>{.class8IsEnd}</t>
-        </is>
-      </c>
-      <c r="BT6" s="44" t="inlineStr">
-        <is>
-          <t>{.class8LhType}</t>
-        </is>
-      </c>
-      <c r="BU6" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="BV6" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="BW6" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="BX6" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="BY6" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="BZ6" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="CA6" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC6" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -4080,197 +4173,247 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="3" style="8" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="8" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="8" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="11" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="11" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="10" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" style="9" customWidth="1"/>
+    <col min="3" max="4" width="5.59765625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="34.09765625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="34.09765625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="11" customWidth="1"/>
+    <col min="11" max="11" width="5.69921875" style="11" customWidth="1"/>
+    <col min="12" max="14" width="5.69921875" style="10" customWidth="1"/>
+    <col min="15" max="15" width="27.3984375" style="10" customWidth="1"/>
     <col min="16" max="16" width="9" style="10" customWidth="1"/>
     <col min="17" max="16384" width="8" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14" t="s">
+    <row r="1" spans="1:16" s="49" customFormat="1" hidden="1">
+      <c r="A1" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="L1" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="M1" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="N1" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="O1" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="P1" s="49" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="33.75" customHeight="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="16"/>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="34.200000000000003" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1">
+      <c r="A4" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="16"/>
+      <c r="D4" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" s="7" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="N2" s="17" t="s">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="P2" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
+      <c r="C5" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="D5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="F5" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="G5" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="I5" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="J5" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="K5" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="L5" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="M5" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="N5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="O5" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="N3" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="K4" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="O4" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>131</v>
+      <c r="P5" s="19" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4284,127 +4427,127 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
-    <col min="2" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.75" style="1"/>
+    <col min="1" max="1" width="18.09765625" style="1" customWidth="1"/>
+    <col min="2" max="5" width="15.59765625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+    <row r="1" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A1" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
-        <v>175</v>
+    <row r="2" spans="1:6" ht="25.2" customHeight="1">
+      <c r="A2" s="68" t="s">
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="65"/>
+    <row r="3" spans="1:6" ht="25.2" customHeight="1">
+      <c r="A3" s="69"/>
       <c r="B3" s="4" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="58"/>
+        <v>168</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="58"/>
+        <v>170</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="58"/>
+        <v>172</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="90" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62"/>
+        <v>175</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64" t="s">
-        <v>193</v>
+    <row r="8" spans="1:6" ht="25.2" customHeight="1">
+      <c r="A8" s="68" t="s">
+        <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="65"/>
+    <row r="9" spans="1:6" ht="25.2" customHeight="1">
+      <c r="A9" s="69"/>
       <c r="B9" s="4">
         <f>硫化日计划!AB3</f>
         <v>0</v>
@@ -4423,9 +4566,9 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="25.2" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="B10" s="4">
         <f>COUNTA(硫化日计划!$AB$6:AB1048576)</f>
@@ -4445,56 +4588,56 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58"/>
+        <v>179</v>
+      </c>
+      <c r="B11" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="59" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58"/>
+        <v>182</v>
+      </c>
+      <c r="B12" s="73"/>
+      <c r="C12" s="63" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="E12" s="62"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66" t="s">
-        <v>200</v>
+    <row r="13" spans="1:6" ht="30" customHeight="1">
+      <c r="A13" s="70" t="s">
+        <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+        <v>185</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="67"/>
+    <row r="14" spans="1:6" ht="30" customHeight="1">
+      <c r="A14" s="71"/>
       <c r="B14" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+        <v>187</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
       <c r="F14" s="2"/>
     </row>
   </sheetData>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254B4A9A-9748-458A-AD8F-B1BE36283C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF42815-C897-43F9-AFA7-031E0BD44769}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,19 +22,6 @@
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1892,7 +1879,7 @@
     <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -2479,6 +2466,36 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2491,15 +2508,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2508,27 +2516,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -3041,41 +3028,41 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" customWidth="1"/>
-    <col min="3" max="3" width="32.59765625" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
-    <col min="5" max="5" width="32.59765625" customWidth="1"/>
-    <col min="6" max="6" width="17.09765625" customWidth="1"/>
-    <col min="7" max="8" width="5.59765625" customWidth="1"/>
-    <col min="9" max="9" width="6.09765625" customWidth="1"/>
-    <col min="10" max="10" width="5.59765625" customWidth="1"/>
-    <col min="11" max="11" width="3.09765625" customWidth="1"/>
-    <col min="12" max="18" width="5.09765625" customWidth="1"/>
-    <col min="19" max="19" width="3.09765625" customWidth="1"/>
-    <col min="20" max="26" width="5.09765625" customWidth="1"/>
-    <col min="27" max="27" width="3.09765625" customWidth="1"/>
-    <col min="28" max="34" width="5.09765625" customWidth="1"/>
-    <col min="35" max="35" width="3.09765625" customWidth="1"/>
-    <col min="36" max="42" width="5.09765625" customWidth="1"/>
-    <col min="43" max="43" width="3.09765625" customWidth="1"/>
-    <col min="44" max="50" width="5.09765625" customWidth="1"/>
-    <col min="51" max="51" width="3.09765625" customWidth="1"/>
-    <col min="52" max="58" width="5.09765625" customWidth="1"/>
-    <col min="59" max="59" width="3.09765625" customWidth="1"/>
-    <col min="60" max="66" width="5.09765625" customWidth="1"/>
-    <col min="67" max="67" width="3.09765625" customWidth="1"/>
-    <col min="68" max="74" width="5.09765625" customWidth="1"/>
-    <col min="75" max="77" width="5.59765625" customWidth="1"/>
-    <col min="78" max="78" width="9.59765625" customWidth="1"/>
-    <col min="79" max="79" width="7.59765625" customWidth="1"/>
-    <col min="80" max="80" width="9.59765625" customWidth="1"/>
-    <col min="81" max="81" width="25.69921875" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="8" width="5.625" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="10" width="5.625" customWidth="1"/>
+    <col min="11" max="11" width="3.125" customWidth="1"/>
+    <col min="12" max="18" width="5.125" customWidth="1"/>
+    <col min="19" max="19" width="3.125" customWidth="1"/>
+    <col min="20" max="26" width="5.125" customWidth="1"/>
+    <col min="27" max="27" width="3.125" customWidth="1"/>
+    <col min="28" max="34" width="5.125" customWidth="1"/>
+    <col min="35" max="35" width="3.125" customWidth="1"/>
+    <col min="36" max="42" width="5.125" customWidth="1"/>
+    <col min="43" max="43" width="3.125" customWidth="1"/>
+    <col min="44" max="50" width="5.125" customWidth="1"/>
+    <col min="51" max="51" width="3.125" customWidth="1"/>
+    <col min="52" max="58" width="5.125" customWidth="1"/>
+    <col min="59" max="59" width="3.125" customWidth="1"/>
+    <col min="60" max="66" width="5.125" customWidth="1"/>
+    <col min="67" max="67" width="3.125" customWidth="1"/>
+    <col min="68" max="74" width="5.125" customWidth="1"/>
+    <col min="75" max="77" width="5.625" customWidth="1"/>
+    <col min="78" max="78" width="9.625" customWidth="1"/>
+    <col min="79" max="79" width="7.625" customWidth="1"/>
+    <col min="80" max="80" width="9.625" customWidth="1"/>
+    <col min="81" max="81" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1">
+    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>189</v>
       </c>
@@ -3320,7 +3307,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="16.95" customHeight="1">
+    <row r="2" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24" t="s">
@@ -3407,7 +3394,7 @@
       <c r="CB2" s="27"/>
       <c r="CC2" s="2"/>
     </row>
-    <row r="3" spans="1:81" ht="16.95" customHeight="1">
+    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -3422,6 +3409,7 @@
       <c r="J3" s="31"/>
       <c r="K3" s="29"/>
       <c r="L3" s="29">
+        <f>SUM(L6:L108139)</f>
         <v>0</v>
       </c>
       <c r="M3" s="29"/>
@@ -3432,6 +3420,7 @@
       <c r="R3" s="28"/>
       <c r="S3" s="32"/>
       <c r="T3" s="28">
+        <f>SUM(T6:T108139)</f>
         <v>0</v>
       </c>
       <c r="U3" s="28"/>
@@ -3520,7 +3509,7 @@
       <c r="CB3" s="31"/>
       <c r="CC3" s="31"/>
     </row>
-    <row r="4" spans="1:81" ht="34.200000000000003">
+    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
       <c r="A4" s="35" t="s">
         <v>3</v>
       </c>
@@ -3651,7 +3640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="46.8">
+    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
       <c r="A5" s="38" t="s">
         <v>27</v>
       </c>
@@ -3896,7 +3885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1">
+    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
@@ -4174,25 +4163,25 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="8" customWidth="1"/>
-    <col min="2" max="2" width="8.8984375" style="9" customWidth="1"/>
-    <col min="3" max="4" width="5.59765625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="4.69921875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="34.09765625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="34.09765625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="8.69921875" style="11" customWidth="1"/>
-    <col min="11" max="11" width="5.69921875" style="11" customWidth="1"/>
-    <col min="12" max="14" width="5.69921875" style="10" customWidth="1"/>
-    <col min="15" max="15" width="27.3984375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="8" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="8" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="11" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="11" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="10" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="10" customWidth="1"/>
     <col min="16" max="16" width="9" style="10" customWidth="1"/>
     <col min="17" max="16384" width="8" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="49" customFormat="1" hidden="1">
+    <row r="1" spans="1:16" s="49" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" s="47" t="s">
         <v>286</v>
       </c>
@@ -4242,7 +4231,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -4262,7 +4251,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
     </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="17" t="s">
         <v>117</v>
       </c>
@@ -4312,7 +4301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1">
+    <row r="4" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
         <v>130</v>
       </c>
@@ -4362,7 +4351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="19" t="s">
         <v>144</v>
       </c>
@@ -4427,25 +4416,25 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.09765625" style="1" customWidth="1"/>
-    <col min="2" max="5" width="15.59765625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.69921875" style="1"/>
+    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A2" s="68" t="s">
+    <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="61" t="s">
         <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4462,8 +4451,8 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A3" s="69"/>
+    <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="62"/>
       <c r="B3" s="4" t="s">
         <v>164</v>
       </c>
@@ -4478,58 +4467,58 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1">
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="59"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="59"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="90" customHeight="1">
+    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="66"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="73"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A8" s="68" t="s">
+    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="61" t="s">
         <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4546,8 +4535,8 @@
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A9" s="69"/>
+    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="62"/>
       <c r="B9" s="4">
         <f>硫化日计划!AB3</f>
         <v>0</v>
@@ -4566,7 +4555,7 @@
       </c>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="25.2" customHeight="1">
+    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>178</v>
       </c>
@@ -4588,60 +4577,65 @@
       </c>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1">
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="62"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="59"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1">
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="73"/>
-      <c r="C12" s="63" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="62"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="59"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="70" t="s">
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="63" t="s">
         <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1">
-      <c r="A14" s="71"/>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="64"/>
       <c r="B14" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
       <c r="F14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
@@ -4650,11 +4644,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF42815-C897-43F9-AFA7-031E0BD44769}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521EA153-F773-4323-88B9-387A0BFC6CA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2298,7 +2298,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2367,12 +2367,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2466,14 +2460,35 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2496,26 +2511,8 @@
     <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -3307,23 +3304,23 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:81" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="24" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="27"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -3361,7 +3358,7 @@
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
-      <c r="AX2" s="27"/>
+      <c r="AX2" s="25"/>
       <c r="AY2" s="2"/>
       <c r="AZ2" s="2"/>
       <c r="BA2" s="2"/>
@@ -3390,498 +3387,498 @@
       <c r="BX2" s="2"/>
       <c r="BY2" s="2"/>
       <c r="BZ2" s="2"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
+      <c r="CA2" s="25"/>
+      <c r="CB2" s="25"/>
       <c r="CC2" s="2"/>
     </row>
     <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29">
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27">
         <f>SUM(L6:L108139)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="28">
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="26">
         <f>SUM(T6:T108139)</f>
         <v>0</v>
       </c>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28">
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="26"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26">
         <f>SUM(AB6:AB108139)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="28"/>
-      <c r="AJ3" s="28">
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="26"/>
+      <c r="AG3" s="26"/>
+      <c r="AH3" s="30"/>
+      <c r="AI3" s="26"/>
+      <c r="AJ3" s="26">
         <f>SUM(AJ6:AJ108139)</f>
         <v>0</v>
       </c>
-      <c r="AK3" s="28"/>
-      <c r="AL3" s="28"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="28"/>
-      <c r="AO3" s="28"/>
-      <c r="AP3" s="28"/>
-      <c r="AQ3" s="28"/>
-      <c r="AR3" s="32">
+      <c r="AK3" s="26"/>
+      <c r="AL3" s="26"/>
+      <c r="AM3" s="30"/>
+      <c r="AN3" s="26"/>
+      <c r="AO3" s="26"/>
+      <c r="AP3" s="26"/>
+      <c r="AQ3" s="26"/>
+      <c r="AR3" s="30">
         <f>SUM(AR6:AR108139)</f>
         <v>0</v>
       </c>
-      <c r="AS3" s="28"/>
-      <c r="AT3" s="28"/>
-      <c r="AU3" s="28"/>
-      <c r="AV3" s="28"/>
-      <c r="AW3" s="32"/>
-      <c r="AX3" s="28"/>
-      <c r="AY3" s="28"/>
-      <c r="AZ3" s="28">
+      <c r="AS3" s="26"/>
+      <c r="AT3" s="26"/>
+      <c r="AU3" s="26"/>
+      <c r="AV3" s="26"/>
+      <c r="AW3" s="30"/>
+      <c r="AX3" s="26"/>
+      <c r="AY3" s="26"/>
+      <c r="AZ3" s="26">
         <f>SUM(AZ6:AZ108139)</f>
         <v>0</v>
       </c>
-      <c r="BA3" s="28"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="31"/>
-      <c r="BG3" s="33"/>
-      <c r="BH3" s="28">
+      <c r="BA3" s="26"/>
+      <c r="BB3" s="30"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="29"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="26">
         <f>SUM(BH6:BH108139)</f>
         <v>0</v>
       </c>
-      <c r="BI3" s="31"/>
-      <c r="BJ3" s="31"/>
-      <c r="BK3" s="31"/>
-      <c r="BL3" s="31"/>
-      <c r="BM3" s="31"/>
-      <c r="BN3" s="31"/>
-      <c r="BO3" s="31"/>
-      <c r="BP3" s="28">
+      <c r="BI3" s="29"/>
+      <c r="BJ3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="29"/>
+      <c r="BM3" s="29"/>
+      <c r="BN3" s="29"/>
+      <c r="BO3" s="29"/>
+      <c r="BP3" s="26">
         <f>SUM(BP6:BP108139)</f>
         <v>0</v>
       </c>
-      <c r="BQ3" s="31"/>
-      <c r="BR3" s="31"/>
-      <c r="BS3" s="31"/>
-      <c r="BT3" s="31"/>
-      <c r="BU3" s="31"/>
-      <c r="BV3" s="31"/>
-      <c r="BW3" s="28">
+      <c r="BQ3" s="29"/>
+      <c r="BR3" s="29"/>
+      <c r="BS3" s="29"/>
+      <c r="BT3" s="29"/>
+      <c r="BU3" s="29"/>
+      <c r="BV3" s="29"/>
+      <c r="BW3" s="26">
         <f>SUM(BW6:BW108139)</f>
         <v>0</v>
       </c>
-      <c r="BX3" s="31"/>
-      <c r="BY3" s="28">
+      <c r="BX3" s="29"/>
+      <c r="BY3" s="26">
         <f>SUM(BY6:BY108139)</f>
         <v>0</v>
       </c>
-      <c r="BZ3" s="34"/>
-      <c r="CA3" s="31"/>
-      <c r="CB3" s="31"/>
-      <c r="CC3" s="31"/>
+      <c r="BZ3" s="32"/>
+      <c r="CA3" s="29"/>
+      <c r="CB3" s="29"/>
+      <c r="CC3" s="29"/>
     </row>
     <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="54" t="s">
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="56" t="s">
+      <c r="T4" s="53"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="56" t="s">
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="54"/>
+      <c r="AI4" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="56"/>
-      <c r="AL4" s="56"/>
-      <c r="AM4" s="56"/>
-      <c r="AN4" s="56"/>
-      <c r="AO4" s="56"/>
-      <c r="AP4" s="56"/>
-      <c r="AQ4" s="56" t="s">
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="54"/>
+      <c r="AL4" s="54"/>
+      <c r="AM4" s="54"/>
+      <c r="AN4" s="54"/>
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="54"/>
+      <c r="AQ4" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="AR4" s="56"/>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="56"/>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="56"/>
-      <c r="AW4" s="56"/>
-      <c r="AX4" s="56"/>
-      <c r="AY4" s="51" t="s">
+      <c r="AR4" s="54"/>
+      <c r="AS4" s="54"/>
+      <c r="AT4" s="54"/>
+      <c r="AU4" s="54"/>
+      <c r="AV4" s="54"/>
+      <c r="AW4" s="54"/>
+      <c r="AX4" s="54"/>
+      <c r="AY4" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="AZ4" s="51"/>
-      <c r="BA4" s="51"/>
-      <c r="BB4" s="51"/>
-      <c r="BC4" s="51"/>
-      <c r="BD4" s="51"/>
-      <c r="BE4" s="51"/>
-      <c r="BF4" s="51"/>
-      <c r="BG4" s="51" t="s">
+      <c r="AZ4" s="49"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="49"/>
+      <c r="BD4" s="49"/>
+      <c r="BE4" s="49"/>
+      <c r="BF4" s="49"/>
+      <c r="BG4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="BH4" s="51"/>
-      <c r="BI4" s="51"/>
-      <c r="BJ4" s="51"/>
-      <c r="BK4" s="51"/>
-      <c r="BL4" s="51"/>
-      <c r="BM4" s="51"/>
-      <c r="BN4" s="51"/>
-      <c r="BO4" s="51" t="s">
+      <c r="BH4" s="49"/>
+      <c r="BI4" s="49"/>
+      <c r="BJ4" s="49"/>
+      <c r="BK4" s="49"/>
+      <c r="BL4" s="49"/>
+      <c r="BM4" s="49"/>
+      <c r="BN4" s="49"/>
+      <c r="BO4" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="BP4" s="51"/>
-      <c r="BQ4" s="51"/>
-      <c r="BR4" s="51"/>
-      <c r="BS4" s="51"/>
-      <c r="BT4" s="51"/>
-      <c r="BU4" s="51"/>
-      <c r="BV4" s="51"/>
-      <c r="BW4" s="52" t="s">
+      <c r="BP4" s="49"/>
+      <c r="BQ4" s="49"/>
+      <c r="BR4" s="49"/>
+      <c r="BS4" s="49"/>
+      <c r="BT4" s="49"/>
+      <c r="BU4" s="49"/>
+      <c r="BV4" s="49"/>
+      <c r="BW4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="BX4" s="53"/>
-      <c r="BY4" s="35" t="s">
+      <c r="BX4" s="51"/>
+      <c r="BY4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="BZ4" s="35" t="s">
+      <c r="BZ4" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="CA4" s="35" t="s">
+      <c r="CA4" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="CB4" s="35" t="s">
+      <c r="CB4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="CC4" s="35" t="s">
+      <c r="CC4" s="33" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="L5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="M5" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="36" t="s">
+      <c r="R5" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="36" t="s">
+      <c r="S5" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="36" t="s">
+      <c r="T5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="U5" s="36" t="s">
+      <c r="U5" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="V5" s="36" t="s">
+      <c r="V5" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="W5" s="36" t="s">
+      <c r="W5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="X5" s="36" t="s">
+      <c r="X5" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="Y5" s="36" t="s">
+      <c r="Y5" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" s="36" t="s">
+      <c r="Z5" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="AA5" s="39" t="s">
+      <c r="AA5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AB5" s="39" t="s">
+      <c r="AB5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="AC5" s="39" t="s">
+      <c r="AC5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="AD5" s="39" t="s">
+      <c r="AD5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" s="39" t="s">
+      <c r="AE5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="AF5" s="39" t="s">
+      <c r="AF5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="AG5" s="39" t="s">
+      <c r="AG5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="AH5" s="39" t="s">
+      <c r="AH5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="AI5" s="39" t="s">
+      <c r="AI5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AJ5" s="39" t="s">
+      <c r="AJ5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="AK5" s="39" t="s">
+      <c r="AK5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="AL5" s="39" t="s">
+      <c r="AL5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="AM5" s="39" t="s">
+      <c r="AM5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="AN5" s="39" t="s">
+      <c r="AN5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="AO5" s="39" t="s">
+      <c r="AO5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="AP5" s="39" t="s">
+      <c r="AP5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="AQ5" s="39" t="s">
+      <c r="AQ5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AR5" s="39" t="s">
+      <c r="AR5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="AS5" s="39" t="s">
+      <c r="AS5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="AT5" s="39" t="s">
+      <c r="AT5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="AU5" s="39" t="s">
+      <c r="AU5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="AV5" s="39" t="s">
+      <c r="AV5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="AW5" s="39" t="s">
+      <c r="AW5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="AX5" s="39" t="s">
+      <c r="AX5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="AY5" s="40" t="s">
+      <c r="AY5" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="AZ5" s="40" t="s">
+      <c r="AZ5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="BA5" s="40" t="s">
+      <c r="BA5" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="BB5" s="40" t="s">
+      <c r="BB5" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="BC5" s="40" t="s">
+      <c r="BC5" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="BD5" s="40" t="s">
+      <c r="BD5" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="BE5" s="40" t="s">
+      <c r="BE5" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="BF5" s="40" t="s">
+      <c r="BF5" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="BG5" s="40" t="s">
+      <c r="BG5" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="BH5" s="40" t="s">
+      <c r="BH5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="BI5" s="40" t="s">
+      <c r="BI5" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="BJ5" s="40" t="s">
+      <c r="BJ5" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="BK5" s="40" t="s">
+      <c r="BK5" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="BL5" s="40" t="s">
+      <c r="BL5" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="BM5" s="40" t="s">
+      <c r="BM5" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="BN5" s="40" t="s">
+      <c r="BN5" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="BO5" s="40" t="s">
+      <c r="BO5" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="BP5" s="40" t="s">
+      <c r="BP5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="BQ5" s="40" t="s">
+      <c r="BQ5" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="BR5" s="40" t="s">
+      <c r="BR5" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="BS5" s="40" t="s">
+      <c r="BS5" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="BT5" s="40" t="s">
+      <c r="BT5" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="BU5" s="40" t="s">
+      <c r="BU5" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="BV5" s="40" t="s">
+      <c r="BV5" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="BW5" s="37" t="s">
+      <c r="BW5" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="BX5" s="37" t="s">
+      <c r="BX5" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="BY5" s="38" t="s">
+      <c r="BY5" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="BZ5" s="38" t="s">
+      <c r="BZ5" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="CA5" s="38" t="s">
+      <c r="CA5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="CB5" s="38" t="s">
+      <c r="CB5" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="CC5" s="38" t="s">
+      <c r="CC5" s="36" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3892,16 +3889,16 @@
       <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="39" t="s">
         <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -3913,214 +3910,214 @@
       <c r="I6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="42" t="s">
+      <c r="J6" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="43" t="s">
+      <c r="K6" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="44" t="s">
+      <c r="N6" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="44" t="s">
+      <c r="O6" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="P6" s="44" t="s">
+      <c r="P6" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="Q6" s="44" t="s">
+      <c r="Q6" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="44" t="s">
+      <c r="R6" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="S6" s="44" t="s">
+      <c r="S6" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="T6" s="44" t="s">
+      <c r="T6" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="U6" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="44" t="s">
+      <c r="V6" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="W6" s="44" t="s">
+      <c r="W6" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="X6" s="44" t="s">
+      <c r="X6" s="42" t="s">
         <v>273</v>
       </c>
-      <c r="Y6" s="44" t="s">
+      <c r="Y6" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="Z6" s="44" t="s">
+      <c r="Z6" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="AA6" s="44" t="s">
+      <c r="AA6" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="AB6" s="44" t="s">
+      <c r="AB6" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="AC6" s="44" t="s">
+      <c r="AC6" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="AD6" s="44" t="s">
+      <c r="AD6" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="AE6" s="44" t="s">
+      <c r="AE6" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="AF6" s="44" t="s">
+      <c r="AF6" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="AG6" s="44" t="s">
+      <c r="AG6" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="AH6" s="44" t="s">
+      <c r="AH6" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="AI6" s="44" t="s">
+      <c r="AI6" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="AJ6" s="44" t="s">
+      <c r="AJ6" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="AK6" s="44" t="s">
+      <c r="AK6" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AL6" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="AM6" s="44" t="s">
+      <c r="AM6" s="42" t="s">
         <v>276</v>
       </c>
-      <c r="AN6" s="44" t="s">
+      <c r="AN6" s="42" t="s">
         <v>277</v>
       </c>
-      <c r="AO6" s="44" t="s">
+      <c r="AO6" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="AP6" s="44" t="s">
+      <c r="AP6" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="AQ6" s="44" t="s">
+      <c r="AQ6" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="AR6" s="44" t="s">
+      <c r="AR6" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="AS6" s="44" t="s">
+      <c r="AS6" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="AT6" s="44" t="s">
+      <c r="AT6" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="AU6" s="44" t="s">
+      <c r="AU6" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="AV6" s="44" t="s">
+      <c r="AV6" s="42" t="s">
         <v>279</v>
       </c>
-      <c r="AW6" s="44" t="s">
+      <c r="AW6" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="AX6" s="44" t="s">
+      <c r="AX6" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="AY6" s="44" t="s">
+      <c r="AY6" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="AZ6" s="44" t="s">
+      <c r="AZ6" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="BA6" s="44" t="s">
+      <c r="BA6" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="BB6" s="44" t="s">
+      <c r="BB6" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="BC6" s="44" t="s">
+      <c r="BC6" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="BD6" s="44" t="s">
+      <c r="BD6" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="BE6" s="44" t="s">
+      <c r="BE6" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="BF6" s="44" t="s">
+      <c r="BF6" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="BG6" s="44" t="s">
+      <c r="BG6" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="BH6" s="44" t="s">
+      <c r="BH6" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="BI6" s="44" t="s">
+      <c r="BI6" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="BJ6" s="44" t="s">
+      <c r="BJ6" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="BK6" s="44" t="s">
+      <c r="BK6" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="BL6" s="44" t="s">
+      <c r="BL6" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="BM6" s="44" t="s">
+      <c r="BM6" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="BN6" s="44" t="s">
+      <c r="BN6" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="BO6" s="44" t="s">
+      <c r="BO6" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="BP6" s="44" t="s">
+      <c r="BP6" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="BQ6" s="44" t="s">
+      <c r="BQ6" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="BR6" s="44" t="s">
+      <c r="BR6" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="BS6" s="44" t="s">
+      <c r="BS6" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="BT6" s="44" t="s">
+      <c r="BT6" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="BU6" s="44" t="s">
+      <c r="BU6" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="BV6" s="45" t="s">
+      <c r="BV6" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="BW6" s="44" t="s">
+      <c r="BW6" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="BX6" s="44" t="s">
+      <c r="BX6" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="BY6" s="44" t="s">
+      <c r="BY6" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="BZ6" s="46" t="s">
+      <c r="BZ6" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="CA6" s="46" t="s">
+      <c r="CA6" s="44" t="s">
         <v>113</v>
       </c>
       <c r="CB6" s="3" t="s">
@@ -4131,7 +4128,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="C2:E2"/>
     <mergeCell ref="AY4:BF4"/>
     <mergeCell ref="BG4:BN4"/>
     <mergeCell ref="BO4:BV4"/>
@@ -4181,53 +4179,53 @@
     <col min="17" max="16384" width="8" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="49" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="47" t="s">
         <v>289</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="47" t="s">
         <v>290</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="45" t="s">
         <v>291</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="48" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="48" t="s">
         <v>294</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="48" t="s">
         <v>295</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="48" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="49" t="s">
+      <c r="L1" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="M1" s="49" t="s">
+      <c r="M1" s="47" t="s">
         <v>298</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="N1" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="O1" s="49" t="s">
+      <c r="O1" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="P1" s="49" t="s">
+      <c r="P1" s="47" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4424,17 +4422,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="66" t="s">
         <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4452,7 +4450,7 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="4" t="s">
         <v>164</v>
       </c>
@@ -4471,36 +4469,36 @@
       <c r="A4" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="61" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="60"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="61" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="60"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
@@ -4510,15 +4508,15 @@
       <c r="B7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="62" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="73"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="66" t="s">
         <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4536,7 +4534,7 @@
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="62"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="4">
         <f>硫化日计划!AB3</f>
         <v>0</v>
@@ -4581,61 +4579,56 @@
       <c r="A11" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="60"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="57" t="s">
+      <c r="B12" s="71"/>
+      <c r="C12" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="60"/>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="68" t="s">
         <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="65" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="64"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
       <c r="F14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
@@ -4644,6 +4637,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C7:E7"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521EA153-F773-4323-88B9-387A0BFC6CA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA14308-E3A4-4498-A9E6-E69C7006FC1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2298,7 +2298,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2364,9 +2364,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2442,6 +2439,9 @@
     <xf numFmtId="180" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2460,6 +2460,36 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2472,15 +2502,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2489,30 +2510,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2559,63 +2556,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>14287</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>33338</xdr:rowOff>
+      <xdr:colOff>61911</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>143193</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13970" y="33020"/>
-          <a:ext cx="1104900" cy="324485"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>14287</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>33338</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>143193</xdr:rowOff>
+      <xdr:rowOff>475426</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2638,8 +2587,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13970" y="33020"/>
-          <a:ext cx="1104900" cy="324485"/>
+          <a:off x="61911" y="0"/>
+          <a:ext cx="900114" cy="475426"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3027,269 +2976,269 @@
   <dimension ref="A1:CC6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="9.625" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="5" max="5" width="32.625" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="8" width="5.625" customWidth="1"/>
-    <col min="9" max="9" width="6.125" customWidth="1"/>
-    <col min="10" max="10" width="5.625" customWidth="1"/>
-    <col min="11" max="11" width="3.125" customWidth="1"/>
-    <col min="12" max="18" width="5.125" customWidth="1"/>
-    <col min="19" max="19" width="3.125" customWidth="1"/>
-    <col min="20" max="26" width="5.125" customWidth="1"/>
-    <col min="27" max="27" width="3.125" customWidth="1"/>
-    <col min="28" max="34" width="5.125" customWidth="1"/>
-    <col min="35" max="35" width="3.125" customWidth="1"/>
-    <col min="36" max="42" width="5.125" customWidth="1"/>
-    <col min="43" max="43" width="3.125" customWidth="1"/>
-    <col min="44" max="50" width="5.125" customWidth="1"/>
-    <col min="51" max="51" width="3.125" customWidth="1"/>
-    <col min="52" max="58" width="5.125" customWidth="1"/>
-    <col min="59" max="59" width="3.125" customWidth="1"/>
-    <col min="60" max="66" width="5.125" customWidth="1"/>
-    <col min="67" max="67" width="3.125" customWidth="1"/>
-    <col min="68" max="74" width="5.125" customWidth="1"/>
-    <col min="75" max="77" width="5.625" customWidth="1"/>
+    <col min="1" max="3" width="5.625" customWidth="1"/>
+    <col min="4" max="4" width="6.5" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="32.625" customWidth="1"/>
+    <col min="7" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="32.625" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="11" width="5.625" customWidth="1"/>
+    <col min="12" max="12" width="6.125" customWidth="1"/>
+    <col min="13" max="13" width="5.625" customWidth="1"/>
+    <col min="14" max="14" width="3.125" customWidth="1"/>
+    <col min="15" max="21" width="5.125" customWidth="1"/>
+    <col min="22" max="22" width="3.125" customWidth="1"/>
+    <col min="23" max="29" width="5.125" customWidth="1"/>
+    <col min="30" max="30" width="3.125" customWidth="1"/>
+    <col min="31" max="37" width="5.125" customWidth="1"/>
+    <col min="38" max="38" width="3.125" customWidth="1"/>
+    <col min="39" max="45" width="5.125" customWidth="1"/>
+    <col min="46" max="46" width="3.125" customWidth="1"/>
+    <col min="47" max="53" width="5.125" customWidth="1"/>
+    <col min="54" max="54" width="3.125" customWidth="1"/>
+    <col min="55" max="61" width="5.125" customWidth="1"/>
+    <col min="62" max="62" width="3.125" customWidth="1"/>
+    <col min="63" max="69" width="5.125" customWidth="1"/>
+    <col min="70" max="70" width="3.125" customWidth="1"/>
+    <col min="71" max="77" width="5.125" customWidth="1"/>
     <col min="78" max="78" width="9.625" customWidth="1"/>
     <col min="79" max="79" width="7.625" customWidth="1"/>
     <col min="80" max="80" width="9.625" customWidth="1"/>
     <col min="81" max="81" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:81" ht="20.25" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" t="s">
         <v>189</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>190</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>191</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>192</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>193</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>194</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>195</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>196</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>197</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>198</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>199</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>200</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>201</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>202</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>254</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>203</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>204</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>205</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>206</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>207</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>208</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>256</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>257</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>209</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>210</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>211</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>212</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>213</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>214</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
         <v>258</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>259</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>215</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>216</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>217</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>218</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>219</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>220</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AP1" t="s">
         <v>260</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AQ1" t="s">
         <v>261</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AR1" t="s">
         <v>221</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AS1" t="s">
         <v>222</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AT1" t="s">
         <v>223</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" t="s">
         <v>224</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AV1" t="s">
         <v>225</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AW1" t="s">
         <v>226</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AX1" t="s">
         <v>262</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AY1" t="s">
         <v>263</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AZ1" t="s">
         <v>227</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BA1" t="s">
         <v>228</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BB1" t="s">
         <v>229</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>230</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>231</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BE1" t="s">
         <v>232</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BF1" t="s">
         <v>264</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BG1" t="s">
         <v>265</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BH1" t="s">
         <v>233</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BI1" t="s">
         <v>234</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BJ1" t="s">
         <v>235</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BK1" t="s">
         <v>236</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BL1" t="s">
         <v>237</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BM1" t="s">
         <v>238</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BN1" t="s">
         <v>266</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BO1" t="s">
         <v>267</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BP1" t="s">
         <v>239</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BQ1" t="s">
         <v>240</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BR1" t="s">
         <v>241</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BS1" t="s">
         <v>242</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BT1" t="s">
         <v>243</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BU1" t="s">
         <v>244</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BV1" t="s">
         <v>268</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BW1" t="s">
         <v>269</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BX1" t="s">
         <v>245</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BY1" t="s">
         <v>246</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>247</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>248</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>249</v>
       </c>
       <c r="BZ1" t="s">
         <v>250</v>
@@ -3304,26 +3253,26 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:81" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="72" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="24" t="s">
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="25"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="O2" s="24"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -3358,10 +3307,10 @@
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
-      <c r="AX2" s="25"/>
+      <c r="AX2" s="2"/>
       <c r="AY2" s="2"/>
       <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
+      <c r="BA2" s="24"/>
       <c r="BB2" s="2"/>
       <c r="BC2" s="2"/>
       <c r="BD2" s="2"/>
@@ -3387,737 +3336,737 @@
       <c r="BX2" s="2"/>
       <c r="BY2" s="2"/>
       <c r="BZ2" s="2"/>
-      <c r="CA2" s="25"/>
-      <c r="CB2" s="25"/>
+      <c r="CA2" s="24"/>
+      <c r="CB2" s="24"/>
       <c r="CC2" s="2"/>
     </row>
     <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28" t="s">
+      <c r="A3" s="25">
+        <f>SUM(A6:A108139)</f>
+        <v>0</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="25">
+        <f>SUM(C6:C108139)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27">
-        <f>SUM(L6:L108139)</f>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26">
+        <f>SUM(O6:O108139)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="26"/>
       <c r="P3" s="26"/>
       <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="26">
-        <f>SUM(T6:T108139)</f>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="25">
+        <f>SUM(W6:W108139)</f>
         <v>0</v>
       </c>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26">
-        <f>SUM(AB6:AB108139)</f>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25">
+        <f>SUM(AE6:AE108139)</f>
         <v>0</v>
       </c>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26">
-        <f>SUM(AJ6:AJ108139)</f>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25">
+        <f>SUM(AM6:AM108139)</f>
         <v>0</v>
       </c>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="30"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="30">
-        <f>SUM(AR6:AR108139)</f>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="29"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="29">
+        <f>SUM(AU6:AU108139)</f>
         <v>0</v>
       </c>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="30"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26">
-        <f>SUM(AZ6:AZ108139)</f>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="29"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25">
+        <f>SUM(BC6:BC108139)</f>
         <v>0</v>
       </c>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="30"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="31"/>
-      <c r="BH3" s="26">
-        <f>SUM(BH6:BH108139)</f>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="26"/>
+      <c r="BG3" s="26"/>
+      <c r="BH3" s="26"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="30"/>
+      <c r="BK3" s="25">
+        <f>SUM(BK6:BK108139)</f>
         <v>0</v>
       </c>
-      <c r="BI3" s="29"/>
-      <c r="BJ3" s="29"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="26">
-        <f>SUM(BP6:BP108139)</f>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="25">
+        <f>SUM(BS6:BS108139)</f>
         <v>0</v>
       </c>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="29"/>
-      <c r="BT3" s="29"/>
-      <c r="BU3" s="29"/>
-      <c r="BV3" s="29"/>
-      <c r="BW3" s="26">
-        <f>SUM(BW6:BW108139)</f>
-        <v>0</v>
-      </c>
-      <c r="BX3" s="29"/>
-      <c r="BY3" s="26">
-        <f>SUM(BY6:BY108139)</f>
-        <v>0</v>
-      </c>
-      <c r="BZ3" s="32"/>
-      <c r="CA3" s="29"/>
-      <c r="CB3" s="29"/>
-      <c r="CC3" s="29"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="31"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
     </row>
     <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="E4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="F4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="G4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="H4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="I4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="J4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="K4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="L4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="M4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="N4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
       <c r="O4" s="53"/>
       <c r="P4" s="53"/>
       <c r="Q4" s="53"/>
       <c r="R4" s="53"/>
-      <c r="S4" s="52" t="s">
-        <v>14</v>
-      </c>
+      <c r="S4" s="53"/>
       <c r="T4" s="53"/>
       <c r="U4" s="53"/>
-      <c r="V4" s="53"/>
+      <c r="V4" s="52" t="s">
+        <v>14</v>
+      </c>
       <c r="W4" s="53"/>
       <c r="X4" s="53"/>
       <c r="Y4" s="53"/>
       <c r="Z4" s="53"/>
-      <c r="AA4" s="54" t="s">
+      <c r="AA4" s="53"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
       <c r="AE4" s="54"/>
       <c r="AF4" s="54"/>
       <c r="AG4" s="54"/>
       <c r="AH4" s="54"/>
-      <c r="AI4" s="54" t="s">
-        <v>16</v>
-      </c>
+      <c r="AI4" s="54"/>
       <c r="AJ4" s="54"/>
       <c r="AK4" s="54"/>
-      <c r="AL4" s="54"/>
+      <c r="AL4" s="54" t="s">
+        <v>16</v>
+      </c>
       <c r="AM4" s="54"/>
       <c r="AN4" s="54"/>
       <c r="AO4" s="54"/>
       <c r="AP4" s="54"/>
-      <c r="AQ4" s="54" t="s">
-        <v>17</v>
-      </c>
+      <c r="AQ4" s="54"/>
       <c r="AR4" s="54"/>
       <c r="AS4" s="54"/>
-      <c r="AT4" s="54"/>
+      <c r="AT4" s="54" t="s">
+        <v>17</v>
+      </c>
       <c r="AU4" s="54"/>
       <c r="AV4" s="54"/>
       <c r="AW4" s="54"/>
       <c r="AX4" s="54"/>
-      <c r="AY4" s="49" t="s">
+      <c r="AY4" s="54"/>
+      <c r="AZ4" s="54"/>
+      <c r="BA4" s="54"/>
+      <c r="BB4" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="AZ4" s="49"/>
-      <c r="BA4" s="49"/>
-      <c r="BB4" s="49"/>
       <c r="BC4" s="49"/>
       <c r="BD4" s="49"/>
       <c r="BE4" s="49"/>
       <c r="BF4" s="49"/>
-      <c r="BG4" s="49" t="s">
-        <v>19</v>
-      </c>
+      <c r="BG4" s="49"/>
       <c r="BH4" s="49"/>
       <c r="BI4" s="49"/>
-      <c r="BJ4" s="49"/>
+      <c r="BJ4" s="49" t="s">
+        <v>19</v>
+      </c>
       <c r="BK4" s="49"/>
       <c r="BL4" s="49"/>
       <c r="BM4" s="49"/>
       <c r="BN4" s="49"/>
-      <c r="BO4" s="49" t="s">
-        <v>20</v>
-      </c>
+      <c r="BO4" s="49"/>
       <c r="BP4" s="49"/>
       <c r="BQ4" s="49"/>
-      <c r="BR4" s="49"/>
+      <c r="BR4" s="49" t="s">
+        <v>20</v>
+      </c>
       <c r="BS4" s="49"/>
       <c r="BT4" s="49"/>
       <c r="BU4" s="49"/>
       <c r="BV4" s="49"/>
-      <c r="BW4" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="BX4" s="51"/>
-      <c r="BY4" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="BZ4" s="33" t="s">
+      <c r="BW4" s="49"/>
+      <c r="BX4" s="49"/>
+      <c r="BY4" s="49"/>
+      <c r="BZ4" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="CA4" s="33" t="s">
+      <c r="CA4" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="CB4" s="33" t="s">
+      <c r="CB4" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="CC4" s="33" t="s">
+      <c r="CC4" s="32" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="E5" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="F5" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="G5" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="H5" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="I5" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="J5" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="K5" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="L5" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="M5" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="N5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="O5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="P5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="Q5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="R5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="S5" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="34" t="s">
+      <c r="T5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="34" t="s">
+      <c r="U5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="34" t="s">
+      <c r="V5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="34" t="s">
+      <c r="W5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="U5" s="34" t="s">
+      <c r="X5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="Y5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="W5" s="34" t="s">
+      <c r="Z5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="X5" s="34" t="s">
+      <c r="AA5" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="Y5" s="34" t="s">
+      <c r="AB5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" s="34" t="s">
+      <c r="AC5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="AA5" s="37" t="s">
+      <c r="AD5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AB5" s="37" t="s">
+      <c r="AE5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="AC5" s="37" t="s">
+      <c r="AF5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="AD5" s="37" t="s">
+      <c r="AG5" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" s="37" t="s">
+      <c r="AH5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="AF5" s="37" t="s">
+      <c r="AI5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="AG5" s="37" t="s">
+      <c r="AJ5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AH5" s="37" t="s">
+      <c r="AK5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="AI5" s="37" t="s">
+      <c r="AL5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AJ5" s="37" t="s">
+      <c r="AM5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="AK5" s="37" t="s">
+      <c r="AN5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="AL5" s="37" t="s">
+      <c r="AO5" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="AM5" s="37" t="s">
+      <c r="AP5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="AN5" s="37" t="s">
+      <c r="AQ5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="AO5" s="37" t="s">
+      <c r="AR5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AP5" s="37" t="s">
+      <c r="AS5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="AQ5" s="37" t="s">
+      <c r="AT5" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="AR5" s="37" t="s">
+      <c r="AU5" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="AS5" s="37" t="s">
+      <c r="AV5" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="AT5" s="37" t="s">
+      <c r="AW5" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="AU5" s="37" t="s">
+      <c r="AX5" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="AV5" s="37" t="s">
+      <c r="AY5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="AW5" s="37" t="s">
+      <c r="AZ5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AX5" s="37" t="s">
+      <c r="BA5" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="AY5" s="38" t="s">
+      <c r="BB5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AZ5" s="38" t="s">
+      <c r="BC5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="BA5" s="38" t="s">
+      <c r="BD5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="BB5" s="38" t="s">
+      <c r="BE5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="BC5" s="38" t="s">
+      <c r="BF5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="BD5" s="38" t="s">
+      <c r="BG5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="BE5" s="38" t="s">
+      <c r="BH5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="BF5" s="38" t="s">
+      <c r="BI5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="BG5" s="38" t="s">
+      <c r="BJ5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="BH5" s="38" t="s">
+      <c r="BK5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="BI5" s="38" t="s">
+      <c r="BL5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="BJ5" s="38" t="s">
+      <c r="BM5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="BK5" s="38" t="s">
+      <c r="BN5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="BL5" s="38" t="s">
+      <c r="BO5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="BM5" s="38" t="s">
+      <c r="BP5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="BN5" s="38" t="s">
+      <c r="BQ5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="BO5" s="38" t="s">
+      <c r="BR5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="BP5" s="38" t="s">
+      <c r="BS5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="BQ5" s="38" t="s">
+      <c r="BT5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="BR5" s="38" t="s">
+      <c r="BU5" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="BS5" s="38" t="s">
+      <c r="BV5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="BT5" s="38" t="s">
+      <c r="BW5" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="BU5" s="38" t="s">
+      <c r="BX5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="BV5" s="38" t="s">
+      <c r="BY5" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="BW5" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="BX5" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="BY5" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="BZ5" s="36" t="s">
+      <c r="BZ5" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="CA5" s="36" t="s">
+      <c r="CA5" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="CB5" s="36" t="s">
+      <c r="CB5" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="CC5" s="36" t="s">
+      <c r="CC5" s="35" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="F6" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="G6" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="H6" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="I6" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="M6" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="41" t="s">
+      <c r="N6" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="O6" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="P6" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="Q6" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="O6" s="42" t="s">
+      <c r="R6" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="S6" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="Q6" s="42" t="s">
+      <c r="T6" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="42" t="s">
+      <c r="U6" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="V6" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="T6" s="42" t="s">
+      <c r="W6" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="42" t="s">
+      <c r="X6" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="V6" s="42" t="s">
+      <c r="Y6" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="W6" s="42" t="s">
+      <c r="Z6" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="X6" s="42" t="s">
+      <c r="AA6" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="Y6" s="42" t="s">
+      <c r="AB6" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="AC6" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="AA6" s="42" t="s">
+      <c r="AD6" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="AB6" s="42" t="s">
+      <c r="AE6" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="AC6" s="42" t="s">
+      <c r="AF6" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="AD6" s="42" t="s">
+      <c r="AG6" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="AE6" s="42" t="s">
+      <c r="AH6" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="AF6" s="42" t="s">
+      <c r="AI6" s="41" t="s">
         <v>275</v>
       </c>
-      <c r="AG6" s="42" t="s">
+      <c r="AJ6" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="AH6" s="42" t="s">
+      <c r="AK6" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="AI6" s="42" t="s">
+      <c r="AL6" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="AJ6" s="42" t="s">
+      <c r="AM6" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="AK6" s="42" t="s">
+      <c r="AN6" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="AL6" s="42" t="s">
+      <c r="AO6" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="AM6" s="42" t="s">
+      <c r="AP6" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="AN6" s="42" t="s">
+      <c r="AQ6" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="AO6" s="42" t="s">
+      <c r="AR6" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="AP6" s="42" t="s">
+      <c r="AS6" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="AQ6" s="42" t="s">
+      <c r="AT6" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="AR6" s="42" t="s">
+      <c r="AU6" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="AS6" s="42" t="s">
+      <c r="AV6" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="AT6" s="42" t="s">
+      <c r="AW6" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="AU6" s="42" t="s">
+      <c r="AX6" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="AV6" s="42" t="s">
+      <c r="AY6" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="AW6" s="42" t="s">
+      <c r="AZ6" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="AX6" s="42" t="s">
+      <c r="BA6" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="AY6" s="42" t="s">
+      <c r="BB6" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="AZ6" s="42" t="s">
+      <c r="BC6" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="BA6" s="42" t="s">
+      <c r="BD6" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="BB6" s="42" t="s">
+      <c r="BE6" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="BC6" s="42" t="s">
+      <c r="BF6" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="BD6" s="42" t="s">
+      <c r="BG6" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="BE6" s="42" t="s">
+      <c r="BH6" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="BF6" s="42" t="s">
+      <c r="BI6" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="BG6" s="42" t="s">
+      <c r="BJ6" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="BH6" s="42" t="s">
+      <c r="BK6" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BI6" s="42" t="s">
+      <c r="BL6" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="BJ6" s="42" t="s">
+      <c r="BM6" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="BK6" s="42" t="s">
+      <c r="BN6" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="BL6" s="42" t="s">
+      <c r="BO6" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="BM6" s="42" t="s">
+      <c r="BP6" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="BN6" s="42" t="s">
+      <c r="BQ6" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="BO6" s="42" t="s">
+      <c r="BR6" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="BP6" s="42" t="s">
+      <c r="BS6" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="BQ6" s="42" t="s">
+      <c r="BT6" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="BR6" s="42" t="s">
+      <c r="BU6" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="BS6" s="42" t="s">
+      <c r="BV6" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="BT6" s="42" t="s">
+      <c r="BW6" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="BU6" s="42" t="s">
+      <c r="BX6" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="BV6" s="43" t="s">
+      <c r="BY6" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="BW6" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="BX6" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="BY6" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="BZ6" s="44" t="s">
+      <c r="BZ6" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="CA6" s="44" t="s">
+      <c r="CA6" s="43" t="s">
         <v>113</v>
       </c>
       <c r="CB6" s="3" t="s">
@@ -4129,23 +4078,23 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="AY4:BF4"/>
-    <mergeCell ref="BG4:BN4"/>
-    <mergeCell ref="BO4:BV4"/>
-    <mergeCell ref="BW4:BX4"/>
-    <mergeCell ref="K4:R4"/>
-    <mergeCell ref="S4:Z4"/>
-    <mergeCell ref="AA4:AH4"/>
-    <mergeCell ref="AI4:AP4"/>
-    <mergeCell ref="AQ4:AX4"/>
+    <mergeCell ref="BB4:BI4"/>
+    <mergeCell ref="BJ4:BQ4"/>
+    <mergeCell ref="BR4:BY4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="N4:U4"/>
+    <mergeCell ref="V4:AC4"/>
+    <mergeCell ref="AD4:AK4"/>
+    <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="AT4:BA4"/>
+    <mergeCell ref="D2:H2"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
-  <conditionalFormatting sqref="C3:D3">
+  <conditionalFormatting sqref="F3:G3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 W5 AE5 AM5 AU5 BC5 BK5 BS5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4179,53 +4128,53 @@
     <col min="17" max="16384" width="8" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:16" s="46" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="46" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="44" t="s">
         <v>291</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="J1" s="48" t="s">
+      <c r="J1" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="K1" s="48" t="s">
+      <c r="K1" s="47" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="47" t="s">
+      <c r="L1" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="M1" s="47" t="s">
+      <c r="M1" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="46" t="s">
         <v>299</v>
       </c>
-      <c r="O1" s="47" t="s">
+      <c r="O1" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="P1" s="47" t="s">
+      <c r="P1" s="46" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4422,17 +4371,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="67"/>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="59" t="s">
         <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -4450,7 +4399,7 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="67"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="4" t="s">
         <v>164</v>
       </c>
@@ -4469,36 +4418,36 @@
       <c r="A4" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="60"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="60"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
@@ -4508,15 +4457,15 @@
       <c r="B7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="63"/>
-      <c r="E7" s="64"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="59" t="s">
         <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -4534,17 +4483,17 @@
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="67"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="4">
-        <f>硫化日计划!AB3</f>
+        <f>硫化日计划!AE3</f>
         <v>0</v>
       </c>
       <c r="C9" s="4">
-        <f>硫化日计划!AJ3</f>
+        <f>硫化日计划!AM3</f>
         <v>0</v>
       </c>
       <c r="D9" s="3">
-        <f>硫化日计划!AR3</f>
+        <f>硫化日计划!AU3</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
@@ -4558,15 +4507,15 @@
         <v>178</v>
       </c>
       <c r="B10" s="4">
-        <f>COUNTA(硫化日计划!$AB$6:AB1048576)</f>
+        <f>COUNTA(硫化日计划!$AE$6:AE1048576)</f>
         <v>1</v>
       </c>
       <c r="C10" s="4">
-        <f>COUNTA(硫化日计划!$AJ$6:AJ1048576)</f>
+        <f>COUNTA(硫化日计划!$AM$6:AM1048576)</f>
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>COUNTA(硫化日计划!$AR$6:AR1048576)</f>
+        <f>COUNTA(硫化日计划!$AU$6:AU1048576)</f>
         <v>1</v>
       </c>
       <c r="E10" s="4">
@@ -4579,56 +4528,61 @@
       <c r="A11" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="55" t="s">
         <v>181</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="60"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="61" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="60"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="57"/>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="61" t="s">
         <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="69"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C7:E7"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
@@ -4637,11 +4591,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA14308-E3A4-4498-A9E6-E69C7006FC1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -22,18 +16,273 @@
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="317">
+  <si>
+    <t>nightPlanQtyTotal</t>
+  </si>
+  <si>
+    <t>nightFinishQtyTotal</t>
+  </si>
+  <si>
+    <t>totalPlanQtyFormula</t>
+  </si>
+  <si>
+    <t>lhMachineCode</t>
+  </si>
+  <si>
+    <t>materialCode</t>
+  </si>
+  <si>
+    <t>materialDesc</t>
+  </si>
+  <si>
+    <t>embryoCode</t>
+  </si>
+  <si>
+    <t>mainMaterialDesc</t>
+  </si>
+  <si>
+    <t>structureName</t>
+  </si>
+  <si>
+    <t>dailyPlanQty</t>
+  </si>
+  <si>
+    <t>embryoStock</t>
+  </si>
+  <si>
+    <t>replaceCapsuleCountLeftRight</t>
+  </si>
+  <si>
+    <t>singleMouldShiftQty</t>
+  </si>
+  <si>
+    <t>class1Order</t>
+  </si>
+  <si>
+    <t>class1PlanQty</t>
+  </si>
+  <si>
+    <t>class1FinishQty</t>
+  </si>
+  <si>
+    <t>class1LeftRightMould</t>
+  </si>
+  <si>
+    <t>class1IsEnd</t>
+  </si>
+  <si>
+    <t>class1LhType</t>
+  </si>
+  <si>
+    <t>class1Analysis</t>
+  </si>
+  <si>
+    <t>class1Dot</t>
+  </si>
+  <si>
+    <t>class2Order</t>
+  </si>
+  <si>
+    <t>class2PlanQty</t>
+  </si>
+  <si>
+    <t>class2FinishQty</t>
+  </si>
+  <si>
+    <t>class2LeftRightMould</t>
+  </si>
+  <si>
+    <t>class2IsEnd</t>
+  </si>
+  <si>
+    <t>class2LhType</t>
+  </si>
+  <si>
+    <t>class2Analysis</t>
+  </si>
+  <si>
+    <t>class2Dot</t>
+  </si>
+  <si>
+    <t>class3Order</t>
+  </si>
+  <si>
+    <t>class3PlanQty</t>
+  </si>
+  <si>
+    <t>class3FinishQty</t>
+  </si>
+  <si>
+    <t>class3LeftRightMould</t>
+  </si>
+  <si>
+    <t>class3IsEnd</t>
+  </si>
+  <si>
+    <t>class3LhType</t>
+  </si>
+  <si>
+    <t>class3Analysis</t>
+  </si>
+  <si>
+    <t>class3Dot</t>
+  </si>
+  <si>
+    <t>class4Order</t>
+  </si>
+  <si>
+    <t>class4PlanQty</t>
+  </si>
+  <si>
+    <t>class4FinishQty</t>
+  </si>
+  <si>
+    <t>class4LeftRightMould</t>
+  </si>
+  <si>
+    <t>class4IsEnd</t>
+  </si>
+  <si>
+    <t>class4LhType</t>
+  </si>
+  <si>
+    <t>class4Analysis</t>
+  </si>
+  <si>
+    <t>class4Dot</t>
+  </si>
+  <si>
+    <t>class5Order</t>
+  </si>
+  <si>
+    <t>class5PlanQty</t>
+  </si>
+  <si>
+    <t>class5FinishQty</t>
+  </si>
+  <si>
+    <t>class5LeftRightMould</t>
+  </si>
+  <si>
+    <t>class5IsEnd</t>
+  </si>
+  <si>
+    <t>class5LhType</t>
+  </si>
+  <si>
+    <t>class5Analysis</t>
+  </si>
+  <si>
+    <t>class5Dot</t>
+  </si>
+  <si>
+    <t>class6Order</t>
+  </si>
+  <si>
+    <t>class6PlanQty</t>
+  </si>
+  <si>
+    <t>class6FinishQty</t>
+  </si>
+  <si>
+    <t>class6LeftRightMould</t>
+  </si>
+  <si>
+    <t>class6IsEnd</t>
+  </si>
+  <si>
+    <t>class6LhType</t>
+  </si>
+  <si>
+    <t>class6Analysis</t>
+  </si>
+  <si>
+    <t>class6Dot</t>
+  </si>
+  <si>
+    <t>class7Order</t>
+  </si>
+  <si>
+    <t>class7PlanQty</t>
+  </si>
+  <si>
+    <t>class7FinishQty</t>
+  </si>
+  <si>
+    <t>class7LeftRightMould</t>
+  </si>
+  <si>
+    <t>class7IsEnd</t>
+  </si>
+  <si>
+    <t>class7LhType</t>
+  </si>
+  <si>
+    <t>class7Analysis</t>
+  </si>
+  <si>
+    <t>class7Dot</t>
+  </si>
+  <si>
+    <t>class8Order</t>
+  </si>
+  <si>
+    <t>class8PlanQty</t>
+  </si>
+  <si>
+    <t>class8FinishQty</t>
+  </si>
+  <si>
+    <t>class8LeftRightMould</t>
+  </si>
+  <si>
+    <t>class8IsEnd</t>
+  </si>
+  <si>
+    <t>class8LhType</t>
+  </si>
+  <si>
+    <t>class8Analysis</t>
+  </si>
+  <si>
+    <t>class8Dot</t>
+  </si>
+  <si>
+    <t>cxMachineCode</t>
+  </si>
+  <si>
+    <t>totalDailyPlanQty</t>
+  </si>
+  <si>
+    <t>todayNightFinishQty</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
   <si>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -45,7 +294,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -55,7 +304,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -66,7 +314,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -76,7 +324,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -87,7 +334,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -97,7 +344,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -108,7 +354,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -118,7 +364,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -129,7 +374,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -139,7 +384,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -150,7 +394,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -160,7 +404,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -171,7 +414,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -181,7 +424,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -192,7 +434,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -202,7 +444,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -213,7 +454,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -223,7 +464,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -235,7 +475,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -245,7 +484,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -254,7 +493,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -265,6 +503,14 @@
 Tổng kế hoạch：</t>
   </si>
   <si>
+    <t>合计
+Tổng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总计
+</t>
+  </si>
+  <si>
     <t>*机台</t>
   </si>
   <si>
@@ -308,7 +554,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -318,7 +563,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -327,7 +572,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate2}</t>
@@ -339,7 +583,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -349,7 +592,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -358,7 +601,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate3}</t>
@@ -373,7 +615,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -383,7 +624,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -392,7 +633,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate5}</t>
@@ -404,7 +644,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -414,7 +653,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -423,7 +662,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate6}</t>
@@ -438,7 +676,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -448,7 +685,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -457,19 +694,10 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate8}</t>
     </r>
-  </si>
-  <si>
-    <t>合计
-Tổng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总计
-</t>
   </si>
   <si>
     <t>对应成型机台号</t>
@@ -486,6 +714,17 @@
 </t>
   </si>
   <si>
+    <t>计划
+Kế hoạch</t>
+  </si>
+  <si>
+    <t>实际
+Thực tế</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
     <t>Máy</t>
   </si>
   <si>
@@ -515,7 +754,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -525,7 +763,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -534,7 +772,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> l</t>
@@ -544,7 +781,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ầ</t>
     </r>
@@ -553,7 +790,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n s</t>
@@ -563,7 +799,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ử</t>
     </r>
@@ -572,7 +808,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> d</t>
@@ -582,7 +817,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ụ</t>
     </r>
@@ -591,7 +826,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng phao L/R</t>
@@ -609,10 +843,6 @@
 Kế hoạch</t>
   </si>
   <si>
-    <t>实际
-Thực tế</t>
-  </si>
-  <si>
     <t>左右模
 Khuôn trái phải</t>
   </si>
@@ -633,19 +863,11 @@
 </t>
   </si>
   <si>
-    <t>计划
-Kế hoạch</t>
-  </si>
-  <si>
-    <t>Tổng</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -655,7 +877,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -664,7 +886,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ng </t>
@@ -674,7 +895,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -683,7 +904,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy TH</t>
@@ -699,6 +919,15 @@
     <t>Ghi chú</t>
   </si>
   <si>
+    <t>{.nightPlanQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.nightFinishQtyTotal}</t>
+  </si>
+  <si>
+    <t>{.totalPlanQtyFormula}</t>
+  </si>
+  <si>
     <t>{.lhMachineCode}</t>
   </si>
   <si>
@@ -741,6 +970,12 @@
     <t>{.class1LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class1IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class1LhType}</t>
+  </si>
+  <si>
     <t>{.class1Analysis}</t>
   </si>
   <si>
@@ -759,6 +994,12 @@
     <t>{.class2LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class2IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class2LhType}</t>
+  </si>
+  <si>
     <t>{.class2Analysis}</t>
   </si>
   <si>
@@ -777,6 +1018,12 @@
     <t>{.class3LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class3IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class3LhType}</t>
+  </si>
+  <si>
     <t>{.class3Analysis}</t>
   </si>
   <si>
@@ -795,6 +1042,12 @@
     <t>{.class4LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class4IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class4LhType}</t>
+  </si>
+  <si>
     <t>{.class4Analysis}</t>
   </si>
   <si>
@@ -813,6 +1066,12 @@
     <t>{.class5LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class5IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class5LhType}</t>
+  </si>
+  <si>
     <t>{.class5Analysis}</t>
   </si>
   <si>
@@ -831,6 +1090,12 @@
     <t>{.class6LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class6IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class6LhType}</t>
+  </si>
+  <si>
     <t>{.class6Analysis}</t>
   </si>
   <si>
@@ -849,6 +1114,12 @@
     <t>{.class7LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class7IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class7LhType}</t>
+  </si>
+  <si>
     <t>{.class7Analysis}</t>
   </si>
   <si>
@@ -867,21 +1138,18 @@
     <t>{.class8LeftRightMould}</t>
   </si>
   <si>
+    <t>{.class8IsEnd}</t>
+  </si>
+  <si>
+    <t>{.class8LhType}</t>
+  </si>
+  <si>
     <t>{.class8Analysis}</t>
   </si>
   <si>
     <t>{.class8Dot}</t>
   </si>
   <si>
-    <t>{.nightPlanQtyTotal}</t>
-  </si>
-  <si>
-    <t>{.nightFinishQtyTotal}</t>
-  </si>
-  <si>
-    <t>{.totalPlanQtyFormula}</t>
-  </si>
-  <si>
     <t>{.cxMachineCode}</t>
   </si>
   <si>
@@ -892,6 +1160,54 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{seq}</t>
+  </si>
+  <si>
+    <t>{planDate}</t>
+  </si>
+  <si>
+    <t>{classIndex}</t>
+  </si>
+  <si>
+    <t>{lhMachineCode}</t>
+  </si>
+  <si>
+    <t>{leftRightMould}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialCode}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialCode}</t>
+  </si>
+  <si>
+    <t>{afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{endType}</t>
+  </si>
+  <si>
+    <t>{isDryIceClean}</t>
+  </si>
+  <si>
+    <t>{isSandblastingClean}</t>
+  </si>
+  <si>
+    <t>{isReplaceBlock}</t>
+  </si>
+  <si>
+    <t>{mouldCode}</t>
+  </si>
+  <si>
+    <t>{remark}</t>
   </si>
   <si>
     <t>{title}</t>
@@ -972,7 +1288,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Lo</t>
@@ -982,7 +1297,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -991,7 +1306,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i ph</t>
@@ -1001,7 +1315,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -1010,7 +1324,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng th</t>
@@ -1020,7 +1333,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -1029,7 +1342,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1041,7 +1353,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Xu</t>
@@ -1051,7 +1362,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1060,7 +1371,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy theo th</t>
@@ -1070,7 +1380,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ờ</t>
     </r>
@@ -1079,7 +1389,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i gian</t>
@@ -1091,7 +1400,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1101,7 +1409,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1110,7 +1418,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh </t>
@@ -1120,7 +1427,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1129,7 +1436,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">á </t>
@@ -1141,7 +1447,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1151,7 +1456,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1160,7 +1465,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh cát （VSC）</t>
@@ -1172,7 +1476,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Ch</t>
@@ -1182,7 +1485,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ỉ</t>
     </r>
@@ -1191,7 +1494,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> thay l</t>
@@ -1201,7 +1503,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ắ</t>
     </r>
@@ -1210,7 +1512,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1222,7 +1523,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã s</t>
@@ -1232,7 +1532,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1241,7 +1541,6 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> khuôn （MSK）</t>
@@ -1291,6 +1590,9 @@
   </si>
   <si>
     <t>{titleDate}</t>
+  </si>
+  <si>
+    <t>{titleDate2}</t>
   </si>
   <si>
     <t>成型计划
@@ -1308,7 +1610,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca tr</t>
@@ -1318,7 +1619,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1328,7 +1628,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a </t>
@@ -1350,18 +1649,32 @@
     <t>{cxTotalQty}</t>
   </si>
   <si>
+    <t>{cxNightQty2}</t>
+  </si>
+  <si>
+    <t>{cxMorningQty2}</t>
+  </si>
+  <si>
+    <t>{cxMiddleQty2}</t>
+  </si>
+  <si>
+    <t>{cxTotalQty2}</t>
+  </si>
+  <si>
     <t xml:space="preserve">试制 Thử nghiệm </t>
   </si>
   <si>
     <t>{cxSetupInfo}</t>
   </si>
   <si>
+    <t>{cxSetupInfo2}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>量试 Thử nghiệm số l</t>
@@ -1371,7 +1684,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1381,7 +1693,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng</t>
@@ -1389,6 +1700,9 @@
   </si>
   <si>
     <t>{cxTrialInfo}</t>
+  </si>
+  <si>
+    <t>{cxTrialInfo2}</t>
   </si>
   <si>
     <t xml:space="preserve">结构切换
@@ -1398,6 +1712,9 @@
     <t>{cxSpecSwitch}</t>
   </si>
   <si>
+    <t>{cxSpecSwitch2}</t>
+  </si>
+  <si>
     <t>TD胶种 
 Loại su nhỏ</t>
   </si>
@@ -1408,13 +1725,18 @@
     <t>{.specPattern}</t>
   </si>
   <si>
+    <t>{.rubberTypeName2}</t>
+  </si>
+  <si>
+    <t>{.specPattern2}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化计划
@@ -1426,7 +1748,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -1436,7 +1758,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1448,7 +1769,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>硫化开动
@@ -1459,7 +1779,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1469,7 +1788,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ợng máy l</t>
@@ -1479,7 +1797,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ư</t>
@@ -1489,7 +1806,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa</t>
@@ -1505,12 +1821,21 @@
     <t>{mouldChangeInfo}</t>
   </si>
   <si>
+    <t>{mouldCleanDate2}</t>
+  </si>
+  <si>
+    <t>{mouldChangeInfo2}</t>
+  </si>
+  <si>
     <t xml:space="preserve">模具清洗 Vệ sinh khuôn </t>
   </si>
   <si>
     <t>{mouldCleanInfo}</t>
   </si>
   <si>
+    <t>{mouldCleanInfo2}</t>
+  </si>
+  <si>
     <t>备注 Ghi chú</t>
   </si>
   <si>
@@ -1520,357 +1845,27 @@
     <t>{cxRemark}</t>
   </si>
   <si>
+    <t>{cxRemark2}</t>
+  </si>
+  <si>
     <t>硫化</t>
   </si>
   <si>
     <t>{lhRemark}</t>
   </si>
   <si>
-    <t>lhMachineCode</t>
-  </si>
-  <si>
-    <t>materialCode</t>
-  </si>
-  <si>
-    <t>materialDesc</t>
-  </si>
-  <si>
-    <t>embryoCode</t>
-  </si>
-  <si>
-    <t>mainMaterialDesc</t>
-  </si>
-  <si>
-    <t>structureName</t>
-  </si>
-  <si>
-    <t>dailyPlanQty</t>
-  </si>
-  <si>
-    <t>embryoStock</t>
-  </si>
-  <si>
-    <t>replaceCapsuleCountLeftRight</t>
-  </si>
-  <si>
-    <t>singleMouldShiftQty</t>
-  </si>
-  <si>
-    <t>class1Order</t>
-  </si>
-  <si>
-    <t>class1PlanQty</t>
-  </si>
-  <si>
-    <t>class1FinishQty</t>
-  </si>
-  <si>
-    <t>class1LeftRightMould</t>
-  </si>
-  <si>
-    <t>class1Analysis</t>
-  </si>
-  <si>
-    <t>class1Dot</t>
-  </si>
-  <si>
-    <t>class2Order</t>
-  </si>
-  <si>
-    <t>class2PlanQty</t>
-  </si>
-  <si>
-    <t>class2FinishQty</t>
-  </si>
-  <si>
-    <t>class2LeftRightMould</t>
-  </si>
-  <si>
-    <t>class2Analysis</t>
-  </si>
-  <si>
-    <t>class2Dot</t>
-  </si>
-  <si>
-    <t>class3Order</t>
-  </si>
-  <si>
-    <t>class3PlanQty</t>
-  </si>
-  <si>
-    <t>class3FinishQty</t>
-  </si>
-  <si>
-    <t>class3LeftRightMould</t>
-  </si>
-  <si>
-    <t>class3Analysis</t>
-  </si>
-  <si>
-    <t>class3Dot</t>
-  </si>
-  <si>
-    <t>class4Order</t>
-  </si>
-  <si>
-    <t>class4PlanQty</t>
-  </si>
-  <si>
-    <t>class4FinishQty</t>
-  </si>
-  <si>
-    <t>class4LeftRightMould</t>
-  </si>
-  <si>
-    <t>class4Analysis</t>
-  </si>
-  <si>
-    <t>class4Dot</t>
-  </si>
-  <si>
-    <t>class5Order</t>
-  </si>
-  <si>
-    <t>class5PlanQty</t>
-  </si>
-  <si>
-    <t>class5FinishQty</t>
-  </si>
-  <si>
-    <t>class5LeftRightMould</t>
-  </si>
-  <si>
-    <t>class5Analysis</t>
-  </si>
-  <si>
-    <t>class5Dot</t>
-  </si>
-  <si>
-    <t>class6Order</t>
-  </si>
-  <si>
-    <t>class6PlanQty</t>
-  </si>
-  <si>
-    <t>class6FinishQty</t>
-  </si>
-  <si>
-    <t>class6LeftRightMould</t>
-  </si>
-  <si>
-    <t>class6Analysis</t>
-  </si>
-  <si>
-    <t>class6Dot</t>
-  </si>
-  <si>
-    <t>class7Order</t>
-  </si>
-  <si>
-    <t>class7PlanQty</t>
-  </si>
-  <si>
-    <t>class7FinishQty</t>
-  </si>
-  <si>
-    <t>class7LeftRightMould</t>
-  </si>
-  <si>
-    <t>class7Analysis</t>
-  </si>
-  <si>
-    <t>class7Dot</t>
-  </si>
-  <si>
-    <t>class8Order</t>
-  </si>
-  <si>
-    <t>class8PlanQty</t>
-  </si>
-  <si>
-    <t>class8FinishQty</t>
-  </si>
-  <si>
-    <t>class8LeftRightMould</t>
-  </si>
-  <si>
-    <t>class8Analysis</t>
-  </si>
-  <si>
-    <t>class8Dot</t>
-  </si>
-  <si>
-    <t>nightPlanQtyTotal</t>
-  </si>
-  <si>
-    <t>nightFinishQtyTotal</t>
-  </si>
-  <si>
-    <t>totalPlanQtyFormula</t>
-  </si>
-  <si>
-    <t>cxMachineCode</t>
-  </si>
-  <si>
-    <t>totalDailyPlanQty</t>
-  </si>
-  <si>
-    <t>todayNightFinishQty</t>
-  </si>
-  <si>
-    <t>remark</t>
-  </si>
-  <si>
-    <t>class1IsEnd</t>
-  </si>
-  <si>
-    <t>class1LhType</t>
-  </si>
-  <si>
-    <t>class2IsEnd</t>
-  </si>
-  <si>
-    <t>class2LhType</t>
-  </si>
-  <si>
-    <t>class3IsEnd</t>
-  </si>
-  <si>
-    <t>class3LhType</t>
-  </si>
-  <si>
-    <t>class4IsEnd</t>
-  </si>
-  <si>
-    <t>class4LhType</t>
-  </si>
-  <si>
-    <t>class5IsEnd</t>
-  </si>
-  <si>
-    <t>class5LhType</t>
-  </si>
-  <si>
-    <t>class6IsEnd</t>
-  </si>
-  <si>
-    <t>class6LhType</t>
-  </si>
-  <si>
-    <t>class7IsEnd</t>
-  </si>
-  <si>
-    <t>class7LhType</t>
-  </si>
-  <si>
-    <t>class8IsEnd</t>
-  </si>
-  <si>
-    <t>class8LhType</t>
-  </si>
-  <si>
-    <t>{.class1IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class1LhType}</t>
-  </si>
-  <si>
-    <t>{.class2IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class2LhType}</t>
-  </si>
-  <si>
-    <t>{.class3IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class3LhType}</t>
-  </si>
-  <si>
-    <t>{.class4IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class4LhType}</t>
-  </si>
-  <si>
-    <t>{.class5IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class5LhType}</t>
-  </si>
-  <si>
-    <t>{.class6IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class6LhType}</t>
-  </si>
-  <si>
-    <t>{.class7IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class7LhType}</t>
-  </si>
-  <si>
-    <t>{.class8IsEnd}</t>
-  </si>
-  <si>
-    <t>{.class8LhType}</t>
-  </si>
-  <si>
-    <t>{seq}</t>
-  </si>
-  <si>
-    <t>{planDate}</t>
-  </si>
-  <si>
-    <t>{classIndex}</t>
-  </si>
-  <si>
-    <t>{lhMachineCode}</t>
-  </si>
-  <si>
-    <t>{leftRightMould}</t>
-  </si>
-  <si>
-    <t>{beforeMaterialCode}</t>
-  </si>
-  <si>
-    <t>{beforeMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{afterMaterialCode}</t>
-  </si>
-  <si>
-    <t>{afterMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{afterMaterialType}</t>
-  </si>
-  <si>
-    <t>{endType}</t>
-  </si>
-  <si>
-    <t>{isDryIceClean}</t>
-  </si>
-  <si>
-    <t>{isSandblastingClean}</t>
-  </si>
-  <si>
-    <t>{isReplaceBlock}</t>
-  </si>
-  <si>
-    <t>{mouldCode}</t>
-  </si>
-  <si>
-    <t>{remark}</t>
+    <t>{lhRemark2}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="11">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -1879,7 +1874,7 @@
     <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="45">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1888,21 +1883,18 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1910,61 +1902,213 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1972,59 +2116,13 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2032,48 +2130,54 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2104,8 +2208,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2272,97 +2562,390 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2373,15 +2956,15 @@
     <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2391,14 +2974,23 @@
     <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2409,6 +3001,9 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2418,114 +3013,78 @@
     <xf numFmtId="182" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="28" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="13">
-    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+  <cellStyles count="61">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma 2" xfId="49"/>
+    <cellStyle name="Excel Built-in Normal" xfId="50"/>
+    <cellStyle name="Normal 10" xfId="51"/>
+    <cellStyle name="Normal 12 3" xfId="52"/>
+    <cellStyle name="Normal 2 2" xfId="53"/>
+    <cellStyle name="Normal 20 3" xfId="54"/>
+    <cellStyle name="Normal 91" xfId="55"/>
+    <cellStyle name="Percent 2" xfId="56"/>
+    <cellStyle name="常规 2" xfId="57"/>
+    <cellStyle name="常规 2 5" xfId="58"/>
+    <cellStyle name="千位分隔 3" xfId="59"/>
+    <cellStyle name="千位分隔 3 3" xfId="60"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2544,15 +3103,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2568,27 +3124,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="61911" y="0"/>
-          <a:ext cx="900114" cy="475426"/>
+          <a:off x="61595" y="0"/>
+          <a:ext cx="900430" cy="474980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2605,7 +3155,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2621,19 +3171,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2648,7 +3192,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="51435" y="20320"/>
-          <a:ext cx="1134745" cy="386715"/>
+          <a:ext cx="1132840" cy="386715"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2964,17 +3508,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="3" width="5.625" customWidth="1"/>
     <col min="4" max="4" width="6.5" customWidth="1"/>
@@ -3008,1591 +3551,1773 @@
     <col min="81" max="81" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" ht="20.25" hidden="1" x14ac:dyDescent="0.15">
+    <row r="1" hidden="1" spans="1:81">
       <c r="A1" t="s">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>189</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>193</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>194</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>195</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>196</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>199</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>254</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="U1" t="s">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>206</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>212</v>
+        <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>213</v>
+        <v>31</v>
       </c>
       <c r="AG1" t="s">
-        <v>214</v>
+        <v>32</v>
       </c>
       <c r="AH1" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="AI1" t="s">
-        <v>259</v>
+        <v>34</v>
       </c>
       <c r="AJ1" t="s">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="AK1" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="AL1" t="s">
-        <v>217</v>
+        <v>37</v>
       </c>
       <c r="AM1" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="AN1" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
       <c r="AO1" t="s">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="AP1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="AQ1" t="s">
-        <v>261</v>
+        <v>42</v>
       </c>
       <c r="AR1" t="s">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="AS1" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="AT1" t="s">
-        <v>223</v>
+        <v>45</v>
       </c>
       <c r="AU1" t="s">
-        <v>224</v>
+        <v>46</v>
       </c>
       <c r="AV1" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="AW1" t="s">
-        <v>226</v>
+        <v>48</v>
       </c>
       <c r="AX1" t="s">
-        <v>262</v>
+        <v>49</v>
       </c>
       <c r="AY1" t="s">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="AZ1" t="s">
-        <v>227</v>
+        <v>51</v>
       </c>
       <c r="BA1" t="s">
-        <v>228</v>
+        <v>52</v>
       </c>
       <c r="BB1" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>230</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>231</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="BJ1" t="s">
-        <v>235</v>
+        <v>61</v>
       </c>
       <c r="BK1" t="s">
-        <v>236</v>
+        <v>62</v>
       </c>
       <c r="BL1" t="s">
-        <v>237</v>
+        <v>63</v>
       </c>
       <c r="BM1" t="s">
-        <v>238</v>
+        <v>64</v>
       </c>
       <c r="BN1" t="s">
-        <v>266</v>
+        <v>65</v>
       </c>
       <c r="BO1" t="s">
-        <v>267</v>
+        <v>66</v>
       </c>
       <c r="BP1" t="s">
-        <v>239</v>
+        <v>67</v>
       </c>
       <c r="BQ1" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="BR1" t="s">
-        <v>241</v>
+        <v>69</v>
       </c>
       <c r="BS1" t="s">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="BT1" t="s">
-        <v>243</v>
+        <v>71</v>
       </c>
       <c r="BU1" t="s">
-        <v>244</v>
+        <v>72</v>
       </c>
       <c r="BV1" t="s">
-        <v>268</v>
+        <v>73</v>
       </c>
       <c r="BW1" t="s">
-        <v>269</v>
+        <v>74</v>
       </c>
       <c r="BX1" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="BY1" t="s">
-        <v>246</v>
+        <v>76</v>
       </c>
       <c r="BZ1" t="s">
-        <v>250</v>
+        <v>77</v>
       </c>
       <c r="CA1" t="s">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="CB1" t="s">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="CC1" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="24"/>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
-      <c r="BL2" s="2"/>
-      <c r="BM2" s="2"/>
-      <c r="BN2" s="2"/>
-      <c r="BO2" s="2"/>
-      <c r="BP2" s="2"/>
-      <c r="BQ2" s="2"/>
-      <c r="BR2" s="2"/>
-      <c r="BS2" s="2"/>
-      <c r="BT2" s="2"/>
-      <c r="BU2" s="2"/>
-      <c r="BV2" s="2"/>
-      <c r="BW2" s="2"/>
-      <c r="BX2" s="2"/>
-      <c r="BY2" s="2"/>
-      <c r="BZ2" s="2"/>
-      <c r="CA2" s="24"/>
-      <c r="CB2" s="24"/>
-      <c r="CC2" s="2"/>
+    <row r="2" ht="37.5" customHeight="1" spans="1:81">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
+      <c r="AZ2" s="5"/>
+      <c r="BA2" s="41"/>
+      <c r="BB2" s="5"/>
+      <c r="BC2" s="5"/>
+      <c r="BD2" s="5"/>
+      <c r="BE2" s="5"/>
+      <c r="BF2" s="5"/>
+      <c r="BG2" s="5"/>
+      <c r="BH2" s="5"/>
+      <c r="BI2" s="5"/>
+      <c r="BJ2" s="5"/>
+      <c r="BK2" s="5"/>
+      <c r="BL2" s="5"/>
+      <c r="BM2" s="5"/>
+      <c r="BN2" s="5"/>
+      <c r="BO2" s="5"/>
+      <c r="BP2" s="5"/>
+      <c r="BQ2" s="5"/>
+      <c r="BR2" s="5"/>
+      <c r="BS2" s="5"/>
+      <c r="BT2" s="5"/>
+      <c r="BU2" s="5"/>
+      <c r="BV2" s="5"/>
+      <c r="BW2" s="5"/>
+      <c r="BX2" s="5"/>
+      <c r="BY2" s="5"/>
+      <c r="BZ2" s="5"/>
+      <c r="CA2" s="41"/>
+      <c r="CB2" s="41"/>
+      <c r="CC2" s="5"/>
     </row>
-    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="25">
+    <row r="3" ht="16.9" customHeight="1" spans="1:81">
+      <c r="A3" s="42">
         <f>SUM(A6:A108139)</f>
         <v>0</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="25">
+      <c r="B3" s="43"/>
+      <c r="C3" s="42">
         <f>SUM(C6:C108139)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26">
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44">
         <f>SUM(O6:O108139)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="25">
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="42">
         <f>SUM(W6:W108139)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25">
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42">
         <f>SUM(AE6:AE108139)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25">
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42">
         <f>SUM(AM6:AM108139)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="29">
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="42"/>
+      <c r="AP3" s="46"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="42"/>
+      <c r="AS3" s="42"/>
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="46">
         <f>SUM(AU6:AU108139)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="25"/>
-      <c r="BB3" s="25"/>
-      <c r="BC3" s="25">
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="46"/>
+      <c r="BA3" s="42"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="42">
         <f>SUM(BC6:BC108139)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="25"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="28"/>
-      <c r="BJ3" s="30"/>
-      <c r="BK3" s="25">
+      <c r="BD3" s="42"/>
+      <c r="BE3" s="46"/>
+      <c r="BF3" s="44"/>
+      <c r="BG3" s="44"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="43"/>
+      <c r="BJ3" s="47"/>
+      <c r="BK3" s="42">
         <f>SUM(BK6:BK108139)</f>
         <v>0</v>
       </c>
-      <c r="BL3" s="28"/>
-      <c r="BM3" s="28"/>
-      <c r="BN3" s="28"/>
-      <c r="BO3" s="28"/>
-      <c r="BP3" s="28"/>
-      <c r="BQ3" s="28"/>
-      <c r="BR3" s="28"/>
-      <c r="BS3" s="25">
+      <c r="BL3" s="43"/>
+      <c r="BM3" s="43"/>
+      <c r="BN3" s="43"/>
+      <c r="BO3" s="43"/>
+      <c r="BP3" s="43"/>
+      <c r="BQ3" s="43"/>
+      <c r="BR3" s="43"/>
+      <c r="BS3" s="42">
         <f>SUM(BS6:BS108139)</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="28"/>
-      <c r="BU3" s="28"/>
-      <c r="BV3" s="28"/>
-      <c r="BW3" s="28"/>
-      <c r="BX3" s="28"/>
-      <c r="BY3" s="28"/>
-      <c r="BZ3" s="31"/>
-      <c r="CA3" s="28"/>
-      <c r="CB3" s="28"/>
-      <c r="CC3" s="28"/>
+      <c r="BT3" s="43"/>
+      <c r="BU3" s="43"/>
+      <c r="BV3" s="43"/>
+      <c r="BW3" s="43"/>
+      <c r="BX3" s="43"/>
+      <c r="BY3" s="43"/>
+      <c r="BZ3" s="48"/>
+      <c r="CA3" s="43"/>
+      <c r="CB3" s="43"/>
+      <c r="CC3" s="43"/>
     </row>
-    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="53"/>
-      <c r="V4" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="W4" s="53"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="53"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="54"/>
-      <c r="AL4" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM4" s="54"/>
-      <c r="AN4" s="54"/>
-      <c r="AO4" s="54"/>
-      <c r="AP4" s="54"/>
-      <c r="AQ4" s="54"/>
-      <c r="AR4" s="54"/>
-      <c r="AS4" s="54"/>
-      <c r="AT4" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="AU4" s="54"/>
-      <c r="AV4" s="54"/>
-      <c r="AW4" s="54"/>
-      <c r="AX4" s="54"/>
-      <c r="AY4" s="54"/>
-      <c r="AZ4" s="54"/>
-      <c r="BA4" s="54"/>
-      <c r="BB4" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC4" s="49"/>
-      <c r="BD4" s="49"/>
-      <c r="BE4" s="49"/>
-      <c r="BF4" s="49"/>
-      <c r="BG4" s="49"/>
-      <c r="BH4" s="49"/>
-      <c r="BI4" s="49"/>
-      <c r="BJ4" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="BK4" s="49"/>
-      <c r="BL4" s="49"/>
-      <c r="BM4" s="49"/>
-      <c r="BN4" s="49"/>
-      <c r="BO4" s="49"/>
-      <c r="BP4" s="49"/>
-      <c r="BQ4" s="49"/>
-      <c r="BR4" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="BS4" s="49"/>
-      <c r="BT4" s="49"/>
-      <c r="BU4" s="49"/>
-      <c r="BV4" s="49"/>
-      <c r="BW4" s="49"/>
-      <c r="BX4" s="49"/>
-      <c r="BY4" s="49"/>
-      <c r="BZ4" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="CA4" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="CB4" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="CC4" s="32" t="s">
-        <v>26</v>
+    <row r="4" ht="34.5" spans="1:81">
+      <c r="A4" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="N4" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE4" s="53"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="53"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
+      <c r="AL4" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="53"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="53"/>
+      <c r="AQ4" s="53"/>
+      <c r="AR4" s="53"/>
+      <c r="AS4" s="53"/>
+      <c r="AT4" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU4" s="53"/>
+      <c r="AV4" s="53"/>
+      <c r="AW4" s="53"/>
+      <c r="AX4" s="53"/>
+      <c r="AY4" s="53"/>
+      <c r="AZ4" s="53"/>
+      <c r="BA4" s="53"/>
+      <c r="BB4" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="BC4" s="54"/>
+      <c r="BD4" s="54"/>
+      <c r="BE4" s="54"/>
+      <c r="BF4" s="54"/>
+      <c r="BG4" s="54"/>
+      <c r="BH4" s="54"/>
+      <c r="BI4" s="54"/>
+      <c r="BJ4" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK4" s="54"/>
+      <c r="BL4" s="54"/>
+      <c r="BM4" s="54"/>
+      <c r="BN4" s="54"/>
+      <c r="BO4" s="54"/>
+      <c r="BP4" s="54"/>
+      <c r="BQ4" s="54"/>
+      <c r="BR4" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS4" s="54"/>
+      <c r="BT4" s="54"/>
+      <c r="BU4" s="54"/>
+      <c r="BV4" s="54"/>
+      <c r="BW4" s="54"/>
+      <c r="BX4" s="54"/>
+      <c r="BY4" s="54"/>
+      <c r="BZ4" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="CA4" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="CB4" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="CC4" s="51" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
-      <c r="A5" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q5" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="S5" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="T5" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="W5" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="X5" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z5" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA5" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB5" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC5" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD5" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF5" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG5" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH5" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI5" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ5" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK5" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL5" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN5" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO5" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP5" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ5" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR5" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS5" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT5" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="AU5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AV5" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="AW5" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="AX5" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="AY5" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="AZ5" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="BA5" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="BB5" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="BC5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="BD5" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="BE5" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="BF5" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="BG5" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="BH5" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="BI5" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="BJ5" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="BK5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="BL5" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="BM5" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN5" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="BO5" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="BP5" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="BQ5" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="BR5" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="BS5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="BT5" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="BU5" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="BV5" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="BW5" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="BX5" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="BY5" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="BZ5" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="CA5" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="CB5" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="CC5" s="35" t="s">
-        <v>50</v>
+    <row r="5" ht="47" spans="1:81">
+      <c r="A5" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="M5" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="N5" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="P5" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q5" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="R5" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="S5" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="T5" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="U5" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="W5" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="X5" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y5" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z5" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA5" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB5" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC5" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD5" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE5" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG5" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI5" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ5" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="AK5" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL5" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM5" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO5" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ5" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="AR5" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="AS5" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT5" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU5" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="AV5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="AW5" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="AY5" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="AZ5" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA5" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB5" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC5" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD5" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE5" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="BF5" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="BG5" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="BH5" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI5" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="BJ5" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="BK5" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="BL5" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM5" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN5" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="BO5" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="BP5" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="BQ5" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="BR5" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="BS5" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="BT5" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="BU5" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="BV5" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="BW5" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX5" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="BY5" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ5" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA5" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="CB5" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC5" s="55" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M6" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="N6" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="O6" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="R6" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="S6" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="T6" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="U6" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="V6" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="W6" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="X6" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y6" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z6" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA6" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB6" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC6" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD6" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE6" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF6" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG6" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH6" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="AI6" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="AJ6" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK6" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL6" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM6" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN6" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO6" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP6" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="AQ6" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="AR6" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS6" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT6" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU6" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="AV6" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW6" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="AX6" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="AY6" s="41" t="s">
-        <v>279</v>
-      </c>
-      <c r="AZ6" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="BA6" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="BB6" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="BC6" s="41" t="s">
-        <v>92</v>
-      </c>
-      <c r="BD6" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE6" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="BF6" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="BG6" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="BH6" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="BI6" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ6" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="BK6" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL6" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="BM6" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="BN6" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="BO6" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="BP6" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="BQ6" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR6" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS6" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="BT6" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="BU6" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="BV6" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="BW6" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="BX6" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="BY6" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="BZ6" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="CA6" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="CB6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CC6" s="3" t="s">
-        <v>115</v>
+    <row r="6" ht="80.1" customHeight="1" spans="1:81">
+      <c r="A6" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="M6" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="N6" s="61" t="s">
+        <v>145</v>
+      </c>
+      <c r="O6" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="P6" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q6" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="R6" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="S6" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="T6" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="U6" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="V6" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="W6" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="X6" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y6" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z6" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA6" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB6" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="AC6" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD6" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE6" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF6" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG6" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="AH6" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI6" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ6" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK6" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL6" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="AM6" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN6" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO6" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP6" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="AQ6" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="AR6" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS6" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="AT6" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU6" s="58" t="s">
+        <v>178</v>
+      </c>
+      <c r="AV6" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="AW6" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX6" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="AY6" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="AZ6" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA6" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="BB6" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="BC6" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="BD6" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="BE6" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="BF6" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="BG6" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="BH6" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="BI6" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="BJ6" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="BK6" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="BL6" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM6" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="BN6" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="BO6" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="BP6" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="BQ6" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="BR6" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="BS6" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="BT6" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="BU6" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="BV6" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="BW6" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="BX6" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="BY6" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="BZ6" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="CA6" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="CB6" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="CC6" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="BB4:BI4"/>
-    <mergeCell ref="BJ4:BQ4"/>
-    <mergeCell ref="BR4:BY4"/>
+    <mergeCell ref="D2:H2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="N4:U4"/>
     <mergeCell ref="V4:AC4"/>
     <mergeCell ref="AD4:AK4"/>
     <mergeCell ref="AL4:AS4"/>
     <mergeCell ref="AT4:BA4"/>
-    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="BB4:BI4"/>
+    <mergeCell ref="BJ4:BQ4"/>
+    <mergeCell ref="BR4:BY4"/>
   </mergeCells>
-  <phoneticPr fontId="27" type="noConversion"/>
   <conditionalFormatting sqref="F3:G3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="3" style="8" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="9" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="8" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="8" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="11" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="11" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="10" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="9" style="10" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="10"/>
+    <col min="1" max="1" width="3" style="25" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="26" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="23" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="23" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="25" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="25" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="27" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="27" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="27" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="23" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="23" customWidth="1"/>
+    <col min="16" max="16" width="9" style="23" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="46" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>292</v>
-      </c>
-      <c r="H1" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="I1" s="47" t="s">
-        <v>294</v>
-      </c>
-      <c r="J1" s="47" t="s">
-        <v>295</v>
-      </c>
-      <c r="K1" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="L1" s="46" t="s">
-        <v>297</v>
-      </c>
-      <c r="M1" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="N1" s="46" t="s">
-        <v>299</v>
-      </c>
-      <c r="O1" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="P1" s="46" t="s">
-        <v>301</v>
+    <row r="1" s="23" customFormat="1" hidden="1" spans="1:16">
+      <c r="A1" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="P1" s="23" t="s">
+        <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="16"/>
+    <row r="2" ht="33.75" customHeight="1" spans="1:16">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="32"/>
     </row>
-    <row r="3" spans="1:16" s="7" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="P3" s="17" t="s">
-        <v>26</v>
+    <row r="3" s="24" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
+      <c r="A3" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="L3" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="18" t="s">
+    <row r="4" s="24" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+      <c r="A4" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="K4" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="L4" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="N4" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="O4" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="P4" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="18" t="s">
+    </row>
+    <row r="5" ht="11.45" customHeight="1" spans="1:16">
+      <c r="A5" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="N4" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="O5" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>115</v>
+      <c r="E5" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="O5" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="P5" s="35" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="27" type="noConversion"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P5" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="11.5"/>
   <cols>
     <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
     <col min="2" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.75" style="1"/>
+    <col min="6" max="6" width="8.75" style="1"/>
+    <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
+    <col min="8" max="11" width="15.625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="2"/>
+    <row r="1" ht="34.5" customHeight="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
     </row>
-    <row r="2" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F2" s="2"/>
+    <row r="2" ht="25.15" customHeight="1" spans="1:11">
+      <c r="A2" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>277</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="60"/>
-      <c r="B3" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="2"/>
+    <row r="3" ht="25.15" customHeight="1" spans="1:11">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="2"/>
+    <row r="4" ht="30" customHeight="1" spans="1:11">
+      <c r="A4" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="12"/>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="2"/>
+    <row r="5" ht="30" customHeight="1" spans="1:11">
+      <c r="A5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12"/>
     </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="2"/>
+    <row r="6" ht="30" customHeight="1" spans="1:11">
+      <c r="A6" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="12"/>
     </row>
-    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="2"/>
+    <row r="7" ht="90" customHeight="1" spans="1:11">
+      <c r="A7" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
     </row>
-    <row r="8" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F8" s="2"/>
+    <row r="8" ht="25.15" customHeight="1" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>277</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="60"/>
-      <c r="B9" s="4">
+    <row r="9" ht="25.15" customHeight="1" spans="1:11">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
         <f>硫化日计划!AE3</f>
         <v>0</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="9">
         <f>硫化日计划!AM3</f>
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="7">
         <f>硫化日计划!AU3</f>
         <v>0</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="9">
         <f>SUM(B9:D9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9">
+        <f>硫化日计划!BC3</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <f>硫化日计划!BK3</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <f>硫化日计划!BS3</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <f>SUM(H9:J9)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="4">
-        <f>COUNTA(硫化日计划!$AE$6:AE1048576)</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="4">
-        <f>COUNTA(硫化日计划!$AM$6:AM1048576)</f>
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
-        <f>COUNTA(硫化日计划!$AU$6:AU1048576)</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
+    <row r="10" ht="25.15" customHeight="1" spans="1:11">
+      <c r="A10" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="9">
+        <f>COUNTIF(硫化日计划!$AE$6:AE1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <f>COUNTIF(硫化日计划!AM$6:$AM1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <f>COUNTIF(硫化日计划!$AU$6:AU1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <f>SUM(B10:D10)</f>
-        <v>3</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="H10" s="9">
+        <f>COUNTIF(硫化日计划!$BC$6:BC1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <f>COUNTIF(硫化日计划!BK$6:$BK1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <f>COUNTIF(硫化日计划!$BS$6:BS1048576,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <f>SUM(H10:J10)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="2"/>
+    <row r="11" ht="30" customHeight="1" spans="1:11">
+      <c r="A11" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="2"/>
+    <row r="12" ht="30" customHeight="1" spans="1:11">
+      <c r="A12" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="2"/>
+    <row r="13" ht="30" customHeight="1" spans="1:11">
+      <c r="A13" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="62"/>
-      <c r="B14" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="2"/>
+    <row r="14" ht="30" customHeight="1" spans="1:11">
+      <c r="A14" s="22"/>
+      <c r="B14" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:K1"/>
     <mergeCell ref="B4:E4"/>
+    <mergeCell ref="H4:K4"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="H5:K5"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="I7:K7"/>
     <mergeCell ref="C11:E11"/>
+    <mergeCell ref="I11:K11"/>
     <mergeCell ref="C12:E12"/>
+    <mergeCell ref="I12:K12"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="I13:K13"/>
     <mergeCell ref="C14:E14"/>
+    <mergeCell ref="I14:K14"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H11:H12"/>
   </mergeCells>
-  <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="325">
   <si>
     <t>nightPlanQtyTotal</t>
   </si>
@@ -1810,6 +1810,30 @@
       </rPr>
       <t>u hóa</t>
     </r>
+  </si>
+  <si>
+    <t>{lhNightMachines}</t>
+  </si>
+  <si>
+    <t>{lhMorningMachines}</t>
+  </si>
+  <si>
+    <t>{lhMiddleMachines}</t>
+  </si>
+  <si>
+    <t>{lhTotalMachines}</t>
+  </si>
+  <si>
+    <t>{lhNightMachines2}</t>
+  </si>
+  <si>
+    <t>{lhMorningMachines2}</t>
+  </si>
+  <si>
+    <t>{lhMiddleMachines2}</t>
+  </si>
+  <si>
+    <t>{lhTotalMachines2}</t>
   </si>
   <si>
     <t xml:space="preserve">模具交替 Thay khuôn </t>
@@ -2121,8 +2145,32 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="0"/>
       <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2140,40 +2188,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Cambria"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5159,110 +5183,102 @@
       <c r="A10" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B10" s="9">
-        <f>COUNTIF(硫化日计划!$AE$6:AE1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="9">
-        <f>COUNTIF(硫化日计划!AM$6:$AM1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>COUNTIF(硫化日计划!$AU$6:AU1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <f>SUM(B10:D10)</f>
-        <v>0</v>
+      <c r="B10" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="H10" s="9">
-        <f>COUNTIF(硫化日计划!$BC$6:BC1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <f>COUNTIF(硫化日计划!BK$6:$BK1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <f>COUNTIF(硫化日计划!$BS$6:BS1048576,"&gt;0")</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <f>SUM(H10:J10)</f>
-        <v>0</v>
+      <c r="H10" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:11">
       <c r="A11" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="12"/>
       <c r="F11" s="5"/>
       <c r="G11" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="12"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11">
       <c r="A12" s="7" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="13" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="12"/>
       <c r="F12" s="5"/>
       <c r="G12" s="7" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="13" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="12"/>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:11">
       <c r="A13" s="20" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
       <c r="F13" s="5"/>
       <c r="G13" s="20" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -5270,20 +5286,20 @@
     <row r="14" ht="30" customHeight="1" spans="1:11">
       <c r="A14" s="22"/>
       <c r="B14" s="7" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D14" s="21"/>
       <c r="E14" s="21"/>
       <c r="F14" s="5"/>
       <c r="G14" s="22"/>
       <c r="H14" s="7" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="2"/>
+    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
     <sheet name="硫化换模计划" sheetId="36" r:id="rId2"/>
-    <sheet name="排产小结" sheetId="34" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">硫化换模计划!$A$4:$P$5</definedName>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="271">
   <si>
     <t>nightPlanQtyTotal</t>
   </si>
@@ -1587,305 +1586,13 @@
   </si>
   <si>
     <t>{.mouldCode}</t>
-  </si>
-  <si>
-    <t>{titleDate}</t>
-  </si>
-  <si>
-    <t>{titleDate2}</t>
-  </si>
-  <si>
-    <t>成型计划
- Thành hình</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜班 Ca đêm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">早班 Ca sáng </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中班 Ca tr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ư</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">a </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">合计 Tổng </t>
-  </si>
-  <si>
-    <t>{cxNightQty}</t>
-  </si>
-  <si>
-    <t>{cxMorningQty}</t>
-  </si>
-  <si>
-    <t>{cxMiddleQty}</t>
-  </si>
-  <si>
-    <t>{cxTotalQty}</t>
-  </si>
-  <si>
-    <t>{cxNightQty2}</t>
-  </si>
-  <si>
-    <t>{cxMorningQty2}</t>
-  </si>
-  <si>
-    <t>{cxMiddleQty2}</t>
-  </si>
-  <si>
-    <t>{cxTotalQty2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试制 Thử nghiệm </t>
-  </si>
-  <si>
-    <t>{cxSetupInfo}</t>
-  </si>
-  <si>
-    <t>{cxSetupInfo2}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>量试 Thử nghiệm số l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ư</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ợng</t>
-    </r>
-  </si>
-  <si>
-    <t>{cxTrialInfo}</t>
-  </si>
-  <si>
-    <t>{cxTrialInfo2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结构切换
-Thay quy cách </t>
-  </si>
-  <si>
-    <t>{cxSpecSwitch}</t>
-  </si>
-  <si>
-    <t>{cxSpecSwitch2}</t>
-  </si>
-  <si>
-    <t>TD胶种 
-Loại su nhỏ</t>
-  </si>
-  <si>
-    <t>{.rubberTypeName}</t>
-  </si>
-  <si>
-    <t>{.specPattern}</t>
-  </si>
-  <si>
-    <t>{.rubberTypeName2}</t>
-  </si>
-  <si>
-    <t>{.specPattern2}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硫化计划
- L</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Cambria"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ư</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>u hóa</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硫化开动
-Số l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ư</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ợng máy l</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ư</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>u hóa</t>
-    </r>
-  </si>
-  <si>
-    <t>{lhNightMachines}</t>
-  </si>
-  <si>
-    <t>{lhMorningMachines}</t>
-  </si>
-  <si>
-    <t>{lhMiddleMachines}</t>
-  </si>
-  <si>
-    <t>{lhTotalMachines}</t>
-  </si>
-  <si>
-    <t>{lhNightMachines2}</t>
-  </si>
-  <si>
-    <t>{lhMorningMachines2}</t>
-  </si>
-  <si>
-    <t>{lhMiddleMachines2}</t>
-  </si>
-  <si>
-    <t>{lhTotalMachines2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模具交替 Thay khuôn </t>
-  </si>
-  <si>
-    <t>{mouldCleanDate}</t>
-  </si>
-  <si>
-    <t>{mouldChangeInfo}</t>
-  </si>
-  <si>
-    <t>{mouldCleanDate2}</t>
-  </si>
-  <si>
-    <t>{mouldChangeInfo2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模具清洗 Vệ sinh khuôn </t>
-  </si>
-  <si>
-    <t>{mouldCleanInfo}</t>
-  </si>
-  <si>
-    <t>{mouldCleanInfo2}</t>
-  </si>
-  <si>
-    <t>备注 Ghi chú</t>
-  </si>
-  <si>
-    <t>成型</t>
-  </si>
-  <si>
-    <t>{cxRemark}</t>
-  </si>
-  <si>
-    <t>{cxRemark2}</t>
-  </si>
-  <si>
-    <t>硫化</t>
-  </si>
-  <si>
-    <t>{lhRemark}</t>
-  </si>
-  <si>
-    <t>{lhRemark2}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1893,12 +1600,11 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="m/d;@"/>
     <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="179" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="180" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="182" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="41">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1906,37 +1612,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="8"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1957,7 +1632,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -2145,14 +1839,14 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2169,8 +1863,8 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2185,19 +1879,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2419,7 +2100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2431,100 +2112,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -2554,6 +2141,45 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2687,19 +2313,28 @@
   </borders>
   <cellStyleXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2708,222 +2343,149 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
@@ -2932,118 +2494,130 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="10" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="11" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="5" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3821,825 +3395,825 @@
       </c>
     </row>
     <row r="2" ht="37.5" customHeight="1" spans="1:81">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="39" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="40" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="41"/>
-      <c r="CB2" s="41"/>
-      <c r="CC2" s="5"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="17"/>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AL2" s="17"/>
+      <c r="AM2" s="17"/>
+      <c r="AN2" s="17"/>
+      <c r="AO2" s="17"/>
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="17"/>
+      <c r="AS2" s="17"/>
+      <c r="AT2" s="17"/>
+      <c r="AU2" s="17"/>
+      <c r="AV2" s="17"/>
+      <c r="AW2" s="17"/>
+      <c r="AX2" s="17"/>
+      <c r="AY2" s="17"/>
+      <c r="AZ2" s="17"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="17"/>
+      <c r="BC2" s="17"/>
+      <c r="BD2" s="17"/>
+      <c r="BE2" s="17"/>
+      <c r="BF2" s="17"/>
+      <c r="BG2" s="17"/>
+      <c r="BH2" s="17"/>
+      <c r="BI2" s="17"/>
+      <c r="BJ2" s="17"/>
+      <c r="BK2" s="17"/>
+      <c r="BL2" s="17"/>
+      <c r="BM2" s="17"/>
+      <c r="BN2" s="17"/>
+      <c r="BO2" s="17"/>
+      <c r="BP2" s="17"/>
+      <c r="BQ2" s="17"/>
+      <c r="BR2" s="17"/>
+      <c r="BS2" s="17"/>
+      <c r="BT2" s="17"/>
+      <c r="BU2" s="17"/>
+      <c r="BV2" s="17"/>
+      <c r="BW2" s="17"/>
+      <c r="BX2" s="17"/>
+      <c r="BY2" s="17"/>
+      <c r="BZ2" s="17"/>
+      <c r="CA2" s="20"/>
+      <c r="CB2" s="20"/>
+      <c r="CC2" s="17"/>
     </row>
     <row r="3" ht="16.9" customHeight="1" spans="1:81">
-      <c r="A3" s="42">
+      <c r="A3" s="21">
         <f>SUM(A6:A108139)</f>
         <v>0</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="42">
+      <c r="B3" s="22"/>
+      <c r="C3" s="21">
         <f>SUM(C6:C108139)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="45" t="s">
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44">
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23">
         <f>SUM(O6:O108139)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="42">
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="21">
         <f>SUM(W6:W108139)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
-      <c r="AE3" s="42">
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21">
         <f>SUM(AE6:AE108139)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="42">
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="21"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="21"/>
+      <c r="AM3" s="21">
         <f>SUM(AM6:AM108139)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="42"/>
-      <c r="AP3" s="46"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="42"/>
-      <c r="AS3" s="42"/>
-      <c r="AT3" s="42"/>
-      <c r="AU3" s="46">
+      <c r="AN3" s="21"/>
+      <c r="AO3" s="21"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="21"/>
+      <c r="AR3" s="21"/>
+      <c r="AS3" s="21"/>
+      <c r="AT3" s="21"/>
+      <c r="AU3" s="25">
         <f>SUM(AU6:AU108139)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="46"/>
-      <c r="BA3" s="42"/>
-      <c r="BB3" s="42"/>
-      <c r="BC3" s="42">
+      <c r="AV3" s="21"/>
+      <c r="AW3" s="21"/>
+      <c r="AX3" s="21"/>
+      <c r="AY3" s="21"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="21"/>
+      <c r="BB3" s="21"/>
+      <c r="BC3" s="21">
         <f>SUM(BC6:BC108139)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="42"/>
-      <c r="BE3" s="46"/>
-      <c r="BF3" s="44"/>
-      <c r="BG3" s="44"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="43"/>
-      <c r="BJ3" s="47"/>
-      <c r="BK3" s="42">
+      <c r="BD3" s="21"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="22"/>
+      <c r="BJ3" s="26"/>
+      <c r="BK3" s="21">
         <f>SUM(BK6:BK108139)</f>
         <v>0</v>
       </c>
-      <c r="BL3" s="43"/>
-      <c r="BM3" s="43"/>
-      <c r="BN3" s="43"/>
-      <c r="BO3" s="43"/>
-      <c r="BP3" s="43"/>
-      <c r="BQ3" s="43"/>
-      <c r="BR3" s="43"/>
-      <c r="BS3" s="42">
+      <c r="BL3" s="22"/>
+      <c r="BM3" s="22"/>
+      <c r="BN3" s="22"/>
+      <c r="BO3" s="22"/>
+      <c r="BP3" s="22"/>
+      <c r="BQ3" s="22"/>
+      <c r="BR3" s="22"/>
+      <c r="BS3" s="21">
         <f>SUM(BS6:BS108139)</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="43"/>
-      <c r="BU3" s="43"/>
-      <c r="BV3" s="43"/>
-      <c r="BW3" s="43"/>
-      <c r="BX3" s="43"/>
-      <c r="BY3" s="43"/>
-      <c r="BZ3" s="48"/>
-      <c r="CA3" s="43"/>
-      <c r="CB3" s="43"/>
-      <c r="CC3" s="43"/>
+      <c r="BT3" s="22"/>
+      <c r="BU3" s="22"/>
+      <c r="BV3" s="22"/>
+      <c r="BW3" s="22"/>
+      <c r="BX3" s="22"/>
+      <c r="BY3" s="22"/>
+      <c r="BZ3" s="27"/>
+      <c r="CA3" s="22"/>
+      <c r="CB3" s="22"/>
+      <c r="CC3" s="22"/>
     </row>
     <row r="4" ht="34.5" spans="1:81">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="L4" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="51" t="s">
+      <c r="M4" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="64" t="s">
+      <c r="N4" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="64" t="s">
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="52"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="53" t="s">
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="53"/>
-      <c r="AI4" s="53"/>
-      <c r="AJ4" s="53"/>
-      <c r="AK4" s="53"/>
-      <c r="AL4" s="53" t="s">
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="53"/>
-      <c r="AN4" s="53"/>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="53"/>
-      <c r="AQ4" s="53"/>
-      <c r="AR4" s="53"/>
-      <c r="AS4" s="53"/>
-      <c r="AT4" s="53" t="s">
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="53"/>
-      <c r="AV4" s="53"/>
-      <c r="AW4" s="53"/>
-      <c r="AX4" s="53"/>
-      <c r="AY4" s="53"/>
-      <c r="AZ4" s="53"/>
-      <c r="BA4" s="53"/>
-      <c r="BB4" s="54" t="s">
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="32"/>
+      <c r="AY4" s="32"/>
+      <c r="AZ4" s="32"/>
+      <c r="BA4" s="32"/>
+      <c r="BB4" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="54"/>
-      <c r="BD4" s="54"/>
-      <c r="BE4" s="54"/>
-      <c r="BF4" s="54"/>
-      <c r="BG4" s="54"/>
-      <c r="BH4" s="54"/>
-      <c r="BI4" s="54"/>
-      <c r="BJ4" s="54" t="s">
+      <c r="BC4" s="33"/>
+      <c r="BD4" s="33"/>
+      <c r="BE4" s="33"/>
+      <c r="BF4" s="33"/>
+      <c r="BG4" s="33"/>
+      <c r="BH4" s="33"/>
+      <c r="BI4" s="33"/>
+      <c r="BJ4" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="BK4" s="54"/>
-      <c r="BL4" s="54"/>
-      <c r="BM4" s="54"/>
-      <c r="BN4" s="54"/>
-      <c r="BO4" s="54"/>
-      <c r="BP4" s="54"/>
-      <c r="BQ4" s="54"/>
-      <c r="BR4" s="54" t="s">
+      <c r="BK4" s="33"/>
+      <c r="BL4" s="33"/>
+      <c r="BM4" s="33"/>
+      <c r="BN4" s="33"/>
+      <c r="BO4" s="33"/>
+      <c r="BP4" s="33"/>
+      <c r="BQ4" s="33"/>
+      <c r="BR4" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="BS4" s="54"/>
-      <c r="BT4" s="54"/>
-      <c r="BU4" s="54"/>
-      <c r="BV4" s="54"/>
-      <c r="BW4" s="54"/>
-      <c r="BX4" s="54"/>
-      <c r="BY4" s="54"/>
-      <c r="BZ4" s="51" t="s">
+      <c r="BS4" s="33"/>
+      <c r="BT4" s="33"/>
+      <c r="BU4" s="33"/>
+      <c r="BV4" s="33"/>
+      <c r="BW4" s="33"/>
+      <c r="BX4" s="33"/>
+      <c r="BY4" s="33"/>
+      <c r="BZ4" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="CA4" s="51" t="s">
+      <c r="CA4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="CB4" s="51" t="s">
+      <c r="CB4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="CC4" s="51" t="s">
+      <c r="CC4" s="30" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" ht="47" spans="1:81">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="55" t="s">
+      <c r="I5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="55" t="s">
+      <c r="J5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="55" t="s">
+      <c r="M5" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="52" t="s">
+      <c r="N5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="52" t="s">
+      <c r="O5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="52" t="s">
+      <c r="P5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="Q5" s="52" t="s">
+      <c r="Q5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="R5" s="52" t="s">
+      <c r="R5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="52" t="s">
+      <c r="S5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="52" t="s">
+      <c r="T5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="U5" s="52" t="s">
+      <c r="U5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="V5" s="52" t="s">
+      <c r="V5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="W5" s="52" t="s">
+      <c r="W5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="52" t="s">
+      <c r="X5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="Y5" s="52" t="s">
+      <c r="Y5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="Z5" s="52" t="s">
+      <c r="Z5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AA5" s="52" t="s">
+      <c r="AA5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AB5" s="52" t="s">
+      <c r="AB5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AC5" s="52" t="s">
+      <c r="AC5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AD5" s="56" t="s">
+      <c r="AD5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="AE5" s="56" t="s">
+      <c r="AE5" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="AF5" s="56" t="s">
+      <c r="AF5" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="AG5" s="56" t="s">
+      <c r="AG5" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="AH5" s="56" t="s">
+      <c r="AH5" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="AI5" s="56" t="s">
+      <c r="AI5" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="AJ5" s="56" t="s">
+      <c r="AJ5" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AK5" s="56" t="s">
+      <c r="AK5" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="AL5" s="56" t="s">
+      <c r="AL5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="AM5" s="56" t="s">
+      <c r="AM5" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="AN5" s="56" t="s">
+      <c r="AN5" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="AO5" s="56" t="s">
+      <c r="AO5" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="AP5" s="56" t="s">
+      <c r="AP5" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="AQ5" s="56" t="s">
+      <c r="AQ5" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="AR5" s="56" t="s">
+      <c r="AR5" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AS5" s="56" t="s">
+      <c r="AS5" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="AT5" s="56" t="s">
+      <c r="AT5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="AU5" s="56" t="s">
+      <c r="AU5" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="AV5" s="56" t="s">
+      <c r="AV5" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="AW5" s="56" t="s">
+      <c r="AW5" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="AX5" s="56" t="s">
+      <c r="AX5" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="AY5" s="56" t="s">
+      <c r="AY5" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="AZ5" s="56" t="s">
+      <c r="AZ5" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="BA5" s="56" t="s">
+      <c r="BA5" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="BB5" s="57" t="s">
+      <c r="BB5" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="BC5" s="57" t="s">
+      <c r="BC5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="BD5" s="57" t="s">
+      <c r="BD5" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="BE5" s="57" t="s">
+      <c r="BE5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="BF5" s="57" t="s">
+      <c r="BF5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="BG5" s="57" t="s">
+      <c r="BG5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="BH5" s="57" t="s">
+      <c r="BH5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="BI5" s="57" t="s">
+      <c r="BI5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="BJ5" s="57" t="s">
+      <c r="BJ5" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="BK5" s="57" t="s">
+      <c r="BK5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="BL5" s="57" t="s">
+      <c r="BL5" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="BM5" s="57" t="s">
+      <c r="BM5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="BN5" s="57" t="s">
+      <c r="BN5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="BO5" s="57" t="s">
+      <c r="BO5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="BP5" s="57" t="s">
+      <c r="BP5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="BQ5" s="57" t="s">
+      <c r="BQ5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="BR5" s="57" t="s">
+      <c r="BR5" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="BS5" s="57" t="s">
+      <c r="BS5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="BT5" s="57" t="s">
+      <c r="BT5" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="BU5" s="57" t="s">
+      <c r="BU5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="BV5" s="57" t="s">
+      <c r="BV5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="BW5" s="57" t="s">
+      <c r="BW5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" s="57" t="s">
+      <c r="BX5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="BY5" s="57" t="s">
+      <c r="BY5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="BZ5" s="55" t="s">
+      <c r="BZ5" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="CA5" s="55" t="s">
+      <c r="CA5" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="CB5" s="55" t="s">
+      <c r="CB5" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="CC5" s="55" t="s">
+      <c r="CC5" s="34" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:81">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="59" t="s">
+      <c r="I6" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="61" t="s">
+      <c r="N6" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="O6" s="58" t="s">
+      <c r="O6" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="P6" s="58" t="s">
+      <c r="P6" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="Q6" s="58" t="s">
+      <c r="Q6" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="R6" s="58" t="s">
+      <c r="R6" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="S6" s="58" t="s">
+      <c r="S6" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="T6" s="58" t="s">
+      <c r="T6" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="U6" s="58" t="s">
+      <c r="U6" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="V6" s="58" t="s">
+      <c r="V6" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="W6" s="58" t="s">
+      <c r="W6" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="X6" s="58" t="s">
+      <c r="X6" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="Y6" s="58" t="s">
+      <c r="Y6" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="Z6" s="58" t="s">
+      <c r="Z6" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="AA6" s="58" t="s">
+      <c r="AA6" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="AB6" s="58" t="s">
+      <c r="AB6" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="AC6" s="58" t="s">
+      <c r="AC6" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="AD6" s="58" t="s">
+      <c r="AD6" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="AE6" s="58" t="s">
+      <c r="AE6" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="AF6" s="58" t="s">
+      <c r="AF6" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="AG6" s="58" t="s">
+      <c r="AG6" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="AH6" s="58" t="s">
+      <c r="AH6" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="AI6" s="58" t="s">
+      <c r="AI6" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="AJ6" s="58" t="s">
+      <c r="AJ6" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="58" t="s">
+      <c r="AK6" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="AL6" s="58" t="s">
+      <c r="AL6" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="AM6" s="58" t="s">
+      <c r="AM6" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="AN6" s="58" t="s">
+      <c r="AN6" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="AO6" s="58" t="s">
+      <c r="AO6" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="AP6" s="58" t="s">
+      <c r="AP6" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="AQ6" s="58" t="s">
+      <c r="AQ6" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="AR6" s="58" t="s">
+      <c r="AR6" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="AS6" s="58" t="s">
+      <c r="AS6" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="AT6" s="58" t="s">
+      <c r="AT6" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="AU6" s="58" t="s">
+      <c r="AU6" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="AV6" s="58" t="s">
+      <c r="AV6" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="AW6" s="58" t="s">
+      <c r="AW6" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="AX6" s="58" t="s">
+      <c r="AX6" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AY6" s="58" t="s">
+      <c r="AY6" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="AZ6" s="58" t="s">
+      <c r="AZ6" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="BA6" s="58" t="s">
+      <c r="BA6" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="BB6" s="58" t="s">
+      <c r="BB6" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="BC6" s="58" t="s">
+      <c r="BC6" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="BD6" s="58" t="s">
+      <c r="BD6" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="BE6" s="58" t="s">
+      <c r="BE6" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="BF6" s="58" t="s">
+      <c r="BF6" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="BG6" s="58" t="s">
+      <c r="BG6" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="BH6" s="58" t="s">
+      <c r="BH6" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="BI6" s="58" t="s">
+      <c r="BI6" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="BJ6" s="58" t="s">
+      <c r="BJ6" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="BK6" s="58" t="s">
+      <c r="BK6" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="BL6" s="58" t="s">
+      <c r="BL6" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="BM6" s="58" t="s">
+      <c r="BM6" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BN6" s="58" t="s">
+      <c r="BN6" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BO6" s="58" t="s">
+      <c r="BO6" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="BP6" s="58" t="s">
+      <c r="BP6" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="BQ6" s="58" t="s">
+      <c r="BQ6" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="BR6" s="58" t="s">
+      <c r="BR6" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="BS6" s="58" t="s">
+      <c r="BS6" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="BT6" s="58" t="s">
+      <c r="BT6" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="BU6" s="58" t="s">
+      <c r="BU6" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="BV6" s="58" t="s">
+      <c r="BV6" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="BW6" s="58" t="s">
+      <c r="BW6" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="BX6" s="58" t="s">
+      <c r="BX6" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="BY6" s="62" t="s">
+      <c r="BY6" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="BZ6" s="63" t="s">
+      <c r="BZ6" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="CA6" s="63" t="s">
+      <c r="CA6" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="CB6" s="7" t="s">
+      <c r="CB6" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="CC6" s="7" t="s">
+      <c r="CC6" s="39" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4679,239 +4253,239 @@
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="26" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="23" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="25" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="27" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="25" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="27" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="27" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="27" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="23" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="23" customWidth="1"/>
-    <col min="16" max="16" width="9" style="23" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="23"/>
+    <col min="1" max="1" width="3" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="4" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="23" customFormat="1" hidden="1" spans="1:16">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="1" customFormat="1" hidden="1" spans="1:16">
+      <c r="A1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="2" ht="33.75" customHeight="1" spans="1:16">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="32"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="10"/>
     </row>
-    <row r="3" s="24" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
-      <c r="A3" s="33" t="s">
+    <row r="3" s="2" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
+      <c r="A3" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="L3" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="M3" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="O3" s="33" t="s">
+      <c r="O3" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="P3" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" s="24" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
-      <c r="A4" s="34" t="s">
+    <row r="4" s="2" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+      <c r="A4" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="N4" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O4" s="34" t="s">
+      <c r="O4" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="P4" s="34" t="s">
+      <c r="P4" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="5" ht="11.45" customHeight="1" spans="1:16">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="M5" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="N5" s="28" t="s">
+      <c r="N5" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="O5" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="P5" s="35" t="s">
+      <c r="P5" s="13" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4924,416 +4498,4 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="11.5"/>
-  <cols>
-    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
-    <col min="2" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" style="1"/>
-    <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
-    <col min="8" max="11" width="15.625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.75" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34.5" customHeight="1" spans="1:11">
-      <c r="A1" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" ht="25.15" customHeight="1" spans="1:11">
-      <c r="A2" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3" ht="25.15" customHeight="1" spans="1:11">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:11">
-      <c r="A4" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:11">
-      <c r="A5" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="12"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:11">
-      <c r="A6" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" ht="90" customHeight="1" spans="1:11">
-      <c r="A7" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" ht="25.15" customHeight="1" spans="1:11">
-      <c r="A8" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" ht="25.15" customHeight="1" spans="1:11">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9">
-        <f>硫化日计划!AE3</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="9">
-        <f>硫化日计划!AM3</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
-        <f>硫化日计划!AU3</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
-        <f>SUM(B9:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9">
-        <f>硫化日计划!BC3</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="9">
-        <f>硫化日计划!BK3</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
-        <f>硫化日计划!BS3</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <f>SUM(H9:J9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="25.15" customHeight="1" spans="1:11">
-      <c r="A10" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:11">
-      <c r="A11" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:11">
-      <c r="A12" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:11">
-      <c r="A13" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:11">
-      <c r="A14" s="22"/>
-      <c r="B14" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H11:H12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D607560-BF16-4A87-A307-A1257CA9D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550" tabRatio="844" activeTab="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -282,6 +288,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">{yearmonthday}全钢硫化工程生产计划单
@@ -293,7 +300,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Đơ</t>
     </r>
@@ -303,6 +310,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n k</t>
@@ -313,7 +321,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ế</t>
     </r>
@@ -323,6 +331,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ho</t>
@@ -333,7 +342,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -343,6 +352,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ch s</t>
@@ -353,7 +363,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -363,6 +373,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n xu</t>
@@ -373,7 +384,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ấ</t>
     </r>
@@ -383,6 +394,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>t c</t>
@@ -393,7 +405,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ủ</t>
     </r>
@@ -403,6 +415,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">a công </t>
@@ -413,7 +426,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -423,6 +436,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>o</t>
@@ -433,7 +447,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -443,6 +457,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n l</t>
@@ -453,7 +468,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ư</t>
     </r>
@@ -463,6 +478,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u hóa toàn thép</t>
@@ -474,6 +490,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 版本号phiên b</t>
@@ -483,7 +500,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ả</t>
     </r>
@@ -492,6 +509,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n：{batchNo}</t>
@@ -553,6 +571,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -562,7 +581,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -571,6 +590,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate2}</t>
@@ -582,6 +602,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -591,7 +612,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -600,6 +621,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate3}</t>
@@ -614,6 +636,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -623,7 +646,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -632,6 +655,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate5}</t>
@@ -643,6 +667,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">夜班 Ca </t>
@@ -652,7 +677,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Cambria"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -661,6 +686,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>êm {shiftDate6}</t>
@@ -675,6 +701,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>中班 Ca chi</t>
@@ -684,7 +711,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>ề</t>
     </r>
@@ -693,6 +720,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>u {shiftDate8}</t>
@@ -753,6 +781,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>S</t>
@@ -762,7 +791,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -771,6 +800,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> l</t>
@@ -780,7 +810,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ầ</t>
     </r>
@@ -789,6 +819,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>n s</t>
@@ -798,7 +829,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ử</t>
     </r>
@@ -807,6 +838,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> d</t>
@@ -816,7 +848,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ụ</t>
     </r>
@@ -825,6 +857,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng phao L/R</t>
@@ -867,6 +900,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>T</t>
@@ -876,7 +910,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -885,6 +919,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">ng </t>
@@ -894,7 +929,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -903,6 +938,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy TH</t>
@@ -1189,9 +1225,6 @@
   </si>
   <si>
     <t>{afterMaterialType}</t>
-  </si>
-  <si>
-    <t>{endType}</t>
   </si>
   <si>
     <t>{isDryIceClean}</t>
@@ -1287,6 +1320,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Lo</t>
@@ -1296,7 +1330,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ạ</t>
     </r>
@@ -1305,6 +1339,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i ph</t>
@@ -1314,7 +1349,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ươ</t>
     </r>
@@ -1323,6 +1358,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng th</t>
@@ -1332,7 +1368,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ứ</t>
     </r>
@@ -1341,6 +1377,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1352,6 +1389,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Xu</t>
@@ -1361,7 +1399,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1370,6 +1408,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>ng máy theo th</t>
@@ -1379,7 +1418,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ờ</t>
     </r>
@@ -1388,6 +1427,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>i gian</t>
@@ -1399,6 +1439,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1408,7 +1449,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1417,6 +1458,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh </t>
@@ -1426,7 +1468,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Segoe UI"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>đ</t>
     </r>
@@ -1435,6 +1477,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">á </t>
@@ -1446,6 +1489,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>V</t>
@@ -1455,7 +1499,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ệ</t>
     </r>
@@ -1464,6 +1508,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> sinh cát （VSC）</t>
@@ -1475,6 +1520,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Ch</t>
@@ -1484,7 +1530,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ỉ</t>
     </r>
@@ -1493,6 +1539,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> thay l</t>
@@ -1502,7 +1549,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ắ</t>
     </r>
@@ -1511,6 +1558,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -1522,6 +1570,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>Mã s</t>
@@ -1531,7 +1580,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ố</t>
     </r>
@@ -1540,6 +1589,7 @@
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> khuôn （MSK）</t>
@@ -1586,25 +1636,26 @@
   </si>
   <si>
     <t>{.mouldCode}</t>
+  </si>
+  <si>
+    <t>{changeType}</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="m/d;@"/>
-    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="m/d;@"/>
+    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="181" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="182" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="183" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1613,40 +1664,47 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1654,179 +1712,21 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1834,6 +1734,26 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1841,48 +1761,61 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cambria"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1913,194 +1846,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -2212,364 +1959,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="61">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="46">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="58" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="58" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2581,108 +2131,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="61">
+  <cellStyles count="13">
+    <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 12 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 20 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 91" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Comma 2" xfId="49"/>
-    <cellStyle name="Excel Built-in Normal" xfId="50"/>
-    <cellStyle name="Normal 10" xfId="51"/>
-    <cellStyle name="Normal 12 3" xfId="52"/>
-    <cellStyle name="Normal 2 2" xfId="53"/>
-    <cellStyle name="Normal 20 3" xfId="54"/>
-    <cellStyle name="Normal 91" xfId="55"/>
-    <cellStyle name="Percent 2" xfId="56"/>
-    <cellStyle name="常规 2" xfId="57"/>
-    <cellStyle name="常规 2 5" xfId="58"/>
-    <cellStyle name="千位分隔 3" xfId="59"/>
-    <cellStyle name="千位分隔 3 3" xfId="60"/>
+    <cellStyle name="常规 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 2 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="千位分隔 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔 3 3" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2701,12 +2164,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2722,13 +2188,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2753,7 +2225,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2769,13 +2241,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 21"/>
+        <xdr:cNvPr id="2" name="图片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3106,50 +2584,51 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="3" width="5.625" customWidth="1"/>
+    <col min="1" max="3" width="5.59765625" customWidth="1"/>
     <col min="4" max="4" width="6.5" customWidth="1"/>
-    <col min="5" max="5" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="32.625" customWidth="1"/>
-    <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="32.625" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
-    <col min="10" max="11" width="5.625" customWidth="1"/>
-    <col min="12" max="12" width="6.125" customWidth="1"/>
-    <col min="13" max="13" width="5.625" customWidth="1"/>
-    <col min="14" max="14" width="3.125" customWidth="1"/>
-    <col min="15" max="21" width="5.125" customWidth="1"/>
-    <col min="22" max="22" width="3.125" customWidth="1"/>
-    <col min="23" max="29" width="5.125" customWidth="1"/>
-    <col min="30" max="30" width="3.125" customWidth="1"/>
-    <col min="31" max="37" width="5.125" customWidth="1"/>
-    <col min="38" max="38" width="3.125" customWidth="1"/>
-    <col min="39" max="45" width="5.125" customWidth="1"/>
-    <col min="46" max="46" width="3.125" customWidth="1"/>
-    <col min="47" max="53" width="5.125" customWidth="1"/>
-    <col min="54" max="54" width="3.125" customWidth="1"/>
-    <col min="55" max="61" width="5.125" customWidth="1"/>
-    <col min="62" max="62" width="3.125" customWidth="1"/>
-    <col min="63" max="69" width="5.125" customWidth="1"/>
-    <col min="70" max="70" width="3.125" customWidth="1"/>
-    <col min="71" max="77" width="5.125" customWidth="1"/>
-    <col min="78" max="78" width="9.625" customWidth="1"/>
-    <col min="79" max="79" width="7.625" customWidth="1"/>
-    <col min="80" max="80" width="9.625" customWidth="1"/>
-    <col min="81" max="81" width="25.75" customWidth="1"/>
+    <col min="5" max="5" width="9.59765625" customWidth="1"/>
+    <col min="6" max="6" width="32.59765625" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" customWidth="1"/>
+    <col min="8" max="8" width="32.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" customWidth="1"/>
+    <col min="10" max="11" width="5.59765625" customWidth="1"/>
+    <col min="12" max="12" width="6.09765625" customWidth="1"/>
+    <col min="13" max="13" width="5.59765625" customWidth="1"/>
+    <col min="14" max="14" width="3.09765625" customWidth="1"/>
+    <col min="15" max="21" width="5.09765625" customWidth="1"/>
+    <col min="22" max="22" width="3.09765625" customWidth="1"/>
+    <col min="23" max="29" width="5.09765625" customWidth="1"/>
+    <col min="30" max="30" width="3.09765625" customWidth="1"/>
+    <col min="31" max="37" width="5.09765625" customWidth="1"/>
+    <col min="38" max="38" width="3.09765625" customWidth="1"/>
+    <col min="39" max="45" width="5.09765625" customWidth="1"/>
+    <col min="46" max="46" width="3.09765625" customWidth="1"/>
+    <col min="47" max="53" width="5.09765625" customWidth="1"/>
+    <col min="54" max="54" width="3.09765625" customWidth="1"/>
+    <col min="55" max="61" width="5.09765625" customWidth="1"/>
+    <col min="62" max="62" width="3.09765625" customWidth="1"/>
+    <col min="63" max="69" width="5.09765625" customWidth="1"/>
+    <col min="70" max="70" width="3.09765625" customWidth="1"/>
+    <col min="71" max="77" width="5.09765625" customWidth="1"/>
+    <col min="78" max="78" width="9.59765625" customWidth="1"/>
+    <col min="79" max="79" width="7.59765625" customWidth="1"/>
+    <col min="80" max="80" width="9.59765625" customWidth="1"/>
+    <col min="81" max="81" width="25.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:81">
+    <row r="1" spans="1:81" hidden="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3394,26 +2873,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" ht="37.5" customHeight="1" spans="1:81">
+    <row r="2" spans="1:81" ht="37.5" customHeight="1">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
       <c r="I2" s="17"/>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="18" t="s">
         <v>82</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
-      <c r="O2" s="20"/>
+      <c r="O2" s="19"/>
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
@@ -3451,7 +2930,7 @@
       <c r="AX2" s="17"/>
       <c r="AY2" s="17"/>
       <c r="AZ2" s="17"/>
-      <c r="BA2" s="20"/>
+      <c r="BA2" s="19"/>
       <c r="BB2" s="17"/>
       <c r="BC2" s="17"/>
       <c r="BD2" s="17"/>
@@ -3477,799 +2956,799 @@
       <c r="BX2" s="17"/>
       <c r="BY2" s="17"/>
       <c r="BZ2" s="17"/>
-      <c r="CA2" s="20"/>
-      <c r="CB2" s="20"/>
+      <c r="CA2" s="19"/>
+      <c r="CB2" s="19"/>
       <c r="CC2" s="17"/>
     </row>
-    <row r="3" ht="16.9" customHeight="1" spans="1:81">
-      <c r="A3" s="21">
+    <row r="3" spans="1:81" ht="16.95" customHeight="1">
+      <c r="A3" s="20">
         <f>SUM(A6:A108139)</f>
         <v>0</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="21">
+      <c r="B3" s="21"/>
+      <c r="C3" s="20">
         <f>SUM(C6:C108139)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="24" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23">
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22">
         <f>SUM(O6:O108139)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="21">
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="20">
         <f>SUM(W6:W108139)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21">
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20">
         <f>SUM(AE6:AE108139)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="21"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="21"/>
-      <c r="AM3" s="21">
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="20"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="20"/>
+      <c r="AM3" s="20">
         <f>SUM(AM6:AM108139)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="21"/>
-      <c r="AO3" s="21"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="21"/>
-      <c r="AR3" s="21"/>
-      <c r="AS3" s="21"/>
-      <c r="AT3" s="21"/>
-      <c r="AU3" s="25">
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="24">
         <f>SUM(AU6:AU108139)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="21"/>
-      <c r="AW3" s="21"/>
-      <c r="AX3" s="21"/>
-      <c r="AY3" s="21"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="21"/>
-      <c r="BB3" s="21"/>
-      <c r="BC3" s="21">
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="24"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20">
         <f>SUM(BC6:BC108139)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="21"/>
-      <c r="BE3" s="25"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="23"/>
-      <c r="BH3" s="23"/>
-      <c r="BI3" s="22"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="21">
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="24"/>
+      <c r="BF3" s="22"/>
+      <c r="BG3" s="22"/>
+      <c r="BH3" s="22"/>
+      <c r="BI3" s="21"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="20">
         <f>SUM(BK6:BK108139)</f>
         <v>0</v>
       </c>
-      <c r="BL3" s="22"/>
-      <c r="BM3" s="22"/>
-      <c r="BN3" s="22"/>
-      <c r="BO3" s="22"/>
-      <c r="BP3" s="22"/>
-      <c r="BQ3" s="22"/>
-      <c r="BR3" s="22"/>
-      <c r="BS3" s="21">
+      <c r="BL3" s="21"/>
+      <c r="BM3" s="21"/>
+      <c r="BN3" s="21"/>
+      <c r="BO3" s="21"/>
+      <c r="BP3" s="21"/>
+      <c r="BQ3" s="21"/>
+      <c r="BR3" s="21"/>
+      <c r="BS3" s="20">
         <f>SUM(BS6:BS108139)</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="22"/>
-      <c r="BU3" s="22"/>
-      <c r="BV3" s="22"/>
-      <c r="BW3" s="22"/>
-      <c r="BX3" s="22"/>
-      <c r="BY3" s="22"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="22"/>
-      <c r="CB3" s="22"/>
-      <c r="CC3" s="22"/>
+      <c r="BT3" s="21"/>
+      <c r="BU3" s="21"/>
+      <c r="BV3" s="21"/>
+      <c r="BW3" s="21"/>
+      <c r="BX3" s="21"/>
+      <c r="BY3" s="21"/>
+      <c r="BZ3" s="26"/>
+      <c r="CA3" s="21"/>
+      <c r="CB3" s="21"/>
+      <c r="CC3" s="21"/>
     </row>
-    <row r="4" ht="34.5" spans="1:81">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:81" ht="34.200000000000003">
+      <c r="A4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="46" t="s">
+      <c r="N4" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="46" t="s">
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="32" t="s">
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32" t="s">
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="32"/>
-      <c r="AO4" s="32"/>
-      <c r="AP4" s="32"/>
-      <c r="AQ4" s="32"/>
-      <c r="AR4" s="32"/>
-      <c r="AS4" s="32"/>
-      <c r="AT4" s="32" t="s">
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="32"/>
-      <c r="AV4" s="32"/>
-      <c r="AW4" s="32"/>
-      <c r="AX4" s="32"/>
-      <c r="AY4" s="32"/>
-      <c r="AZ4" s="32"/>
-      <c r="BA4" s="32"/>
-      <c r="BB4" s="33" t="s">
+      <c r="AU4" s="47"/>
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47"/>
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="47"/>
+      <c r="BA4" s="47"/>
+      <c r="BB4" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="33"/>
-      <c r="BD4" s="33"/>
-      <c r="BE4" s="33"/>
-      <c r="BF4" s="33"/>
-      <c r="BG4" s="33"/>
-      <c r="BH4" s="33"/>
-      <c r="BI4" s="33"/>
-      <c r="BJ4" s="33" t="s">
+      <c r="BC4" s="48"/>
+      <c r="BD4" s="48"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="48"/>
+      <c r="BG4" s="48"/>
+      <c r="BH4" s="48"/>
+      <c r="BI4" s="48"/>
+      <c r="BJ4" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="BK4" s="33"/>
-      <c r="BL4" s="33"/>
-      <c r="BM4" s="33"/>
-      <c r="BN4" s="33"/>
-      <c r="BO4" s="33"/>
-      <c r="BP4" s="33"/>
-      <c r="BQ4" s="33"/>
-      <c r="BR4" s="33" t="s">
+      <c r="BK4" s="48"/>
+      <c r="BL4" s="48"/>
+      <c r="BM4" s="48"/>
+      <c r="BN4" s="48"/>
+      <c r="BO4" s="48"/>
+      <c r="BP4" s="48"/>
+      <c r="BQ4" s="48"/>
+      <c r="BR4" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="BS4" s="33"/>
-      <c r="BT4" s="33"/>
-      <c r="BU4" s="33"/>
-      <c r="BV4" s="33"/>
-      <c r="BW4" s="33"/>
-      <c r="BX4" s="33"/>
-      <c r="BY4" s="33"/>
-      <c r="BZ4" s="30" t="s">
+      <c r="BS4" s="48"/>
+      <c r="BT4" s="48"/>
+      <c r="BU4" s="48"/>
+      <c r="BV4" s="48"/>
+      <c r="BW4" s="48"/>
+      <c r="BX4" s="48"/>
+      <c r="BY4" s="48"/>
+      <c r="BZ4" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="CA4" s="30" t="s">
+      <c r="CA4" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="CB4" s="30" t="s">
+      <c r="CB4" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="CC4" s="30" t="s">
+      <c r="CC4" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" ht="47" spans="1:81">
-      <c r="A5" s="28" t="s">
+    <row r="5" spans="1:81" ht="46.8">
+      <c r="A5" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="31" t="s">
+      <c r="O5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="31" t="s">
+      <c r="P5" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="Q5" s="31" t="s">
+      <c r="Q5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="R5" s="31" t="s">
+      <c r="R5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="31" t="s">
+      <c r="S5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="31" t="s">
+      <c r="T5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="U5" s="31" t="s">
+      <c r="U5" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="W5" s="31" t="s">
+      <c r="W5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="31" t="s">
+      <c r="X5" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="Y5" s="31" t="s">
+      <c r="Y5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="Z5" s="31" t="s">
+      <c r="Z5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="AA5" s="31" t="s">
+      <c r="AA5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AB5" s="31" t="s">
+      <c r="AB5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="AC5" s="31" t="s">
+      <c r="AC5" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="AD5" s="35" t="s">
+      <c r="AD5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AE5" s="35" t="s">
+      <c r="AE5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AG5" s="35" t="s">
+      <c r="AG5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AH5" s="35" t="s">
+      <c r="AH5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AI5" s="35" t="s">
+      <c r="AI5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AJ5" s="35" t="s">
+      <c r="AJ5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AK5" s="35" t="s">
+      <c r="AK5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AL5" s="35" t="s">
+      <c r="AL5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AM5" s="35" t="s">
+      <c r="AM5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AN5" s="35" t="s">
+      <c r="AN5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AO5" s="35" t="s">
+      <c r="AO5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AP5" s="35" t="s">
+      <c r="AP5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AQ5" s="35" t="s">
+      <c r="AQ5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AR5" s="35" t="s">
+      <c r="AR5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AS5" s="35" t="s">
+      <c r="AS5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AT5" s="35" t="s">
+      <c r="AT5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AU5" s="35" t="s">
+      <c r="AU5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AV5" s="35" t="s">
+      <c r="AV5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AW5" s="35" t="s">
+      <c r="AW5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AX5" s="35" t="s">
+      <c r="AX5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AY5" s="35" t="s">
+      <c r="AY5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AZ5" s="35" t="s">
+      <c r="AZ5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="BA5" s="35" t="s">
+      <c r="BA5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="BB5" s="36" t="s">
+      <c r="BB5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BC5" s="36" t="s">
+      <c r="BC5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BD5" s="36" t="s">
+      <c r="BD5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BE5" s="36" t="s">
+      <c r="BE5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BF5" s="36" t="s">
+      <c r="BF5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BG5" s="36" t="s">
+      <c r="BG5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BH5" s="36" t="s">
+      <c r="BH5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BI5" s="36" t="s">
+      <c r="BI5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BJ5" s="36" t="s">
+      <c r="BJ5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BK5" s="36" t="s">
+      <c r="BK5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BL5" s="36" t="s">
+      <c r="BL5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BM5" s="36" t="s">
+      <c r="BM5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BN5" s="36" t="s">
+      <c r="BN5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BO5" s="36" t="s">
+      <c r="BO5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BP5" s="36" t="s">
+      <c r="BP5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BQ5" s="36" t="s">
+      <c r="BQ5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BR5" s="36" t="s">
+      <c r="BR5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BS5" s="36" t="s">
+      <c r="BS5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BT5" s="36" t="s">
+      <c r="BT5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BU5" s="36" t="s">
+      <c r="BU5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BV5" s="36" t="s">
+      <c r="BV5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BW5" s="36" t="s">
+      <c r="BW5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" s="36" t="s">
+      <c r="BX5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BY5" s="36" t="s">
+      <c r="BY5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BZ5" s="34" t="s">
+      <c r="BZ5" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="CA5" s="34" t="s">
+      <c r="CA5" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="CB5" s="34" t="s">
+      <c r="CB5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="CC5" s="34" t="s">
+      <c r="CC5" s="30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" ht="80.1" customHeight="1" spans="1:81">
-      <c r="A6" s="37" t="s">
+    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1">
+      <c r="A6" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="41" t="s">
+      <c r="L6" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="N6" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="P6" s="37" t="s">
+      <c r="P6" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="Q6" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="R6" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="S6" s="37" t="s">
+      <c r="S6" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="T6" s="37" t="s">
+      <c r="T6" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="U6" s="37" t="s">
+      <c r="U6" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="V6" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="W6" s="37" t="s">
+      <c r="W6" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="X6" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="Y6" s="37" t="s">
+      <c r="Y6" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="Z6" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="AB6" s="37" t="s">
+      <c r="AB6" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="AC6" s="37" t="s">
+      <c r="AC6" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="AD6" s="37" t="s">
+      <c r="AD6" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AE6" s="37" t="s">
+      <c r="AE6" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="AF6" s="37" t="s">
+      <c r="AF6" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="AG6" s="37" t="s">
+      <c r="AG6" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="AH6" s="37" t="s">
+      <c r="AH6" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="AI6" s="37" t="s">
+      <c r="AI6" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="AJ6" s="37" t="s">
+      <c r="AJ6" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="37" t="s">
+      <c r="AK6" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="AL6" s="37" t="s">
+      <c r="AL6" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="AM6" s="37" t="s">
+      <c r="AM6" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="AN6" s="37" t="s">
+      <c r="AN6" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="AO6" s="37" t="s">
+      <c r="AO6" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="AP6" s="37" t="s">
+      <c r="AP6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AQ6" s="37" t="s">
+      <c r="AQ6" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="AR6" s="37" t="s">
+      <c r="AR6" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="AS6" s="37" t="s">
+      <c r="AS6" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="AT6" s="37" t="s">
+      <c r="AT6" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="AU6" s="37" t="s">
+      <c r="AU6" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="AV6" s="37" t="s">
+      <c r="AV6" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="AW6" s="37" t="s">
+      <c r="AW6" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AX6" s="37" t="s">
+      <c r="AX6" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AY6" s="37" t="s">
+      <c r="AY6" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AZ6" s="37" t="s">
+      <c r="AZ6" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="BA6" s="37" t="s">
+      <c r="BA6" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="BB6" s="37" t="s">
+      <c r="BB6" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="BC6" s="37" t="s">
+      <c r="BC6" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="BD6" s="37" t="s">
+      <c r="BD6" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="BE6" s="37" t="s">
+      <c r="BE6" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="BF6" s="37" t="s">
+      <c r="BF6" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="BG6" s="37" t="s">
+      <c r="BG6" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="BH6" s="37" t="s">
+      <c r="BH6" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="BI6" s="37" t="s">
+      <c r="BI6" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="BJ6" s="37" t="s">
+      <c r="BJ6" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="BK6" s="37" t="s">
+      <c r="BK6" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="BL6" s="37" t="s">
+      <c r="BL6" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="BM6" s="37" t="s">
+      <c r="BM6" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="BN6" s="37" t="s">
+      <c r="BN6" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="BO6" s="37" t="s">
+      <c r="BO6" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="BP6" s="37" t="s">
+      <c r="BP6" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="BQ6" s="37" t="s">
+      <c r="BQ6" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="BR6" s="37" t="s">
+      <c r="BR6" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="BS6" s="37" t="s">
+      <c r="BS6" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="BT6" s="37" t="s">
+      <c r="BT6" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="BU6" s="37" t="s">
+      <c r="BU6" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="BV6" s="37" t="s">
+      <c r="BV6" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="BW6" s="37" t="s">
+      <c r="BW6" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="BX6" s="37" t="s">
+      <c r="BX6" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="BY6" s="44" t="s">
+      <c r="BY6" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="BZ6" s="45" t="s">
+      <c r="BZ6" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="CA6" s="45" t="s">
+      <c r="CA6" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="CB6" s="39" t="s">
+      <c r="CB6" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="CC6" s="39" t="s">
+      <c r="CC6" s="35" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="AT4:BA4"/>
+    <mergeCell ref="BB4:BI4"/>
+    <mergeCell ref="BJ4:BQ4"/>
+    <mergeCell ref="BR4:BY4"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="N4:U4"/>
     <mergeCell ref="V4:AC4"/>
     <mergeCell ref="AD4:AK4"/>
-    <mergeCell ref="AL4:AS4"/>
-    <mergeCell ref="AT4:BA4"/>
-    <mergeCell ref="BB4:BI4"/>
-    <mergeCell ref="BJ4:BQ4"/>
-    <mergeCell ref="BR4:BY4"/>
   </mergeCells>
+  <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="F3:G3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="3" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="4" customWidth="1"/>
-    <col min="3" max="4" width="5.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="27.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="5.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.69921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="27.3984375" style="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="1" customWidth="1"/>
     <col min="17" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" hidden="1" spans="1:16">
+    <row r="1" spans="1:16" hidden="1">
       <c r="A1" s="3" t="s">
         <v>213</v>
       </c>
@@ -4301,25 +3780,25 @@
         <v>222</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>228</v>
-      </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" spans="1:16">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4327,7 +3806,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -4339,163 +3818,161 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="34.15" customHeight="1" spans="1:16">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>235</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>88</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>88</v>
       </c>
       <c r="J3" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>242</v>
       </c>
       <c r="P3" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="68.25" customHeight="1" spans="1:16">
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="68.25" customHeight="1">
       <c r="A4" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>245</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>111</v>
       </c>
       <c r="E4" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="M4" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>255</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>256</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="5" ht="11.45" customHeight="1" spans="1:16">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>258</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>259</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="I5" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="L5" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>270</v>
       </c>
       <c r="P5" s="13" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:P5" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D607560-BF16-4A87-A307-A1257CA9D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6671925E-A483-4789-B0C7-06909388C31D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化日计划" sheetId="35" r:id="rId1"/>
@@ -27,10 +27,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1648,14 +1648,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="m/d;@"/>
-    <numFmt numFmtId="180" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="181" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="182" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="183" formatCode="[$-10804]0;\(0\)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="m/d;@"/>
+    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="179" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="[$-10804]0;\(0\)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1962,15 +1962,15 @@
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1978,7 +1978,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1987,10 +1987,10 @@
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
@@ -1999,22 +1999,22 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2029,7 +2029,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2044,25 +2044,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2083,7 +2083,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2101,14 +2101,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2124,12 +2130,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2594,41 +2594,41 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:CC6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="3" width="5.59765625" customWidth="1"/>
+    <col min="1" max="3" width="5.625" customWidth="1"/>
     <col min="4" max="4" width="6.5" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" customWidth="1"/>
-    <col min="6" max="6" width="32.59765625" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" customWidth="1"/>
-    <col min="8" max="8" width="32.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.09765625" customWidth="1"/>
-    <col min="10" max="11" width="5.59765625" customWidth="1"/>
-    <col min="12" max="12" width="6.09765625" customWidth="1"/>
-    <col min="13" max="13" width="5.59765625" customWidth="1"/>
-    <col min="14" max="14" width="3.09765625" customWidth="1"/>
-    <col min="15" max="21" width="5.09765625" customWidth="1"/>
-    <col min="22" max="22" width="3.09765625" customWidth="1"/>
-    <col min="23" max="29" width="5.09765625" customWidth="1"/>
-    <col min="30" max="30" width="3.09765625" customWidth="1"/>
-    <col min="31" max="37" width="5.09765625" customWidth="1"/>
-    <col min="38" max="38" width="3.09765625" customWidth="1"/>
-    <col min="39" max="45" width="5.09765625" customWidth="1"/>
-    <col min="46" max="46" width="3.09765625" customWidth="1"/>
-    <col min="47" max="53" width="5.09765625" customWidth="1"/>
-    <col min="54" max="54" width="3.09765625" customWidth="1"/>
-    <col min="55" max="61" width="5.09765625" customWidth="1"/>
-    <col min="62" max="62" width="3.09765625" customWidth="1"/>
-    <col min="63" max="69" width="5.09765625" customWidth="1"/>
-    <col min="70" max="70" width="3.09765625" customWidth="1"/>
-    <col min="71" max="77" width="5.09765625" customWidth="1"/>
-    <col min="78" max="78" width="9.59765625" customWidth="1"/>
-    <col min="79" max="79" width="7.59765625" customWidth="1"/>
-    <col min="80" max="80" width="9.59765625" customWidth="1"/>
-    <col min="81" max="81" width="25.69921875" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="32.625" customWidth="1"/>
+    <col min="7" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="32.625" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="11" width="5.625" customWidth="1"/>
+    <col min="12" max="12" width="6.125" customWidth="1"/>
+    <col min="13" max="13" width="5.625" customWidth="1"/>
+    <col min="14" max="14" width="3.125" customWidth="1"/>
+    <col min="15" max="21" width="5.125" customWidth="1"/>
+    <col min="22" max="22" width="3.125" customWidth="1"/>
+    <col min="23" max="29" width="5.125" customWidth="1"/>
+    <col min="30" max="30" width="3.125" customWidth="1"/>
+    <col min="31" max="37" width="5.125" customWidth="1"/>
+    <col min="38" max="38" width="3.125" customWidth="1"/>
+    <col min="39" max="45" width="5.125" customWidth="1"/>
+    <col min="46" max="46" width="3.125" customWidth="1"/>
+    <col min="47" max="53" width="5.125" customWidth="1"/>
+    <col min="54" max="54" width="3.125" customWidth="1"/>
+    <col min="55" max="61" width="5.125" customWidth="1"/>
+    <col min="62" max="62" width="3.125" customWidth="1"/>
+    <col min="63" max="69" width="5.125" customWidth="1"/>
+    <col min="70" max="70" width="3.125" customWidth="1"/>
+    <col min="71" max="77" width="5.125" customWidth="1"/>
+    <col min="78" max="78" width="9.625" customWidth="1"/>
+    <col min="79" max="79" width="7.625" customWidth="1"/>
+    <col min="80" max="80" width="9.625" customWidth="1"/>
+    <col min="81" max="81" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1">
+    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2873,17 +2873,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="37.5" customHeight="1">
+    <row r="2" spans="1:81" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="17"/>
       <c r="J2" s="18" t="s">
         <v>82</v>
@@ -2960,7 +2960,7 @@
       <c r="CB2" s="19"/>
       <c r="CC2" s="17"/>
     </row>
-    <row r="3" spans="1:81" ht="16.95" customHeight="1">
+    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="20">
         <f>SUM(A6:A108139)</f>
         <v>0</v>
@@ -3075,11 +3075,11 @@
       <c r="CB3" s="21"/>
       <c r="CC3" s="21"/>
     </row>
-    <row r="4" spans="1:81" ht="34.200000000000003">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
+      <c r="A4" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="44"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
@@ -3113,86 +3113,86 @@
       <c r="M4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="N4" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="45" t="s">
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="47" t="s">
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="47"/>
-      <c r="AK4" s="47"/>
-      <c r="AL4" s="47" t="s">
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="47"/>
-      <c r="AN4" s="47"/>
-      <c r="AO4" s="47"/>
-      <c r="AP4" s="47"/>
-      <c r="AQ4" s="47"/>
-      <c r="AR4" s="47"/>
-      <c r="AS4" s="47"/>
-      <c r="AT4" s="47" t="s">
+      <c r="AM4" s="42"/>
+      <c r="AN4" s="42"/>
+      <c r="AO4" s="42"/>
+      <c r="AP4" s="42"/>
+      <c r="AQ4" s="42"/>
+      <c r="AR4" s="42"/>
+      <c r="AS4" s="42"/>
+      <c r="AT4" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="47"/>
-      <c r="AV4" s="47"/>
-      <c r="AW4" s="47"/>
-      <c r="AX4" s="47"/>
-      <c r="AY4" s="47"/>
-      <c r="AZ4" s="47"/>
-      <c r="BA4" s="47"/>
-      <c r="BB4" s="48" t="s">
+      <c r="AU4" s="42"/>
+      <c r="AV4" s="42"/>
+      <c r="AW4" s="42"/>
+      <c r="AX4" s="42"/>
+      <c r="AY4" s="42"/>
+      <c r="AZ4" s="42"/>
+      <c r="BA4" s="42"/>
+      <c r="BB4" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="48"/>
-      <c r="BD4" s="48"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="48"/>
-      <c r="BG4" s="48"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="48"/>
-      <c r="BJ4" s="48" t="s">
+      <c r="BC4" s="43"/>
+      <c r="BD4" s="43"/>
+      <c r="BE4" s="43"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
+      <c r="BI4" s="43"/>
+      <c r="BJ4" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="BK4" s="48"/>
-      <c r="BL4" s="48"/>
-      <c r="BM4" s="48"/>
-      <c r="BN4" s="48"/>
-      <c r="BO4" s="48"/>
-      <c r="BP4" s="48"/>
-      <c r="BQ4" s="48"/>
-      <c r="BR4" s="48" t="s">
+      <c r="BK4" s="43"/>
+      <c r="BL4" s="43"/>
+      <c r="BM4" s="43"/>
+      <c r="BN4" s="43"/>
+      <c r="BO4" s="43"/>
+      <c r="BP4" s="43"/>
+      <c r="BQ4" s="43"/>
+      <c r="BR4" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="BS4" s="48"/>
-      <c r="BT4" s="48"/>
-      <c r="BU4" s="48"/>
-      <c r="BV4" s="48"/>
-      <c r="BW4" s="48"/>
-      <c r="BX4" s="48"/>
-      <c r="BY4" s="48"/>
+      <c r="BS4" s="43"/>
+      <c r="BT4" s="43"/>
+      <c r="BU4" s="43"/>
+      <c r="BV4" s="43"/>
+      <c r="BW4" s="43"/>
+      <c r="BX4" s="43"/>
+      <c r="BY4" s="43"/>
       <c r="BZ4" s="28" t="s">
         <v>104</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="46.8">
+    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
       <c r="A5" s="27" t="s">
         <v>108</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1">
+    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="33" t="s">
         <v>132</v>
       </c>
@@ -3698,16 +3698,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="N4:U4"/>
+    <mergeCell ref="V4:AC4"/>
+    <mergeCell ref="AD4:AK4"/>
     <mergeCell ref="AL4:AS4"/>
     <mergeCell ref="AT4:BA4"/>
     <mergeCell ref="BB4:BI4"/>
     <mergeCell ref="BJ4:BQ4"/>
     <mergeCell ref="BR4:BY4"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="N4:U4"/>
-    <mergeCell ref="V4:AC4"/>
-    <mergeCell ref="AD4:AK4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="F3:G3">
@@ -3719,8 +3719,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3730,25 +3730,25 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.8984375" style="4" customWidth="1"/>
-    <col min="3" max="4" width="5.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.69921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="34.09765625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="34.09765625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.69921875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="5.69921875" style="5" customWidth="1"/>
-    <col min="12" max="14" width="5.69921875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="27.3984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="4" customWidth="1"/>
+    <col min="3" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="34.125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="34.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="5.75" style="5" customWidth="1"/>
+    <col min="12" max="14" width="5.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="1" customWidth="1"/>
     <col min="17" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>213</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="33.75" customHeight="1">
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3818,7 +3818,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
         <v>229</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" ht="68.25" customHeight="1">
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12" t="s">
         <v>242</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+    <row r="5" spans="1:16" ht="11.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
         <v>256</v>
       </c>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6671925E-A483-4789-B0C7-06909388C31D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE26E829-3F6B-4C33-8C5A-C1C8782B05EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2110,26 +2110,26 @@
     <xf numFmtId="181" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2877,13 +2877,13 @@
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
       <c r="I2" s="17"/>
       <c r="J2" s="18" t="s">
         <v>82</v>
@@ -3076,10 +3076,10 @@
       <c r="CC3" s="21"/>
     </row>
     <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="46"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
@@ -3113,86 +3113,86 @@
       <c r="M4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="47" t="s">
+      <c r="N4" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="47" t="s">
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="42" t="s">
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="42"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="42"/>
-      <c r="AH4" s="42"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="42"/>
-      <c r="AK4" s="42"/>
-      <c r="AL4" s="42" t="s">
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="42"/>
-      <c r="AN4" s="42"/>
-      <c r="AO4" s="42"/>
-      <c r="AP4" s="42"/>
-      <c r="AQ4" s="42"/>
-      <c r="AR4" s="42"/>
-      <c r="AS4" s="42"/>
-      <c r="AT4" s="42" t="s">
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="42"/>
-      <c r="AV4" s="42"/>
-      <c r="AW4" s="42"/>
-      <c r="AX4" s="42"/>
-      <c r="AY4" s="42"/>
-      <c r="AZ4" s="42"/>
-      <c r="BA4" s="42"/>
-      <c r="BB4" s="43" t="s">
+      <c r="AU4" s="47"/>
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47"/>
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="47"/>
+      <c r="BA4" s="47"/>
+      <c r="BB4" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="43"/>
-      <c r="BD4" s="43"/>
-      <c r="BE4" s="43"/>
-      <c r="BF4" s="43"/>
-      <c r="BG4" s="43"/>
-      <c r="BH4" s="43"/>
-      <c r="BI4" s="43"/>
-      <c r="BJ4" s="43" t="s">
+      <c r="BC4" s="48"/>
+      <c r="BD4" s="48"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="48"/>
+      <c r="BG4" s="48"/>
+      <c r="BH4" s="48"/>
+      <c r="BI4" s="48"/>
+      <c r="BJ4" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="BK4" s="43"/>
-      <c r="BL4" s="43"/>
-      <c r="BM4" s="43"/>
-      <c r="BN4" s="43"/>
-      <c r="BO4" s="43"/>
-      <c r="BP4" s="43"/>
-      <c r="BQ4" s="43"/>
-      <c r="BR4" s="43" t="s">
+      <c r="BK4" s="48"/>
+      <c r="BL4" s="48"/>
+      <c r="BM4" s="48"/>
+      <c r="BN4" s="48"/>
+      <c r="BO4" s="48"/>
+      <c r="BP4" s="48"/>
+      <c r="BQ4" s="48"/>
+      <c r="BR4" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="BS4" s="43"/>
-      <c r="BT4" s="43"/>
-      <c r="BU4" s="43"/>
-      <c r="BV4" s="43"/>
-      <c r="BW4" s="43"/>
-      <c r="BX4" s="43"/>
-      <c r="BY4" s="43"/>
+      <c r="BS4" s="48"/>
+      <c r="BT4" s="48"/>
+      <c r="BU4" s="48"/>
+      <c r="BV4" s="48"/>
+      <c r="BW4" s="48"/>
+      <c r="BX4" s="48"/>
+      <c r="BY4" s="48"/>
       <c r="BZ4" s="28" t="s">
         <v>104</v>
       </c>
@@ -3698,16 +3698,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AL4:AS4"/>
+    <mergeCell ref="AT4:BA4"/>
+    <mergeCell ref="BB4:BI4"/>
+    <mergeCell ref="BJ4:BQ4"/>
+    <mergeCell ref="BR4:BY4"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="N4:U4"/>
     <mergeCell ref="V4:AC4"/>
     <mergeCell ref="AD4:AK4"/>
-    <mergeCell ref="AL4:AS4"/>
-    <mergeCell ref="AT4:BA4"/>
-    <mergeCell ref="BB4:BI4"/>
-    <mergeCell ref="BJ4:BQ4"/>
-    <mergeCell ref="BR4:BY4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="F3:G3">

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE26E829-3F6B-4C33-8C5A-C1C8782B05EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5893B34C-A032-40FF-B895-0532B37FBB90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,19 +21,6 @@
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2175,13 +2162,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>61911</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>475426</xdr:rowOff>
@@ -2593,307 +2580,307 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:CC6"/>
+  <dimension ref="A1:CD6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="3" width="5.625" customWidth="1"/>
-    <col min="4" max="4" width="6.5" customWidth="1"/>
-    <col min="5" max="5" width="9.625" customWidth="1"/>
-    <col min="6" max="6" width="32.625" customWidth="1"/>
-    <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="32.625" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
-    <col min="10" max="11" width="5.625" customWidth="1"/>
-    <col min="12" max="12" width="6.125" customWidth="1"/>
-    <col min="13" max="13" width="5.625" customWidth="1"/>
-    <col min="14" max="14" width="3.125" customWidth="1"/>
-    <col min="15" max="21" width="5.125" customWidth="1"/>
-    <col min="22" max="22" width="3.125" customWidth="1"/>
-    <col min="23" max="29" width="5.125" customWidth="1"/>
-    <col min="30" max="30" width="3.125" customWidth="1"/>
-    <col min="31" max="37" width="5.125" customWidth="1"/>
-    <col min="38" max="38" width="3.125" customWidth="1"/>
-    <col min="39" max="45" width="5.125" customWidth="1"/>
-    <col min="46" max="46" width="3.125" customWidth="1"/>
-    <col min="47" max="53" width="5.125" customWidth="1"/>
-    <col min="54" max="54" width="3.125" customWidth="1"/>
-    <col min="55" max="61" width="5.125" customWidth="1"/>
-    <col min="62" max="62" width="3.125" customWidth="1"/>
-    <col min="63" max="69" width="5.125" customWidth="1"/>
-    <col min="70" max="70" width="3.125" customWidth="1"/>
-    <col min="71" max="77" width="5.125" customWidth="1"/>
-    <col min="78" max="78" width="9.625" customWidth="1"/>
-    <col min="79" max="79" width="7.625" customWidth="1"/>
-    <col min="80" max="80" width="9.625" customWidth="1"/>
-    <col min="81" max="81" width="25.75" customWidth="1"/>
+    <col min="1" max="1" width="4.875" customWidth="1"/>
+    <col min="2" max="4" width="5.625" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="6" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="32.625" customWidth="1"/>
+    <col min="8" max="8" width="9.625" customWidth="1"/>
+    <col min="9" max="9" width="32.625" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="12" width="5.625" customWidth="1"/>
+    <col min="13" max="13" width="6.125" customWidth="1"/>
+    <col min="14" max="14" width="5.625" customWidth="1"/>
+    <col min="15" max="15" width="3.125" customWidth="1"/>
+    <col min="16" max="22" width="5.125" customWidth="1"/>
+    <col min="23" max="23" width="3.125" customWidth="1"/>
+    <col min="24" max="30" width="5.125" customWidth="1"/>
+    <col min="31" max="31" width="3.125" customWidth="1"/>
+    <col min="32" max="38" width="5.125" customWidth="1"/>
+    <col min="39" max="39" width="3.125" customWidth="1"/>
+    <col min="40" max="46" width="5.125" customWidth="1"/>
+    <col min="47" max="47" width="3.125" customWidth="1"/>
+    <col min="48" max="54" width="5.125" customWidth="1"/>
+    <col min="55" max="55" width="3.125" customWidth="1"/>
+    <col min="56" max="62" width="5.125" customWidth="1"/>
+    <col min="63" max="63" width="3.125" customWidth="1"/>
+    <col min="64" max="70" width="5.125" customWidth="1"/>
+    <col min="71" max="71" width="3.125" customWidth="1"/>
+    <col min="72" max="78" width="5.125" customWidth="1"/>
+    <col min="79" max="79" width="9.625" customWidth="1"/>
+    <col min="80" max="80" width="7.625" customWidth="1"/>
+    <col min="81" max="81" width="9.625" customWidth="1"/>
+    <col min="82" max="82" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" hidden="1" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.15">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17"/>
+    <row r="2" spans="1:82" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="42"/>
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18" t="s">
+      <c r="I2" s="42"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="19"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="17"/>
@@ -2930,8 +2917,8 @@
       <c r="AX2" s="17"/>
       <c r="AY2" s="17"/>
       <c r="AZ2" s="17"/>
-      <c r="BA2" s="19"/>
-      <c r="BB2" s="17"/>
+      <c r="BA2" s="17"/>
+      <c r="BB2" s="19"/>
       <c r="BC2" s="17"/>
       <c r="BD2" s="17"/>
       <c r="BE2" s="17"/>
@@ -2956,765 +2943,770 @@
       <c r="BX2" s="17"/>
       <c r="BY2" s="17"/>
       <c r="BZ2" s="17"/>
-      <c r="CA2" s="19"/>
+      <c r="CA2" s="17"/>
       <c r="CB2" s="19"/>
-      <c r="CC2" s="17"/>
+      <c r="CC2" s="19"/>
+      <c r="CD2" s="17"/>
     </row>
-    <row r="3" spans="1:81" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="20">
-        <f>SUM(A6:A108139)</f>
+    <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="20">
+        <f>SUM(B6:B108139)</f>
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="20">
-        <f>SUM(C6:C108139)</f>
+      <c r="C3" s="21"/>
+      <c r="D3" s="20">
+        <f>SUM(D6:D108139)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="20"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="23" t="s">
+      <c r="J3" s="20"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="21"/>
       <c r="M3" s="21"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22">
-        <f>SUM(O6:O108139)</f>
+      <c r="N3" s="21"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22">
+        <f>SUM(P6:P108139)</f>
         <v>0</v>
       </c>
-      <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
-      <c r="R3" s="20"/>
+      <c r="R3" s="22"/>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
       <c r="U3" s="20"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="20">
-        <f>SUM(W6:W108139)</f>
+      <c r="V3" s="20"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="20">
+        <f>SUM(X6:X108139)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="20"/>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="24"/>
       <c r="AC3" s="20"/>
       <c r="AD3" s="20"/>
-      <c r="AE3" s="20">
-        <f>SUM(AE6:AE108139)</f>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20">
+        <f>SUM(AF6:AF108139)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="20"/>
+      <c r="AG3" s="24"/>
       <c r="AH3" s="20"/>
       <c r="AI3" s="20"/>
       <c r="AJ3" s="20"/>
-      <c r="AK3" s="24"/>
-      <c r="AL3" s="20"/>
-      <c r="AM3" s="20">
-        <f>SUM(AM6:AM108139)</f>
+      <c r="AK3" s="20"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20">
+        <f>SUM(AN6:AN108139)</f>
         <v>0</v>
       </c>
-      <c r="AN3" s="20"/>
       <c r="AO3" s="20"/>
-      <c r="AP3" s="24"/>
-      <c r="AQ3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="24"/>
       <c r="AR3" s="20"/>
       <c r="AS3" s="20"/>
       <c r="AT3" s="20"/>
-      <c r="AU3" s="24">
-        <f>SUM(AU6:AU108139)</f>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="24">
+        <f>SUM(AV6:AV108139)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="20"/>
       <c r="AW3" s="20"/>
       <c r="AX3" s="20"/>
       <c r="AY3" s="20"/>
-      <c r="AZ3" s="24"/>
-      <c r="BA3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="24"/>
       <c r="BB3" s="20"/>
-      <c r="BC3" s="20">
-        <f>SUM(BC6:BC108139)</f>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20">
+        <f>SUM(BD6:BD108139)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="20"/>
-      <c r="BE3" s="24"/>
-      <c r="BF3" s="22"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="24"/>
       <c r="BG3" s="22"/>
       <c r="BH3" s="22"/>
-      <c r="BI3" s="21"/>
-      <c r="BJ3" s="25"/>
-      <c r="BK3" s="20">
-        <f>SUM(BK6:BK108139)</f>
+      <c r="BI3" s="22"/>
+      <c r="BJ3" s="21"/>
+      <c r="BK3" s="25"/>
+      <c r="BL3" s="20">
+        <f>SUM(BL6:BL108139)</f>
         <v>0</v>
       </c>
-      <c r="BL3" s="21"/>
       <c r="BM3" s="21"/>
       <c r="BN3" s="21"/>
       <c r="BO3" s="21"/>
       <c r="BP3" s="21"/>
       <c r="BQ3" s="21"/>
       <c r="BR3" s="21"/>
-      <c r="BS3" s="20">
-        <f>SUM(BS6:BS108139)</f>
+      <c r="BS3" s="21"/>
+      <c r="BT3" s="20">
+        <f>SUM(BT6:BT108139)</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="21"/>
       <c r="BU3" s="21"/>
       <c r="BV3" s="21"/>
       <c r="BW3" s="21"/>
       <c r="BX3" s="21"/>
       <c r="BY3" s="21"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="21"/>
+      <c r="BZ3" s="21"/>
+      <c r="CA3" s="26"/>
       <c r="CB3" s="21"/>
       <c r="CC3" s="21"/>
+      <c r="CD3" s="21"/>
     </row>
-    <row r="4" spans="1:81" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:82" ht="36" x14ac:dyDescent="0.15">
+      <c r="B4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="F4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="G4" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="H4" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="I4" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="J4" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="K4" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="L4" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="M4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="N4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="45" t="s">
+      <c r="O4" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="46"/>
       <c r="P4" s="46"/>
       <c r="Q4" s="46"/>
       <c r="R4" s="46"/>
       <c r="S4" s="46"/>
       <c r="T4" s="46"/>
       <c r="U4" s="46"/>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="46"/>
+      <c r="W4" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="46"/>
       <c r="X4" s="46"/>
       <c r="Y4" s="46"/>
       <c r="Z4" s="46"/>
       <c r="AA4" s="46"/>
       <c r="AB4" s="46"/>
       <c r="AC4" s="46"/>
-      <c r="AD4" s="47" t="s">
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="AE4" s="47"/>
       <c r="AF4" s="47"/>
       <c r="AG4" s="47"/>
       <c r="AH4" s="47"/>
       <c r="AI4" s="47"/>
       <c r="AJ4" s="47"/>
       <c r="AK4" s="47"/>
-      <c r="AL4" s="47" t="s">
+      <c r="AL4" s="47"/>
+      <c r="AM4" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="AM4" s="47"/>
       <c r="AN4" s="47"/>
       <c r="AO4" s="47"/>
       <c r="AP4" s="47"/>
       <c r="AQ4" s="47"/>
       <c r="AR4" s="47"/>
       <c r="AS4" s="47"/>
-      <c r="AT4" s="47" t="s">
+      <c r="AT4" s="47"/>
+      <c r="AU4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="AU4" s="47"/>
       <c r="AV4" s="47"/>
       <c r="AW4" s="47"/>
       <c r="AX4" s="47"/>
       <c r="AY4" s="47"/>
       <c r="AZ4" s="47"/>
       <c r="BA4" s="47"/>
-      <c r="BB4" s="48" t="s">
+      <c r="BB4" s="47"/>
+      <c r="BC4" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="BC4" s="48"/>
       <c r="BD4" s="48"/>
       <c r="BE4" s="48"/>
       <c r="BF4" s="48"/>
       <c r="BG4" s="48"/>
       <c r="BH4" s="48"/>
       <c r="BI4" s="48"/>
-      <c r="BJ4" s="48" t="s">
+      <c r="BJ4" s="48"/>
+      <c r="BK4" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="BK4" s="48"/>
       <c r="BL4" s="48"/>
       <c r="BM4" s="48"/>
       <c r="BN4" s="48"/>
       <c r="BO4" s="48"/>
       <c r="BP4" s="48"/>
       <c r="BQ4" s="48"/>
-      <c r="BR4" s="48" t="s">
+      <c r="BR4" s="48"/>
+      <c r="BS4" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="BS4" s="48"/>
       <c r="BT4" s="48"/>
       <c r="BU4" s="48"/>
       <c r="BV4" s="48"/>
       <c r="BW4" s="48"/>
       <c r="BX4" s="48"/>
       <c r="BY4" s="48"/>
-      <c r="BZ4" s="28" t="s">
+      <c r="BZ4" s="48"/>
+      <c r="CA4" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="CA4" s="28" t="s">
+      <c r="CB4" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="CB4" s="28" t="s">
+      <c r="CC4" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="CC4" s="28" t="s">
+      <c r="CD4" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="48" x14ac:dyDescent="0.15">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:82" ht="48" x14ac:dyDescent="0.15">
+      <c r="B5" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="C5" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="D5" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="E5" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="F5" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="G5" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="H5" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="I5" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="J5" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="K5" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="L5" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="M5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M5" s="30" t="s">
+      <c r="N5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="O5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="29" t="s">
+      <c r="P5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="29" t="s">
+      <c r="Q5" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="Q5" s="29" t="s">
+      <c r="R5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="R5" s="29" t="s">
+      <c r="S5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="29" t="s">
+      <c r="T5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="U5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="U5" s="29" t="s">
+      <c r="V5" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="W5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="W5" s="29" t="s">
+      <c r="X5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="29" t="s">
+      <c r="Y5" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="Y5" s="29" t="s">
+      <c r="Z5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="Z5" s="29" t="s">
+      <c r="AA5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="AA5" s="29" t="s">
+      <c r="AB5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AB5" s="29" t="s">
+      <c r="AC5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="AC5" s="29" t="s">
+      <c r="AD5" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="AD5" s="31" t="s">
+      <c r="AE5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AE5" s="31" t="s">
+      <c r="AF5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AF5" s="31" t="s">
+      <c r="AG5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AG5" s="31" t="s">
+      <c r="AH5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AH5" s="31" t="s">
+      <c r="AI5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AI5" s="31" t="s">
+      <c r="AJ5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AJ5" s="31" t="s">
+      <c r="AK5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AK5" s="31" t="s">
+      <c r="AL5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AL5" s="31" t="s">
+      <c r="AM5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AM5" s="31" t="s">
+      <c r="AN5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AN5" s="31" t="s">
+      <c r="AO5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AO5" s="31" t="s">
+      <c r="AP5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AP5" s="31" t="s">
+      <c r="AQ5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AQ5" s="31" t="s">
+      <c r="AR5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AR5" s="31" t="s">
+      <c r="AS5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="AS5" s="31" t="s">
+      <c r="AT5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AT5" s="31" t="s">
+      <c r="AU5" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="AU5" s="31" t="s">
+      <c r="AV5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="AV5" s="31" t="s">
+      <c r="AW5" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="AW5" s="31" t="s">
+      <c r="AX5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="AX5" s="31" t="s">
+      <c r="AY5" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="AY5" s="31" t="s">
+      <c r="AZ5" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AZ5" s="31" t="s">
+      <c r="BA5" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="BA5" s="31" t="s">
+      <c r="BB5" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="BB5" s="32" t="s">
+      <c r="BC5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BC5" s="32" t="s">
+      <c r="BD5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BD5" s="32" t="s">
+      <c r="BE5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BE5" s="32" t="s">
+      <c r="BF5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BF5" s="32" t="s">
+      <c r="BG5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BG5" s="32" t="s">
+      <c r="BH5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BH5" s="32" t="s">
+      <c r="BI5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BI5" s="32" t="s">
+      <c r="BJ5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BJ5" s="32" t="s">
+      <c r="BK5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BK5" s="32" t="s">
+      <c r="BL5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BL5" s="32" t="s">
+      <c r="BM5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BM5" s="32" t="s">
+      <c r="BN5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BN5" s="32" t="s">
+      <c r="BO5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BO5" s="32" t="s">
+      <c r="BP5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BP5" s="32" t="s">
+      <c r="BQ5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BQ5" s="32" t="s">
+      <c r="BR5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BR5" s="32" t="s">
+      <c r="BS5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="BS5" s="32" t="s">
+      <c r="BT5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BT5" s="32" t="s">
+      <c r="BU5" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="BU5" s="32" t="s">
+      <c r="BV5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="BV5" s="32" t="s">
+      <c r="BW5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="BW5" s="32" t="s">
+      <c r="BX5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="BX5" s="32" t="s">
+      <c r="BY5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="BY5" s="32" t="s">
+      <c r="BZ5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="BZ5" s="30" t="s">
+      <c r="CA5" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="CA5" s="30" t="s">
+      <c r="CB5" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="CB5" s="30" t="s">
+      <c r="CC5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="CC5" s="30" t="s">
+      <c r="CD5" s="30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:82" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <f>SUMIF($F$6:$F$233,F8,$D$6:$D$233)</f>
+        <v>0</v>
+      </c>
+      <c r="B6" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="C6" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="D6" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="E6" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="F6" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="G6" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="H6" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="I6" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="J6" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="K6" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="L6" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="M6" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="M6" s="38" t="s">
+      <c r="N6" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="39" t="s">
+      <c r="O6" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="O6" s="33" t="s">
+      <c r="P6" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="P6" s="33" t="s">
+      <c r="Q6" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="Q6" s="33" t="s">
+      <c r="R6" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="R6" s="33" t="s">
+      <c r="S6" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="S6" s="33" t="s">
+      <c r="T6" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="T6" s="33" t="s">
+      <c r="U6" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="U6" s="33" t="s">
+      <c r="V6" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="V6" s="33" t="s">
+      <c r="W6" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="W6" s="33" t="s">
+      <c r="X6" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="X6" s="33" t="s">
+      <c r="Y6" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="Y6" s="33" t="s">
+      <c r="Z6" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="Z6" s="33" t="s">
+      <c r="AA6" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="AA6" s="33" t="s">
+      <c r="AB6" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="AB6" s="33" t="s">
+      <c r="AC6" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="AC6" s="33" t="s">
+      <c r="AD6" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="AD6" s="33" t="s">
+      <c r="AE6" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="AE6" s="33" t="s">
+      <c r="AF6" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="AF6" s="33" t="s">
+      <c r="AG6" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="AG6" s="33" t="s">
+      <c r="AH6" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="AH6" s="33" t="s">
+      <c r="AI6" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="AI6" s="33" t="s">
+      <c r="AJ6" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="AJ6" s="33" t="s">
+      <c r="AK6" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="33" t="s">
+      <c r="AL6" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="AL6" s="33" t="s">
+      <c r="AM6" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="AM6" s="33" t="s">
+      <c r="AN6" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="AN6" s="33" t="s">
+      <c r="AO6" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="AO6" s="33" t="s">
+      <c r="AP6" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="AP6" s="33" t="s">
+      <c r="AQ6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AQ6" s="33" t="s">
+      <c r="AR6" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="AR6" s="33" t="s">
+      <c r="AS6" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="AS6" s="33" t="s">
+      <c r="AT6" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="AT6" s="33" t="s">
+      <c r="AU6" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="AU6" s="33" t="s">
+      <c r="AV6" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="AV6" s="33" t="s">
+      <c r="AW6" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="AW6" s="33" t="s">
+      <c r="AX6" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AX6" s="33" t="s">
+      <c r="AY6" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AY6" s="33" t="s">
+      <c r="AZ6" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AZ6" s="33" t="s">
+      <c r="BA6" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="BA6" s="33" t="s">
+      <c r="BB6" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="BB6" s="33" t="s">
+      <c r="BC6" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="BC6" s="33" t="s">
+      <c r="BD6" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="BD6" s="33" t="s">
+      <c r="BE6" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="BE6" s="33" t="s">
+      <c r="BF6" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="BF6" s="33" t="s">
+      <c r="BG6" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="BG6" s="33" t="s">
+      <c r="BH6" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="BH6" s="33" t="s">
+      <c r="BI6" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="BI6" s="33" t="s">
+      <c r="BJ6" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="BJ6" s="33" t="s">
+      <c r="BK6" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="BK6" s="33" t="s">
+      <c r="BL6" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="BL6" s="33" t="s">
+      <c r="BM6" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="BM6" s="33" t="s">
+      <c r="BN6" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="BN6" s="33" t="s">
+      <c r="BO6" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="BO6" s="33" t="s">
+      <c r="BP6" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="BP6" s="33" t="s">
+      <c r="BQ6" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="BQ6" s="33" t="s">
+      <c r="BR6" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="BR6" s="33" t="s">
+      <c r="BS6" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="BS6" s="33" t="s">
+      <c r="BT6" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="BT6" s="33" t="s">
+      <c r="BU6" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="BU6" s="33" t="s">
+      <c r="BV6" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="BV6" s="33" t="s">
+      <c r="BW6" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="BW6" s="33" t="s">
+      <c r="BX6" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="BX6" s="33" t="s">
+      <c r="BY6" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="BY6" s="40" t="s">
+      <c r="BZ6" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="BZ6" s="41" t="s">
+      <c r="CA6" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="CA6" s="41" t="s">
+      <c r="CB6" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="CB6" s="35" t="s">
+      <c r="CC6" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="CC6" s="35" t="s">
+      <c r="CD6" s="35" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="AL4:AS4"/>
-    <mergeCell ref="AT4:BA4"/>
-    <mergeCell ref="BB4:BI4"/>
-    <mergeCell ref="BJ4:BQ4"/>
-    <mergeCell ref="BR4:BY4"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="N4:U4"/>
-    <mergeCell ref="V4:AC4"/>
-    <mergeCell ref="AD4:AK4"/>
+    <mergeCell ref="AM4:AT4"/>
+    <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BJ4"/>
+    <mergeCell ref="BK4:BR4"/>
+    <mergeCell ref="BS4:BZ4"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="AE4:AL4"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
-  <conditionalFormatting sqref="F3:G3">
+  <conditionalFormatting sqref="G3:H3">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5 Z5 AH5 AP5 AX5 BF5 BN5 BV5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5 AA5 AI5 AQ5 AY5 BG5 BO5 BW5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"正常,首检,试验,收尾,量试"</formula1>
     </dataValidation>
   </dataValidations>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhjhtemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94341612-1CED-4F0C-97DE-829660349362}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6674513-7BAB-4938-A28C-E16C9648AE30}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1375,7 +1375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1517,6 +1517,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1990,7 +1999,7 @@
     <col min="79" max="79" width="9.625" customWidth="1"/>
     <col min="80" max="80" width="7.625" customWidth="1"/>
     <col min="81" max="81" width="9.625" customWidth="1"/>
-    <col min="82" max="82" width="25.75" customWidth="1"/>
+    <col min="82" max="82" width="37.625" style="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:82" hidden="1" x14ac:dyDescent="0.15">
@@ -2237,7 +2246,7 @@
       <c r="CC1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CD1" s="50" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2326,7 +2335,7 @@
       <c r="CA2" s="9"/>
       <c r="CB2" s="11"/>
       <c r="CC2" s="11"/>
-      <c r="CD2" s="9"/>
+      <c r="CD2" s="51"/>
     </row>
     <row r="3" spans="1:82" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="25">
@@ -2441,7 +2450,7 @@
       <c r="CA3" s="29"/>
       <c r="CB3" s="12"/>
       <c r="CC3" s="12"/>
-      <c r="CD3" s="12"/>
+      <c r="CD3" s="52"/>
     </row>
     <row r="4" spans="1:82" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="48" t="s">
@@ -3063,7 +3072,7 @@
       <c r="CC6" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="CD6" s="19" t="s">
+      <c r="CD6" s="21" t="s">
         <v>213</v>
       </c>
     </row>
